--- a/blogs_export.xlsx
+++ b/blogs_export.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I124"/>
+  <dimension ref="A1:I132"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="35.83203125" customWidth="1"/>
@@ -444,298 +444,201 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>wallpaper-vs-paint-for-indian-homes</v>
+        <v>wardrobe-cost-india-materials-labour-quote-guide</v>
       </c>
       <c r="C2" t="str">
-        <v>Wallpaper vs Paint for Indian Homes: Where to Use Each &amp; How to Install Wallpaper Yourself</v>
+        <v>Wardrobe Cost in India: Materials, Labour &amp; Complete Quotation Guide</v>
       </c>
       <c r="D2" t="str">
-        <v>Wallpaper</v>
+        <v>Carpentry</v>
       </c>
       <c r="E2" t="str">
         <v>October 23, 2026</v>
       </c>
       <c r="F2" t="str">
-        <v>9 min read</v>
+        <v>8 min read</v>
       </c>
       <c r="G2" t="str">
-        <v>A living room can feel tired even when most paint is fine. Compare wallpaper vs paint for Indian homes, budget per sq. ft., room suitability, and follow our 8-step DIY peel-and-stick installation guide.</v>
+        <v>Understand wardrobe costs in India, compare materials and door styles, calculate the right area and check what a complete quotation should include.</v>
       </c>
       <c r="H2" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
   &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
-  &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;For Indian homes, the most practical approach is combining finishes: use wallpaper on dry, prominent accent walls (such as behind the master bed or living room sofa) for instant designer texture and pattern, while keeping washable emulsion paint in high-traffic, humid, or splash-prone zones like kitchens, corridors, and bathrooms. Always resolve underlying wall dampness first and test an inconspicuous sample before installing peel-and-stick panels.&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;A living room can feel tired even when most of its paint is perfectly fine. Perhaps the wall behind the sofa looks bare, or the bedroom needs a little more warmth. Before booking painters for the whole flat, take a closer look at what actually needs changing.&lt;/p&gt;
-&lt;p&gt;Wallpaper can give a dry interior wall a pattern or finish that would take considerably more work to create with paint. A botanical print behind the bed, a quiet linen effect in the living room, or a small patterned corner beside a desk can be enough to completely transform the space.&lt;/p&gt;
-&lt;p&gt;For many homes, a sensible plan is to use both finishes: wallpaper on selected interior walls, paint wherever it suits the surface and daily use, and suitable exterior coatings outside. The budget depends on the area you change and the material you choose. Wallpaper is not automatically the cheaper option.&lt;/p&gt;
-&lt;h2&gt;Wallpaper and Paint Compared&lt;/h2&gt;
-&lt;p&gt;Wallpaper works particularly well when the design itself is the main reason for changing a wall. Paint makes sense when you want a plain finish, need to refresh a large area, or expect regular cleaning and future colour changes.&lt;/p&gt;
+  &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;When comparing wardrobe quotes in India, never rely on headline square-foot rates alone. A complete quote must specify carcass and shutter substrate (BWR vs commercial ply/MDF), laminate thickness, brand-specific hardware (hinges, runners, handles), internal drawer counts, and loft inclusion. Expect ₹1,400–₹2,200/sq.ft for commercial ply with laminate and ₹1,800–₹3,200+/sq.ft for BWR/marine ply with premium acrylic or PU finishes.&lt;/p&gt;
+&lt;/div&gt;
+&lt;div style="background: rgba(239, 68, 68, 0.08); border-left: 4px solid #ef4444; padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: #dc2626;"&gt;⚠️ Critical Safety Warnings &amp; Precautions&lt;/p&gt;
+  &lt;p style="margin: 0; line-height: 1.7; font-size: 0.95rem;"&gt;Ensure tall wardrobes and floor-to-ceiling carcasses are securely anchored to the brickwork with heavy-duty rawl plugs and L-brackets to prevent anti-tip hazards, especially in households with small children or pets. Wear dust masks and eye protection when cutting laminated ply on site.&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;Two wardrobes can look almost identical in a photograph and still have very different prices. One may include drawers, a loft and good-quality fittings. The other may cover little more than the outer cabinet and doors.&lt;/p&gt;
+&lt;p&gt;That is why the first question to ask is what the quote includes. Once the size, material and storage layout are clear, you can compare prices without guessing which contractor has quietly left something out.&lt;/p&gt;
+&lt;p&gt;This guide helps you plan a wardrobe for an Indian home, understand the way it is measured and decide where extra spending will make a difference.&lt;/p&gt;
+&lt;h2&gt;Understanding wardrobe prices&lt;/h2&gt;
+&lt;p&gt;There is no single price that covers every wardrobe sold in India. A freestanding cupboard, a fitted unit and a wardrobe built around a bedroom corner are different projects.&lt;/p&gt;
+&lt;p&gt;For a published reference, Livspace lists basic fitted hinged wardrobes from ₹53,000 and sliding-door wardrobes from ₹1,10,000. These are examples from one provider, with different specifications, rather than a direct comparison of equal-sized units. Check the current scope before using them as a benchmark. [1]&lt;/p&gt;
+&lt;p&gt;Your quote will depend on cabinet dimensions, internal partitions, the board and finish, fittings, installation conditions and local labour. A smaller unit with several drawers can cost more than a larger one containing mostly shelves.&lt;/p&gt;
+&lt;p&gt;The site matters too. Uneven floors, a damp back wall or difficult access can add work. Coastal humidity and a dry inland bedroom also call for different conversations about material selection and protection.&lt;/p&gt;
+&lt;h2&gt;Measuring the work correctly&lt;/h2&gt;
+&lt;p&gt;Ask whether the price is calculated by front elevation, panel area, running foot or a complete-unit price. These methods should not be mixed.&lt;/p&gt;
+&lt;p&gt;If a contractor quotes by front elevation, a wardrobe 6 ft wide and 7 ft high has an elevation area of 42 sq. ft. That measurement does not tell you the depth, number of shelves or quantity of board inside.&lt;/p&gt;
+&lt;p&gt;At an illustrative quoted rate of ₹1,800 per sq. ft., the arithmetic is 42 × ₹1,800 = ₹75,600. This is a calculation example, not a market rate. A loft, mirror or extra drawer may still be outside that figure.&lt;/p&gt;
+&lt;p&gt;Write the width, height and depth on the drawing. Mark the loft separately and show whether the wardrobe includes a full back panel, side fillers and a plinth. Small details become expensive disagreements when the drawing is vague.&lt;/p&gt;
+&lt;p&gt;For a sloping ceiling or an awkward recess, get the measurement checked on site before paying for factory production.&lt;/p&gt;
+&lt;h2&gt;Choosing materials and doors&lt;/h2&gt;
+&lt;h3&gt;Match the board to the room&lt;/h3&gt;
+&lt;p&gt;Plywood and MDF are broad material families. Their grade, thickness and suitability for the application matter more than the label alone.&lt;/p&gt;
+&lt;p&gt;Greenply distinguishes moisture-resistant, boiling-water-resistant and boiling-water-proof plywood grades for different exposure conditions. Discuss the actual room conditions with the supplier. A bedroom that stays dry does not have the same requirements as cabinetry beside a leaking bathroom wall. [2]&lt;/p&gt;
+&lt;p&gt;MDF can provide a smooth surface for some finishes, but ordinary MDF should not be treated as a solution to recurring dampness. A suitable board still needs well-finished edges, appropriate detailing and a dry installation area. [3]&lt;/p&gt;
+&lt;p&gt;Ask for the product name and grade on the quotation. “Premium ply” is too vague to verify later.&lt;/p&gt;
+&lt;h3&gt;Decide how the doors will open&lt;/h3&gt;
 &lt;div style="overflow-x: auto; margin: 1.5rem 0 2rem 0;"&gt;
-  &lt;table&gt;
+  &lt;table style="width: 100%; border-collapse: collapse; text-align: left; font-size: 0.95rem;"&gt;
     &lt;thead&gt;
-      &lt;tr&gt;
-        &lt;th&gt;What matters&lt;/th&gt;
-        &lt;th&gt;Interior paint&lt;/th&gt;
-        &lt;th&gt;Peel and stick wallpaper&lt;/th&gt;
-        &lt;th&gt;Traditional pasted wallpaper&lt;/th&gt;
+      &lt;tr style="background: rgba(0,0,0,0.04); border-bottom: 2px solid var(--border, #e2e8f0);"&gt;
+        &lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Door style&lt;/th&gt;&lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Where it can work well&lt;/th&gt;&lt;th style="padding: 12px 16px; font-weight: 600;"&gt;What to check before ordering&lt;/th&gt;
       &lt;/tr&gt;
     &lt;/thead&gt;
     &lt;tbody&gt;
-      &lt;tr&gt;
-        &lt;td&gt;&lt;strong&gt;Appearance&lt;/strong&gt;&lt;/td&gt;
-        &lt;td&gt;Plain colour and painted texture effects&lt;/td&gt;
-        &lt;td&gt;Printed patterns, murals, and textured films&lt;/td&gt;
-        &lt;td&gt;Broad choice of prints, fabrics, and deep textures&lt;/td&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Hinged&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Rooms with enough opening space&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Clearance beside the bed and access to internal drawers&lt;/td&gt;
       &lt;/tr&gt;
-      &lt;tr&gt;
-        &lt;td&gt;&lt;strong&gt;Preparation&lt;/strong&gt;&lt;/td&gt;
-        &lt;td&gt;Plaster repairs, putty sanding, and primer coat&lt;/td&gt;
-        &lt;td&gt;A sound, dust-free surface compatible with adhesive&lt;/td&gt;
-        &lt;td&gt;Surface repairs and specified acrylic primer or sealer&lt;/td&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Sliding&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Rooms where swing clearance is limited&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Track quality, overlap and which parts of the wardrobe are accessible&lt;/td&gt;
       &lt;/tr&gt;
-      &lt;tr&gt;
-        &lt;td&gt;&lt;strong&gt;DIY Work&lt;/strong&gt;&lt;/td&gt;
-        &lt;td&gt;Masking, rolling, cutting in, and drying between coats&lt;/td&gt;
-        &lt;td&gt;Careful vertical alignment, peeling backing, and smoothing&lt;/td&gt;
-        &lt;td&gt;Adhesive mixing, pasting table, soaking, and accurate hanging&lt;/td&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Open storage&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Dressing spaces where dust can be managed&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Visibility, cleaning and the appearance of stored items&lt;/td&gt;
       &lt;/tr&gt;
-      &lt;tr&gt;
-        &lt;td&gt;&lt;strong&gt;Repairs&lt;/strong&gt;&lt;/td&gt;
-        &lt;td&gt;Local touch-ups may show a slight sheen or shade difference&lt;/td&gt;
-        &lt;td&gt;Matching saved offcuts can cleanly patch damaged sections&lt;/td&gt;
-        &lt;td&gt;Matching dye-lot paper and careful seam insertion&lt;/td&gt;
-      &lt;/tr&gt;
-      &lt;tr&gt;
-        &lt;td&gt;&lt;strong&gt;Removal&lt;/strong&gt;&lt;/td&gt;
-        &lt;td&gt;Sand, prime, and repaint over the previous surface&lt;/td&gt;
-        &lt;td&gt;Product quality and underlying paint bond determine clean peel&lt;/td&gt;
-        &lt;td&gt;Removal method depends on paper backing and paste dissolver&lt;/td&gt;
-      &lt;/tr&gt;
-      &lt;tr&gt;
-        &lt;td&gt;&lt;strong&gt;Budget&lt;/strong&gt;&lt;/td&gt;
-        &lt;td&gt;Compare complete square-foot quote (prep + labor + paint)&lt;/td&gt;
-        &lt;td&gt;Account for square footage, wastage allowance, and smoother tool&lt;/td&gt;
-        &lt;td&gt;Include wall prep, roll cost, adhesive, and skilled installer fee&lt;/td&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Mixed layout&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;A combination of closed storage and a small display area&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Whether the extra divisions are useful&lt;/td&gt;
       &lt;/tr&gt;
     &lt;/tbody&gt;
   &lt;/table&gt;
 &lt;/div&gt;
-&lt;p&gt;Both finishes depend entirely on the wall underneath. Wallpaper can cover an outdated colour, but raised plaster patches, loose paint, and damp plaster still demand thorough repair before anything is applied.&lt;/p&gt;
-&lt;h2&gt;Where to Use Wallpaper and Where to Keep Paint&lt;/h2&gt;
-&lt;p&gt;Walk through the house before choosing a design. Note where people lean against walls, where direct sunlight falls, and which corners become damp during the monsoon season.&lt;/p&gt;
+&lt;p&gt;Sliding doors save swing space, but the door arrangement can restrict access to one section at a time. Try a display unit with a similar layout before deciding.&lt;/p&gt;
+&lt;h3&gt;Spend on fittings you will use&lt;/h3&gt;
+&lt;p&gt;A soft-close label does not identify the hinge or drawer system. Ask for the manufacturer, model and load suitability.&lt;/p&gt;
+&lt;p&gt;Blum’s planning guidance relates hinge selection to factors such as door size and weight. That is a useful reason to specify the fitting rather than accepting the same hinge arrangement for every shutter. [4]&lt;/p&gt;
+&lt;p&gt;For a family wardrobe, smooth everyday access may be more useful than a large collection of specialised pull-outs. Count how many drawers you actually need before paying for them.&lt;/p&gt;
+&lt;h2&gt;Preparing an itemised budget&lt;/h2&gt;
+&lt;p&gt;A complete quote should show the cabinet structure, shutters, internal finish, external finish and hardware. It should also state what happens at the wall, floor and ceiling edges.&lt;/p&gt;
+&lt;p&gt;Here is a fictional budget for comparing scope. It is not an advertised price or a national rate card.&lt;/p&gt;
 &lt;div style="overflow-x: auto; margin: 1.5rem 0 2rem 0;"&gt;
-  &lt;table&gt;
+  &lt;table style="width: 100%; border-collapse: collapse; text-align: left; font-size: 0.95rem;"&gt;
     &lt;thead&gt;
-      &lt;tr&gt;
-        &lt;th&gt;Area&lt;/th&gt;
-        &lt;th&gt;A practical starting choice&lt;/th&gt;
-        &lt;th&gt;What to check&lt;/th&gt;
+      &lt;tr style="background: rgba(0,0,0,0.04); border-bottom: 2px solid var(--border, #e2e8f0);"&gt;
+        &lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Item&lt;/th&gt;&lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Illustrative allowance&lt;/th&gt;
       &lt;/tr&gt;
     &lt;/thead&gt;
     &lt;tbody&gt;
-      &lt;tr&gt;
-        &lt;td&gt;&lt;strong&gt;Wall behind the bed&lt;/strong&gt;&lt;/td&gt;
-        &lt;td&gt;Wallpaper&lt;/td&gt;
-        &lt;td&gt;Wall dryness and how the pattern sits above the headboard&lt;/td&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Main wardrobe including agreed shelves and shutters&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹72,000&lt;/td&gt;
       &lt;/tr&gt;
-      &lt;tr&gt;
-        &lt;td&gt;&lt;strong&gt;Living room feature wall&lt;/strong&gt;&lt;/td&gt;
-        &lt;td&gt;Wallpaper or paint&lt;/td&gt;
-        &lt;td&gt;Furniture placement, natural lighting, and visible wall area&lt;/td&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Loft above the main unit&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹12,000&lt;/td&gt;
       &lt;/tr&gt;
-      &lt;tr&gt;
-        &lt;td&gt;&lt;strong&gt;Study or work corner&lt;/strong&gt;&lt;/td&gt;
-        &lt;td&gt;Wallpaper on one wall&lt;/td&gt;
-        &lt;td&gt;Pattern scale and the background framing behind your video desk&lt;/td&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Two additional drawers&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹6,000&lt;/td&gt;
       &lt;/tr&gt;
-      &lt;tr&gt;
-        &lt;td&gt;&lt;strong&gt;Corridors and utility areas&lt;/strong&gt;&lt;/td&gt;
-        &lt;td&gt;Suitable washable paint&lt;/td&gt;
-        &lt;td&gt;Daily scuffing, handprints, and frequent wipe-down frequency&lt;/td&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Mirror and agreed fitting work&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹4,000&lt;/td&gt;
       &lt;/tr&gt;
-      &lt;tr&gt;
-        &lt;td&gt;&lt;strong&gt;Kitchen cooking and sink zones&lt;/strong&gt;&lt;/td&gt;
-        &lt;td&gt;A finish rated for the exposure&lt;/td&gt;
-        &lt;td&gt;Cooking heat, airborne oil/grease, water splashes, and cleaning&lt;/td&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Delivery and installation&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹5,000&lt;/td&gt;
       &lt;/tr&gt;
-      &lt;tr&gt;
-        &lt;td&gt;&lt;strong&gt;Shower walls and persistently wet areas&lt;/strong&gt;&lt;/td&gt;
-        &lt;td&gt;A properly specified wet-area finish&lt;/td&gt;
-        &lt;td&gt;Tile waterproofing and direct high-pressure water exposure&lt;/td&gt;
-      &lt;/tr&gt;
-      &lt;tr&gt;
-        &lt;td&gt;&lt;strong&gt;Exterior walls and open balconies&lt;/strong&gt;&lt;/td&gt;
-        &lt;td&gt;Exterior paint or specified coating&lt;/td&gt;
-        &lt;td&gt;Heavy monsoon rain, UV radiation, hairline cracks, and drainage&lt;/td&gt;
-      &lt;/tr&gt;
-      &lt;tr&gt;
-        &lt;td&gt;&lt;strong&gt;A wall with seepage&lt;/strong&gt;&lt;/td&gt;
-        &lt;td&gt;Repair and dry the wall first&lt;/td&gt;
-        &lt;td&gt;Identify and fix the water source before applying any finish&lt;/td&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Subtotal before applicable taxes and any other agreed charges&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹99,000&lt;/td&gt;
       &lt;/tr&gt;
     &lt;/tbody&gt;
   &lt;/table&gt;
 &lt;/div&gt;
-&lt;h3&gt;Interior Walls Where Wallpaper Earns Its Place&lt;/h3&gt;
-&lt;p&gt;Start with a wall you will actually see and enjoy every day. A stunning mural hidden behind a tall modular wardrobe adds very little value to the room. Behind a bed or sofa, choose a design whose primary focal point remains visible above the headboard or back cushions.&lt;/p&gt;
-&lt;p&gt;For compact Indian apartments, always order a physical sample swatch before committing to a full wall order. Hold the swatch against your curtains, tile flooring, and existing painted walls. Check it in natural daylight and again under warm evening artificial lights; a subtle cream background seen on a phone screen may read as stark grey under your home LEDs.&lt;/p&gt;
-&lt;h3&gt;Places Where Paint Remains Indispensable&lt;/h3&gt;
-&lt;p&gt;Wallpapering one feature wall does not mean every adjacent wall requires a fresh coat. Keep sound, clean paint if the shade already harmonizes with the room decor.&lt;/p&gt;
-&lt;p&gt;Repaint where the surface is scuffed, where you need a superior washable acrylic emulsion, or where a deliberate color shift ties the space together. Ceilings should almost always remain coated with high-hiding matte ceiling paint in good condition.&lt;/p&gt;
-&lt;p&gt;For open balconies, utility ducts, and weather-facing facades, use products engineered specifically for exterior exposure. Ordinary interior wallpaper will rapidly bubble and peel on an open balcony or rain-facing wall. If exterior walls exhibit cracks or water ingress, an exterior repaint alone will not resolve structural seepage without proper waterproofing primers.&lt;/p&gt;
-&lt;h3&gt;A Note for Bangalore Homes: Monsoons &amp;amp; Hidden Seepage&lt;/h3&gt;
-&lt;p&gt;Check walls adjoining bathrooms, directly beneath aluminum sliding windows, and along the lower 2 feet of ground-floor rooms — especially if dampness tends to return during heavy Bangalore monsoon spells. A dry-looking wall on a warm sunny afternoon does not guarantee that historic plumbing leaks or capillary rising damp have been rectified.&lt;/p&gt;
-&lt;p&gt;Leading manufacturers like Asian Paints explicitly advise treating all subsurface dampness and efflorescence before installing wallpaper. Sticking wallpaper over an active moisture patch merely conceals the visual symptoms while allowing hidden mould to proliferate underneath.&lt;/p&gt;
-&lt;h2&gt;Choosing Wallpaper for an Indian DIY Project&lt;/h2&gt;
-&lt;p&gt;For your first DIY home makeover, a modest, unobstructed rectangular accent wall with a forgiving, non-geometric pattern is the safest place to begin.&lt;/p&gt;
-&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Peel and Stick (Self-Adhesive) Wallpaper:&lt;/strong&gt; Features a pre-applied adhesive backing protected by a peel-off liner. You expose and smooth the backing gradually as you hang each panel. Always verify that the adhesive formulation is compatible with your wall's paint sheen (satin and semi-gloss generally hold peel-and-stick far better than powdery matte distempers).&lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Traditional Pasted Wallpaper:&lt;/strong&gt; Requires dedicated wallpaper paste. Some non-woven wallpapers require "paste-the-wall" technique, while traditional papers require "paste-the-paper" with specific booking and resting times. Follow the roll packaging instructions meticulously.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p&gt;Remember that material terminology and hanging methods are two separate considerations. Descriptions such as &lt;em&gt;vinyl&lt;/em&gt;, &lt;em&gt;non-woven&lt;/em&gt;, or &lt;em&gt;linen fabric finish&lt;/em&gt; describe the surface material — they do not inherently mean the roll is self-adhesive peel-and-stick.&lt;/p&gt;
-&lt;p&gt;Large repeating geometric patterns demand millimeter-accurate seam alignment. Custom photo murals also have a fixed sequential panel order: verify where the main visual subject falls relative to doors and switchboards before placing your order. An inexpensive spare roll cannot simply substitute for a mismatched custom mural drop.&lt;/p&gt;
-&lt;h2&gt;Planning Your Budget and Quantity Accurately&lt;/h2&gt;
-&lt;p&gt;When comparing costs, always calculate the finished installation, including prep work. A wallpaper quotation per roll and a painting estimate per square foot describe fundamentally different deliverables.&lt;/p&gt;
-&lt;p&gt;For wallpaper, account for the core material, trimming and pattern repeat waste (typically 10%–15%), wall priming, shipping, smoother tools, and installer labor if needed. For painting, verify whether your painter's per-square-foot quote includes putty repairs, double coats of primer, masking plastic, and post-job cleanup.&lt;/p&gt;
-&lt;h3&gt;A Realistic Price Comparison&lt;/h3&gt;
-&lt;p&gt;Material choices dramatically influence total expenditure. For example, in October 2026, a contemporary marble design on Giffywalls India listed Standard Paper at ₹129 per sq. ft., whereas the Peel and Stick option was priced at ₹209 per sq. ft. The base headline price on an e-commerce page rarely reflects the self-adhesive variant.&lt;/p&gt;
-&lt;p&gt;At ₹209 per sq. ft., covering a standard 10 ft by 9 ft bedroom accent wall (90 sq. ft.) comes to approximately ₹18,810 for the wallpaper panels alone before trimming allowances or freight. While this is an illustrative designer benchmark, it highlights why wallpaper is an accent luxury rather than an automatic budget saver.&lt;/p&gt;
-&lt;p&gt;If your priority is optimizing your home renovation budget, focus your wallpaper investment on a single impactful feature wall while leaving sound painted walls intact.&lt;/p&gt;
-&lt;h3&gt;Why Roll Coverage Calculations Can Mislead You&lt;/h3&gt;
-&lt;p&gt;Always measure your wall height and width at three separate points (left, middle, right) to capture uneven slabs, using the maximum dimensions with a 2-inch trimming margin.&lt;/p&gt;
-&lt;p&gt;When ordering standard commercial rolls, calculate the number of full-height vertical drops rather than simply dividing wall square footage by roll area:&lt;/p&gt;
-&lt;ul&gt;
-  &lt;li&gt;Consider a wall 3.0 meters wide and 2.7 meters high.&lt;/li&gt;
-  &lt;li&gt;With a standard 0.53-meter-wide wallpaper roll, you require 6 full vertical drops across the 3.0m width.&lt;/li&gt;
-  &lt;li&gt;If each drop needs to be cut to 2.8 meters (accounting for trimming margins), a standard 10-meter roll yields only 3 full drops.&lt;/li&gt;
-  &lt;li&gt;Therefore, you need exactly 2 full rolls to produce 6 drops — even before accounting for pattern repeat offsets or printing imperfections.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p&gt;A pattern with a large vertical repeat (e.g., 64 cm drop match) increases paper waste per cut. Always verify dimensions and pattern repeat with the vendor, and ensure all rolls share the exact same factory batch or dye-lot number to prevent subtle shading discrepancies.&lt;/p&gt;
-&lt;h2&gt;Where to Order Quality Wallpaper in India&lt;/h2&gt;
-&lt;p&gt;These established platforms offer reliable wallpaper collections and sample swatches for Indian homeowners:&lt;/p&gt;
-&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Giffywalls India:&lt;/strong&gt; Offers an extensive catalogue of peel-and-stick murals, custom wall dimensions, and dedicated installation instructions for self-adhesive substrates. Always select the peel-and-stick material dropdown explicitly when ordering sample swatches.&lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Magicdecor:&lt;/strong&gt; Specializes in custom-sized, eco-friendly self-adhesive wall murals with zero-VOC inks. You can order swatch kits to test finish textures and adhesive grip on your specific plaster type prior to bulk order.&lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Asian Paints Nilaya:&lt;/strong&gt; Curates luxury designer collections through an established nationwide dealer network. Nilaya systems typically utilize specialized wall sealers and heavy-duty adhesives, making them ideal when opting for authorized professional installation.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p&gt;Before confirming any online wallpaper purchase, ask customer support one essential question: &lt;em&gt;"Can you share the exact installation specification sheet for this particular batch and material?"&lt;/em&gt; A detailed technical sheet is infinitely more valuable than a generic sales claim.&lt;/p&gt;
-&lt;h2&gt;What You Will Need for DIY Installation&lt;/h2&gt;
-&lt;p&gt;Assemble these essential tools and materials before peeling back the first panel:&lt;/p&gt;
-&lt;h3&gt;Essential Tools:&lt;/h3&gt;
-&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;The wallpaper panels:&lt;/strong&gt; Stored flat in the room for 24 hours to acclimate to indoor humidity.&lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Spirit level or laser level / plumb line:&lt;/strong&gt; To establish an impeccably vertical starting reference line.&lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Felt-edged squeegee / wallpaper smoother:&lt;/strong&gt; Smooths out trapped air without scratching printed vinyl.&lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Sharp snap-off utility knife &amp;amp; fresh blades:&lt;/strong&gt; Dull blades tear wet paper or stretch vinyl film.&lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Metal straightedge / ruler:&lt;/strong&gt; For clean edge trimming along skirting boards and ceiling cornices.&lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Measuring tape &amp;amp; fine pencil:&lt;/strong&gt; For layout marks.&lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Microfiber cloths:&lt;/strong&gt; To wipe away surface dust and finger oils.&lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Stable stepladder &amp;amp; drop cloth:&lt;/strong&gt; For safe access to upper ceiling joints.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;div style="background: rgba(239, 68, 68, 0.08); border-left: 4px solid #ef4444; padding: 1.25rem 1.5rem; border-radius: 8px; margin: 2rem 0;"&gt;
-  &lt;h3 style="color: #ef4444; margin-top: 0; display: flex; align-items: center; gap: 0.5rem;"&gt;⚠️ Critical Safety Warnings &amp;amp; Pre-Installation Checks&lt;/h3&gt;
-  &lt;p&gt;&lt;strong&gt;Review these mandatory safety guidelines before starting:&lt;/strong&gt;&lt;/p&gt;
-  &lt;ul style="margin: 0; padding-left: 1.2rem; line-height: 1.7;"&gt;
-    &lt;li&gt;&lt;strong&gt;Turn off circuit breakers before trimming near electrical sockets:&lt;/strong&gt; When trimming around switchboard plates or running a metal utility knife along conduits, switch off the corresponding MCB in your distribution board to eliminate shock hazards.&lt;/li&gt;
-    &lt;li&gt;&lt;strong&gt;Never apply wallpaper over damp or efflorescent walls:&lt;/strong&gt; White salt deposits (efflorescence) and cool-to-touch damp plaster prevent adhesive bonding and will cause fungal mould. Fix plumbing or external seepage first.&lt;/li&gt;
-    &lt;li&gt;&lt;strong&gt;Allow fresh wall paint to cure completely:&lt;/strong&gt; Touch-dry paint is not cured. Giffywalls recommends waiting at least 3 to 4 weeks, while WallPops advises 30 to 60 days of curing before applying self-adhesive wallpaper. Applying too early traps outgassing solvents, destroying the adhesive bond.&lt;/li&gt;
-    &lt;li&gt;&lt;strong&gt;Perform an inconspicuous 48-hour patch test:&lt;/strong&gt; Apply a sample swatch in an out-of-sight corner. Verify whether removing it lifts the underlying paint film. If the paint peels with the sample, the underlying plaster requires sealing.&lt;/li&gt;
+&lt;p&gt;A quote of ₹85,000 may be better value if all these items are included. A quote of ₹72,000 may become more expensive after the extras are added.&lt;/p&gt;
+&lt;p&gt;Ask about handles, locks, hanging rods, edge finishing, wall fillers and removal of old furniture. Confirm whether polishing or painting the surrounding wall is included. If you are comparing separate labour and material arrangements, agree who buys consumables and who is responsible for shortages.&lt;/p&gt;
+&lt;p&gt;Keep a reserve for genuinely unforeseen repairs, but require a written price before approving additional work.&lt;/p&gt;
+&lt;h2&gt;Planning the wardrobe step by step&lt;/h2&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 1 - List what must fit inside&lt;/strong&gt;: Count long hanging clothes, folded clothes, bags, suitcases and everyday accessories. Think about who will use the shelves. A storage compartment that can only be reached with a stool may suit seasonal items better than daily clothes.&lt;/li&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 2 - Check the room before designing&lt;/strong&gt;: Measure the bed position, door movement, switches and windows. Note any existing damp patches. Resolve moisture problems before covering the wall with a fitted unit.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Leave access to electrical fittings and other services. Avoid designing a cupboard around equipment that must remain accessible for maintenance.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 3 - Approve the internal layout&lt;/strong&gt;: Ask for a drawing that shows shelves, drawers and hanging areas. Check whether a drawer can open fully when the main door is open. For sliding units, check its position behind the overlap.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Put the approved drawing number or date on the quote so everyone is working from the same version.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 4 - Confirm the specification&lt;/strong&gt;: Record board names, grades and thicknesses, finish codes and hardware models. Look at physical samples where possible. A finish seen on a phone screen may look different beside your bedroom flooring.&lt;/li&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 5 - Agree the work sequence and payments&lt;/strong&gt;: Tie payments to clear stages such as approved drawings, delivery of agreed materials, installation and final inspection. Specify who protects floors, clears packaging and removes waste.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;For factory-made units, ask which dimensions become final when production starts and how changes after that point are charged.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 6 - Inspect before the final payment&lt;/strong&gt;: Open every door and drawer. Check alignment, rubbing, rough edges and exposed fasteners. Examine the inside corners with good light.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Ask the installer to demonstrate adjustments and care instructions. Keep the invoice, material details and warranty terms together.&lt;/p&gt;
+&lt;h2&gt;Before and after checklist&lt;/h2&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1rem 1.25rem; margin: 1rem 0;"&gt;
+  &lt;p style="font-weight: 600; margin: 0 0 0.25rem 0; color: #1e293b;"&gt;Before work:&lt;/p&gt;
+  &lt;p style="margin: 0; color: #475569; font-size: 0.95rem; line-height: 1.6;"&gt;Confirm measurements, room dryness, approved drawings, material specifications and the complete price.&lt;/p&gt;
+&lt;/div&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1rem 1.25rem; margin: 1rem 0;"&gt;
+  &lt;p style="font-weight: 600; margin: 0 0 0.25rem 0; color: #1e293b;"&gt;During work:&lt;/p&gt;
+  &lt;p style="margin: 0; color: #475569; font-size: 0.95rem; line-height: 1.6;"&gt;Compare delivered material and fittings with the order. Raise discrepancies while they are still accessible.&lt;/p&gt;
+&lt;/div&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1rem 1.25rem; margin: 1rem 0;"&gt;
+  &lt;p style="font-weight: 600; margin: 0 0 0.25rem 0; color: #1e293b;"&gt;At handover:&lt;/p&gt;
+  &lt;p style="margin: 0; color: #475569; font-size: 0.95rem; line-height: 1.6;"&gt;Check every moving part, inspect the finish and record any unfinished items with an agreed completion date.&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;Photographs of the finished internal layout are useful if you later need replacement fittings or matching shelves.&lt;/p&gt;
+&lt;h2&gt;Troubleshooting &amp; Common Problems: Common quotation problems&lt;/h2&gt;
+&lt;h3&gt;The rate is low but the total keeps growing&lt;/h3&gt;
+&lt;p&gt;Check whether the loft, drawers, backing, fillers or installation were omitted. Compare a complete written scope rather than the first headline number.&lt;/p&gt;
+&lt;h3&gt;The cabinet is deep but hanging clothes still touch the doors&lt;/h3&gt;
+&lt;p&gt;The usable space may have been reduced by tracks, backing or internal fittings. Ask for internal clear dimensions during planning.&lt;/p&gt;
+&lt;h3&gt;The finish looks different from the sample&lt;/h3&gt;
+&lt;p&gt;Check the product code and view both under the same light. For natural materials, discuss acceptable variation before production.&lt;/p&gt;
+&lt;p&gt;A damp smell appears inside&lt;/p&gt;
+&lt;p&gt;Inspect the wall and room ventilation rather than immediately adding fragrance products. A hidden leak or damp surface needs investigation.&lt;/p&gt;
+&lt;h2&gt;Frequently asked questions&lt;/h2&gt;
+&lt;h3&gt;Choosing between a carpenter and a modular supplier&lt;/h3&gt;
+&lt;p&gt;Both can deliver useful results. Compare the specification, measurement responsibility, installation process and after-sales support. The production method alone does not establish quality.&lt;/p&gt;
+&lt;h3&gt;Saving money without weakening the wardrobe&lt;/h3&gt;
+&lt;p&gt;Simplify decorative detailing, unnecessary partitions and accessories. Keep the agreed material and hardware appropriate for the room and the load.&lt;/p&gt;
+&lt;h3&gt;Adding a loft later&lt;/h3&gt;
+&lt;p&gt;It may be possible, but matching finishes and fixing details can become harder. Ask for the loft option separately in the first quotation, even if you postpone it.&lt;/p&gt;
+&lt;h3&gt;Reusing an existing wardrobe&lt;/h3&gt;
+&lt;p&gt;Check the cabinet structure, dampness and fittings before replacing it. New doors or internal changes may be sufficient if the main unit is sound.&lt;/p&gt;
+&lt;h2&gt;Wrapping up&lt;/h2&gt;
+&lt;p&gt;Start with the storage you need and the room you have. A measured drawing and a detailed quote will tell you more about value than a photograph or a low square-foot rate.&lt;/p&gt;
+&lt;p&gt;Once the design is agreed, keep the specification close at hand during installation. It is much easier to question an omitted drawer before the work is finished.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.25rem 1.5rem; margin: 2rem 0;"&gt;
+  &lt;p style="font-weight: 700; margin-bottom: 0.75rem; color: #1e293b; font-size: 1.05rem;"&gt;Related Guides &amp; Services on Carpenterwala:&lt;/p&gt;
+  &lt;ul style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+&lt;li style="margin-bottom: 0.5rem;"&gt;&lt;a href="/blog/kitchen-cabinet-materials-guide" style="color: var(--primary, #2563eb); text-decoration: underline; font-weight: 500;"&gt;Kitchen Cabinet Materials Guide&lt;/a&gt;&lt;/li&gt;
+&lt;li style="margin-bottom: 0.5rem;"&gt;&lt;a href="/blog/carpenter-vs-modular-furniture" style="color: var(--primary, #2563eb); text-decoration: underline; font-weight: 500;"&gt;Custom Carpenter vs Modular Furniture&lt;/a&gt;&lt;/li&gt;
+&lt;li style="margin-bottom: 0.5rem;"&gt;&lt;a href="/services/carpentry" style="color: var(--primary, #2563eb); text-decoration: underline; font-weight: 500;"&gt;Verified Professional Carpentry Services&lt;/a&gt;&lt;/li&gt;
   &lt;/ul&gt;
 &lt;/div&gt;
-&lt;h2&gt;Step-by-Step Peel-and-Stick Wallpaper Installation Guide&lt;/h2&gt;
-&lt;p&gt;Follow these 8 field-tested steps to hang peel-and-stick wallpaper with professional results:&lt;/p&gt;
-&lt;ol style="margin-left: 1.5rem; line-height: 1.8;"&gt;
-  &lt;li&gt;
-    &lt;strong&gt;Step 1: Inspect, Smooth, and Prepare the Substrate&lt;/strong&gt;&lt;br /&gt;
-    Scrape off any peeling paint or protruding plaster bumps. Fill small nail holes and hairline cracks with acrylic wall putty. Sand the repaired patches flush with fine 180-grit sandpaper. If the wall has raw plaster or chalky distemper, apply a coat of acrylic primer or wall sealer and allow it to cure thoroughly.
-  &lt;/li&gt;
-  &lt;li&gt;
-    &lt;strong&gt;Step 2: Clean the Surface and Allow Complete Drying&lt;/strong&gt;&lt;br /&gt;
-    Wipe the entire wall down with a damp microfiber cloth lightly moistened with clean water or a mild isopropyl alcohol mix to lift dust, cooking oils, and spiderwebs. Allow the wall to dry completely for several hours; even microscopic moisture pockets under vinyl film prevent adhesive tack.
-  &lt;/li&gt;
-  &lt;li&gt;
-    &lt;strong&gt;Step 3: Unroll, Inspect, and Sequence the Panels&lt;/strong&gt;&lt;br /&gt;
-    Lay out all wallpaper panels side-by-side on a clean, protected floor. Verify that colors match seamlessly across panel seams, the pattern aligns correctly, and no transit creasing exists before cutting or exposing any adhesive backing.
-  &lt;/li&gt;
-  &lt;li&gt;
-    &lt;strong&gt;Step 4: Mark a True Vertical Plumb Line&lt;/strong&gt;&lt;br /&gt;
-    Room corners in Indian residential apartments are rarely perfectly plumb. Measure out from the corner by the width of the first wallpaper panel minus 1 inch, and draw a light pencil line down the wall using a spirit level or plumb line. This line serves as your absolute vertical anchor for the entire project.
-  &lt;/li&gt;
-  &lt;li&gt;
-    &lt;strong&gt;Step 5: Position and Tack the First Panel&lt;/strong&gt;&lt;br /&gt;
-    Peel back approximately 6 to 10 inches of the protective backing paper from the top of the first panel. Align the straight edge of the panel with your penciled plumb line, allowing a 1-to-2-inch excess at the ceiling for final trimming. Press the exposed adhesive firmly onto the wall.
-  &lt;/li&gt;
-  &lt;li&gt;
-    &lt;strong&gt;Step 6: Work Downward Gradually and Smooth Trapped Air&lt;/strong&gt;&lt;br /&gt;
-    Slowly peel down the backing paper in manageable 12-inch increments with one hand, while simultaneously smoothing the front of the paper with your felt-edged squeegee using the other. Always stroke from the center outward toward the edges to push trapped air out freely. Avoid pulling or stretching the paper, which causes subsequent shrinkage.
-  &lt;/li&gt;
-  &lt;li&gt;
-    &lt;strong&gt;Step 7: Pattern-Match and Butt-Joint Adjacent Strips&lt;/strong&gt;&lt;br /&gt;
-    Position the second strip so its pattern aligns seamlessly with the first strip at eye level. Depending on manufacturer specifications, either butt the edges together tightly without overlapping, or create the specified 0.5-inch overlap. Smooth the joint firmly with your squeegee.
-  &lt;/li&gt;
-  &lt;li&gt;
-    &lt;strong&gt;Step 8: Precision Trim Edges and Inspect Seams&lt;/strong&gt;&lt;br /&gt;
-    Place your metal straightedge firmly into the crease where the wall meets the ceiling and skirting board. Using a fresh, razor-sharp utility knife blade held at a low 45-degree angle, cleanly slice off the excess paper. Snap off a fresh blade segment every two cuts to ensure crisp edges without tearing.
-  &lt;/li&gt;
-&lt;/ol&gt;
-&lt;div style="background: rgba(16, 185, 129, 0.08); border-left: 4px solid #10b981; padding: 1.25rem 1.5rem; border-radius: 8px; margin: 2rem 0;"&gt;
-  &lt;h3 style="color: #10b981; margin-top: 0; display: flex; align-items: center; gap: 0.5rem;"&gt;💡 Pro-Tips From the Field&lt;/h3&gt;
-  &lt;ul style="margin: 0; padding-left: 1.2rem; line-height: 1.7;"&gt;
-    &lt;li&gt;&lt;strong&gt;A second set of hands is invaluable:&lt;/strong&gt; While one person aligns the top edge and monitors the vertical plumb line, the second person can hold the weight of the roll off the wall to prevent premature accidental sticking.&lt;/li&gt;
-    &lt;li&gt;&lt;strong&gt;Tackle switch plates cleanly:&lt;/strong&gt; Unscrew the external switchboard cover after switching off the MCB. Hang the wallpaper sheet directly over the open box, make an "X" cut through the center opening, fold the flaps inward, and screw the cover plate back on for a flawless factory look.&lt;/li&gt;
-    &lt;li&gt;&lt;strong&gt;Keep offcuts and packaging tubes:&lt;/strong&gt; Roll up remaining paper scraps and store them in the original protective postal tube. If an accidental furniture scratch or water spot damages a panel two years later, you have an exact dye-matched patch ready.&lt;/li&gt;
-  &lt;/ul&gt;
-&lt;/div&gt;
-&lt;h2&gt;Before, During, and After Installation Checklist&lt;/h2&gt;
-&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Before Installation:&lt;/strong&gt; Verify wall is dry and smooth; confirm sample swatch test adhesion; calculate rolls with 10%–15% waste; confirm all rolls share the same batch number; gather level, smoother, and fresh blades.&lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;During Installation:&lt;/strong&gt; Establish a true plumb line; align patterns at eye level; peel backing in gradual stages; smooth from center outward; snap blades frequently for clean razor trims.&lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;After Installation:&lt;/strong&gt; Inspect all seams in daylight; avoid touching newly adhered seams for 48 hours; wipe surface only with a dry microfiber cloth or lightly damp sponge; avoid solvent-based chemical cleaners.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2&gt;Troubleshooting Common Wallpaper Problems&lt;/h2&gt;
-&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Edges keep lifting along the seam:&lt;/strong&gt;&lt;br /&gt;This is typically caused by residual drywall dust, porous unprimed putty, or localized humidity. Avoid using random synthetic superglues, which permanently stain vinyl and ruin plaster. Use a tube of specialized wallpaper seam repair adhesive, press down with a roller, and hold until bonded.&lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Persistent air bubbles trapped under the surface:&lt;/strong&gt;&lt;br /&gt;If discovered during installation, gently lift the affected panel section back up to the bubble and resmooth with your squeegee. For a small bubble discovered days later on self-adhesive vinyl, use a fine sewing needle to make a microscopic pin-prick at the center, then gently press the trapped air out toward the pinhole.&lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;The pattern drifts or slopes between panels:&lt;/strong&gt;&lt;br /&gt;This occurs when the first panel was slightly off plumb or if the paper was stretched diagonally during hanging. Do not attempt to pull or stretch subsequent panels to compensate. Peel the strip back up immediately and re-align along a verified plumb line.&lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Paint peels off when removing peel-and-stick wallpaper:&lt;/strong&gt;&lt;br /&gt;This indicates the original wall paint was poorly bonded to underlying putty or lacked a proper primer coat. Warm the wallpaper surface gently with a hairdryer on low heat to soften the adhesive, and peel back slowly at a flat 180-degree angle rather than pulling outward.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2&gt;Frequently Asked Questions&lt;/h2&gt;
-&lt;h3&gt;Can I install peel-and-stick wallpaper directly over existing paint?&lt;/h3&gt;
-&lt;p&gt;Yes, provided the existing paint is completely sound, free from flaking or chalking, and has a satin or semi-gloss sheen. Chalky distemper or flat builder-grade matte paints should be cleaned, lightly scuffed, and treated with an acrylic wall primer before applying self-adhesive wallpaper.&lt;/p&gt;
-&lt;h3&gt;How do I prepare an unpainted or freshly plastered wall?&lt;/h3&gt;
-&lt;p&gt;Raw cement plaster or drywall putty cannot be wallpapered directly because the porous surface absorbs adhesive instantly. The wall must be fully cured (typically 28 days for new plaster), smoothed with wall putty, sanded, and sealed with high-adhesion interior acrylic wall primer.&lt;/p&gt;
-&lt;h3&gt;Is peel-and-stick wallpaper safe for rented apartments in India?&lt;/h3&gt;
-&lt;p&gt;Peel-and-stick wallpaper is designed to be removable without damaging quality paint. However, if the apartment was painted using cheap local distemper over unprimed putty, removing the paper may pull paint flecks off. Always test an inconspicuous patch before doing an entire wall.&lt;/p&gt;
-&lt;h3&gt;Can wallpaper be installed in Indian bathrooms or kitchens?&lt;/h3&gt;
-&lt;p&gt;While specialized vinyl wallpapers exist, standard peel-and-stick wallpaper is not recommended directly inside shower wet-zones or right behind a gas stove due to constant steam, soap scum, and high heat. For kitchens and powder rooms, install only on well-ventilated accent walls away from grease splashes and direct running water.&lt;/p&gt;
-&lt;h3&gt;When should I hire a professional wallpaper installer?&lt;/h3&gt;
-&lt;p&gt;DIY installation is ideal for single rectangular feature walls. For double-height ceilings, staircases, intricate archways, expensive imported silk/fabric wallpapers, or walls requiring extensive plaster repair, hiring experienced wall-decor specialists guarantees seamless results without costly material wastage.&lt;/p&gt;
-&lt;h2&gt;Conclusion &amp;amp; Related Reads&lt;/h2&gt;
-&lt;p&gt;Choosing between wallpaper and paint does not have to be an all-or-nothing decision. By strategically combining a designer wallpaper feature wall with durable, washable interior paint throughout the rest of your home, you achieve high-end visual elegance while keeping maintenance manageable.&lt;/p&gt;
-&lt;p&gt;Explore related home improvement and wall care guides on Carpenterwala:&lt;/p&gt;
-&lt;ul&gt;
-  &lt;li&gt;&lt;a href="/blog/how-to-estimate-interior-painting-cost-distemper-emulsion-royale"&gt;Interior Painting Cost Guide: Distemper vs. Plastic Emulsion vs. Royale&lt;/a&gt;&lt;/li&gt;
-  &lt;li&gt;&lt;a href="/blog/modern-wall-panel-designs"&gt;Modern Wall Panel Designs: Material Options and Ideas for Your Home&lt;/a&gt;&lt;/li&gt;
-  &lt;li&gt;&lt;a href="/blog/how-to-fix-ground-dampness-capillary-action-walls"&gt;Dealing with Ground Dampness: How to Treat Rising Moisture &amp;amp; Peeling Paint&lt;/a&gt;&lt;/li&gt;
-  &lt;li&gt;&lt;a href="/services/painting"&gt;Carpenterwala Professional Painting &amp;amp; Waterproofing Services in Bangalore&lt;/a&gt;&lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2&gt;Sources and Product Guidance&lt;/h2&gt;
-&lt;p style="font-size: 0.9rem; opacity: 0.85;"&gt;Product specifications, technical curing times, and market benchmark pricing were reviewed on 23 October 2026. Material options and pricing are subject to manufacturer updates.&lt;/p&gt;
-&lt;ol style="font-size: 0.85rem; opacity: 0.8; line-height: 1.6;"&gt;
-  &lt;li&gt;WallPops product installation technical FAQs and indoor usage specifications.&lt;/li&gt;
-  &lt;li&gt;Asian Paints exterior wall coatings and monsoon waterproofing guidelines.&lt;/li&gt;
-  &lt;li&gt;Asian Paints Nilaya application manual and wall seepage remediation protocol.&lt;/li&gt;
-  &lt;li&gt;Giffywalls India marble and floral collection pricing and material options.&lt;/li&gt;
-  &lt;li&gt;Giffywalls wallpaper technical FAQs, sample program, and acrylic curing requirements.&lt;/li&gt;
-  &lt;li&gt;Magicdecor eco-friendly self-adhesive collection, seam treatment, and material swatch kit.&lt;/li&gt;
-  &lt;li&gt;WallPops paint curing timeline and substrate compatibility advisory (NuWallpaper).&lt;/li&gt;
-  &lt;li&gt;Giffywalls peel and stick step-by-step installation instructions.&lt;/li&gt;
-  &lt;li&gt;Asian Paints Nilaya wallpaper care, seam maintenance, and surface preparation FAQs.&lt;/li&gt;
-&lt;/ol&gt;</v>
+&lt;h2&gt;Sources and product guidance&lt;/h2&gt;
+&lt;p&gt;Sources checked on 23 October 2026. Published prices can change; obtain a quote for the actual dimensions and specification.&lt;/p&gt;
+&lt;ul style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 1.5rem;"&gt;
+  &lt;li&gt;[1] Livspace wardrobe pricing examples&lt;/li&gt;
+  &lt;li&gt;[2] Greenply guide to MR BWR and BWP plywood&lt;/li&gt;
+  &lt;li&gt;[3] Greenply comparison of plywood and MDF for wardrobes&lt;/li&gt;
+  &lt;li&gt;[4] Blum guidance on choosing the number of hinges&lt;/li&gt;
+&lt;/ul&gt;</v>
       </c>
       <c r="I2" t="str">
-        <v>/images/blogs/wallpaper-vs-paint-for-indian-homes.jpg</v>
+        <v>/images/blogs/wardrobe-cost-india-materials-labour-quote-guide.jpg</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
@@ -743,24 +646,1711 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
+        <v>modular-kitchen-cost-india-budget-materials-hidden-extras</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Modular Kitchen Cost in India: Budgeting, Materials &amp; What Quotes Leave Out</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Carpentry</v>
+      </c>
+      <c r="E3" t="str">
+        <v>October 23, 2026</v>
+      </c>
+      <c r="F3" t="str">
+        <v>8 min read</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Plan a modular kitchen budget with clear measurements, material comparisons, an itemised example and a checklist of costs that quotes often leave out.</v>
+      </c>
+      <c r="H3" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
+  &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;A realistic modular kitchen budget in India ranges from ₹1.5 lakh for compact straight/L-shaped setups in laminate to ₹4.5+ lakh for acrylic/PU parallel or island layouts. Over 30% of actual expenses come from items omitted in initial cabinet quotes: granite or quartz countertop cutting, dado tiles, sink plumbing, chimney ducting, core cutting, and internal wire baskets.&lt;/p&gt;
+&lt;/div&gt;
+&lt;div style="background: rgba(239, 68, 68, 0.08); border-left: 4px solid #ef4444; padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: #dc2626;"&gt;⚠️ Critical Safety Warnings &amp; Precautions&lt;/p&gt;
+  &lt;p style="margin: 0; line-height: 1.7; font-size: 0.95rem;"&gt;Always verify LPG or piped gas cylinder hose clearances and ensure chimney duct pipes maintain fireproof distances from electrical wiring conduits. Never run 16A power points directly under the kitchen sink where drainage drips can trigger dangerous short circuits.&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;A kitchen quote often looks simple until you start asking questions. Does the price include the countertop? What about the sink, the plumbing changes and the wall tiles behind the hob? Are the appliances included, or have they only been shown in the design?&lt;/p&gt;
+&lt;p&gt;A useful kitchen budget begins with those answers. The number printed beside “per square foot” is only meaningful once you know what is being measured and what will be delivered.&lt;/p&gt;
+&lt;p&gt;Whether you are fitting out a new flat or replacing an old kitchen, this guide explains how to organise the work and compare quotes across India.&lt;/p&gt;
+&lt;h2&gt;Setting a realistic budget&lt;/h2&gt;
+&lt;p&gt;Published kitchen prices cover very different scopes. DesignCafe’s India guide describes budget kitchens around ₹1.5–2 lakh, mid-range examples around ₹2.5–3.15 lakh and higher-end examples around ₹3.5–4 lakh. These are the provider’s indicative examples, not a national quotation for every layout. [1]&lt;/p&gt;
+&lt;p&gt;A compact cabinet package can exclude civil work and appliances. An older kitchen may need repairs before a new cabinet is installed. A more useful first budget separates the cabinets, countertop, services and appliances.&lt;/p&gt;
+&lt;p&gt;Your local market will affect labour and transport. The condition of the room can matter just as much. A kitchen with sound plumbing and a usable countertop is a different project from one that needs to be stripped back.&lt;/p&gt;
+&lt;p&gt;Make a list of what can stay. Reusing something suitable reduces the amount of work without forcing you to choose a poor replacement.&lt;/p&gt;
+&lt;h2&gt;Understanding kitchen measurements&lt;/h2&gt;
+&lt;p&gt;Kitchen quotations may use running feet, cabinet elevation area, panel area or a complete package. Ask the supplier to show its method on a drawing.&lt;/p&gt;
+&lt;p&gt;A 10 ft length of base units and an 8 ft length of wall units should not be treated as the same cabinet simply because both are quoted by length. Height, depth and internal fittings differ.&lt;/p&gt;
+&lt;p&gt;A square-foot rate may apply to the cabinet front rather than the floor area of the room. Multiplying the kitchen’s floor area by an unexplained rate can produce a misleading estimate.&lt;/p&gt;
+&lt;p&gt;For a corner unit, ask how the two adjoining runs are counted. Mark tall units, lofts and open shelves separately. Check whether an empty appliance space is being charged as a complete cabinet.&lt;/p&gt;
+&lt;p&gt;Ask for the dimensions of each cabinet and a schedule listing its shutters, drawers and accessories. That gives you a way to compare one supplier with another.&lt;/p&gt;
+&lt;h2&gt;Comparing layouts and materials&lt;/h2&gt;
+&lt;p&gt;Choose the layout around daily use&lt;/p&gt;
+&lt;div style="overflow-x: auto; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;table style="width: 100%; border-collapse: collapse; text-align: left; font-size: 0.95rem;"&gt;
+    &lt;thead&gt;
+      &lt;tr style="background: rgba(0,0,0,0.04); border-bottom: 2px solid var(--border, #e2e8f0);"&gt;
+        &lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Layout&lt;/th&gt;&lt;th style="padding: 12px 16px; font-weight: 600;"&gt;A practical use&lt;/th&gt;&lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Budget detail to check&lt;/th&gt;
+      &lt;/tr&gt;
+    &lt;/thead&gt;
+    &lt;tbody&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Straight&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;A compact kitchen along one wall&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Whether there is enough usable preparation space&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;L shaped&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;A room with two adjoining usable walls&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;The cost and usefulness of the corner&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Parallel&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;A kitchen with two facing work runs&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Clear movement space between open doors&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;U shaped&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;A room needing storage on three sides&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Extra cabinetry and access to two corners&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Island or peninsula&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Larger rooms with suitable circulation&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Worktop support and any additional service routes&lt;/td&gt;
+      &lt;/tr&gt;
+    &lt;/tbody&gt;
+  &lt;/table&gt;
+&lt;/div&gt;
+&lt;p&gt;A more elaborate layout is useful only if the room can accommodate it. Drawers that collide with a dishwasher or a walkway narrowed by an island are expensive design errors.&lt;/p&gt;
+&lt;p&gt;Specify the cabinet structure and the visible finish separately&lt;/p&gt;
+&lt;p&gt;The cabinet box and the shutter finish perform different jobs. “Acrylic kitchen” usually describes a visible finish rather than every part of the cabinet.&lt;/p&gt;
+&lt;p&gt;Discuss the substrate, edge treatment and hardware separately from colour and gloss. Greenply’s grade guidance distinguishes plywood intended for different moisture conditions. Under-sink units deserve particular attention, but even a water-resistant board should be protected from continuing leaks. [2]&lt;/p&gt;
+&lt;p&gt;Ordinary MDF, plywood, metal and other cabinet systems have different strengths and limitations. Ask about the exact product and its intended use. A broad material name cannot tell you how the completed cabinet will perform.&lt;/p&gt;
+&lt;p&gt;For the finish, take a sample home. Look at fingerprints, reflections and how easily the approved cleaner removes a small mark. A finish that photographs well may need more upkeep than you want.&lt;/p&gt;
+&lt;p&gt;Choose storage by what you keep&lt;/p&gt;
+&lt;p&gt;Deep drawers can make pots easier to reach. A tall pull-out may help with a particular storage problem, but it can also consume a large part of the fittings budget.&lt;/p&gt;
+&lt;p&gt;Blum’s cabinet planning tools include fitting selection and collision checks. The practical lesson is to design the internal storage and door movements together, rather than ordering accessories at the end. [3]&lt;/p&gt;
+&lt;p&gt;Start with the everyday cooking tools, food containers and cleaning supplies you already own. Keep frequently used items within comfortable reach.&lt;/p&gt;
+&lt;h2&gt;Finding the costs outside the cabinet quote&lt;/h2&gt;
+&lt;p&gt;Ask about demolition, debris removal, wall repairs, the countertop, sink cut-outs, plumbing, electrical work, wall finishes and installation.&lt;/p&gt;
+&lt;p&gt;Gas-line changes need the appropriate authorised professional. Do not allow cabinetry to cover a gas shut-off, an electrical junction or a plumbing point that needs maintenance.&lt;/p&gt;
+&lt;p&gt;The following fictional budget shows how separate items can accumulate. It is an illustration of scope, not a current market quotation.&lt;/p&gt;
+&lt;div style="overflow-x: auto; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;table style="width: 100%; border-collapse: collapse; text-align: left; font-size: 0.95rem;"&gt;
+    &lt;thead&gt;
+      &lt;tr style="background: rgba(0,0,0,0.04); border-bottom: 2px solid var(--border, #e2e8f0);"&gt;
+        &lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Work item&lt;/th&gt;&lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Illustrative allowance&lt;/th&gt;
+      &lt;/tr&gt;
+    &lt;/thead&gt;
+    &lt;tbody&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Cabinets with agreed finish and standard fittings&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹1,60,000&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Countertop including agreed cut-outs&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹35,000&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Sink and tap&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹12,000&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Plumbing and electrical alterations&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹18,000&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Wall repairs and backsplash work&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹15,000&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Demolition and debris removal&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹10,000&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Subtotal before applicable taxes and other agreed charges&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹2,50,000&lt;/td&gt;
+      &lt;/tr&gt;
+    &lt;/tbody&gt;
+  &lt;/table&gt;
+&lt;/div&gt;
+&lt;p&gt;Appliances, a chimney, major waterproofing work and unexpected concealed damage are outside this example. A sample budget is useful only when its exclusions remain visible.&lt;/p&gt;
+&lt;p&gt;If your old countertop is staying, confirm whether it can be supported safely during cabinet removal. Ask who pays if it breaks and whether reuse is technically practical.&lt;/p&gt;
+&lt;h2&gt;Planning the project step by step&lt;/h2&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 1 - Record how the kitchen is used&lt;/strong&gt;: Note how many people cook at once, the type of cooking, large vessels and the storage you lack. Add the exact dimensions of appliances you plan to retain.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;A household that uses several large pressure cookers needs different internal storage from one that mostly reheats food.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 2 - Inspect the room and service points&lt;/strong&gt;: Check walls, floor levels, water supply, drainage and ventilation. Repair leaks before fitting new cabinets.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Map gas and electrical requirements with the appropriate professionals. Avoid making the layout depend on a service change that has not been assessed.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 3 - Freeze the appliance and sink positions&lt;/strong&gt;: Confirm model dimensions, service clearances and manufacturer ventilation requirements. Leave access for maintenance.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Do this before cabinet production and countertop cutting. A late appliance change can affect several neighbouring units.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 4 - Approve the cabinet schedule&lt;/strong&gt;: Check the number of drawers, shelves, hinges and pull-outs. Confirm usable internal space and opening clearances.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Compare physical material samples with the written specification. Keep the approved drawing and finish codes with the order.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 5 - Agree the site sequence&lt;/strong&gt;: For a renovation, coordinate removal, repairs, concealed services, surface work, cabinetry and final connections. The precise order depends on the construction method and what is being retained.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Ask each trade when its work must be inspected before another layer covers it. Plan a temporary cooking arrangement if the room will be unusable.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 6 - Check the work at handover&lt;/strong&gt;: Run water through the sink and look for leaks below. Have the professionals test the service connections and appliances they installed.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Open drawers and shutters, inspect the countertop edges and check access to shut-offs. Ask for a demonstration of removable baskets and adjustable fittings.&lt;/p&gt;
+&lt;h2&gt;Checking the finished kitchen&lt;/h2&gt;
+&lt;p&gt;Before installation: Confirm room readiness, appliance dimensions, materials, drawings and the complete scope.&lt;/p&gt;
+&lt;p&gt;During installation: Check that service points remain accessible and that damaged material is addressed before it is hidden.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1rem 1.25rem; margin: 1rem 0;"&gt;
+  &lt;p style="font-weight: 600; margin: 0 0 0.25rem 0; color: #1e293b;"&gt;At handover:&lt;/p&gt;
+  &lt;p style="margin: 0; color: #475569; font-size: 0.95rem; line-height: 1.6;"&gt;Check moving parts, finish defects, sink drainage, cleaning and the agreed snag list.&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;Keep product manuals, invoices and the final layout. Photos of service routes before closing walls can help with future repairs.&lt;/p&gt;
+&lt;h2&gt;Troubleshooting &amp; Common Problems: Common budgeting mistakes&lt;/h2&gt;
+&lt;p&gt;Buying a low cabinet rate and discovering expensive extras&lt;/p&gt;
+&lt;p&gt;Ask for a complete project total alongside the unit rate. Clarify delivery, fitting, site visits and finishing work.&lt;/p&gt;
+&lt;h3&gt;Adding every accessory shown in a display kitchen&lt;/h3&gt;
+&lt;p&gt;Remove items that do not solve an everyday problem. A simpler cabinet with good access can be more useful than a complicated fitting you rarely use.&lt;/p&gt;
+&lt;p&gt;Ignoring the old plumbing&lt;/p&gt;
+&lt;p&gt;New cabinets can hide the same leak that damaged the previous set. Inspect and repair the services before fitting replacements.&lt;/p&gt;
+&lt;p&gt;Approving a design without appliance models&lt;/p&gt;
+&lt;p&gt;Nominal appliance widths do not establish installation clearance. Use the actual product instructions.&lt;/p&gt;
+&lt;h2&gt;Frequently asked questions&lt;/h2&gt;
+&lt;h3&gt;Choosing modular or carpenter made cabinetry&lt;/h3&gt;
+&lt;p&gt;Compare the finished specification and accountability. Site-built and factory-built kitchens both need accurate measurements, suitable materials and competent installation.&lt;/p&gt;
+&lt;p&gt;Using different finishes to control cost&lt;/p&gt;
+&lt;p&gt;You can use a more expensive finish selectively, provided the cabinet design and material compatibility are agreed. Check the total saving after additional detailing and fabrication.&lt;/p&gt;
+&lt;p&gt;Keeping the kitchen layout unchanged&lt;/p&gt;
+&lt;p&gt;Retaining suitable service positions can reduce alterations. Still inspect the pipes, wiring and supporting surfaces before deciding.&lt;/p&gt;
+&lt;p&gt;Deciding whether to change the countertop&lt;/p&gt;
+&lt;p&gt;Check damage, support, cut-outs and compatibility with the new cabinets. Reuse should be assessed before demolition begins.&lt;/p&gt;
+&lt;h2&gt;Wrapping up&lt;/h2&gt;
+&lt;p&gt;Plan the kitchen as a complete room. Cabinets are a large part of the cost, but the countertop, services and site work decide whether the project stays within budget.&lt;/p&gt;
+&lt;p&gt;An accurate drawing and an itemised quote give you room to make sensible choices before production starts.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.25rem 1.5rem; margin: 2rem 0;"&gt;
+  &lt;p style="font-weight: 700; margin-bottom: 0.75rem; color: #1e293b; font-size: 1.05rem;"&gt;Related Guides &amp; Services on Carpenterwala:&lt;/p&gt;
+  &lt;ul style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+&lt;li style="margin-bottom: 0.5rem;"&gt;&lt;a href="/blog/how-to-adjust-loose-modular-kitchen-cabinet-hinges" style="color: var(--primary, #2563eb); text-decoration: underline; font-weight: 500;"&gt;How to Adjust Loose Modular Kitchen Cabinet Hinges&lt;/a&gt;&lt;/li&gt;
+&lt;li style="margin-bottom: 0.5rem;"&gt;&lt;a href="/blog/kitchen-cabinet-materials-guide" style="color: var(--primary, #2563eb); text-decoration: underline; font-weight: 500;"&gt;Kitchen Cabinet Materials Guide: Plywood vs MDF vs HDF&lt;/a&gt;&lt;/li&gt;
+&lt;li style="margin-bottom: 0.5rem;"&gt;&lt;a href="/services/carpentry" style="color: var(--primary, #2563eb); text-decoration: underline; font-weight: 500;"&gt;Book Verified Kitchen Carpentry &amp; Repair&lt;/a&gt;&lt;/li&gt;
+  &lt;/ul&gt;
+&lt;/div&gt;
+&lt;h2&gt;Sources and product guidance&lt;/h2&gt;
+&lt;p&gt;Sources checked on 23 October 2026. Published price examples are indicative and their scope should be confirmed with the provider.&lt;/p&gt;
+&lt;ul style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 1.5rem;"&gt;
+  &lt;li&gt;[1] DesignCafe kitchen interior cost guide for India&lt;/li&gt;
+  &lt;li&gt;[2] Greenply guide to plywood grades and moisture exposure&lt;/li&gt;
+  &lt;li&gt;[3] Blum cabinet planning and fitting selection&lt;/li&gt;
+&lt;/ul&gt;</v>
+      </c>
+      <c r="I3" t="str">
+        <v>/images/blogs/modular-kitchen-cost-india-budget-materials-hidden-extras.jpg</v>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>false-ceiling-cost-india-pop-gypsum-pvc</v>
+      </c>
+      <c r="C4" t="str">
+        <v>False Ceiling Cost in India: POP vs Gypsum vs PVC &amp; Installation Guide</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Carpentry</v>
+      </c>
+      <c r="E4" t="str">
+        <v>October 23, 2026</v>
+      </c>
+      <c r="F4" t="str">
+        <v>8 min read</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Compare POP, gypsum and PVC ceilings, understand the complete installation cost and plan lighting, access and ceiling height before work starts.</v>
+      </c>
+      <c r="H4" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
+  &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;Standard gypsum board false ceilings cost ₹95–₹145/sq.ft for basic framing and sheet installation, while intricate POP cove designs run ₹120–₹180/sq.ft. Moisture-prone bathrooms and balconies should utilize PVC panels (₹110–₹160/sq.ft). Always budget an extra 40–50% for electrical point creation, concealed LED cove strips, COB spotlights, and ceiling primer/emulsion painting.&lt;/p&gt;
+&lt;/div&gt;
+&lt;div style="background: rgba(239, 68, 68, 0.08); border-left: 4px solid #ef4444; padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: #dc2626;"&gt;⚠️ Critical Safety Warnings &amp; Precautions&lt;/p&gt;
+  &lt;p style="margin: 0; line-height: 1.7; font-size: 0.95rem;"&gt;Ceiling fans, chandeliers, and heavy hanging swing hooks must NEVER be anchored to gypsum boards or GI channel grids. They must be fastened directly into the parent RCC slab with industrial anchor expansion bolts through pre-marked trap openings.&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;A false ceiling can tidy a room, conceal services and give lighting a planned position. It can also make a room feel lower than expected if the design is chosen from a photograph without measuring the space.&lt;/p&gt;
+&lt;p&gt;Before comparing a POP quote with a gypsum quote, decide what the ceiling needs to do. A simple border for a few lights is a different job from a full ceiling with several levels, concealed fittings and access panels.&lt;/p&gt;
+&lt;p&gt;This guide explains how to compare materials and installation scope for homes across India. It also covers the details that should be settled before the frame goes up.&lt;/p&gt;
+&lt;h2&gt;Comparing the main ceiling materials&lt;/h2&gt;
+&lt;p&gt;A ceiling’s performance depends on the complete assembly, including framing, boards or panels, fixing details and finishing. Choosing a familiar brand name for the visible surface is only one part of that decision.&lt;/p&gt;
+&lt;div style="overflow-x: auto; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;table style="width: 100%; border-collapse: collapse; text-align: left; font-size: 0.95rem;"&gt;
+    &lt;thead&gt;
+      &lt;tr style="background: rgba(0,0,0,0.04); border-bottom: 2px solid var(--border, #e2e8f0);"&gt;
+        &lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Material or system&lt;/th&gt;&lt;th style="padding: 12px 16px; font-weight: 600;"&gt;A typical reason to consider it&lt;/th&gt;&lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Important detail to confirm&lt;/th&gt;
+      &lt;/tr&gt;
+    &lt;/thead&gt;
+    &lt;tbody&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Gypsum board ceiling&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Flat surfaces and planned lighting layouts&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Board type, framing specification and joint treatment&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;POP work&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Moulded details and shaped decorative work&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Supporting system, workmanship and drying requirements&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;PVC panel ceiling&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Panelled finishes and selected humid interiors&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Product suitability, heat limits and complete fire-performance information&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;A limited border or ceiling feature&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Concealing a small service zone or adding selected lights&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Whether a full-room ceiling is necessary&lt;/td&gt;
+      &lt;/tr&gt;
+    &lt;/tbody&gt;
+  &lt;/table&gt;
+&lt;/div&gt;
+&lt;p&gt;Gyproc supplies different plasterboard types for different performance requirements, including moisture and fire resistance. That does not make every board suitable for every wet location. Specify the actual product and the complete tested or approved system where those properties matter. [1]&lt;/p&gt;
+&lt;p&gt;For PVC, request the manufacturer’s technical information rather than accepting “waterproof” or “fireproof” as a complete specification. A water-resistant panel cannot fix a leak above it, and fire behaviour depends on the product and installation.&lt;/p&gt;
+&lt;p&gt;For all three options, ask how the ceiling will be supported, finished and accessed for repairs. Avoid fixing a fan or heavy decorative fitting to a board or panel alone. The installer must provide the appropriate independent or engineered support.&lt;/p&gt;
+&lt;h2&gt;Understanding the complete cost&lt;/h2&gt;
+&lt;p&gt;An online square-foot price can omit finishing, lights, wiring or difficult site access. Livspace’s false-ceiling guide separates costs by material and design, which is a useful starting point for comparison, but a site quotation still needs the full scope. [2]&lt;/p&gt;
+&lt;p&gt;As a published reference, NoBroker’s interior rate sheet lists gypsum false ceilings at ₹70–120 per sq. ft. and POP false ceilings at ₹90–150 per sq. ft., with the stated inclusions. These are provider examples, not a quote for your design or a guarantee of local rates. [4]&lt;/p&gt;
+&lt;p&gt;Ask what the quoted rate includes: framing, hangers, boards or panels, trims, joint treatment, paint preparation, painting and waste removal. Confirm the treatment of stepped edges, vertical faces, curved sections and small rooms.&lt;/p&gt;
+&lt;p&gt;Lighting is often a separate budget. “Light points included” may cover wiring or cut-outs without including the fittings themselves.&lt;/p&gt;
+&lt;p&gt;Here is a fictional example for a 120 sq. ft. room. It is a budgeting illustration, not a market rate.&lt;/p&gt;
+&lt;div style="overflow-x: auto; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;table style="width: 100%; border-collapse: collapse; text-align: left; font-size: 0.95rem;"&gt;
+    &lt;thead&gt;
+      &lt;tr style="background: rgba(0,0,0,0.04); border-bottom: 2px solid var(--border, #e2e8f0);"&gt;
+        &lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Work item&lt;/th&gt;&lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Illustrative calculation&lt;/th&gt;
+      &lt;/tr&gt;
+    &lt;/thead&gt;
+    &lt;tbody&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Agreed ceiling system and installation&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;120 sq. ft. × ₹110 = ₹13,200&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Surface finishing and painting&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹3,600&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Electrical point alterations&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹3,000&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Selected light fittings&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹4,000&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Access panel and other agreed details&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹1,200&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Subtotal before applicable taxes and other charges&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹25,000&lt;/td&gt;
+      &lt;/tr&gt;
+    &lt;/tbody&gt;
+  &lt;/table&gt;
+&lt;/div&gt;
+&lt;p&gt;A price that initially appears to be ₹13,200 can therefore describe only part of the finished project. Compare totals with equal inclusions.&lt;/p&gt;
+&lt;p&gt;Local labour, room access, the amount of detailed work and the condition of the structure can affect the final quote. Do not assume the same area in every Indian city will cost the same.&lt;/p&gt;
+&lt;h2&gt;Measuring the room and planning the height&lt;/h2&gt;
+&lt;p&gt;Measure the existing floor-to-ceiling height and mark the proposed finished ceiling level on the walls. Stand in the room and look at that line before approving the design.&lt;/p&gt;
+&lt;p&gt;Check door tops, windows, curtain arrangements, overhead cupboards and air-conditioning equipment. A drawing should show how the ceiling meets each of them.&lt;/p&gt;
+&lt;p&gt;Ask why the proposed drop is needed. A simple light layout may need less space than a design with ducts and several layers. The installer should work from the equipment and system requirements rather than a standard drop used everywhere.&lt;/p&gt;
+&lt;p&gt;For a compact room, consider doing less. A narrow feature or a plain ceiling with surface-mounted lighting may meet the need while keeping more height.&lt;/p&gt;
+&lt;p&gt;The best measurement is a complete dimensioned layout. It should show ceiling levels, lighting positions, access points and the way the edge detail is charged.&lt;/p&gt;
+&lt;h2&gt;Preparing for installation&lt;/h2&gt;
+&lt;p&gt;Resolve the condition above the ceiling&lt;/p&gt;
+&lt;p&gt;Look for seepage, loose plaster and damaged services. Repair the source before covering the area.&lt;/p&gt;
+&lt;p&gt;Photograph the visible services and note where valves, junctions or equipment need future access. A concealed leak becomes harder to find once the ceiling is finished.&lt;/p&gt;
+&lt;p&gt;Coordinate the light fittings&lt;/p&gt;
+&lt;p&gt;Choose the fitting models before the cut-outs are made. Check their installation depth, heat clearances and whether the driver or other components need access.&lt;/p&gt;
+&lt;p&gt;Discuss the appearance with the lights switched on, not just the drawing. Several closely spaced bright downlights can be uncomfortable even when the ceiling looks attractive in a photograph.&lt;/p&gt;
+&lt;p&gt;Confirm the materials&lt;/p&gt;
+&lt;p&gt;Ask for the board or panel identification, framing specification and finishing products on the order. Check delivered materials before they are installed.&lt;/p&gt;
+&lt;p&gt;For claims about acoustics, fire or moisture resistance, ask what the complete assembly achieves. A single component does not establish the performance of the entire ceiling.&lt;/p&gt;
+&lt;h2&gt;Following the work sequence&lt;/h2&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 1 - Approve a coordinated drawing&lt;/strong&gt;: Agree the finished height, material, edge details, light positions and access panels. Mark any heavy fitting that needs separate support.&lt;/li&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 2 - Protect the room&lt;/strong&gt;: Remove or cover furniture and protect floors. Arrange safe access for the installation team. Ceiling work involves overhead tasks and is not a suitable first DIY project.&lt;/li&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 3 - Complete repairs and service preparation&lt;/strong&gt;: Resolve leaks and required repairs. Have the electrical work planned and carried out by a qualified professional before the relevant areas are closed.&lt;/li&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 4 - Inspect the supporting system&lt;/strong&gt;: Ask the installer to show the agreed framing and fixing arrangement before the visible finish hides it. Use the system manufacturer’s requirements rather than improvised fixing details.&lt;/li&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 5 - Install and finish the surface&lt;/strong&gt;: The method differs between gypsum, POP and panel systems. Joint treatment, drying and finishing should follow the selected products. Avoid rushing painting over material that is not ready.&lt;/li&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 6 - Complete electrical fittings and access details&lt;/strong&gt;: Have the electrician fit and test the lights. Check that service access panels can be opened without damaging the finished ceiling.&lt;/li&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 7 - Inspect in daylight and under the room lights&lt;/strong&gt;: Look along the surface from different positions. Check uneven joints, cracks, chipped edges and poorly positioned cut-outs. Record the snag list before settling the final balance.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;h2&gt;Handover checklist&lt;/h2&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1rem 1.25rem; margin: 1rem 0;"&gt;
+  &lt;p style="font-weight: 600; margin: 0 0 0.25rem 0; color: #1e293b;"&gt;Before work:&lt;/p&gt;
+  &lt;p style="margin: 0; color: #475569; font-size: 0.95rem; line-height: 1.6;"&gt;Confirm ceiling height, approved drawings, material specifications, service access and the complete price.&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;Before closing the surface: Check required supports and service positions with the responsible trades.&lt;/p&gt;
+&lt;p&gt;At completion: Inspect finishes, lighting operation, access panels and clean-up. Keep invoices, product information and photographs of concealed routes.&lt;/p&gt;
+&lt;p&gt;Avoid drilling into a finished ceiling without checking what is above it. For additional fixtures, get the support arrangement assessed first.&lt;/p&gt;
+&lt;h2&gt;Troubleshooting &amp; Common Problems: Troubleshooting and maintenance&lt;/h2&gt;
+&lt;p&gt;A crack appears along a joint&lt;/p&gt;
+&lt;p&gt;Ask the installer to investigate the joint treatment, framing or movement. Repeatedly covering the line with paint may hide the symptom briefly without resolving its cause.&lt;/p&gt;
+&lt;p&gt;A stain appears after rain&lt;/p&gt;
+&lt;p&gt;Investigate the water source above the ceiling. Keep people away from sagging or softened areas and arrange professional inspection.&lt;/p&gt;
+&lt;h3&gt;The room feels darker after installation&lt;/h3&gt;
+&lt;p&gt;Check light output, placement and the colours of the room. Additional ceiling layers do not necessarily improve illumination.&lt;/p&gt;
+&lt;p&gt;A driver or fitting fails but cannot be reached&lt;/p&gt;
+&lt;p&gt;This is an access-planning problem. Discuss access during design, especially where components will need replacement.&lt;/p&gt;
+&lt;h2&gt;Frequently asked questions&lt;/h2&gt;
+&lt;h3&gt;Choosing the cheapest ceiling material&lt;/h3&gt;
+&lt;p&gt;Compare the complete installed and finished project. A lower material rate may be outweighed by detailed labour, extra painting or additional fittings.&lt;/p&gt;
+&lt;p&gt;Using a false ceiling in a humid room&lt;/p&gt;
+&lt;p&gt;Select a system specifically suitable for the conditions and follow its ventilation and exposure requirements. Persistent dampness needs repair before any ceiling is fitted.&lt;/p&gt;
+&lt;p&gt;Keeping the existing fan&lt;/p&gt;
+&lt;p&gt;Confirm its mounting and the relationship between the new ceiling level, fan and room. Have the support assessed and retained or altered correctly.&lt;/p&gt;
+&lt;p&gt;Installing a ceiling in only part of a room&lt;/p&gt;
+&lt;p&gt;A limited feature can work well if it has a clear purpose. Check how it meets walls, lights and furniture rather than extending it simply to fill the room.&lt;/p&gt;
+&lt;h2&gt;Wrapping up&lt;/h2&gt;
+&lt;p&gt;Agree the height and the purpose first. Then compare complete systems with the same lighting, painting and access requirements.&lt;/p&gt;
+&lt;p&gt;A modest ceiling with good proportions and useful lighting can be a better fit for the room than an elaborate design that leaves little height or difficult maintenance.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.25rem 1.5rem; margin: 2rem 0;"&gt;
+  &lt;p style="font-weight: 700; margin-bottom: 0.75rem; color: #1e293b; font-size: 1.05rem;"&gt;Related Guides &amp; Services on Carpenterwala:&lt;/p&gt;
+  &lt;ul style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+&lt;li style="margin-bottom: 0.5rem;"&gt;&lt;a href="/blog/fall-ceiling-repair-cost-india" style="color: var(--primary, #2563eb); text-decoration: underline; font-weight: 500;"&gt;False Ceiling Repair Cost &amp; Guide in India&lt;/a&gt;&lt;/li&gt;
+&lt;li style="margin-bottom: 0.5rem;"&gt;&lt;a href="/blog/how-to-fix-ceiling-seepage-patches-stains-leak" style="color: var(--primary, #2563eb); text-decoration: underline; font-weight: 500;"&gt;How to Fix Ceiling Seepage Patches &amp; Stains&lt;/a&gt;&lt;/li&gt;
+&lt;li style="margin-bottom: 0.5rem;"&gt;&lt;a href="/services/carpentry" style="color: var(--primary, #2563eb); text-decoration: underline; font-weight: 500;"&gt;Professional Carpentry &amp; Ceiling Services&lt;/a&gt;&lt;/li&gt;
+  &lt;/ul&gt;
+&lt;/div&gt;
+&lt;h2&gt;Sources and product guidance&lt;/h2&gt;
+&lt;p&gt;Sources checked on 23 October 2026. The budget table is illustrative; obtain a quote for the actual design and complete system.&lt;/p&gt;
+&lt;ul style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 1.5rem;"&gt;
+  &lt;li&gt;[1] Gyproc plasterboard types and performance information&lt;/li&gt;
+  &lt;li&gt;[2] Livspace false-ceiling cost and material guide&lt;/li&gt;
+  &lt;li&gt;[3] Gyproc residential ceiling and drywall systems&lt;/li&gt;
+  &lt;li&gt;[4] NoBroker published interior work rates and inclusions&lt;/li&gt;
+&lt;/ul&gt;</v>
+      </c>
+      <c r="I4" t="str">
+        <v>/images/blogs/false-ceiling-cost-india-pop-gypsum-pvc.jpg</v>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>wallpaper-vs-paint-for-indian-homes</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Wallpaper vs Paint for Indian Homes: Where to Use Each, Practical Costs &amp; DIY Guide</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Wallpaper</v>
+      </c>
+      <c r="E5" t="str">
+        <v>October 23, 2026</v>
+      </c>
+      <c r="F5" t="str">
+        <v>10 min read</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Compare wallpaper and paint for Indian homes, choose the right walls, find suppliers and follow a practical peel-and-stick installation guide.</v>
+      </c>
+      <c r="H5" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
+  &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;For Indian homes, the most practical approach is combining finishes: use wallpaper on dry, prominent accent walls (behind the master bed or living room sofa) for instant designer texture and pattern, while keeping washable emulsion paint in high-traffic, humid, or splash-prone zones like kitchens, corridors, and bathrooms. Always resolve underlying wall dampness first and test an inconspicuous sample before installing peel-and-stick panels.&lt;/p&gt;
+&lt;/div&gt;
+&lt;div style="background: rgba(239, 68, 68, 0.08); border-left: 4px solid #ef4444; padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: #dc2626;"&gt;⚠️ Critical Safety Warnings &amp; Precautions&lt;/p&gt;
+  &lt;p style="margin: 0; line-height: 1.7; font-size: 0.95rem;"&gt;When trimming wallpaper edges around live modular switchboards and plug sockets, switch OFF the room’s main MCB at the distribution board. Never use metallic utility knives near live electrical socket contacts.&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;A living room can feel tired even when most of its paint is perfectly fine. Perhaps the wall behind the sofa looks bare, or the bedroom needs a little more warmth. Before booking painters for the whole flat, take a closer look at what actually needs changing.&lt;/p&gt;
+&lt;p&gt;Wallpaper can give a dry interior wall a pattern or finish that would take considerably more work to create with paint. A botanical print behind the bed, a quiet linen effect in the living room or a small patterned corner beside a desk can be enough.&lt;/p&gt;
+&lt;p&gt;For many homes, a sensible plan is to use both finishes: wallpaper on selected interior walls, paint wherever it suits the surface and daily use, and suitable exterior coatings outside. The budget depends on the area you change and the material you choose. Wallpaper is not automatically the cheaper option.&lt;/p&gt;
+&lt;h2&gt;Wallpaper and paint compared&lt;/h2&gt;
+&lt;p&gt;Wallpaper works particularly well when the design itself is the main reason for changing a wall. Paint makes sense when you want a plain finish, need to refresh a large area or expect regular cleaning and future colour changes.&lt;/p&gt;
+&lt;div style="overflow-x: auto; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;table style="width: 100%; border-collapse: collapse; text-align: left; font-size: 0.95rem;"&gt;
+    &lt;thead&gt;
+      &lt;tr style="background: rgba(0,0,0,0.04); border-bottom: 2px solid var(--border, #e2e8f0);"&gt;
+        &lt;th style="padding: 12px 16px; font-weight: 600;"&gt;What matters&lt;/th&gt;&lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Interior paint&lt;/th&gt;&lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Peel and stick wallpaper&lt;/th&gt;&lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Traditional pasted wallpaper&lt;/th&gt;
+      &lt;/tr&gt;
+    &lt;/thead&gt;
+    &lt;tbody&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Appearance&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Plain colour and painted effects&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Printed patterns and murals&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Broad choice of prints and textures&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Preparation&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Repairs and the specified paint system&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;A sound surface compatible with the adhesive&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Repairs and the specified primer or sealer&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;DIY work&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Masking, painting and drying between coats&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Careful alignment and smoothing&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Adhesive preparation and accurate hanging&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Repairs&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Local touch-ups may show a shade difference&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Matching offcuts may help with small repairs&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Matching paper and careful repair work&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Removal&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Prepare the surface for the next coat&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Product and paint condition affect removal&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Method depends on the paper and adhesive&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Budget&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Compare the complete painting quote&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Include prep, quantity and tools&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Include prep, paper, adhesive and labour&lt;/td&gt;
+      &lt;/tr&gt;
+    &lt;/tbody&gt;
+  &lt;/table&gt;
+&lt;/div&gt;
+&lt;p&gt;Both finishes depend on the wall underneath. Wallpaper can cover the old colour, but raised patches, loose paint and damp plaster still need attention.&lt;/p&gt;
+&lt;h2&gt;Where to use wallpaper and where to keep paint&lt;/h2&gt;
+&lt;p&gt;Walk through the house before choosing a design. Note where people lean against walls, where the sunlight falls and which corners become damp during the monsoon.&lt;/p&gt;
+&lt;div style="overflow-x: auto; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;table style="width: 100%; border-collapse: collapse; text-align: left; font-size: 0.95rem;"&gt;
+    &lt;thead&gt;
+      &lt;tr style="background: rgba(0,0,0,0.04); border-bottom: 2px solid var(--border, #e2e8f0);"&gt;
+        &lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Area&lt;/th&gt;&lt;th style="padding: 12px 16px; font-weight: 600;"&gt;A practical starting choice&lt;/th&gt;&lt;th style="padding: 12px 16px; font-weight: 600;"&gt;What to check&lt;/th&gt;
+      &lt;/tr&gt;
+    &lt;/thead&gt;
+    &lt;tbody&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Wall behind the bed&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Wallpaper&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Dryness and how the pattern sits above the headboard&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Living room feature wall&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Wallpaper or paint&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Furniture placement, lighting and visible wall area&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Study or work corner&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Wallpaper on one wall&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Pattern scale and the view behind your desk&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Corridors and utility areas&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Suitable washable paint&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Scuffing and how often the surface needs cleaning&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Kitchen cooking and sink zones&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;A finish rated for the exposure&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Heat, grease, splashes and cleaning requirements&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Shower walls and persistently wet areas&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;A properly specified wet-area finish&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Waterproofing and direct water exposure&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Exterior walls and open balconies&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Exterior paint or a specified coating system&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Rain, UV exposure, cracks and drainage&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;A wall with seepage&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Repair and dry the wall first&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Find and fix the source before decorating&lt;/td&gt;
+      &lt;/tr&gt;
+    &lt;/tbody&gt;
+  &lt;/table&gt;
+&lt;/div&gt;
+&lt;p&gt;Interior walls where wallpaper earns its place&lt;/p&gt;
+&lt;p&gt;Start with a wall you will actually see. A mural hidden behind a tall wardrobe adds very little to the room. Behind a bed or sofa, choose a design whose main detail remains visible above the furniture.&lt;/p&gt;
+&lt;p&gt;For a small room, order a sample before committing to a large print. Hold it against the curtains, flooring and existing paint. Check it in daylight and again under your evening lights; a background that looks cream online may look grey at home.&lt;/p&gt;
+&lt;p&gt;Places where paint remains useful&lt;/p&gt;
+&lt;p&gt;Wallpapering one wall does not mean the other walls need a fresh coat. Keep sound, clean paint if it already works with the room.&lt;/p&gt;
+&lt;p&gt;Repaint where the finish is worn, where you need better washability or where a colour change will make the space feel more coherent. Ceilings can usually stay with their existing painted finish if they are in good condition.&lt;/p&gt;
+&lt;p&gt;Outside, use products specified for exterior exposure. Ordinary interior wallpaper is unsuitable for an open balcony or a rain-facing wall. Also investigate cracks and leaks before coating them; an exterior repaint alone may not resolve seepage. [1][2]&lt;/p&gt;
+&lt;p&gt;Check moisture in every climate&lt;/p&gt;
+&lt;p&gt;Check walls beside bathrooms, below windows and along the lower parts of ground-floor rooms, especially if dampness returns during the rains. A dry-looking patch on a sunny afternoon does not establish that an old leak has been fixed. In humid coastal homes, consider ventilation and seasonal moisture; in hot, dry regions, still check plumbing-adjacent walls and past rain damage before covering them.&lt;/p&gt;
+&lt;p&gt;Asian Paints advises treating seepage before installing wallpaper. Covering the patch can hide the warning signs while leaving the cause in place. [3]&lt;/p&gt;
+&lt;h2&gt;Choosing wallpaper for a DIY project&lt;/h2&gt;
+&lt;p&gt;For a first attempt, a modest, mostly uninterrupted wall with a forgiving pattern is a good place to begin.&lt;/p&gt;
+&lt;p&gt;Peel and stick wallpaper has an adhesive backing. You remove the backing gradually as you hang it. Check that the particular product is suitable for your paint finish and wall texture.&lt;/p&gt;
+&lt;p&gt;Traditional wallpaper needs adhesive. Some products require paste on the wall; others require it on the paper. Follow the roll instructions, including any resting time after applying paste.&lt;/p&gt;
+&lt;p&gt;The material description and installation method are separate details. Words such as “vinyl”, “non-woven” or “fabric finish” do not, by themselves, mean that a wallpaper is self-adhesive.&lt;/p&gt;
+&lt;p&gt;Large geometric prints need accurate matching. A mural also has a fixed arrangement: check where its main subject will fall before ordering. An inexpensive extra roll cannot necessarily extend a custom mural.&lt;/p&gt;
+&lt;h2&gt;Planning your budget and quantity&lt;/h2&gt;
+&lt;p&gt;Compare the finished job, including preparation. A wallpaper price per roll and a painting quote per square foot describe different things.&lt;/p&gt;
+&lt;p&gt;For wallpaper, allow for the material, trimming and pattern matching, wall preparation, delivery, tools and any installation help. For paint, check whether the quote includes repairs, primer, the specified coats, masking and clean-up.&lt;/p&gt;
+&lt;p&gt;A realistic price comparison&lt;/p&gt;
+&lt;p&gt;Material choice can change the bill substantially. When checked on 23 October 2026, one Giffywalls marble design listed Standard Paper at ₹129 per sq. ft. and Peel and Stick at ₹209 per sq. ft. The lower displayed price therefore did not describe the self-adhesive option. [4]&lt;/p&gt;
+&lt;p&gt;At ₹209 per sq. ft., a 10 ft by 9 ft wall would cost ₹18,810 for 90 sq. ft. of wallpaper before any additional allowances or charges. This is one product example, not a general market rate. Confirm the final price and material at checkout.&lt;/p&gt;
+&lt;p&gt;If the aim is to spend less, start by reducing the area of work. One wallpaper feature wall, with the other sound walls left alone, may suit the room better than redecorating every surface.&lt;/p&gt;
+&lt;h3&gt;Why roll coverage can be misleading&lt;/h3&gt;
+&lt;p&gt;Measure the wall at several points. Use the largest dimensions and the supplier’s specified trimming allowance.&lt;/p&gt;
+&lt;p&gt;For rolls, calculate how many full-height strips you can cut. For example, consider a wall 3 metres wide and 2.7 metres high:&lt;/p&gt;
+&lt;p&gt;With a 0.53-metre-wide roll, you need six strips across the wall.&lt;/p&gt;
+&lt;p&gt;If each cut strip is 2.8 metres long, including trimming, a 10-metre roll gives three strips.&lt;/p&gt;
+&lt;p&gt;Two rolls would cover those six strips before allowing for pattern matching or defects.&lt;/p&gt;
+&lt;p&gt;A large pattern repeat can increase that quantity. Send the dimensions and the chosen pattern to the supplier for confirmation. For custom murals, ask how to measure around doors and windows before subtracting openings.&lt;/p&gt;
+&lt;p&gt;Order matching rolls from the same batch where applicable. Keep a labelled offcut for future repairs.&lt;/p&gt;
+&lt;h2&gt;Where to order wallpaper in India&lt;/h2&gt;
+&lt;p&gt;These are useful starting points for comparing materials and ordering samples. Confirm delivery to your PIN code, the installation method and the return policy for your exact order.&lt;/p&gt;
+&lt;p&gt;Giffywalls India&lt;/p&gt;
+&lt;p&gt;Giffywalls offers a dedicated peel and stick wallpaper collection, custom wall sizes and a separate installation guide for self-adhesive materials.&lt;/p&gt;
+&lt;p&gt;Select the material explicitly on the product page. The same design can be offered in several materials at different prices. Its wallpaper FAQs also explain sample ordering. [4][5]&lt;/p&gt;
+&lt;p&gt;Magicdecor&lt;/p&gt;
+&lt;p&gt;Magicdecor has a self-adhesive wallpaper collection with custom sizing. Its collection page offers material samples, which are useful for checking the finish before placing a larger order.&lt;/p&gt;
+&lt;p&gt;Confirm that the final product selection says peel and stick or self-adhesive. Ask about panel sizes, trimming allowances and the treatment of joins for the design you choose. [6]&lt;/p&gt;
+&lt;p&gt;Asian Paints Nilaya&lt;/p&gt;
+&lt;p&gt;Asian Paints Nilaya is another option for browsing wallpaper and arranging the appropriate material and application system.&lt;/p&gt;
+&lt;p&gt;Its guidance describes using a sealer and wallpaper adhesive, so check the exact product before treating it as a peel-and-stick purchase. It is worth considering when you prefer assistance with preparation or installation. [3]&lt;/p&gt;
+&lt;p&gt;Before paying, ask one particularly useful question: “Can you send me the installation instructions for this exact material?” That answer is more useful than a general promise that the wallpaper is easy to apply.&lt;/p&gt;
+&lt;h2&gt;What you will need&lt;/h2&gt;
+&lt;p&gt;For a straightforward peel-and-stick installation, gather:&lt;/p&gt;
+&lt;p&gt;The wallpaper and its installation instructions.&lt;/p&gt;
+&lt;p&gt;A measuring tape, pencil and spirit level or plumb line.&lt;/p&gt;
+&lt;p&gt;A wallpaper smoother or felt-edged squeegee.&lt;/p&gt;
+&lt;p&gt;A sharp trimming knife, spare blades and a straightedge.&lt;/p&gt;
+&lt;p&gt;Clean cloths and the cleaner recommended for the surface.&lt;/p&gt;
+&lt;p&gt;Floor protection and a stable stepladder.&lt;/p&gt;
+&lt;p&gt;A second pair of hands helps with long panels. Traditional pasted paper also needs the specified adhesive and application tools.&lt;/p&gt;
+&lt;h2&gt;Checks before you start&lt;/h2&gt;
+&lt;p&gt;Resolve dampness first. Stop if there is active seepage, mould, loose plaster or recurring salt deposits. Arrange the repair and allow the wall to dry before decorating.&lt;/p&gt;
+&lt;p&gt;Allow new paint to cure. Touch-dry paint may still be unsuitable for adhesive wallpaper. Waiting times vary: Giffywalls advises at least three to four weeks, while WallPops specifies 30 to 60 days for NuWallpaper. Follow the requirements of your chosen wallpaper and paint system. [5][7]&lt;/p&gt;
+&lt;p&gt;Test a sample. Use it to check adhesion, appearance and removal on an inconspicuous part of the actual wall. Follow the supplier’s test period. “Removable” wallpaper can still lift poorly bonded paint.&lt;/p&gt;
+&lt;p&gt;Plan around electrical fittings. Keep blades and moisture away from sockets. If a cover needs removing, have the circuit safely isolated and get qualified help where needed.&lt;/p&gt;
+&lt;h2&gt;How to apply peel and stick wallpaper&lt;/h2&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 1 - Inspect and prepare the surface&lt;/strong&gt;: Remove loose material and repair small holes or uneven patches. Follow the wallpaper supplier’s requirements for priming or sealing. Avoid sticking directly onto dusty putty, chalking paint or unfinished plaster unless the product specifically permits it.&lt;/li&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 2 - Clean the wall and let it dry&lt;/strong&gt;: Remove dust and grease with the recommended method. Give any damp cleaning time to dry fully. Even a small dirty patch can interfere with adhesion.&lt;/li&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 3 - Lay out the panels&lt;/strong&gt;: Check the design, colour and panel sequence before removing any backing. Report printing damage or a mismatch before cutting or hanging the material.&lt;/li&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 4 - Mark a vertical starting line&lt;/strong&gt;: Use a spirit level or plumb line. A room corner may be slightly out of square, so use a measured vertical guide for the first panel.&lt;/li&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 5 - Position the first panel&lt;/strong&gt;: Expose a small section of backing at the top. Align the panel with your guide and leave the trimming allowance specified in the instructions. Check its position before pressing firmly.&lt;/li&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 6 - Work down gradually&lt;/strong&gt;: Peel away more backing in manageable sections. Smooth the paper from the centre towards the edges as you go. Keep the loose section supported and avoid pulling the material to force it into position.&lt;/li&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 7 - Match the next panel&lt;/strong&gt;: Check the pattern at eye level and lower down before fixing the whole strip. Follow the product instructions for the join: some materials require touching edges, while others specify an overlap or trimming method.&lt;/li&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 8 - Trim and inspect&lt;/strong&gt;: Use a sharp blade and straightedge for the edges, protecting the underlying surface. Leave complicated fittings or awkward access to an installer. Check seams and corners in good light, then keep the room conditions within the manufacturer’s guidance.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Use the Giffywalls peel and stick installation guide alongside the instructions supplied with your order. The sequence above is a general guide; product-specific requirements take priority. [8]&lt;/p&gt;
+&lt;h2&gt;Before and after checklist&lt;/h2&gt;
+&lt;p&gt;Before installation: Confirm that the wall is sound and dry, the sample works, the quantity is sufficient and the panels match.&lt;/p&gt;
+&lt;p&gt;During installation: Check the first panel carefully, match each strip before pressing it down and follow the specified seam method.&lt;/p&gt;
+&lt;p&gt;After installation: Inspect the joins, save the order details and offcuts, and keep the care instructions somewhere easy to find.&lt;/p&gt;
+&lt;p&gt;Clean according to the material. A dry soft brush may suit a delicate finish; a washable product may permit gentle wiping. Test first, and avoid soaking seams or using abrasive cleaners. [9]&lt;/p&gt;
+&lt;h2&gt;Troubleshooting &amp; Common Problems: Troubleshooting common problems&lt;/h2&gt;
+&lt;p&gt;Edges keep lifting&lt;/p&gt;
+&lt;p&gt;Check for dust, unsuitable paint, wall texture or moisture. Ask the supplier about a compatible repair method. Adding random household glue can leave marks and make later removal harder.&lt;/p&gt;
+&lt;p&gt;Bubbles appear while hanging&lt;/p&gt;
+&lt;p&gt;Where the product allows repositioning, gently lift the affected section and smooth it down again. Persistent or later bubbles need a closer look at the bond and wall condition. Check with the supplier before puncturing the paper.&lt;/p&gt;
+&lt;h3&gt;The pattern drifts between strips&lt;/h3&gt;
+&lt;p&gt;Recheck the first panel’s vertical alignment and the panel order. Stretching the next strip to compensate can make the mismatch worse. Stop early while correction is still manageable.&lt;/p&gt;
+&lt;p&gt;Paint comes away during removal&lt;/p&gt;
+&lt;p&gt;The underlying paint bond may have failed. Pause and ask the supplier for its removal method. Repair the surface before applying another finish.&lt;/p&gt;
+&lt;h2&gt;Frequently asked questions&lt;/h2&gt;
+&lt;p&gt;Using wallpaper over existing paint&lt;/p&gt;
+&lt;p&gt;Sound existing paint may be a suitable base if the wallpaper manufacturer approves the surface and finish. Flaking, powdery or damp paint needs attention first.&lt;/p&gt;
+&lt;p&gt;Preparing an unpainted wall&lt;/p&gt;
+&lt;p&gt;You may not need a decorative colour coat, but the wall can still require repairs, primer or sealer. Ask the supplier to specify the full preparation system.&lt;/p&gt;
+&lt;h3&gt;Choosing wallpaper for a rented flat&lt;/h3&gt;
+&lt;p&gt;Get the landlord’s agreement and test the product on the actual surface. Consider possible paint repair costs when comparing removable options.&lt;/p&gt;
+&lt;h3&gt;Choosing wallpaper for kitchens and bathrooms&lt;/h3&gt;
+&lt;p&gt;Some products permit use in humid rooms, but suitability depends on the exact product, ventilation and exposure. For a first DIY project, choose a dry wall away from cooking heat and direct splashes.&lt;/p&gt;
+&lt;p&gt;Deciding when to call an installer&lt;/p&gt;
+&lt;p&gt;Get help with stairwells, high walls, expensive murals, extensive repairs or complicated corners. A small, accessible wall is a more manageable first project.&lt;/p&gt;
+&lt;h2&gt;Wrapping up&lt;/h2&gt;
+&lt;p&gt;Choose the wall before you choose the wallpaper. A well-placed print can give a bedroom or living room the change you want while allowing you to keep existing paint that still looks good.&lt;/p&gt;
+&lt;p&gt;Order a sample, confirm the material and spend time on preparation. Keep exterior work on a suitable exterior coating system, and fix moisture problems before choosing either finish.&lt;/p&gt;
+&lt;p&gt;If the wall needs repairs or a fresh painted base, explore Carpenterwala’s painting services before starting the wallpaper installation.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.25rem 1.5rem; margin: 2rem 0;"&gt;
+  &lt;p style="font-weight: 700; margin-bottom: 0.75rem; color: #1e293b; font-size: 1.05rem;"&gt;Related Guides &amp; Services on Carpenterwala:&lt;/p&gt;
+  &lt;ul style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+&lt;li style="margin-bottom: 0.5rem;"&gt;&lt;a href="/blog/asian-paints-royale-vs-berger-silk-luxury-paint-comparison-guide" style="color: var(--primary, #2563eb); text-decoration: underline; font-weight: 500;"&gt;Asian Paints Royale vs Berger Silk Luxury Paint Guide&lt;/a&gt;&lt;/li&gt;
+&lt;li style="margin-bottom: 0.5rem;"&gt;&lt;a href="/blog/choosing-the-right-paint" style="color: var(--primary, #2563eb); text-decoration: underline; font-weight: 500;"&gt;Choosing the Right Interior Paint for Indian Homes&lt;/a&gt;&lt;/li&gt;
+&lt;li style="margin-bottom: 0.5rem;"&gt;&lt;a href="/services/painting" style="color: var(--primary, #2563eb); text-decoration: underline; font-weight: 500;"&gt;Professional Wall Painting &amp; Wallpaper Services&lt;/a&gt;&lt;/li&gt;
+  &lt;/ul&gt;
+&lt;/div&gt;
+&lt;h2&gt;Sources and product guidance&lt;/h2&gt;
+&lt;p&gt;Product information and the example price were checked on 23 October 2026. Prices, material options and delivery terms can change.&lt;/p&gt;
+&lt;ul style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 1.5rem;"&gt;
+  &lt;li&gt;[1] WallPops product FAQs including indoor use&lt;/li&gt;
+  &lt;li&gt;[2] Asian Paints exterior wall coatings and waterproofing&lt;/li&gt;
+  &lt;li&gt;[3] Asian Paints Nilaya application and seepage guidance&lt;/li&gt;
+  &lt;li&gt;[4] Giffywalls marble design and material prices&lt;/li&gt;
+  &lt;li&gt;[5] Giffywalls wallpaper FAQs and samples&lt;/li&gt;
+  &lt;li&gt;[6] Magicdecor self-adhesive collection and samples&lt;/li&gt;
+  &lt;li&gt;[7] WallPops curing and product compatibility guidance&lt;/li&gt;
+  &lt;li&gt;[8] Giffywalls peel and stick installation instructions&lt;/li&gt;
+  &lt;li&gt;[9] Asian Paints wallpaper care and preparation FAQs&lt;/li&gt;
+&lt;/ul&gt;</v>
+      </c>
+      <c r="I5" t="str">
+        <v>/images/blogs/wallpaper-vs-paint-for-indian-homes.jpg</v>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>terrace-waterproofing-india-methods-cost-contractor-checklist</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Terrace Waterproofing for Indian Homes: Methods, Costs &amp; Contractor Checklist</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Home Maintenance</v>
+      </c>
+      <c r="E6" t="str">
+        <v>October 23, 2026</v>
+      </c>
+      <c r="F6" t="str">
+        <v>8 min read</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Understand terrace waterproofing methods, compare complete quotes and plan repairs, drainage, testing and maintenance for Indian homes.</v>
+      </c>
+      <c r="H6" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
+  &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;Never apply waterproofing chemicals over loose dust, moss, or active hairline cracks without surface grinding and polymer modified mortar repairs. Liquid elastomeric polyurethane/acrylic membranes cost ₹45–₹90/sq.ft, while APP bituminous membranes cost ₹65–₹110/sq.ft. Ensure parapet wall flashing (coving) reaches at least 300mm high and mandate a 48-hour ponding flood test before final contractor payment.&lt;/p&gt;
+&lt;/div&gt;
+&lt;div style="background: rgba(239, 68, 68, 0.08); border-left: 4px solid #ef4444; padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: #dc2626;"&gt;⚠️ Critical Safety Warnings &amp; Precautions&lt;/p&gt;
+  &lt;p style="margin: 0; line-height: 1.7; font-size: 0.95rem;"&gt;Ensure all rooftop workers use safety harnesses and non-slip rubber footwear. Never carry out torch-applied bituminous membrane work near overhead electrical cables, gas vents, or dry debris.&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;A ceiling stain after the first heavy rain often sends the household looking for a bucket of waterproof paint. But water may be entering through a terrace crack, a pipe penetration, a damaged outlet or a poorly finished parapet junction.&lt;/p&gt;
+&lt;p&gt;The stain tells you where the water has appeared. It does not necessarily show where it entered.&lt;/p&gt;
+&lt;p&gt;A lasting repair starts with an inspection of the whole terrace and the way it drains. This guide explains the main choices, how to compare contractor quotations and what to check before the work is covered by tiles or another finish.&lt;/p&gt;
+&lt;h2&gt;Finding the cause of terrace leakage&lt;/h2&gt;
+&lt;p&gt;Walk through the problem with a competent waterproofing contractor. Note when the stain appears, whether it follows rain and whether it is near a bathroom, water tank or pipe route.&lt;/p&gt;
+&lt;p&gt;Water from an internal plumbing leak needs a different investigation from rain entering through the roof. Photograph the affected rooms and terrace details, and keep a record of when the marks change.&lt;/p&gt;
+&lt;p&gt;On the terrace, inspect outlets, corners, pipe penetrations, visible cracks and the junction between the roof and parapet. Look for water that remains after rain.&lt;/p&gt;
+&lt;p&gt;Dr. Fixit identifies slope, drainage, surface condition, cracks and expected foot traffic as important factors in selecting a terrace system. A new coating should be chosen after these conditions are understood. [1]&lt;/p&gt;
+&lt;p&gt;Widespread cracking, loose concrete, exposed reinforcement or a sagging slab needs appropriate structural assessment. A surface coating is not a repair for structural distress.&lt;/p&gt;
+&lt;h2&gt;Comparing waterproofing systems&lt;/h2&gt;
+&lt;p&gt;There is no universally best bucket or membrane for every roof. The intended surface, existing layers, exposure and future use determine the choice.&lt;/p&gt;
+&lt;div style="overflow-x: auto; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;table style="width: 100%; border-collapse: collapse; text-align: left; font-size: 0.95rem;"&gt;
+    &lt;thead&gt;
+      &lt;tr style="background: rgba(0,0,0,0.04); border-bottom: 2px solid var(--border, #e2e8f0);"&gt;
+        &lt;th style="padding: 12px 16px; font-weight: 600;"&gt;System family&lt;/th&gt;&lt;th style="padding: 12px 16px; font-weight: 600;"&gt;A reason it may be considered&lt;/th&gt;&lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Detail to discuss&lt;/th&gt;
+      &lt;/tr&gt;
+    &lt;/thead&gt;
+    &lt;tbody&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Liquid-applied membrane&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Terraces with complicated junctions and penetrations&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Substrate preparation, reinforcement and required consumption&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Cementitious or polymer-modified system&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Compatible mineral surfaces and specified protected assemblies&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Flexibility, curing and whether a protective finish is required&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Sheet membrane system&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Projects designed around a continuous membrane layer&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Seams, terminations, penetrations and protection&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;A protected waterproofing assembly&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Terraces with regular use or a planned finished surface&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Membrane protection, drainage and added load&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Local repair within an existing system&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;A genuinely isolated defect in an otherwise sound roof&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Compatibility and evidence that the wider system is serviceable&lt;/td&gt;
+      &lt;/tr&gt;
+    &lt;/tbody&gt;
+  &lt;/table&gt;
+&lt;/div&gt;
+&lt;p&gt;For example, Sika lists liquid-applied roof membranes with different uses and system requirements. The product data sheet, rather than the word “waterproof”, establishes where and how the material should be applied. [2]&lt;/p&gt;
+&lt;p&gt;A coating intended to remain exposed may differ from one that must be protected. A terrace used for regular gatherings or a garden also faces different demands from an occasional-access roof.&lt;/p&gt;
+&lt;p&gt;Ask about UV exposure, standing water, expected movement and permitted traffic. A coating’s stated resistance to ponding does not remove the need to address poor drainage.&lt;/p&gt;
+&lt;p&gt;Avoid mixing products from unrelated systems without written compatibility guidance. The cheapest material substitution can undermine the agreed assembly.&lt;/p&gt;
+&lt;h2&gt;Understanding area and cost&lt;/h2&gt;
+&lt;p&gt;Measure the horizontal terrace and identify which vertical junctions, upstands and parapet faces are included. Ask how outlets, corners and equipment bases are priced.&lt;/p&gt;
+&lt;p&gt;A quote based only on floor area can omit the details where water is entering. It can also omit removal of failed layers, repairs, slope correction and protection.&lt;/p&gt;
+&lt;p&gt;Published square-foot prices are useful only when the system build-up is comparable. Dr. Fixit’s terrace guidance distinguishes exposed coatings and systems with additional protective finishes, which helps explain why apparently similar quotes can cover different work. [3]&lt;/p&gt;
+&lt;p&gt;The following fictional budget shows one way to itemise a 500 sq. ft. project. It is not a market rate or a recommendation for a particular system.&lt;/p&gt;
+&lt;div style="overflow-x: auto; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;table style="width: 100%; border-collapse: collapse; text-align: left; font-size: 0.95rem;"&gt;
+    &lt;thead&gt;
+      &lt;tr style="background: rgba(0,0,0,0.04); border-bottom: 2px solid var(--border, #e2e8f0);"&gt;
+        &lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Work item&lt;/th&gt;&lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Illustrative allowance&lt;/th&gt;
+      &lt;/tr&gt;
+    &lt;/thead&gt;
+    &lt;tbody&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Cleaning and agreed surface preparation&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹5,000&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Identified crack and junction repairs&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹4,500&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Specified membrane system including application&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;500 sq. ft. × ₹75 = ₹37,500&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Outlet and penetration detailing&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹3,000&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Agreed protective finish&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹10,000&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Subtotal before applicable taxes and other agreed charges&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹60,000&lt;/td&gt;
+      &lt;/tr&gt;
+    &lt;/tbody&gt;
+  &lt;/table&gt;
+&lt;/div&gt;
+&lt;p&gt;In this example, slope reconstruction, major demolition and structural repairs are excluded. If the site needs them, the budget must change before work starts.&lt;/p&gt;
+&lt;p&gt;The material quantity also deserves attention. Ask for the treated area, specified consumption and number of layers in the approved system. “Two coats” is not enough information if each contractor plans to spread a different amount of product over the same roof.&lt;/p&gt;
+&lt;h2&gt;Questions for the contractor&lt;/h2&gt;
+&lt;p&gt;Ask the contractor to explain the likely entry points and the evidence supporting the diagnosis. A survey should produce more than a product name.&lt;/p&gt;
+&lt;p&gt;Get the product names, preparation method, treatment of cracks and junctions, planned consumption and finished surface in writing. Confirm who is responsible for clearing outlets and correcting drainage defects.&lt;/p&gt;
+&lt;p&gt;Discuss how the work will be checked before it is accepted. Any water test should be planned and supervised by the responsible professional, with the building’s condition and drainage considered. Do not improvise a deep flood test on a shared or unassessed roof.&lt;/p&gt;
+&lt;p&gt;Read warranty terms carefully. Ask what is covered, who responds to a complaint and whether maintenance, site conditions or workmanship are excluded. A long warranty headline does not explain the repair process.&lt;/p&gt;
+&lt;h2&gt;Planning the work step by step&lt;/h2&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 1 - Document the problem&lt;/strong&gt;: Record the stains and terrace condition. Note previous repairs and provide the contractor with any old product or warranty information.&lt;/li&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 2 - Decide how the terrace will be used&lt;/strong&gt;: Tell the contractor about washing, drying clothes, furniture, water tanks, solar equipment or a future garden. The finished system must suit the intended use.&lt;/li&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 3 - Approve the repair specification&lt;/strong&gt;: Agree what is being removed, repaired and retained. Set out drainage work, junction details, material quantities and the acceptance procedure.&lt;/li&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 4 - Choose a suitable weather window&lt;/strong&gt;: Application and curing conditions vary by product. The contractor should follow the data sheet for temperature, substrate moisture and rain exposure.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Do not assume that all seasons described as “dry” are suitable everywhere in India. Coastal humidity, summer surface heat and cold conditions can affect work planning differently.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 5 - Inspect preparation before coating&lt;/strong&gt;: Check that agreed loose layers and contaminants have been dealt with and that repairs and critical details are visible for inspection.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Photograph these stages. They become difficult to verify after the surface has been covered.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 6 - Apply and protect the specified system&lt;/strong&gt;: The trained crew should follow the complete product instructions, including layer requirements and curing. Ask for records of the products and quantities used.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Keep traffic and other trades off the area for the period required by the chosen system.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 7 - Complete the agreed checks and handover&lt;/strong&gt;: Carry out the acceptance procedure with the responsible contractor. Record unfinished details, maintenance instructions and warranty contacts.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;If another trade will later install tiles, solar supports or planters, tell them where the waterproofing is and how it must be protected.&lt;/p&gt;
+&lt;h2&gt;Completion and maintenance checklist&lt;/h2&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1rem 1.25rem; margin: 1rem 0;"&gt;
+  &lt;p style="font-weight: 600; margin: 0 0 0.25rem 0; color: #1e293b;"&gt;Before work:&lt;/p&gt;
+  &lt;p style="margin: 0; color: #475569; font-size: 0.95rem; line-height: 1.6;"&gt;Resolve the diagnosis, terrace use, drainage needs, specification and quotation.&lt;/p&gt;
+&lt;/div&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1rem 1.25rem; margin: 1rem 0;"&gt;
+  &lt;p style="font-weight: 600; margin: 0 0 0.25rem 0; color: #1e293b;"&gt;During work:&lt;/p&gt;
+  &lt;p style="margin: 0; color: #475569; font-size: 0.95rem; line-height: 1.6;"&gt;Record preparation, junction details and product quantities before they are hidden.&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;After work: Keep the test record and warranty. Check outlets and visible damage periodically, especially before the main rainy season in your region.&lt;/p&gt;
+&lt;p&gt;Use safe access when inspecting. Leave roof-edge work, difficult outlets and work around electrical equipment to the appropriate professionals.&lt;/p&gt;
+&lt;h2&gt;Troubleshooting &amp; Common Problems: Troubleshooting recurring problems&lt;/h2&gt;
+&lt;h3&gt;The leak returns in the same place&lt;/h3&gt;
+&lt;p&gt;Ask whether the original entry point was correctly identified. Water may be travelling from another part of the roof or from a service route.&lt;/p&gt;
+&lt;p&gt;Water stands on the new surface&lt;/p&gt;
+&lt;p&gt;Check outlet blockage and the drainage design. Repeatedly applying more coating does not correct an unsuitable slope.&lt;/p&gt;
+&lt;h3&gt;The surface is damaged around planters or furniture&lt;/h3&gt;
+&lt;p&gt;Review the system’s permitted traffic and protection requirements. Relocate or support items using an arrangement approved for the finished roof.&lt;/p&gt;
+&lt;h3&gt;The contractor offers to coat over everything&lt;/h3&gt;
+&lt;p&gt;Ask how adhesion and compatibility with old layers will be established. Keeping an existing layer should be a technical decision, not simply a way to shorten preparation.&lt;/p&gt;
+&lt;h2&gt;Frequently asked questions&lt;/h2&gt;
+&lt;p&gt;Waterproofing from inside the room&lt;/p&gt;
+&lt;p&gt;Some products can treat particular internal symptoms, but the rain-entry source should still be investigated. Discuss whether the proposed repair addresses the cause.&lt;/p&gt;
+&lt;h3&gt;Choosing work only by a square-foot rate&lt;/h3&gt;
+&lt;p&gt;Compare equal systems, preparation, junction treatment and finishes. A low rate with omitted repairs may cost more after the extras are added.&lt;/p&gt;
+&lt;p&gt;Waterproofing under terrace tiles&lt;/p&gt;
+&lt;p&gt;Tiles and grout alone should not be assumed to form the complete waterproofing system. Ask for the specified assembly and drainage details.&lt;/p&gt;
+&lt;p&gt;Planning a terrace garden&lt;/p&gt;
+&lt;p&gt;Review load, waterproofing, drainage and root protection with the appropriate professionals before building permanent beds or placing heavy planters.&lt;/p&gt;
+&lt;h2&gt;Wrapping up&lt;/h2&gt;
+&lt;p&gt;Begin with the water route and the condition of the terrace. Once those are understood, the coating or membrane can be selected as part of a complete repair.&lt;/p&gt;
+&lt;p&gt;A written specification, visible preparation and an agreed checking process make a quote easier to judge and a repair easier to maintain.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.25rem 1.5rem; margin: 2rem 0;"&gt;
+  &lt;p style="font-weight: 700; margin-bottom: 0.75rem; color: #1e293b; font-size: 1.05rem;"&gt;Related Guides &amp; Services on Carpenterwala:&lt;/p&gt;
+  &lt;ul style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+&lt;li style="margin-bottom: 0.5rem;"&gt;&lt;a href="/blog/how-to-waterproof-paint-balcony-exterior-walls-monsoon-guide" style="color: var(--primary, #2563eb); text-decoration: underline; font-weight: 500;"&gt;Balcony &amp; Exterior Wall Waterproofing Monsoon Guide&lt;/a&gt;&lt;/li&gt;
+&lt;li style="margin-bottom: 0.5rem;"&gt;&lt;a href="/blog/how-to-fix-ceiling-seepage-patches-stains-leak" style="color: var(--primary, #2563eb); text-decoration: underline; font-weight: 500;"&gt;How to Fix Ceiling Seepage Patches &amp; Stains&lt;/a&gt;&lt;/li&gt;
+&lt;li style="margin-bottom: 0.5rem;"&gt;&lt;a href="/services" style="color: var(--primary, #2563eb); text-decoration: underline; font-weight: 500;"&gt;Comprehensive Home Maintenance &amp; Waterproofing Services&lt;/a&gt;&lt;/li&gt;
+  &lt;/ul&gt;
+&lt;/div&gt;
+&lt;h2&gt;Sources and product guidance&lt;/h2&gt;
+&lt;p&gt;Sources checked on 23 October 2026. Application details and acceptance procedures must follow the specified system and site assessment.&lt;/p&gt;
+&lt;ul style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 1.5rem;"&gt;
+  &lt;li&gt;[1] Dr. Fixit terrace condition and system-selection guidance&lt;/li&gt;
+  &lt;li&gt;[2] Sika India liquid-applied roofing membrane systems&lt;/li&gt;
+  &lt;li&gt;[3] Dr. Fixit guide to terrace waterproofing assemblies&lt;/li&gt;
+  &lt;li&gt;[4] Sikalastic 590 IN product and system information&lt;/li&gt;
+&lt;/ul&gt;</v>
+      </c>
+      <c r="I6" t="str">
+        <v>/images/blogs/terrace-waterproofing-india-methods-cost-contractor-checklist.jpg</v>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>bathroom-renovation-cost-india-plumbing-tiles-fixtures</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Bathroom Renovation Cost in India: Plumbing, Tiles, Fixtures &amp; Work Sequence</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Plumbing</v>
+      </c>
+      <c r="E7" t="str">
+        <v>October 23, 2026</v>
+      </c>
+      <c r="F7" t="str">
+        <v>8 min read</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Budget for bathroom renovation with a clear breakdown of plumbing, waterproofing, tiles, fixtures and labour, plus a practical work-sequence checklist.</v>
+      </c>
+      <c r="H7" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
+  &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;A complete standard 5x7 ft bathroom renovation in India costs between ₹75,000 to ₹1,80,000 depending on fixture tiers (Jaquar/Kohler) and tile specifications. Strict work sequencing is essential: core plumbing lines and concealed diverters must undergo hydraulic pressure testing at 10 bar before floor waterproofing, followed by 48-hour ponding testing before laying anti-skid vitrified tiles.&lt;/p&gt;
+&lt;/div&gt;
+&lt;div style="background: rgba(239, 68, 68, 0.08); border-left: 4px solid #ef4444; padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: #dc2626;"&gt;⚠️ Critical Safety Warnings &amp; Precautions&lt;/p&gt;
+  &lt;p style="margin: 0; line-height: 1.7; font-size: 0.95rem;"&gt;Always verify plumbing lines with a 24-hour pressure test before plastering walls or tiling over concealed pipes. In the electrical scope, install only IP44 moisture-rated light fixtures and ground all metal frames via dedicated earth wires.&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;If your home has only one bathroom, the first renovation decision is how the household will manage while it is out of use. Tile colours can wait until the work sequence and basic facilities have been planned.&lt;/p&gt;
+&lt;p&gt;The next decision is the scope. Replacing a basin and a few fittings is a very different job from removing tiles, changing pipes and rebuilding the floor.&lt;/p&gt;
+&lt;p&gt;This guide helps you put a complete bathroom budget together, compare quotations and ask for the right checks before each layer is covered.&lt;/p&gt;
+&lt;h2&gt;Deciding how much renovation is needed&lt;/h2&gt;
+&lt;p&gt;Look at function before appearance. Does the floor drain properly? Are there leaks, recurring damp patches, loose tiles or fittings that no longer work well?&lt;/p&gt;
+&lt;p&gt;Separate the work into a cosmetic refresh, a partial renovation or a full rebuild.&lt;/p&gt;
+&lt;div style="overflow-x: auto; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;table style="width: 100%; border-collapse: collapse; text-align: left; font-size: 0.95rem;"&gt;
+    &lt;thead&gt;
+      &lt;tr style="background: rgba(0,0,0,0.04); border-bottom: 2px solid var(--border, #e2e8f0);"&gt;
+        &lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Scope&lt;/th&gt;&lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Typical work to consider&lt;/th&gt;&lt;th style="padding: 12px 16px; font-weight: 600;"&gt;What must be checked&lt;/th&gt;
+      &lt;/tr&gt;
+    &lt;/thead&gt;
+    &lt;tbody&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Cosmetic refresh&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Selected fittings, accessories and finishes&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Whether hidden services and existing surfaces remain sound&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Partial renovation&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Specific plumbing, tiling or shower-area changes&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;How the new work connects to the retained waterproofing and finishes&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Full rebuild&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Removal, service changes, waterproofing and new finishes&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;The complete work sequence, testing and disposal&lt;/td&gt;
+      &lt;/tr&gt;
+    &lt;/tbody&gt;
+  &lt;/table&gt;
+&lt;/div&gt;
+&lt;p&gt;A partial repair can be sensible, but joining a new waterproof layer to an old one needs proper assessment. An attractive new tile does not establish that the layers beneath it are serviceable.&lt;/p&gt;
+&lt;p&gt;Published bathroom guides, including NoBroker’s, vary prices by size and work scope. Use those guides to frame questions, then obtain a site quote that identifies the actual work. [1]&lt;/p&gt;
+&lt;h2&gt;Measuring floors and walls&lt;/h2&gt;
+&lt;p&gt;A 5 ft by 8 ft bathroom has a floor area of 40 sq. ft. That is not the total tiling area.&lt;/p&gt;
+&lt;p&gt;If its perimeter is 26 ft and the planned wall tiling is 8 ft high, the gross wall area is 208 sq. ft. A 3 ft by 7 ft door would reduce that by 21 sq. ft., leaving 187 sq. ft. before adjusting for other openings and the actual design.&lt;/p&gt;
+&lt;p&gt;Adding the 40 sq. ft. floor gives 227 sq. ft. of net tiled surface in this simplified example. Order quantities still need allowances for the layout, cuts, breakage and product packaging.&lt;/p&gt;
+&lt;p&gt;Ask for floor and wall quantities separately. Check whether niches, ledges and concealed pipe boxes add surfaces or special cutting work.&lt;/p&gt;
+&lt;p&gt;Confirm the basis for labour too. Some trades quote per fixture or point; others quote by area or by the complete job.&lt;/p&gt;
+&lt;h2&gt;Building a complete budget&lt;/h2&gt;
+&lt;p&gt;The quote should identify demolition, waste removal, pipe work, waterproofing, surface preparation, tiling, sanitaryware, taps, electrical work and installation.&lt;/p&gt;
+&lt;p&gt;Here is a fictional budget for explaining how those items fit together. It is not a market quotation.&lt;/p&gt;
+&lt;div style="overflow-x: auto; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;table style="width: 100%; border-collapse: collapse; text-align: left; font-size: 0.95rem;"&gt;
+    &lt;thead&gt;
+      &lt;tr style="background: rgba(0,0,0,0.04); border-bottom: 2px solid var(--border, #e2e8f0);"&gt;
+        &lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Work item&lt;/th&gt;&lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Illustrative allowance&lt;/th&gt;
+      &lt;/tr&gt;
+    &lt;/thead&gt;
+    &lt;tbody&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Demolition and debris removal&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹12,000&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Plumbing package with agreed materials and labour&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹25,000&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Specified waterproofing package&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹15,000&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Tiles, adhesive and grout&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹35,000&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Sanitaryware and taps&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹28,000&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Electrical work and ventilation allowance&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹10,000&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Tiling labour and surface preparation&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹25,000&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Subtotal before applicable taxes and other charges&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹1,50,000&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Owner’s provisional reserve for approved extra work&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹15,000&lt;/td&gt;
+      &lt;/tr&gt;
+    &lt;/tbody&gt;
+  &lt;/table&gt;
+&lt;/div&gt;
+&lt;p&gt;The reserve is an example budget choice. It does not authorise a contractor to spend it without approval.&lt;/p&gt;
+&lt;p&gt;This example excludes major structural changes, an elaborate glass enclosure and extensive concealed damage. List your own exclusions just as clearly.&lt;/p&gt;
+&lt;p&gt;Ask who pays for disposal, carrying materials to an upper floor and final cleaning. Check building work-hour rules and any permissions before demolition is scheduled.&lt;/p&gt;
+&lt;h2&gt;Choosing fixtures and materials&lt;/h2&gt;
+&lt;p&gt;Choose fittings that suit the water supply&lt;/p&gt;
+&lt;p&gt;A shower chosen only for its appearance may disappoint if the available pressure does not suit it. Jaquar advises checking water pressure and other installation requirements when selecting a shower. Have the plumber assess the actual supply and product compatibility. [2]&lt;/p&gt;
+&lt;p&gt;Confirm the water-heating arrangement, available space and access for future servicing. For concealed fittings, choose the model before the wall is closed.&lt;/p&gt;
+&lt;p&gt;Record the exact product codes. “Premium mixer” does not tell you what will arrive.&lt;/p&gt;
+&lt;p&gt;Treat the tiled surface as a complete system&lt;/p&gt;
+&lt;p&gt;Waterproofing, adhesive, tile and grout each have a role. Weber’s bathroom guidance treats them as coordinated stages, which is useful when checking whether a quote has left a layer out. [3]&lt;/p&gt;
+&lt;p&gt;Ask for products suitable for the substrate, tile type, exposure and cleaning method. A grout upgrade should not be sold as a substitute for addressing a failed waterproofing layer.&lt;/p&gt;
+&lt;p&gt;Choose floor tiles suitable for wet use and comfortable underfoot. Inspect a sample rather than deciding entirely from a glossy catalogue.&lt;/p&gt;
+&lt;p&gt;Keep maintenance practical&lt;/p&gt;
+&lt;p&gt;Check access to isolation valves, traps, flush mechanisms and concealed service components. A removable panel may be more useful than a completely sealed decorative surface.&lt;/p&gt;
+&lt;p&gt;For elderly users or anyone with limited mobility, discuss access, thresholds, support fittings and usable space early. Appropriate supports need suitable fixing arrangements behind the finish.&lt;/p&gt;
+&lt;h2&gt;Planning the renovation sequence&lt;/h2&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 1 - Inspect and agree the scope&lt;/strong&gt;: Record leaks and drainage problems. Decide what is being retained and whether the layout needs to change.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Moving the toilet, shower or drain can affect more than the visible fitting. Get the feasibility checked before selecting finishes.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 2 - Finalise the layout and product models&lt;/strong&gt;: Mark the positions of sanitaryware, taps, shower controls, accessories and electrical equipment. Check door movement and cleaning access.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Provide the trades with the selected product instructions before rough work begins.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 3 - Plan the household disruption&lt;/strong&gt;: Agree the expected period without a usable bathroom, water-shut-off arrangements and waste removal. If there is another bathroom, confirm how it will stay accessible during the work.&lt;/li&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 4 - Remove old finishes and assess what is exposed&lt;/strong&gt;: Demolition may reveal damaged pipes or weak surfaces. Require photographs and a written proposal before approving extra work.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Do not allow structural members to be cut or altered as an informal plumbing adjustment.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 5 - Complete and check concealed services&lt;/strong&gt;: Have the responsible professionals complete the pipe and electrical work and carry out appropriate tests before it is covered.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Photograph routes with measurements from fixed reference points. This can help avoid accidental drilling into a pipe later.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 6 - Prepare and waterproof the required areas&lt;/strong&gt;: The chosen system should specify substrate preparation, junction treatment, layers, curing and the checking procedure. Have any water test supervised and timed according to the system and site requirements.&lt;/li&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 7 - Tile and finish&lt;/strong&gt;: Check the intended falls towards drains before accepting the floor. Adhesive, grout, movement joints and curing should follow the specified products.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Avoid using the bathroom before the relevant materials are ready.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 8 - Install and inspect fittings&lt;/strong&gt;: Run the taps and shower, observe drainage and inspect accessible joints. Check flush operation, sealant details, door movement and ventilation.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Have electrical equipment and protective measures checked by the qualified electrician.&lt;/p&gt;
+&lt;h2&gt;Handover checklist&lt;/h2&gt;
+&lt;p&gt;Before demolition: Confirm access, household arrangements, drawings, products and the complete quote.&lt;/p&gt;
+&lt;p&gt;Before covering services: Retain photographs and the agreed test records.&lt;/p&gt;
+&lt;p&gt;At completion: Inspect drainage, leaks, fixture operation, finishes and cleaning. Keep product details and the final snag list.&lt;/p&gt;
+&lt;p&gt;Ask who will respond if a concealed problem appears and how workmanship complaints are handled. Keep that responsibility separate from individual product warranties.&lt;/p&gt;
+&lt;h2&gt;Troubleshooting &amp; Common Problems: Problems worth preventing&lt;/h2&gt;
+&lt;p&gt;Water collects away from the drain&lt;/p&gt;
+&lt;p&gt;Raise the issue before accepting the floor. A better drain cover will not correct the wrong floor slope.&lt;/p&gt;
+&lt;p&gt;A concealed mixer cannot be serviced&lt;/p&gt;
+&lt;p&gt;Ask about access and replaceable parts during product selection. A neat appearance should still allow maintenance.&lt;/p&gt;
+&lt;p&gt;Old dampness reappears outside the bathroom&lt;/p&gt;
+&lt;p&gt;Investigate supply lines, drainage and the waterproofing system. Repainting the adjoining room alone may not solve the cause.&lt;/p&gt;
+&lt;p&gt;Costs rise after demolition&lt;/p&gt;
+&lt;p&gt;Some hidden damage is unavoidable, but the variation process should be agreed in advance. Get the problem, proposed work and price documented before proceeding.&lt;/p&gt;
+&lt;h2&gt;Frequently asked questions&lt;/h2&gt;
+&lt;p&gt;Renovating without changing the layout&lt;/p&gt;
+&lt;p&gt;Retaining suitable service positions can reduce work. Inspect the existing pipes and waterproofing before deciding what can stay.&lt;/p&gt;
+&lt;p&gt;Tiling over existing tiles&lt;/p&gt;
+&lt;p&gt;This is possible only with a suitable, sound base and an approved product system. Check the extra height, thresholds, drainage and hidden problems before choosing it.&lt;/p&gt;
+&lt;h3&gt;Choosing an expensive shower before checking pressure&lt;/h3&gt;
+&lt;p&gt;Confirm the supply first. The right product for the available pressure is more useful than an unsuitable high-end model.&lt;/p&gt;
+&lt;p&gt;Buying materials yourself&lt;/p&gt;
+&lt;p&gt;You can, but agree quantities, product compatibility, delivery timing and responsibility for shortages or damage. Keep invoices and batch information where relevant.&lt;/p&gt;
+&lt;h2&gt;Wrapping up&lt;/h2&gt;
+&lt;p&gt;Set the scope and work sequence before spending on finishes. A well-planned bathroom budget gives enough attention to the pipes, waterproofing and drainage beneath the visible surface.&lt;/p&gt;
+&lt;p&gt;Once those details are sound, choosing the tiles and fittings becomes a much simpler decision.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.25rem 1.5rem; margin: 2rem 0;"&gt;
+  &lt;p style="font-weight: 700; margin-bottom: 0.75rem; color: #1e293b; font-size: 1.05rem;"&gt;Related Guides &amp; Services on Carpenterwala:&lt;/p&gt;
+  &lt;ul style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+&lt;li style="margin-bottom: 0.5rem;"&gt;&lt;a href="/blog/how-to-fix-kitchen-bathroom-mixer-taps-leaks-diverter" style="color: var(--primary, #2563eb); text-decoration: underline; font-weight: 500;"&gt;How to Fix Leaking Kitchen &amp; Bathroom Mixer Taps &amp; Diverters&lt;/a&gt;&lt;/li&gt;
+&lt;li style="margin-bottom: 0.5rem;"&gt;&lt;a href="/blog/how-to-fix-bathroom-wall-efflorescence-salt-formation" style="color: var(--primary, #2563eb); text-decoration: underline; font-weight: 500;"&gt;Bathroom Wall Efflorescence &amp; Salt Deposit Fix&lt;/a&gt;&lt;/li&gt;
+&lt;li style="margin-bottom: 0.5rem;"&gt;&lt;a href="/services/plumbing" style="color: var(--primary, #2563eb); text-decoration: underline; font-weight: 500;"&gt;Verified Plumbing Services&lt;/a&gt;&lt;/li&gt;
+  &lt;/ul&gt;
+&lt;/div&gt;
+&lt;h2&gt;Sources and product guidance&lt;/h2&gt;
+&lt;p&gt;Sources checked on 23 October 2026. The sample budget is illustrative and should be replaced by a quote for the actual site.&lt;/p&gt;
+&lt;ul style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 1.5rem;"&gt;
+  &lt;li&gt;[1] NoBroker bathroom renovation planning and cost guide&lt;/li&gt;
+  &lt;li&gt;[2] Jaquar shower selection and installation considerations&lt;/li&gt;
+  &lt;li&gt;[3] Weber coordinated bathroom tiling and waterproofing guidance&lt;/li&gt;
+  &lt;li&gt;[4] Jaquar concealed and exposed diverter options&lt;/li&gt;
+&lt;/ul&gt;</v>
+      </c>
+      <c r="I7" t="str">
+        <v>/images/blogs/bathroom-renovation-cost-india-plumbing-tiles-fixtures.jpg</v>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>house-wiring-rewiring-cost-india-points-materials-labour</v>
+      </c>
+      <c r="C8" t="str">
+        <v>House Wiring and Rewiring Cost in India: Points, Materials &amp; Homeowner Guide</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Electrical</v>
+      </c>
+      <c r="E8" t="str">
+        <v>October 23, 2026</v>
+      </c>
+      <c r="F8" t="str">
+        <v>8 min read</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Compare house wiring quotes by scope, point counts, materials, protective devices and finishing, with a homeowner checklist for qualified electrical work.</v>
+      </c>
+      <c r="H8" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
+  &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;Complete electrical wiring in India typically costs ₹650–₹1,200 per point (labour + conduit + FR/FRLS copper wire + modular switch/plate) or ₹110–₹180/sq.ft of built-up area. For a standard 2BHK/3BHK, allocate ₹45,000–₹1,15,000. Never compromise on fire-retardant FRLS copper cables (Finolex/Polycab/Havells), dedicated 30mA RCCB/ELCB shock protection, and minimum 2.5 sq.mm dedicated lines for ACs, geysers, and kitchen appliances.&lt;/p&gt;
+&lt;/div&gt;
+&lt;div style="background: rgba(239, 68, 68, 0.08); border-left: 4px solid #ef4444; padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: #dc2626;"&gt;⚠️ Critical Safety Warnings &amp; Precautions&lt;/p&gt;
+  &lt;p style="margin: 0; line-height: 1.7; font-size: 0.95rem;"&gt;Never perform concealed electrical chasing, wire pulling, or distribution box work while the main meter line is energized. Ensure a certified licensed electrician checks insulation resistance with a 500V Megger tester and verifies earth loop impedance (&lt;1 Ohm) before energizing.&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;A new air conditioner, an induction hob and a second work desk can change what a home needs from its wiring. Yet a quote based only on the number of rooms may tell you very little about the circuits required.&lt;/p&gt;
+&lt;p&gt;Rewiring an occupied home also includes work that a new-build quote may leave out: opening access, protecting furniture, repairing walls and coordinating power shut-offs.&lt;/p&gt;
+&lt;p&gt;This guide explains how to compare the scope and cost with a qualified electrician. It is a planning guide for homeowners; circuit design, wiring, connection and electrical testing belong with the appropriate professional.&lt;/p&gt;
+&lt;h2&gt;Deciding what work is needed&lt;/h2&gt;
+&lt;p&gt;Separate a faulty accessory from a wider installation problem. One damaged switch does not automatically mean the whole home needs rewiring, while repeated symptoms should not be dismissed as a minor inconvenience.&lt;/p&gt;
+&lt;p&gt;Ask for an inspection if there are recurring trips, burning smells, scorch marks, damaged insulation or unreliable earthing. Stop using affected equipment or circuits and arrange qualified help rather than repeatedly resetting or bypassing a protective device.&lt;/p&gt;
+&lt;p&gt;The electrician should assess the existing wiring, available routes, loads, protective devices and earthing before recommending the work.&lt;/p&gt;
+&lt;p&gt;A renovation may involve new points on suitable existing circuits, partial rewiring, a distribution-board upgrade or a complete installation. These are different scopes and should be described separately.&lt;/p&gt;
+&lt;p&gt;Building access, meter and supply requirements, and local rules may also affect the job. Confirm responsibilities with the relevant professionals and building management before work starts.&lt;/p&gt;
+&lt;h2&gt;Understanding points and area rates&lt;/h2&gt;
+&lt;p&gt;A “point” is a quotation unit, not a universal description. Ask the contractor to define it.&lt;/p&gt;
+&lt;p&gt;Does a light point include the switch, wiring, conduit and fitting? Is a socket beside that switch counted separately? What route length is included? Are appliance circuits priced differently?&lt;/p&gt;
+&lt;div style="overflow-x: auto; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;table style="width: 100%; border-collapse: collapse; text-align: left; font-size: 0.95rem;"&gt;
+    &lt;thead&gt;
+      &lt;tr style="background: rgba(0,0,0,0.04); border-bottom: 2px solid var(--border, #e2e8f0);"&gt;
+        &lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Quotation basis&lt;/th&gt;&lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Why it is used&lt;/th&gt;&lt;th style="padding: 12px 16px; font-weight: 600;"&gt;What to ask&lt;/th&gt;
+      &lt;/tr&gt;
+    &lt;/thead&gt;
+    &lt;tbody&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Per point&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Comparing a defined set of outlets or lights&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Exact inclusions, route length and point definition&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Per square foot&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Early budgeting for a defined property and scope&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Which area is measured and what the rate covers&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Per circuit&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Pricing a particular circuit or appliance requirement&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Design, route, protection and termination inclusions&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Itemised package&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Comparing the complete installation&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Quantities, material specifications and exclusions&lt;/td&gt;
+      &lt;/tr&gt;
+    &lt;/tbody&gt;
+  &lt;/table&gt;
+&lt;/div&gt;
+&lt;p&gt;If one contractor counts 30 points and another counts 45, compare the point schedule before comparing their rates.&lt;/p&gt;
+&lt;p&gt;An area rate should not be used to choose wire size or breaker rating. Those are design decisions based on the actual installation and applicable requirements.&lt;/p&gt;
+&lt;h2&gt;Building an itemised wiring budget&lt;/h2&gt;
+&lt;p&gt;Ask for materials, labour, protective devices, earthing work, making good and testing to be visible in the quote.&lt;/p&gt;
+&lt;p&gt;For a published reference, NoBroker’s interior rate sheet gives electrical work at ₹50–120 per sq. ft., combining its stated labour and material ranges. Treat that as a provider’s broad benchmark; the actual point schedule, existing condition and inclusions still need a site quote. [5]&lt;/p&gt;
+&lt;p&gt;The following is a fictional example showing how a small project might be itemised. The figures are not market rates, and the point count is not a wiring design.&lt;/p&gt;
+&lt;div style="overflow-x: auto; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;table style="width: 100%; border-collapse: collapse; text-align: left; font-size: 0.95rem;"&gt;
+    &lt;thead&gt;
+      &lt;tr style="background: rgba(0,0,0,0.04); border-bottom: 2px solid var(--border, #e2e8f0);"&gt;
+        &lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Work item&lt;/th&gt;&lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Illustrative allowance&lt;/th&gt;
+      &lt;/tr&gt;
+    &lt;/thead&gt;
+    &lt;tbody&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Labour for 28 defined points&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;28 × ₹450 = ₹12,600&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Agreed wiring, conduit and accessories&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹22,000&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Distribution-board and protection allowance&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹9,000&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Identified earthing work allowance&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹6,500&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Wall repairs and making good&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹8,000&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Testing and documentation&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹3,000&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Subtotal before applicable taxes and other charges&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹61,100&lt;/td&gt;
+      &lt;/tr&gt;
+    &lt;/tbody&gt;
+  &lt;/table&gt;
+&lt;/div&gt;
+&lt;p&gt;Heavy-appliance circuits, a supply upgrade or extensive concealed damage may need separate assessment. Remove or change allowances that do not apply to your installation.&lt;/p&gt;
+&lt;p&gt;Ask whether the switches and socket faceplates are included. Decorative ranges can change the total without changing the underlying safety design.&lt;/p&gt;
+&lt;p&gt;For an occupied home, discuss furniture movement, work hours, dust and temporary power arrangements. A low installation quote may leave you with a separate wall-repair bill.&lt;/p&gt;
+&lt;h2&gt;Comparing materials and protective devices&lt;/h2&gt;
+&lt;p&gt;Record exact material specifications&lt;/p&gt;
+&lt;p&gt;The quote should identify cable and wire products, conductors, insulation type, conduit, accessories and protective devices. Let the electrician determine suitable sizes and ratings for the design.&lt;/p&gt;
+&lt;p&gt;Finolex, for example, offers house-wire products with specified insulation and flame-retardant characteristics. Read the actual product description rather than treating a brand name or “fireproof wire” claim as a complete specification. Flame retardance does not make an installation incapable of causing a fire. [1]&lt;/p&gt;
+&lt;p&gt;Ask how the delivered products will be verified and invoiced. Avoid approving unrecorded substitutions simply because the outer colour looks similar.&lt;/p&gt;
+&lt;p&gt;Understand the purpose of the protection&lt;/p&gt;
+&lt;p&gt;Schneider Electric distinguishes overcurrent protection from residual-current protection. An MCB addresses overload and short-circuit conditions; an RCCB addresses residual-current imbalance and does not by itself provide overload protection. An RCBO combines the relevant overcurrent and residual-current functions. [2][3]&lt;/p&gt;
+&lt;p&gt;The appropriate devices and their coordination must be selected for the installation. Do not choose a bigger breaker simply to stop tripping.&lt;/p&gt;
+&lt;p&gt;Earthing remains part of the installation design and verification. A new board with modern-looking switches does not demonstrate that the rest of the system has been checked.&lt;/p&gt;
+&lt;p&gt;Keep future additions specific&lt;/p&gt;
+&lt;p&gt;Tell the electrician about planned appliances and likely locations. A future work desk may need useful socket positions; a future large appliance may need a separately assessed circuit.&lt;/p&gt;
+&lt;p&gt;Leave space and provision according to the professional design. Avoid the assumption that spare conduits or an empty board position alone make any future load safe.&lt;/p&gt;
+&lt;h2&gt;Planning the work with your electrician&lt;/h2&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 1 - Prepare a room and appliance list&lt;/strong&gt;: Mark the current and proposed furniture. List appliances you use and expect to add, including their model information where available.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Note inconvenient extension leads and places where existing sockets are inaccessible behind furniture.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 2 - Have the installation assessed&lt;/strong&gt;: Ask the electrician to explain which parts can remain and which need replacement. Request the basis for the recommendation and the testing or inspection it relies on.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Keep any existing drawings and previous installation records available.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 3 - Approve a point and circuit schedule&lt;/strong&gt;: The agreed schedule should identify outlet and fitting positions and the professional design requirements. Check room usability without trying to replace the electrician’s calculations.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Confirm that switch positions, door swings, cupboards and countertop heights have been coordinated.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 4 - Compare complete written quotes&lt;/strong&gt;: Use the same schedule for each bidder. Record product specifications, labour, repair work, testing and responsibility for approvals or supply-related changes.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Agree how additional concealed damage or scope changes will be priced.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 5 - Plan isolation and access&lt;/strong&gt;: The electrician should arrange safe isolation and controlled work. Discuss when rooms will be without power and how essential household needs will be managed.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Keep children and other occupants out of the work area. Do not open boards or fittings to inspect energised work yourself.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 6 - Record routes before walls are closed&lt;/strong&gt;: Ask for photographs and measurements from fixed reference points. Confirm that the required professional checks have been completed before concealing the work.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Coordinate wall repairs and painting after the electrical stages that need access are finished.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 7 - Collect test results and a clear handover&lt;/strong&gt;: Ask the electrician for the relevant test records, including checks such as protective-conductor continuity, insulation resistance, polarity, earthing and residual-current-device operation where applicable to the installation.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;The tests and acceptance criteria must follow the design and applicable requirements. A homeowner pressing a few switches is not a substitute for electrical verification. [4]&lt;/p&gt;
+&lt;h2&gt;Handover checklist&lt;/h2&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1rem 1.25rem; margin: 1rem 0;"&gt;
+  &lt;p style="font-weight: 600; margin: 0 0 0.25rem 0; color: #1e293b;"&gt;Before work:&lt;/p&gt;
+  &lt;p style="margin: 0; color: #475569; font-size: 0.95rem; line-height: 1.6;"&gt;Confirm inspection findings, drawings, point definitions, material specifications and the complete quote.&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;Before closing routes: Retain photographs and the required professional inspection records.&lt;/p&gt;
+&lt;p&gt;At completion: Collect circuit labels, test documentation, invoices and product manuals. Ask the electrician to explain normal operation and what to do if a device trips.&lt;/p&gt;
+&lt;p&gt;Keep the final records where a future electrician can find them. Labels should make sense to the household, not only to the installer.&lt;/p&gt;
+&lt;h2&gt;Troubleshooting &amp; Common Problems: Common quotation problems&lt;/h2&gt;
+&lt;h3&gt;The cheaper quote counts fewer points&lt;/h3&gt;
+&lt;p&gt;Compare the schedule and inclusions. A fan regulator, socket or appliance circuit may have been treated differently.&lt;/p&gt;
+&lt;p&gt;Rewiring is priced without wall repair&lt;/p&gt;
+&lt;p&gt;Ask whether chasing, plaster repairs, debris removal and painting are included or separate.&lt;/p&gt;
+&lt;h3&gt;The contractor proposes a larger breaker to stop trips&lt;/h3&gt;
+&lt;p&gt;Ask for a proper diagnosis and a design check. A protective device should not be uprated as a shortcut around an unresolved fault or overload.&lt;/p&gt;
+&lt;p&gt;Everything is called a complete electrical package&lt;/p&gt;
+&lt;p&gt;Request quantities, product models, testing and exclusions. A package name alone is difficult to compare or enforce.&lt;/p&gt;
+&lt;h2&gt;Frequently asked questions&lt;/h2&gt;
+&lt;p&gt;Rewiring because a home is a certain age&lt;/p&gt;
+&lt;p&gt;Age can prompt inspection, but condition, use, alterations and test results should inform the decision. Avoid choosing a scope from age alone.&lt;/p&gt;
+&lt;h3&gt;Reusing existing conduits&lt;/h3&gt;
+&lt;p&gt;The electrician should assess their condition, route and suitability. Reuse can reduce disruption when appropriate, but it should not be assumed before inspection.&lt;/p&gt;
+&lt;p&gt;Buying the materials yourself&lt;/p&gt;
+&lt;p&gt;Use the electrician’s final specification and agree responsibility for compatibility, quantities, shortages and warranties. Do not substitute ratings based on a shop recommendation alone.&lt;/p&gt;
+&lt;p&gt;Completing electrical work before painting&lt;/p&gt;
+&lt;p&gt;Finish work that needs access to walls and ceilings first. Coordinate final accessories and protective covering with the painter and electrician.&lt;/p&gt;
+&lt;h2&gt;Wrapping up&lt;/h2&gt;
+&lt;p&gt;Compare the point schedule, design, materials and test records alongside the price. That makes it easier to see whether two contractors are quoting for the same work.&lt;/p&gt;
+&lt;p&gt;A clear handover is part of the project. It should leave you with a usable installation and records that help the next person maintain it properly.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.25rem 1.5rem; margin: 2rem 0;"&gt;
+  &lt;p style="font-weight: 700; margin-bottom: 0.75rem; color: #1e293b; font-size: 1.05rem;"&gt;Related Guides &amp; Services on Carpenterwala:&lt;/p&gt;
+  &lt;ul style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+&lt;li style="margin-bottom: 0.5rem;"&gt;&lt;a href="/blog/dangers-of-old-wiring" style="color: var(--primary, #2563eb); text-decoration: underline; font-weight: 500;"&gt;Dangers of Old Wiring in Indian Homes&lt;/a&gt;&lt;/li&gt;
+&lt;li style="margin-bottom: 0.5rem;"&gt;&lt;a href="/blog/electrical-safety-basics-testers-tape-mcbs-guide" style="color: var(--primary, #2563eb); text-decoration: underline; font-weight: 500;"&gt;Electrical Safety Basics: Testers, Tape &amp; MCBs&lt;/a&gt;&lt;/li&gt;
+&lt;li style="margin-bottom: 0.5rem;"&gt;&lt;a href="/services/electrical" style="color: var(--primary, #2563eb); text-decoration: underline; font-weight: 500;"&gt;Licensed Electrical Services&lt;/a&gt;&lt;/li&gt;
+  &lt;/ul&gt;
+&lt;/div&gt;
+&lt;h2&gt;Sources and product guidance&lt;/h2&gt;
+&lt;p&gt;Sources checked on 23 October 2026. The sample budget illustrates quotation structure and does not specify a circuit design.&lt;/p&gt;
+&lt;ul style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 1.5rem;"&gt;
+  &lt;li&gt;[1] Finolex house-wire product information&lt;/li&gt;
+  &lt;li&gt;[2] Schneider Electric guide to MCBs RCCBs and isolators&lt;/li&gt;
+  &lt;li&gt;[3] Schneider Electric comparison of circuit-protection devices&lt;/li&gt;
+  &lt;li&gt;[4] IET technical background on initial verification and testing&lt;/li&gt;
+  &lt;li&gt;[5] NoBroker published electrical work rate example&lt;/li&gt;
+&lt;/ul&gt;</v>
+      </c>
+      <c r="I8" t="str">
+        <v>/images/blogs/house-wiring-rewiring-cost-india-points-materials-labour.jpg</v>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>cpvc-vs-upvc-pipes-home-plumbing-india</v>
+      </c>
+      <c r="C9" t="str">
+        <v>CPVC vs UPVC Pipes for Home Plumbing: Pressure Ratings, Hot Water &amp; Selection</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Plumbing</v>
+      </c>
+      <c r="E9" t="str">
+        <v>October 23, 2026</v>
+      </c>
+      <c r="F9" t="str">
+        <v>8 min read</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Compare CPVC and UPVC for household water supply, understand pressure and temperature ratings, and check pipe, fitting and solvent compatibility.</v>
+      </c>
+      <c r="H9" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
+  &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;For internal potable water supply in Indian homes, CPVC is the industry standard for both hot and cold lines due to its high temperature rating (up to 93°C) and resistance to chlorine and scaling. UPVC is strictly limited to cold water (up to 60°C) and external plumbing/borewell supply. Never mix CPVC and UPVC solvent cements, and always use transition brass fittings when connecting geysers or diverters.&lt;/p&gt;
+&lt;/div&gt;
+&lt;div style="background: rgba(239, 68, 68, 0.08); border-left: 4px solid #ef4444; padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: #dc2626;"&gt;⚠️ Critical Safety Warnings &amp; Precautions&lt;/p&gt;
+  &lt;p style="margin: 0; line-height: 1.7; font-size: 0.95rem;"&gt;Allow solvent cement joints to cure for a minimum of 2 to 4 hours in dry weather (and up to 24 hours in humid coastal monsoon conditions) before conducting water pressure tests. Test lines hydraulically with cold water, never with compressed air or gas.&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;Pipes are usually discussed when a wall is already open and the plumber is waiting for a decision. At that point, “take the better one” sounds convenient, but it leaves several questions unanswered.&lt;/p&gt;
+&lt;p&gt;Will the line carry hot water? Is it a pressure water-supply line or a drain? Which fittings and jointing products belong with it? The answer to each question affects what should be bought.&lt;/p&gt;
+&lt;p&gt;CPVC and UPVC both have useful applications in Indian homes. This guide explains the difference and helps you prepare a clear specification with your plumber.&lt;/p&gt;
+&lt;h2&gt;Understanding CPVC and UPVC&lt;/h2&gt;
+&lt;p&gt;CPVC is chlorinated polyvinyl chloride. It is used in purpose-designed hot- and cold-water plumbing systems. UPVC, also written uPVC, means unplasticised polyvinyl chloride and is used in several different piping systems.&lt;/p&gt;
+&lt;p&gt;Astral’s comparison identifies CPVC for hot- and cold-water service and appropriate UPVC systems for cold-water applications. The selected product’s pressure and temperature ratings remain essential. Do not apply one product’s maximum temperature to every CPVC pipe sold in the market. [1]&lt;/p&gt;
+&lt;p&gt;The material name also does not establish drinking-water suitability. Choose a product specifically intended and appropriately certified for the water-supply application.&lt;/p&gt;
+&lt;p&gt;Water-supply pipe, drainage pipe and other UPVC products can look familiar while serving different purposes. A pipe that works well for wastewater is not automatically suitable for a pressurised potable-water line.&lt;/p&gt;
+&lt;h2&gt;Comparing the two systems&lt;/h2&gt;
+&lt;div style="overflow-x: auto; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;table style="width: 100%; border-collapse: collapse; text-align: left; font-size: 0.95rem;"&gt;
+    &lt;thead&gt;
+      &lt;tr style="background: rgba(0,0,0,0.04); border-bottom: 2px solid var(--border, #e2e8f0);"&gt;
+        &lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Question&lt;/th&gt;&lt;th style="padding: 12px 16px; font-weight: 600;"&gt;CPVC plumbing system&lt;/th&gt;&lt;th style="padding: 12px 16px; font-weight: 600;"&gt;UPVC plumbing system&lt;/th&gt;
+      &lt;/tr&gt;
+    &lt;/thead&gt;
+    &lt;tbody&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Intended water service&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Hot and cold supply within the product ratings&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Typically cold supply where the specific system is approved&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Hot-water suitability&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Confirm temperature and pressure together&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Do not use a cold-water product for a hot-water line&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Drinking water&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Check the actual product certification and intended use&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Check the actual product certification and intended use&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Jointing&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Use the approved fittings and jointing method&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Use the approved fittings and jointing method&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Outdoor installation&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Follow the system’s exposure and support guidance&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Follow the system’s exposure and support guidance&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Price comparison&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Compare the full specified installation&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Compare the full specified installation&lt;/td&gt;
+      &lt;/tr&gt;
+    &lt;/tbody&gt;
+  &lt;/table&gt;
+&lt;/div&gt;
+&lt;p&gt;A suitable cold-water UPVC system does not need replacing simply because CPVC is described as a premium option. Equally, a cheaper cold-water pipe should not be selected for a hot-water route.&lt;/p&gt;
+&lt;p&gt;The useful comparison is the complete system in its intended application.&lt;/p&gt;
+&lt;h2&gt;Matching the pipe to its use&lt;/h2&gt;
+&lt;p&gt;Hot water from a geyser&lt;/p&gt;
+&lt;p&gt;Have the plumber confirm the heater manufacturer’s connection requirements and the pipe system’s operating limits. Temperature, pressure and the installation arrangement must be considered together.&lt;/p&gt;
+&lt;p&gt;Astral and Ashirvad offer CPVC systems intended for hot and cold potable water, with product-specific guidance on connections and installation. Use that guidance for the chosen system. [2][3]&lt;/p&gt;
+&lt;p&gt;The short connector near the heater and the rest of the pipe route may have different requirements. Avoid treating every component as interchangeable.&lt;/p&gt;
+&lt;p&gt;Cold water to bathrooms and the kitchen&lt;/p&gt;
+&lt;p&gt;A suitable pressure-rated cold-water system may be appropriate. Ask about water source, operating pressure, pump arrangements and pressure variation.&lt;/p&gt;
+&lt;p&gt;An overhead tank does not establish the pressure at every fitting. Building height and pumping arrangements should be considered by the plumber.&lt;/p&gt;
+&lt;p&gt;Drainage and waste lines&lt;/p&gt;
+&lt;p&gt;Specify the drainage system separately. Flow arrangement, slope, access and fittings differ from a supply line.&lt;/p&gt;
+&lt;p&gt;Do not compare a drainage-pipe price with a pressure-supply-pipe price and assume the cheaper one can perform both jobs.&lt;/p&gt;
+&lt;p&gt;Exposed routes and different climates&lt;/p&gt;
+&lt;p&gt;Ask about support, movement, sunlight exposure and protection from damage. Very cold conditions can require a specific freeze-protection plan; a general claim that plastic pipe suits “all weather” is insufficient.&lt;/p&gt;
+&lt;p&gt;In hot and humid regions, check the real service temperature and installation conditions. For concealed work, document routes before they are covered.&lt;/p&gt;
+&lt;h2&gt;Understanding the complete plumbing cost&lt;/h2&gt;
+&lt;p&gt;A pipe price per metre describes only part of the work. Fittings, valves, transitions, supports, jointing products, labour, testing and making good can materially change the total.&lt;/p&gt;
+&lt;p&gt;A short route with several bends and connections may require more work than a longer straight run. Pipe diameter and system specification also affect cost.&lt;/p&gt;
+&lt;p&gt;Here is a fictional example showing the structure of a small quotation. It does not recommend a particular size or design.&lt;/p&gt;
+&lt;div style="overflow-x: auto; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;table style="width: 100%; border-collapse: collapse; text-align: left; font-size: 0.95rem;"&gt;
+    &lt;thead&gt;
+      &lt;tr style="background: rgba(0,0,0,0.04); border-bottom: 2px solid var(--border, #e2e8f0);"&gt;
+        &lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Work item&lt;/th&gt;&lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Illustrative allowance&lt;/th&gt;
+      &lt;/tr&gt;
+    &lt;/thead&gt;
+    &lt;tbody&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Specified pipes, fittings and valves&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹6,000&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Installation labour&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹4,000&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Agreed testing and commissioning&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹1,000&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Opening and reinstating surfaces&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹2,500&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Subtotal before applicable taxes and other charges&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹13,500&lt;/td&gt;
+      &lt;/tr&gt;
+    &lt;/tbody&gt;
+  &lt;/table&gt;
+&lt;/div&gt;
+&lt;p&gt;Compare quotations using the same route, fitting schedule and test requirements. Ask whether old-pipe removal, debris disposal and painting are included.&lt;/p&gt;
+&lt;p&gt;If you buy materials separately, agree who checks compatibility and quantities. Saving on the wrong fittings or solvent can create a much larger repair bill after the wall is closed.&lt;/p&gt;
+&lt;h2&gt;Planning installation and testing&lt;/h2&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 1 - Map the actual application&lt;/strong&gt;: Mark hot-water supply, cold-water supply and drainage separately. Note the source, heater and fixtures. Let the plumber assess the operating conditions and suitable system.&lt;/li&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 2 - Agree the product specification&lt;/strong&gt;: Record the manufacturer, product range, size and rating, matching fittings, valves and approved jointing products. Keep the approved list with the order.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Check potable-water suitability where relevant. Avoid relying only on pipe colour, a verbal description or a similar-looking logo.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 3 - Plan routes and maintenance access&lt;/strong&gt;: Choose practical positions for valves and connections that need future servicing. Coordinate cabinets, tiles and electrical routes.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Structural elements should not be cut as an informal shortcut. Have difficult routes assessed before the work begins.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 4 - Check the delivered materials&lt;/strong&gt;: Compare markings and packaging with the specification. Keep invoices. Raise damage, unclear identification and substitutions before installation.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;A fitting that can be pushed onto a pipe is not automatically an approved system connection.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 5 - Have the joints made using the approved method&lt;/strong&gt;: Solvent cement is part of a jointing system, not a general household glue. Ashirvad’s guidance emphasises appropriate preparation, compatible solvent and curing as part of reliable CPVC work. [4]&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Cure time varies with the product, pipe dimensions, temperature and test conditions. Do not impose a universal “ready in an hour” rule or pressurise a line because the outside looks dry.&lt;/p&gt;
+&lt;p&gt;This is a stage for a competent installer following the manufacturer’s instructions, especially on hot-water or concealed routes.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 6 - Test before covering&lt;/strong&gt;: Agree the test method and acceptance record with the plumber. Use the manufacturer’s requirements for the system; do not improvise a compressed-air test on thermoplastic water pipe. [5]&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Repair and retest any problem before tiling or closing the wall. Photograph the routes and valve locations.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 7 - Commission and keep the records&lt;/strong&gt;: The installer should complete the required flushing and other commissioning procedures before use. Ask for a demonstration of accessible isolation valves.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Keep the system details so a future repair uses appropriate materials.&lt;/p&gt;
+&lt;h2&gt;Buying and handover checklist&lt;/h2&gt;
+&lt;p&gt;Before buying: Confirm the application, product range, size, rating, drinking-water suitability and complete fitting list.&lt;/p&gt;
+&lt;p&gt;Before closing surfaces: Retain the agreed test record and photographs of concealed routes.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1rem 1.25rem; margin: 1rem 0;"&gt;
+  &lt;p style="font-weight: 600; margin: 0 0 0.25rem 0; color: #1e293b;"&gt;At handover:&lt;/p&gt;
+  &lt;p style="margin: 0; color: #475569; font-size: 0.95rem; line-height: 1.6;"&gt;Check accessible joints, valve operation and the commissioned supply with the installer. Keep invoices and maintenance details.&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;If an existing leak recurs, investigate the failure rather than repeatedly covering it with an external patch.&lt;/p&gt;
+&lt;h2&gt;Troubleshooting &amp; Common Problems: Common pipe-selection mistakes&lt;/h2&gt;
+&lt;h3&gt;Choosing only by colour&lt;/h3&gt;
+&lt;p&gt;Colours differ between manufacturers and product ranges. Read the markings and the actual specification.&lt;/p&gt;
+&lt;p&gt;Treating all solvent cements as the same&lt;/p&gt;
+&lt;p&gt;Use a product approved for the pipe material and application. Follow any primer and curing requirements for that system.&lt;/p&gt;
+&lt;p&gt;Assuming a pressure rating applies at every temperature&lt;/p&gt;
+&lt;p&gt;Ask the plumber to use the manufacturer’s pressure-temperature guidance. Hot-water conditions can change the allowable operating pressure.&lt;/p&gt;
+&lt;p&gt;Replacing pipes to solve hard water&lt;/p&gt;
+&lt;p&gt;A new pipe does not soften the water. Hardness and scale require a separate assessment of water quality and suitable treatment.&lt;/p&gt;
+&lt;h2&gt;Frequently asked questions&lt;/h2&gt;
+&lt;p&gt;Using CPVC for every line&lt;/p&gt;
+&lt;p&gt;It may be technically suitable for some applications, but a blanket choice can overlook drainage requirements or add unnecessary cost. Specify each application.&lt;/p&gt;
+&lt;p&gt;Connecting a new system to an old one&lt;/p&gt;
+&lt;p&gt;Use an approved transition arrangement. The materials, dimensions and jointing method need to be compatible.&lt;/p&gt;
+&lt;p&gt;Mixing brands&lt;/p&gt;
+&lt;p&gt;Do not assume physical fit establishes compatibility or warranty coverage. Ask the manufacturers or responsible installer for the approved arrangement.&lt;/p&gt;
+&lt;p&gt;Repairing concealed pipework yourself&lt;/p&gt;
+&lt;p&gt;An incorrect joint can remain hidden until it causes damage. Use a competent plumber and have the relevant section tested before restoring finishes.&lt;/p&gt;
+&lt;h2&gt;Wrapping up&lt;/h2&gt;
+&lt;p&gt;Identify the water service first, then select a pipe system with suitable ratings and compatible components. The fitting and the joint deserve as much attention as the length of pipe.&lt;/p&gt;
+&lt;p&gt;A clear specification and a test record are particularly valuable when the work will disappear behind a wall.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.25rem 1.5rem; margin: 2rem 0;"&gt;
+  &lt;p style="font-weight: 700; margin-bottom: 0.75rem; color: #1e293b; font-size: 1.05rem;"&gt;Related Guides &amp; Services on Carpenterwala:&lt;/p&gt;
+  &lt;ul style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+&lt;li style="margin-bottom: 0.5rem;"&gt;&lt;a href="/blog/emergency-pipe-repair-guide" style="color: var(--primary, #2563eb); text-decoration: underline; font-weight: 500;"&gt;Emergency Pipe Repair Guide for Homeowners&lt;/a&gt;&lt;/li&gt;
+&lt;li style="margin-bottom: 0.5rem;"&gt;&lt;a href="/blog/how-to-fix-leaking-pipe-dripping-tap" style="color: var(--primary, #2563eb); text-decoration: underline; font-weight: 500;"&gt;How to Fix Leaking Pipes &amp; Dripping Taps&lt;/a&gt;&lt;/li&gt;
+&lt;li style="margin-bottom: 0.5rem;"&gt;&lt;a href="/services/plumbing" style="color: var(--primary, #2563eb); text-decoration: underline; font-weight: 500;"&gt;Expert Plumbing Services&lt;/a&gt;&lt;/li&gt;
+  &lt;/ul&gt;
+&lt;/div&gt;
+&lt;h2&gt;Sources and product guidance&lt;/h2&gt;
+&lt;p&gt;Sources checked on 23 October 2026. Ratings, jointing and testing requirements must be confirmed for the actual product system.&lt;/p&gt;
+&lt;ul style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 1.5rem;"&gt;
+  &lt;li&gt;[1] Astral comparison of CPVC and UPVC&lt;/li&gt;
+  &lt;li&gt;[2] Astral CPVC hot and cold water system&lt;/li&gt;
+  &lt;li&gt;[3] Ashirvad FlowPro CPVC system and installation guidance&lt;/li&gt;
+  &lt;li&gt;[4] Ashirvad guide to CPVC solvent cement and curing&lt;/li&gt;
+  &lt;li&gt;[5] Astral CPVC technical manual including pressure-testing precautions&lt;/li&gt;
+&lt;/ul&gt;</v>
+      </c>
+      <c r="I9" t="str">
+        <v>/images/blogs/cpvc-vs-upvc-pipes-home-plumbing-india.jpg</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>balcony-terrace-gardening-beginners-india</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Balcony and Terrace Gardening for Beginners in India: Sunlight, Soil &amp; Pots</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Home Maintenance</v>
+      </c>
+      <c r="E10" t="str">
+        <v>October 23, 2026</v>
+      </c>
+      <c r="F10" t="str">
+        <v>9 min read</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Start a manageable balcony or terrace garden with practical advice on sunlight, seasonal plant choices, containers, potting mix, watering and drainage.</v>
+      </c>
+      <c r="H10" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
+  &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;The key to a thriving apartment balcony garden in India is matching plant species to actual daily direct sunlight (North vs South/East/West facing). Use a lightweight potting blend of 40% garden red soil, 30% cocopeat (to reduce structural slab load), and 30% vermicompost/cow manure. Always elevate pots on planter stands or drainage saucers to safeguard terrace/balcony waterproofing and prevent stained tiles.&lt;/p&gt;
+&lt;/div&gt;
+&lt;div style="background: rgba(239, 68, 68, 0.08); border-left: 4px solid #ef4444; padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: #dc2626;"&gt;⚠️ Critical Safety Warnings &amp; Precautions&lt;/p&gt;
+  &lt;p style="margin: 0; line-height: 1.7; font-size: 0.95rem;"&gt;Check your apartment balcony slab weight limits before placing massive ceramic or stone planters. Ensure all railing planters are secured with heavy-duty metal safety brackets to prevent falling pot hazards during high monsoon winds.&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;Balcony and Terrace Gardening for Beginners&lt;/p&gt;
+&lt;p&gt;Starting a manageable garden in your part of India&lt;/p&gt;
+&lt;p&gt;Gardening &amp; Outdoor | Beginner Guide | Seasonal Planning&lt;/p&gt;
+&lt;p&gt;The first few pots are easy to buy. Keeping them watered through a hot week, moving around them on laundry day and finding space for the next plant takes more thought.&lt;/p&gt;
+&lt;p&gt;A good beginner garden starts small enough to care for. You can learn a great deal from a few well-placed containers before spending on a large vertical wall or a permanent raised bed.&lt;/p&gt;
+&lt;p&gt;This guide helps you plan a balcony or terrace garden around your light, local seasons and daily routine. A sunny coastal terrace and a shaded balcony in a colder region will need different choices.&lt;/p&gt;
+&lt;h2&gt;Checking the space before buying plants&lt;/h2&gt;
+&lt;p&gt;Spend a few days observing the balcony or terrace. Note where direct sun falls in the morning, midday and late afternoon. A space can be bright without receiving much direct sunlight.&lt;/p&gt;
+&lt;p&gt;Look at the wind, available water and the route to the drain. Keep a clear walkway and access to outlets, equipment and doors.&lt;/p&gt;
+&lt;p&gt;For terraces and balconies, consider the weight of wet growing media, containers, water and any structures. Get building or structural guidance before adding heavy planters, masonry beds or large collections. Do not use a generic internet load figure as approval for your roof.&lt;/p&gt;
+&lt;p&gt;Check the waterproofing and drainage before arranging pots. A plant collection should not hide an outlet or make inspection impossible. Keep containers securely inside the balcony rather than balanced on an unprotected edge.&lt;/p&gt;
+&lt;p&gt;TNAU’s gardening guidance recommends matching pot placement to sunshine needs and checking drainage. Those two observations are a useful starting point even before you decide what to grow. [1]&lt;/p&gt;
+&lt;h2&gt;Choosing plants for light and season&lt;/h2&gt;
+&lt;p&gt;Pick plants for the conditions you can provide. Moving a sun-loving crop into a deeply shaded corner will not be corrected by buying more fertiliser.&lt;/p&gt;
+&lt;div style="overflow-x: auto; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;table style="width: 100%; border-collapse: collapse; text-align: left; font-size: 0.95rem;"&gt;
+    &lt;thead&gt;
+      &lt;tr style="background: rgba(0,0,0,0.04); border-bottom: 2px solid var(--border, #e2e8f0);"&gt;
+        &lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Space or condition&lt;/th&gt;&lt;th style="padding: 12px 16px; font-weight: 600;"&gt;A sensible starting approach&lt;/th&gt;&lt;th style="padding: 12px 16px; font-weight: 600;"&gt;What to verify locally&lt;/th&gt;
+      &lt;/tr&gt;
+    &lt;/thead&gt;
+    &lt;tbody&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Good direct sunlight&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;A small trial of suitable seasonal vegetables or flowers&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Crop variety, planting season and heat tolerance&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Partial sun or filtered light&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Selected herbs, leafy plants or ornamentals suited to that light&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Actual direct-sun period and plant requirements&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Deep shade&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Suitable foliage plants rather than ambitious fruiting crops&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Whether the location has enough usable light&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Exposed windy terrace&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Sturdy containers and a modest number of suitable plants&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Secure supports and the need for an assessed windbreak&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;A spot that stays wet after rain&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Resolve drainage before planting&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;Whether water is collecting under containers&lt;/td&gt;
+      &lt;/tr&gt;
+    &lt;/tbody&gt;
+  &lt;/table&gt;
+&lt;/div&gt;
+&lt;p&gt;For an edible garden, choose a few things you actually use. Herbs or a small seasonal crop can be a practical beginning, provided the light and local weather suit them. Ask a good local nursery or agricultural extension source about the variety and planting window.&lt;/p&gt;
+&lt;p&gt;Adjust the plan to your region&lt;/p&gt;
+&lt;p&gt;In hot and dry conditions, small containers may lose moisture quickly. Observe the growing mix and plant response, and plan watering access before expanding.&lt;/p&gt;
+&lt;p&gt;In humid or heavy-rainfall periods, pay particular attention to drainage, spacing and air movement. Pots that were easy to water in summer may stay wet much longer during rain.&lt;/p&gt;
+&lt;p&gt;In colder regions, match planting to the local season and protect tender plants according to their requirements. A calendar written for a warm southern city should not be used unchanged in a place with frost.&lt;/p&gt;
+&lt;p&gt;Your balcony’s microclimate can differ from the general weather report. Watch the actual site, particularly when the season changes.&lt;/p&gt;
+&lt;h2&gt;Selecting containers and potting mix&lt;/h2&gt;
+&lt;p&gt;Start with containers you can move and clean around&lt;/p&gt;
+&lt;p&gt;Choose a size suited to the plant’s mature roots. A tiny decorative pot can be attractive but may leave little growing space.&lt;/p&gt;
+&lt;p&gt;Check drainage holes and the way water leaves the container. Use supports or arrangements that protect the underlying surface without blocking drainage.&lt;/p&gt;
+&lt;p&gt;TNAU notes that deeper-rooted plants need appropriately deep containers and recommends watering according to the moisture condition of the pot. [1]&lt;/p&gt;
+&lt;p&gt;Do not turn every container into a large water reservoir. If saucers are used, manage them so they do not remain full of stagnant water.&lt;/p&gt;
+&lt;p&gt;Buy a growing mix suited to containers&lt;/p&gt;
+&lt;p&gt;Heavy garden soil can compact in a pot. A container mix should balance drainage, air and moisture retention.&lt;/p&gt;
+&lt;p&gt;TNAU’s nursery guidance describes a suitable potting medium as open, well drained, moisture-retentive and sufficiently light. [2] The precise mix should suit the plant and the materials available locally.&lt;/p&gt;
+&lt;p&gt;You do not need one universal ratio for every plant. Ask what is in a ready-made mix and whether it contains nutrients. That avoids adding repeated fertiliser before understanding the starting medium.&lt;/p&gt;
+&lt;p&gt;Use mature compost from a reliable source. Avoid adding kitchen waste directly to a small pot simply because it is biodegradable.&lt;/p&gt;
+&lt;p&gt;Give supports a proper job&lt;/p&gt;
+&lt;p&gt;A climber may need a stable support, but a heavy trellis or vertical system also changes loading and wind exposure. Have substantial structures assessed.&lt;/p&gt;
+&lt;p&gt;Keep supports away from waterproofing details unless the fixing has been designed to protect them. A drilled hole can create a much larger problem than the plant solves.&lt;/p&gt;
+&lt;h2&gt;Preparing a small starter budget&lt;/h2&gt;
+&lt;p&gt;Buy enough for a manageable trial and leave room to learn. Several healthy plants with suitable containers are more useful than a crowded collection of unsuitable ones.&lt;/p&gt;
+&lt;p&gt;The following is a fictional allowance for a small garden. It is not a national retail price list.&lt;/p&gt;
+&lt;div style="overflow-x: auto; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;table style="width: 100%; border-collapse: collapse; text-align: left; font-size: 0.95rem;"&gt;
+    &lt;thead&gt;
+      &lt;tr style="background: rgba(0,0,0,0.04); border-bottom: 2px solid var(--border, #e2e8f0);"&gt;
+        &lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Item&lt;/th&gt;&lt;th style="padding: 12px 16px; font-weight: 600;"&gt;Illustrative allowance&lt;/th&gt;
+      &lt;/tr&gt;
+    &lt;/thead&gt;
+    &lt;tbody&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Six suitable containers or grow bags&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹900&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Container growing mix&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹900&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Seeds or small plants&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹450&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Hand tool and watering arrangement&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹550&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Surface-protection and drainage accessories&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹400&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Basic supports and labels&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹300&lt;/td&gt;
+      &lt;/tr&gt;
+      &lt;tr style="border-bottom: 1px solid var(--border, #e2e8f0);"&gt;
+        &lt;td style="padding: 12px 16px; font-weight: 500;"&gt;Total illustrative starter allowance&lt;/td&gt;&lt;td style="padding: 12px 16px; "&gt;₹3,500&lt;/td&gt;
+      &lt;/tr&gt;
+    &lt;/tbody&gt;
+  &lt;/table&gt;
+&lt;/div&gt;
+&lt;p&gt;This excludes structural work, waterproofing repairs, permanent beds and automated irrigation. Size, material and local availability will change the actual bill.&lt;/p&gt;
+&lt;p&gt;A reliable nearby nursery is useful because plants can be checked before buying and the advice can reflect your local season. When ordering online, verify the mature plant size, container dimensions and delivery condition.&lt;/p&gt;
+&lt;h2&gt;Setting up the garden step by step&lt;/h2&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 1 - Make a light and access plan&lt;/strong&gt;: Mark the sunny positions, water source, drains and a clear walkway. Decide how many containers you can inspect and water comfortably.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;TNAU’s kitchen-garden guidance includes sunlight, water access and the time available for care in the planning process. [3]&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 2 - Choose a short plant list&lt;/strong&gt;: Pick a few plants with similar care requirements. Check their mature size and seasonal suitability.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;If you are starting from seed, sow a manageable quantity. Germinating an entire packet can quickly create more seedlings than the balcony can hold.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 3 - Prepare the containers and medium&lt;/strong&gt;: Check drainage and use a suitable potting mix. Leave practical watering space at the top according to the container and crop.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Label plants and sowing dates. Labels are especially useful when several seedlings look alike.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 4 - Place plants and observe them&lt;/strong&gt;: Position the pots according to light needs and the site plan. Avoid blocking drains or filling every gap.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Give plants room to grow, and make changes gradually when moving them between significantly different light conditions.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 5 - Develop a watering routine&lt;/strong&gt;: Check the medium rather than following the same number of minutes every day. Container size, sun, wind and rain all change water use.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Water in a way that wets the relevant root zone and allows appropriate drainage. Avoid leaving the surface beneath the pots continually wet.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 6 - Add nutrition according to need&lt;/strong&gt;: Follow the crop and product guidance. More fertiliser is not a reliable response to every yellow leaf or slow-growing plant.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;p&gt;Keep a simple note of what was added and when. Change one thing at a time where practical so you can see the result.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.5rem 1.75rem; margin: 1.5rem 0 2rem 0;"&gt;
+  &lt;h3 style="margin-top: 0; margin-bottom: 1rem; color: #1e293b;"&gt;Structured Step-by-Step Execution Guide&lt;/h3&gt;
+  &lt;ol style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+    &lt;li style="margin-bottom: 0.75rem;"&gt;&lt;strong&gt;Step 7 - Expand only after the first group settles&lt;/strong&gt;: Notice which plants fit the light and your routine. Repeat those successes before investing in a much larger setup.&lt;/li&gt;
+  &lt;/ol&gt;
+&lt;/div&gt;
+&lt;h2&gt;Weekly care and holiday planning&lt;/h2&gt;
+&lt;p&gt;Look under leaves, inspect new growth and check drainage. Remove dead material and keep tools and containers reasonably clean.&lt;/p&gt;
+&lt;p&gt;Avoid spraying an unidentified problem with a strong chemical or an improvised household mixture. Identify the pest or disease first and follow suitable local guidance and any product label.&lt;/p&gt;
+&lt;p&gt;For holidays, test the watering arrangement well before leaving. An automated kit should be checked under real conditions, including its battery or power needs and the way each container drains.&lt;/p&gt;
+&lt;p&gt;TNAU’s vertical-garden guidance also makes the choice of plants, growing media and irrigation part of the system design. A vertical display needs a maintenance plan just as much as a row of pots. [4]&lt;/p&gt;
+&lt;h2&gt;Troubleshooting &amp; Common Problems: Troubleshooting beginner problems&lt;/h2&gt;
+&lt;p&gt;Leaves wilt even though the pot is wet&lt;/p&gt;
+&lt;p&gt;Do not automatically add more water. Check drainage, root condition, recent weather and the plant’s requirements. Seek local advice if the cause remains unclear.&lt;/p&gt;
+&lt;p&gt;Water runs straight through a hard root ball&lt;/p&gt;
+&lt;p&gt;Inspect the medium and root condition. A compacted or root-bound plant may need appropriate repotting rather than repeated quick splashes.&lt;/p&gt;
+&lt;p&gt;Plants grow tall and weak&lt;/p&gt;
+&lt;p&gt;Check whether the light suits the crop and whether plants are overcrowded. Fertiliser will not replace suitable light.&lt;/p&gt;
+&lt;h3&gt;The balcony becomes difficult to use&lt;/h3&gt;
+&lt;p&gt;Reduce the number of containers or rearrange them. A garden that leaves access for cleaning and watering is easier to keep healthy.&lt;/p&gt;
+&lt;h2&gt;Frequently asked questions&lt;/h2&gt;
+&lt;p&gt;Growing food on a shaded balcony&lt;/p&gt;
+&lt;p&gt;Start by measuring the light. Some plants tolerate partial shade better than others, but deep shade can limit edible-crop performance. Choose locally appropriate options.&lt;/p&gt;
+&lt;p&gt;Using the same planting calendar across India&lt;/p&gt;
+&lt;p&gt;Adjust for region, season and balcony conditions. Check local crop guidance before sowing.&lt;/p&gt;
+&lt;p&gt;Installing a permanent terrace bed&lt;/p&gt;
+&lt;p&gt;Have loading, waterproofing, drainage and root protection assessed before construction. Movable containers can be a more manageable starting point.&lt;/p&gt;
+&lt;p&gt;Beginning without automatic irrigation&lt;/p&gt;
+&lt;p&gt;A small garden can be watered by hand if the routine is practical. Add automation when it solves a clear need and has been tested.&lt;/p&gt;
+&lt;h2&gt;Wrapping up&lt;/h2&gt;
+&lt;p&gt;Start with the light, the drainage and the time you can give the garden. A few suitable plants will teach you more than a large shopping list.&lt;/p&gt;
+&lt;p&gt;As the seasons change, keep observing the space. The plants that thrive in your balcony’s actual conditions are the best guide to what you should grow next.&lt;/p&gt;
+&lt;div style="background: #f8fafc; border: 1px solid #e2e8f0; border-radius: 8px; padding: 1.25rem 1.5rem; margin: 2rem 0;"&gt;
+  &lt;p style="font-weight: 700; margin-bottom: 0.75rem; color: #1e293b; font-size: 1.05rem;"&gt;Related Guides &amp; Services on Carpenterwala:&lt;/p&gt;
+  &lt;ul style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 0;"&gt;
+&lt;li style="margin-bottom: 0.5rem;"&gt;&lt;a href="/blog/regenerate-hard-potting-soil-repot-balcony-plants-guide" style="color: var(--primary, #2563eb); text-decoration: underline; font-weight: 500;"&gt;How to Regenerate Hard Potting Soil &amp; Repot Balcony Plants&lt;/a&gt;&lt;/li&gt;
+&lt;li style="margin-bottom: 0.5rem;"&gt;&lt;a href="/blog/diy-balcony-automatic-drip-irrigation-setup-guide" style="color: var(--primary, #2563eb); text-decoration: underline; font-weight: 500;"&gt;DIY Balcony Automatic Drip Irrigation Setup Guide&lt;/a&gt;&lt;/li&gt;
+&lt;li style="margin-bottom: 0.5rem;"&gt;&lt;a href="/services" style="color: var(--primary, #2563eb); text-decoration: underline; font-weight: 500;"&gt;Balcony Safety Nets &amp; Maintenance Services&lt;/a&gt;&lt;/li&gt;
+  &lt;/ul&gt;
+&lt;/div&gt;
+&lt;ul style="padding-left: 1.5rem; line-height: 1.8; margin-bottom: 1.5rem;"&gt;
+  &lt;li&gt;[1] TNAU guidance on container placement drainage and watering&lt;/li&gt;
+  &lt;li&gt;[2] TNAU nursery and potting-medium guidance&lt;/li&gt;
+  &lt;li&gt;[3] TNAU kitchen-garden planning guidance&lt;/li&gt;
+  &lt;li&gt;[4] TNAU vertical-gardening systems and maintenance&lt;/li&gt;
+&lt;/ul&gt;</v>
+      </c>
+      <c r="I10" t="str">
+        <v>/images/blogs/balcony-terrace-gardening-beginners-india.jpg</v>
+      </c>
+    </row>
+    <row r="11" xml:space="preserve">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
         <v>how-to-unclog-a-grease-filled-kitchen-sink-drain-naturally</v>
       </c>
-      <c r="C3" t="str">
+      <c r="C11" t="str">
         <v>How to Unclog a Grease-Filled Kitchen Sink Drain Naturally</v>
       </c>
-      <c r="D3" t="str">
+      <c r="D11" t="str">
         <v>How to</v>
       </c>
-      <c r="E3" t="str">
+      <c r="E11" t="str">
         <v>September 27, 2026</v>
       </c>
-      <c r="F3" t="str">
+      <c r="F11" t="str">
         <v>7 min read</v>
       </c>
-      <c r="G3" t="str">
+      <c r="G11" t="str">
         <v>Kitchen sink draining slowly from grease buildup? Here's how to clear it using baking soda, vinegar, and hot water — no harsh chemicals needed.</v>
       </c>
-      <c r="H3" t="str" xml:space="preserve">
+      <c r="H11" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
   &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
   &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To unclog a kitchen sink drain full of grease without chemicals, pour boiling-hot water down the drain first to soften buildup, follow with half a cup of baking soda then half a cup of vinegar, let the mixture fizz and sit for 30 minutes to an hour, then flush with more hot water — repeating if the drain is still slow.&lt;/p&gt;
@@ -860,33 +2450,33 @@
   &lt;li&gt;&lt;a href="/blog/how-to-replace-a-worn-washer-in-a-dripping-quarter-turn-tap"&gt;How to Replace a Worn Washer in a Dripping Quarter-Turn Tap&lt;/a&gt;&lt;/li&gt;
 &lt;/ul&gt;</v>
       </c>
-      <c r="I3" t="str">
+      <c r="I11" t="str">
         <v>https://abuaziyfhgmzeiqjtcas.supabase.co/storage/v1/object/public/blog-images/how-to-unclog-a-grease-filled-kitchen-sink-drain-naturally.jpg</v>
       </c>
     </row>
-    <row r="4" xml:space="preserve">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="str">
+    <row r="12" xml:space="preserve">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
         <v>how-to-fix-a-dual-flush-toilet-button-stuck-pressed-down</v>
       </c>
-      <c r="C4" t="str">
+      <c r="C12" t="str">
         <v>How to Fix a Dual-Flush Toilet Button Stuck Pressed Down</v>
       </c>
-      <c r="D4" t="str">
+      <c r="D12" t="str">
         <v>How to</v>
       </c>
-      <c r="E4" t="str">
+      <c r="E12" t="str">
         <v>September 27, 2026</v>
       </c>
-      <c r="F4" t="str">
+      <c r="F12" t="str">
         <v>7 min read</v>
       </c>
-      <c r="G4" t="str">
+      <c r="G12" t="str">
         <v>Dual-flush button jammed in or stuck pressed down? Here's how to open the cistern, free the internal mechanism, and stop the continuous flush.</v>
       </c>
-      <c r="H4" t="str" xml:space="preserve">
+      <c r="H12" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
   &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
   &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To fix a dual-flush toilet button that stays pressed down, remove the button's outer cap by twisting or unclipping it, check the internal spring and plunger mechanism for misalignment or debris, clean and realign it, and if the spring itself is broken, replace the button assembly entirely to restore proper spring-back action.&lt;/p&gt;
@@ -985,33 +2575,33 @@
   &lt;li&gt;&lt;a href="/blog/how-to-fix-a-leaking-kitchen-sink-drain-pipe-joint"&gt;How to Fix a Leaking Kitchen Sink Drain Pipe Joint&lt;/a&gt;&lt;/li&gt;
 &lt;/ul&gt;</v>
       </c>
-      <c r="I4" t="str">
+      <c r="I12" t="str">
         <v>https://abuaziyfhgmzeiqjtcas.supabase.co/storage/v1/object/public/blog-images/how-to-fix-a-dual-flush-toilet-button-stuck-pressed-down.jpg</v>
       </c>
     </row>
-    <row r="5" xml:space="preserve">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="str">
+    <row r="13" xml:space="preserve">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
         <v>how-to-clear-a-blocked-bathroom-floor-drain-full-of-hair</v>
       </c>
-      <c r="C5" t="str">
+      <c r="C13" t="str">
         <v>How to Clear a Blocked Bathroom Floor Drain Full of Hair</v>
       </c>
-      <c r="D5" t="str">
+      <c r="D13" t="str">
         <v>How to</v>
       </c>
-      <c r="E5" t="str">
+      <c r="E13" t="str">
         <v>September 27, 2026</v>
       </c>
-      <c r="F5" t="str">
+      <c r="F13" t="str">
         <v>7 min read</v>
       </c>
-      <c r="G5" t="str">
+      <c r="G13" t="str">
         <v>Bathroom floor drain draining slowly or gurgling? Here's how to remove the jaali, clear hair buildup, and restore full drainage without chemicals.</v>
       </c>
-      <c r="H5" t="str" xml:space="preserve">
+      <c r="H13" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
   &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
   &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To clear a blocked bathroom floor drain full of hair, lift out the drain grating (jaali) first and physically remove visible hair clumps, use a bent wire or drain hair-removal tool to pull out deeper buildup, flush with hot water and a baking soda-vinegar treatment, then replace the grating and test drainage.&lt;/p&gt;
@@ -1114,33 +2704,33 @@
   &lt;li&gt;&lt;a href="/blog/how-to-clear-drainage-p-trap-clogs-sewer-smell"&gt;How to Clear Drainage P-Trap Clogs &amp;amp; Eliminate Sewer Smell&lt;/a&gt;&lt;/li&gt;
 &lt;/ul&gt;</v>
       </c>
-      <c r="I5" t="str">
+      <c r="I13" t="str">
         <v>https://abuaziyfhgmzeiqjtcas.supabase.co/storage/v1/object/public/blog-images/how-to-clear-a-blocked-bathroom-floor-drain-full-of-hair.jpg</v>
       </c>
     </row>
-    <row r="6" xml:space="preserve">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="str">
+    <row r="14" xml:space="preserve">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
         <v>how-to-fix-a-leaking-washing-machine-inlet-pipe-at-the-tap</v>
       </c>
-      <c r="C6" t="str">
+      <c r="C14" t="str">
         <v>How to Fix a Leaking Washing Machine Inlet Pipe at the Tap</v>
       </c>
-      <c r="D6" t="str">
+      <c r="D14" t="str">
         <v>How to</v>
       </c>
-      <c r="E6" t="str">
+      <c r="E14" t="str">
         <v>September 27, 2026</v>
       </c>
-      <c r="F6" t="str">
+      <c r="F14" t="str">
         <v>7 min read</v>
       </c>
-      <c r="G6" t="str">
+      <c r="G14" t="str">
         <v>Washing machine inlet hose leaking at the tap connection? Here's how to reseal or replace the fitting to stop water wastage and floor damage.</v>
       </c>
-      <c r="H6" t="str" xml:space="preserve">
+      <c r="H14" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
   &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
   &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To fix a leaking washing machine inlet pipe at the tap, shut off the tap supply, unscrew the inlet hose connector, check the rubber washer inside the connector for wear and replace it, wrap the tap's threaded spout with Teflon tape if needed, then reattach the hose hand-tight plus a quarter turn and test for leaks.&lt;/p&gt;
@@ -1243,33 +2833,33 @@
   &lt;li&gt;&lt;a href="/blog/how-to-fix-a-leaking-kitchen-sink-drain-pipe-joint"&gt;How to Fix a Leaking Kitchen Sink Drain Pipe Joint&lt;/a&gt;&lt;/li&gt;
 &lt;/ul&gt;</v>
       </c>
-      <c r="I6" t="str">
+      <c r="I14" t="str">
         <v>https://abuaziyfhgmzeiqjtcas.supabase.co/storage/v1/object/public/blog-images/how-to-fix-a-leaking-washing-machine-inlet-pipe-at-the-tap.jpg</v>
       </c>
     </row>
-    <row r="7" xml:space="preserve">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="str">
+    <row r="15" xml:space="preserve">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="str">
         <v>how-to-replace-a-rusted-washbasin-bottle-trap-setup</v>
       </c>
-      <c r="C7" t="str">
+      <c r="C15" t="str">
         <v>How to Replace a Rusted Washbasin Bottle Trap Setup</v>
       </c>
-      <c r="D7" t="str">
+      <c r="D15" t="str">
         <v>How to</v>
       </c>
-      <c r="E7" t="str">
+      <c r="E15" t="str">
         <v>September 27, 2026</v>
       </c>
-      <c r="F7" t="str">
+      <c r="F15" t="str">
         <v>7 min read</v>
       </c>
-      <c r="G7" t="str">
+      <c r="G15" t="str">
         <v>Washbasin bottle trap rusted, leaking, or smelling bad? Here's how to remove the old one and install a new trap correctly, step by step.</v>
       </c>
-      <c r="H7" t="str" xml:space="preserve">
+      <c r="H15" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
   &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
   &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To replace a rusted washbasin bottle trap, place a bucket underneath, loosen the connecting nuts on both sides of the trap, remove the old corroded unit, fit a new matching bottle trap, hand-tighten the nuts then snug with pliers, and run water through to confirm a leak-free seal.&lt;/p&gt;
@@ -1369,33 +2959,33 @@
   &lt;li&gt;&lt;a href="/blog/how-to-unclog-a-grease-filled-kitchen-sink-drain-naturally"&gt;How to Unclog a Grease-Filled Kitchen Sink Drain Naturally&lt;/a&gt;&lt;/li&gt;
 &lt;/ul&gt;</v>
       </c>
-      <c r="I7" t="str">
+      <c r="I15" t="str">
         <v>https://abuaziyfhgmzeiqjtcas.supabase.co/storage/v1/object/public/blog-images/how-to-replace-a-rusted-washbasin-bottle-trap-setup.jpg</v>
       </c>
     </row>
-    <row r="8" xml:space="preserve">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="str">
+    <row r="16" xml:space="preserve">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="str">
         <v>how-to-fix-low-shower-pressure-caused-by-hard-water-scale</v>
       </c>
-      <c r="C8" t="str">
+      <c r="C16" t="str">
         <v>How to Fix Low Shower Pressure Caused by Hard Water Scale</v>
       </c>
-      <c r="D8" t="str">
+      <c r="D16" t="str">
         <v>How to</v>
       </c>
-      <c r="E8" t="str">
+      <c r="E16" t="str">
         <v>September 27, 2026</v>
       </c>
-      <c r="F8" t="str">
+      <c r="F16" t="str">
         <v>7 min read</v>
       </c>
-      <c r="G8" t="str">
+      <c r="G16" t="str">
         <v>Shower head spraying weak or uneven water? Here's how to remove hard water scaling from the nozzle holes and restore full pressure in minutes.</v>
       </c>
-      <c r="H8" t="str" xml:space="preserve">
+      <c r="H16" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
   &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
   &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To fix a shower head with low pressure from hard water scaling, unscrew the shower head (or leave attached if removable nozzle plate), soak it in a vinegar solution for 30 minutes to a few hours, scrub the nozzle holes with an old toothbrush or needle to dislodge mineral deposits, rinse thoroughly, and reattach to test the restored spray pattern.&lt;/p&gt;
@@ -1497,33 +3087,33 @@
   &lt;li&gt;&lt;a href="/blog/how-to-fix-a-leaking-washing-machine-inlet-pipe-at-the-tap"&gt;How to Fix a Leaking Washing Machine Inlet Pipe at the Tap&lt;/a&gt;&lt;/li&gt;
 &lt;/ul&gt;</v>
       </c>
-      <c r="I8" t="str">
+      <c r="I16" t="str">
         <v>https://abuaziyfhgmzeiqjtcas.supabase.co/storage/v1/object/public/blog-images/how-to-fix-low-shower-pressure-caused-by-hard-water-scale.jpg</v>
       </c>
     </row>
-    <row r="9" xml:space="preserve">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="str">
+    <row r="17" xml:space="preserve">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="str">
         <v>how-to-reseal-silicone-caulking-around-a-kitchen-sink</v>
       </c>
-      <c r="C9" t="str">
+      <c r="C17" t="str">
         <v>How to Reseal Silicone Caulking Around a Kitchen Sink</v>
       </c>
-      <c r="D9" t="str">
+      <c r="D17" t="str">
         <v>How to</v>
       </c>
-      <c r="E9" t="str">
+      <c r="E17" t="str">
         <v>September 27, 2026</v>
       </c>
-      <c r="F9" t="str">
+      <c r="F17" t="str">
         <v>7 min read</v>
       </c>
-      <c r="G9" t="str">
+      <c r="G17" t="str">
         <v>Kitchen sink countertop seal cracked or leaking? Here's how to remove old silicone caulk and apply a fresh, waterproof bead the right way.</v>
       </c>
-      <c r="H9" t="str" xml:space="preserve">
+      <c r="H17" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
   &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
   &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To reseal silicone caulking around a leaking kitchen sink countertop, scrape out all old, cracked silicone completely, clean the joint with isopropyl alcohol, apply a continuous new bead of kitchen-grade silicone sealant along the sink-to-countertop joint, smooth it with a wet finger or caulking tool, and let it cure fully before using the sink.&lt;/p&gt;
@@ -1628,33 +3218,33 @@
   &lt;li&gt;&lt;a href="/blog/how-to-repair-a-deep-scratch-in-a-laminate-countertop"&gt;How to Repair a Deep Scratch in a Laminate Countertop&lt;/a&gt;&lt;/li&gt;
 &lt;/ul&gt;</v>
       </c>
-      <c r="I9" t="str">
+      <c r="I17" t="str">
         <v>https://abuaziyfhgmzeiqjtcas.supabase.co/storage/v1/object/public/blog-images/how-to-reseal-silicone-caulking-around-a-kitchen-sink.jpg</v>
       </c>
     </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="str">
+    <row r="18" xml:space="preserve">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="str">
         <v>how-to-fix-a-refrigerator-drip-pan-thats-overflowing</v>
       </c>
-      <c r="C10" t="str">
+      <c r="C18" t="str">
         <v>How to Fix a Refrigerator Drip Pan That's Overflowing</v>
       </c>
-      <c r="D10" t="str">
+      <c r="D18" t="str">
         <v>How to</v>
       </c>
-      <c r="E10" t="str">
+      <c r="E18" t="str">
         <v>September 27, 2026</v>
       </c>
-      <c r="F10" t="str">
+      <c r="F18" t="str">
         <v>7 min read</v>
       </c>
-      <c r="G10" t="str">
+      <c r="G18" t="str">
         <v>Water pooling under your fridge or a rattling tray at the back? Here's how to locate, clean, and correctly reposition the defrost drip pan.</v>
       </c>
-      <c r="H10" t="str" xml:space="preserve">
+      <c r="H18" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin-bottom: 2rem;"&gt;
   &lt;p style="margin: 0; font-weight: 600; color: var(--primary, #2563eb); text-transform: uppercase; font-size: 0.85rem; letter-spacing: 0.05em;"&gt;Quick Takeaway (Google Position-0 Summary)&lt;/p&gt;
   &lt;p style="margin: 0.5rem 0 0 0; font-size: 1.05rem; line-height: 1.6;"&gt;To fix an overflowing or rattling refrigerator drip pan, locate the pan at the back base of the fridge (behind the rear access panel or beneath the compressor), remove and clean it of accumulated dust, mold, and debris, check that it's seated correctly and level on its mounting brackets, and ensure the defrost drain tube feeding into it isn't blocked, which is the most common cause of overflow.&lt;/p&gt;
@@ -1765,33 +3355,33 @@
   &lt;li&gt;&lt;a href="/blog/how-to-fix-a-leaking-washing-machine-inlet-pipe-at-the-tap"&gt;How to Fix a Leaking Washing Machine Inlet Pipe at the Tap&lt;/a&gt;&lt;/li&gt;
 &lt;/ul&gt;</v>
       </c>
-      <c r="I10" t="str">
+      <c r="I18" t="str">
         <v>https://abuaziyfhgmzeiqjtcas.supabase.co/storage/v1/object/public/blog-images/how-to-fix-a-refrigerator-drip-pan-thats-overflowing.jpg</v>
       </c>
     </row>
-    <row r="11" xml:space="preserve">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="str">
+    <row r="19" xml:space="preserve">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="str">
         <v>how-to-replace-a-worn-washer-in-a-dripping-quarter-turn-tap</v>
       </c>
-      <c r="C11" t="str">
+      <c r="C19" t="str">
         <v>How to Replace a Worn Washer in a Dripping Quarter-Turn Tap</v>
       </c>
-      <c r="D11" t="str">
+      <c r="D19" t="str">
         <v>How to</v>
       </c>
-      <c r="E11" t="str">
+      <c r="E19" t="str">
         <v>September 27, 2026</v>
       </c>
-      <c r="F11" t="str">
+      <c r="F19" t="str">
         <v>7 min read</v>
       </c>
-      <c r="G11" t="str">
+      <c r="G19" t="str">
         <v>Modern quarter-turn tap still dripping? Here's how to replace the internal ceramic disc cartridge that's actually causing the leak.</v>
       </c>
-      <c r="H11" t="str" xml:space="preserve">
+      <c r="H19" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
   &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
   &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To fix a dripping quarter-turn tap, recognize that modern 90-degree taps do not use traditional rubber washers — they rely on an internal brass and ceramic disc spindle cartridge. Shut off the under-sink angle valve, pry off the decorative index cap, unscrew the hidden Allen grub screw to remove the handle, unscrew the brass cartridge using an adjustable spanner, replace the whole ceramic cartridge with an exact matching replacement, and reassemble for a permanent leak-free seal.&lt;/p&gt;
@@ -1892,33 +3482,33 @@
   &lt;li&gt;&lt;a href="/blog/how-to-cut-mild-steel-angle-iron-at-home-with-a-grinder"&gt;How to Cut Mild Steel Angle Iron at Home With a Grinder&lt;/a&gt;&lt;/li&gt;
 &lt;/ul&gt;</v>
       </c>
-      <c r="I11" t="str">
+      <c r="I19" t="str">
         <v>https://abuaziyfhgmzeiqjtcas.supabase.co/storage/v1/object/public/blog-images/how-to-replace-a-worn-washer-in-a-dripping-quarter-turn-tap.jpg</v>
       </c>
     </row>
-    <row r="12" xml:space="preserve">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="str">
+    <row r="20" xml:space="preserve">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="str">
         <v>how-to-fix-a-leaking-kitchen-sink-drain-pipe-joint</v>
       </c>
-      <c r="C12" t="str">
+      <c r="C20" t="str">
         <v>How to Fix a Leaking Kitchen Sink Drain Pipe Joint</v>
       </c>
-      <c r="D12" t="str">
+      <c r="D20" t="str">
         <v>How to</v>
       </c>
-      <c r="E12" t="str">
+      <c r="E20" t="str">
         <v>September 27, 2026</v>
       </c>
-      <c r="F12" t="str">
+      <c r="F20" t="str">
         <v>7 min read</v>
       </c>
-      <c r="G12" t="str">
+      <c r="G20" t="str">
         <v>Water pooling under your kitchen sink? Here's how to identify and seal a leaking PVC drain pipe joint using the right seals and slip nuts.</v>
       </c>
-      <c r="H12" t="str" xml:space="preserve">
+      <c r="H20" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
   &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
   &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To fix a leaking kitchen sink drain pipe joint, position a bucket beneath the P-trap, unscrew the offending plastic slip nut by hand or with adjustable pliers, inspect the beveled rubber or nylon slip washer for degradation or inversion, clean the mating pipe threads of grime, install a fresh matching washer with the taper facing into the pipe socket, hand-tighten firmly, and add a quarter-turn with pliers to achieve a 100% watertight seal.&lt;/p&gt;
@@ -2016,33 +3606,33 @@
   &lt;li&gt;&lt;a href="/blog/how-to-clean-and-unstick-a-rusted-padlock-mechanism"&gt;How to Clean and Unstick a Rusted Padlock Mechanism&lt;/a&gt;&lt;/li&gt;
 &lt;/ul&gt;</v>
       </c>
-      <c r="I12" t="str">
+      <c r="I20" t="str">
         <v>https://abuaziyfhgmzeiqjtcas.supabase.co/storage/v1/object/public/blog-images/how-to-fix-a-leaking-kitchen-sink-drain-pipe-joint.jpg</v>
       </c>
     </row>
-    <row r="13" xml:space="preserve">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="str">
+    <row r="21" xml:space="preserve">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="str">
         <v>how-to-cut-mild-steel-angle-iron-at-home-with-a-grinder</v>
       </c>
-      <c r="C13" t="str">
+      <c r="C21" t="str">
         <v>How to Cut Mild Steel Angle Iron at Home With a Grinder</v>
       </c>
-      <c r="D13" t="str">
+      <c r="D21" t="str">
         <v>How to</v>
       </c>
-      <c r="E13" t="str">
+      <c r="E21" t="str">
         <v>September 27, 2026</v>
       </c>
-      <c r="F13" t="str">
+      <c r="F21" t="str">
         <v>7 min read</v>
       </c>
-      <c r="G13" t="str">
+      <c r="G21" t="str">
         <v>Need to cut angle iron for a home project? Here's how to measure, mark, and cut mild steel cleanly and safely using a hand angle grinder.</v>
       </c>
-      <c r="H13" t="str" xml:space="preserve">
+      <c r="H21" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
   &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
   &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To cut mild steel angle iron at home, mark your cut line accurately across both outer faces using an engineer's try square, clamp the steel solidly in a bench vice right next to the cut line, fit your 4-inch angle grinder with a 1.0mm ultra-thin metal abrasive cutting wheel, and let the high RPM disc slice through each face with light, steady pressure without forcing or twisting the disc.&lt;/p&gt;
@@ -2145,33 +3735,33 @@
   &lt;li&gt;&lt;a href="/blog/how-to-apply-rust-converter-primer-to-iron-railings"&gt;How to Apply Rust Converter Primer to Iron Railings&lt;/a&gt;&lt;/li&gt;
 &lt;/ul&gt;</v>
       </c>
-      <c r="I13" t="str">
+      <c r="I21" t="str">
         <v>https://abuaziyfhgmzeiqjtcas.supabase.co/storage/v1/object/public/blog-images/how-to-cut-mild-steel-angle-iron-at-home-with-a-grinder.jpg</v>
       </c>
     </row>
-    <row r="14" xml:space="preserve">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="str">
+    <row r="22" xml:space="preserve">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="str">
         <v>how-to-apply-rust-converter-primer-to-iron-railings</v>
       </c>
-      <c r="C14" t="str">
+      <c r="C22" t="str">
         <v>How to Apply Rust Converter Primer to Iron Railings</v>
       </c>
-      <c r="D14" t="str">
+      <c r="D22" t="str">
         <v>How to</v>
       </c>
-      <c r="E14" t="str">
+      <c r="E22" t="str">
         <v>September 27, 2026</v>
       </c>
-      <c r="F14" t="str">
+      <c r="F22" t="str">
         <v>7 min read</v>
       </c>
-      <c r="G14" t="str">
+      <c r="G22" t="str">
         <v>Learn how to properly apply rust converter primer to outdoor iron railings for long-lasting rust prevention before your final paint coat.</v>
       </c>
-      <c r="H14" t="str" xml:space="preserve">
+      <c r="H22" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
   &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
   &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To apply rust converter primer to outdoor iron railings, scrape away flaking rust and debris with a wire brush, apply the converter solution in a thin, uniform coat directly over remaining tight rust using a dedicated paintbrush, allow it to react chemically until it converts into a dark blue-black magnetite shield, and finish with a durable outdoor enamel topcoat.&lt;/p&gt;
@@ -2274,33 +3864,33 @@
   &lt;li&gt;&lt;a href="/blog/how-to-remove-deep-rust-from-metal-window-grills-before-paint"&gt;How to Remove Deep Rust From Metal Window Grills Before Paint&lt;/a&gt;&lt;/li&gt;
 &lt;/ul&gt;</v>
       </c>
-      <c r="I14" t="str">
+      <c r="I22" t="str">
         <v>https://abuaziyfhgmzeiqjtcas.supabase.co/storage/v1/object/public/blog-images/how-to-apply-rust-converter-primer-to-iron-railings.jpg</v>
       </c>
     </row>
-    <row r="15" xml:space="preserve">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="str">
+    <row r="23" xml:space="preserve">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="str">
         <v>how-to-clean-and-unstick-a-rusted-padlock-mechanism</v>
       </c>
-      <c r="C15" t="str">
+      <c r="C23" t="str">
         <v>How to Clean and Unstick a Rusted Padlock Mechanism</v>
       </c>
-      <c r="D15" t="str">
+      <c r="D23" t="str">
         <v>How to</v>
       </c>
-      <c r="E15" t="str">
+      <c r="E23" t="str">
         <v>September 27, 2026</v>
       </c>
-      <c r="F15" t="str">
+      <c r="F23" t="str">
         <v>7 min read</v>
       </c>
-      <c r="G15" t="str">
+      <c r="G23" t="str">
         <v>Padlock stuck, key won't turn, or shackle won't open? Here's how to safely free up a rusted lock using WD-40, graphite, and gentle manipulation.</v>
       </c>
-      <c r="H15" t="str" xml:space="preserve">
+      <c r="H23" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
   &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
   &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To clean and unstick a rusted padlock, spray penetrating oil (WD-40 or Zorrik 88) into the keyhole and shackle joints, let it soak for 10–15 minutes, gently work the key back and forth without forcing it, then once loosened, follow up with dry graphite powder for long-term smooth operation, since wet oil alone attracts airborne dust over time.&lt;/p&gt;
@@ -2396,33 +3986,33 @@
   &lt;li&gt;&lt;a href="/blog/how-to-remove-deep-rust-from-metal-window-grills-before-paint"&gt;How to Remove Deep Rust From Metal Window Grills Before Paint&lt;/a&gt;&lt;/li&gt;
 &lt;/ul&gt;</v>
       </c>
-      <c r="I15" t="str">
+      <c r="I23" t="str">
         <v>https://abuaziyfhgmzeiqjtcas.supabase.co/storage/v1/object/public/blog-images/how-to-clean-and-unstick-a-rusted-padlock-mechanism.jpg</v>
       </c>
     </row>
-    <row r="16" xml:space="preserve">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="str">
+    <row r="24" xml:space="preserve">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="str">
         <v>how-to-repair-a-broken-weld-on-a-metal-lawn-chair</v>
       </c>
-      <c r="C16" t="str">
+      <c r="C24" t="str">
         <v>How to Repair a Broken Weld on a Metal Lawn Chair</v>
       </c>
-      <c r="D16" t="str">
+      <c r="D24" t="str">
         <v>How to</v>
       </c>
-      <c r="E16" t="str">
+      <c r="E24" t="str">
         <v>September 27, 2026</v>
       </c>
-      <c r="F16" t="str">
+      <c r="F24" t="str">
         <v>7 min read</v>
       </c>
-      <c r="G16" t="str">
+      <c r="G24" t="str">
         <v>Metal lawn or garden chair weld snapped? Here's how to re-weld or reinforce it using a budget welder or no-weld epoxy alternative.</v>
       </c>
-      <c r="H16" t="str" xml:space="preserve">
+      <c r="H24" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
   &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
   &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To repair a broken weld on a metal lawn chair, clean both broken surfaces to bare metal, realign the pieces precisely using clamps, then either re-weld the joint with an inverter welder for a permanent structural fix, or apply a structural metal epoxy as a no-weld alternative for lighter-duty seating repairs, before sanding smooth and repainting.&lt;/p&gt;
@@ -2513,33 +4103,33 @@
   &lt;li&gt;&lt;a href="/blog/how-to-remove-deep-rust-from-metal-window-grills-before-paint"&gt;How to Remove Deep Rust From Metal Window Grills Before Paint&lt;/a&gt;&lt;/li&gt;
 &lt;/ul&gt;</v>
       </c>
-      <c r="I16" t="str">
+      <c r="I24" t="str">
         <v>https://abuaziyfhgmzeiqjtcas.supabase.co/storage/v1/object/public/blog-images/how-to-repair-a-broken-weld-on-a-metal-lawn-chair.jpg</v>
       </c>
     </row>
-    <row r="17" xml:space="preserve">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="str">
+    <row r="25" xml:space="preserve">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="str">
         <v>how-to-reinforce-a-rusted-metal-pipe-structure-without-welding</v>
       </c>
-      <c r="C17" t="str">
+      <c r="C25" t="str">
         <v>How to Reinforce a Rusted Metal Pipe Structure Without Welding</v>
       </c>
-      <c r="D17" t="str">
+      <c r="D25" t="str">
         <v>How to</v>
       </c>
-      <c r="E17" t="str">
+      <c r="E25" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F17" t="str">
+      <c r="F25" t="str">
         <v>8 min read</v>
       </c>
-      <c r="G17" t="str">
+      <c r="G25" t="str">
         <v>Rusted metal pipe railing or structure weakened but no welder handy? Here's how to reinforce it using clamps, epoxy, and sleeve techniques.</v>
       </c>
-      <c r="H17" t="str" xml:space="preserve">
+      <c r="H25" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
   &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
   &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To reinforce a rusted metal pipe structure without welding, clean the rusted section to bare metal, wrap it with a fiberglass repair wrap or steel repair clamp/sleeve designed for pipe reinforcement, secure it firmly, and finish with epoxy putty and rust-proof paint — a genuine structural alternative when welding equipment or skill isn't available.&lt;/p&gt;
@@ -2637,33 +4227,33 @@
   &lt;li&gt;&lt;a href="/blog/how-to-remove-deep-rust-from-metal-window-grills-before-paint"&gt;How to Remove Deep Rust From Metal Window Grills Before Paint&lt;/a&gt;&lt;/li&gt;
 &lt;/ul&gt;</v>
       </c>
-      <c r="I17" t="str">
+      <c r="I25" t="str">
         <v>/images/blogs/how-to-reinforce-a-rusted-metal-pipe-structure-without-welding.jpg</v>
       </c>
     </row>
-    <row r="18" xml:space="preserve">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="str">
+    <row r="26" xml:space="preserve">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="str">
         <v>how-to-fix-a-sticking-metal-sliding-gate-wheel-track</v>
       </c>
-      <c r="C18" t="str">
+      <c r="C26" t="str">
         <v>How to Fix a Sticking Metal Sliding Gate Wheel Track</v>
       </c>
-      <c r="D18" t="str">
+      <c r="D26" t="str">
         <v>How to</v>
       </c>
-      <c r="E18" t="str">
+      <c r="E26" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F18" t="str">
+      <c r="F26" t="str">
         <v>8 min read</v>
       </c>
-      <c r="G18" t="str">
+      <c r="G26" t="str">
         <v>Sliding gate jamming or hard to push? Here's how to clean, realign, and lubricate the wheel and track system for smooth movement again.</v>
       </c>
-      <c r="H18" t="str" xml:space="preserve">
+      <c r="H26" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
   &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
   &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To fix a sticking sliding gate wheel track, clear debris and rust buildup from the ground track channel, check if the gate's wheels are misaligned or worn flat, realign the track if it's shifted out of level, and apply grease or lubricant to both the wheel bearings and track surface for smooth, effortless sliding.&lt;/p&gt;
@@ -2761,33 +4351,33 @@
   &lt;li&gt;&lt;a href="/blog/how-to-fix-an-extension-cord-reel-that-wont-retract"&gt;How to Fix an Extension Cord Reel That Won't Retract&lt;/a&gt;&lt;/li&gt;
 &lt;/ul&gt;</v>
       </c>
-      <c r="I18" t="str">
+      <c r="I26" t="str">
         <v>/images/blogs/how-to-fix-a-sticking-metal-sliding-gate-wheel-track.jpg</v>
       </c>
     </row>
-    <row r="19" xml:space="preserve">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="str">
+    <row r="27" xml:space="preserve">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="str">
         <v>how-to-remove-deep-rust-from-metal-window-grills-before-paint</v>
       </c>
-      <c r="C19" t="str">
+      <c r="C27" t="str">
         <v>How to Remove Deep Rust From Metal Window Grills Before Paint</v>
       </c>
-      <c r="D19" t="str">
+      <c r="D27" t="str">
         <v>How to</v>
       </c>
-      <c r="E19" t="str">
+      <c r="E27" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F19" t="str">
+      <c r="F27" t="str">
         <v>8 min read</v>
       </c>
-      <c r="G19" t="str">
+      <c r="G27" t="str">
         <v>Heavily rusted window grills before painting? Here's the wire brush, rust converter, and sanding process for a clean, paint-ready metal surface.</v>
       </c>
-      <c r="H19" t="str" xml:space="preserve">
+      <c r="H27" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
   &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
   &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To remove deep rust from metal window grills before painting, scrub thoroughly with a wire brush (handheld or drill-attachment) down to bare metal, apply a rust converter solution to any remaining stubborn or pitted rust, sand smooth, then wipe clean with mineral spirits before priming — never paint directly over unremoved rust, since it will bleed through and continue spreading underneath.&lt;/p&gt;
@@ -2886,33 +4476,33 @@
   &lt;li&gt;&lt;a href="/blog/how-to-reset-a-frequently-tripping-home-mcb-circuit-breaker"&gt;How to Reset a Frequently Tripping Home MCB Circuit Breaker&lt;/a&gt;&lt;/li&gt;
 &lt;/ul&gt;</v>
       </c>
-      <c r="I19" t="str">
+      <c r="I27" t="str">
         <v>/images/blogs/how-to-remove-deep-rust-from-metal-window-grills-before-paint.jpg</v>
       </c>
     </row>
-    <row r="20" xml:space="preserve">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" t="str">
+    <row r="28" xml:space="preserve">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="str">
         <v>how-to-weld-a-broken-gate-hinge-using-a-budget-inverter-welder</v>
       </c>
-      <c r="C20" t="str">
+      <c r="C28" t="str">
         <v>How to Weld a Broken Gate Hinge Using a Budget Inverter Welder</v>
       </c>
-      <c r="D20" t="str">
+      <c r="D28" t="str">
         <v>How to</v>
       </c>
-      <c r="E20" t="str">
+      <c r="E28" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F20" t="str">
+      <c r="F28" t="str">
         <v>8 min read</v>
       </c>
-      <c r="G20" t="str">
+      <c r="G28" t="str">
         <v>Iron gate hinge cracked or snapped? Here's how to weld it back together using an affordable inverter welder — safely and with a strong, lasting bond.</v>
       </c>
-      <c r="H20" t="str" xml:space="preserve">
+      <c r="H28" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
   &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
   &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To weld a broken iron gate hinge, clean the break thoroughly to bare metal, set your inverter welder to the correct amperage for your rod thickness and metal gauge, strike the arc, run a steady bead along the joint using a slight weaving motion, let it cool naturally, then chip off the slag and inspect the weld for full penetration before repainting.&lt;/p&gt;
@@ -3019,33 +4609,33 @@
   &lt;li&gt;&lt;a href="/blog/how-to-wire-a-new-3-pin-plug-securely-for-appliances"&gt;How to Wire a New 3-Pin Plug Securely for Appliances&lt;/a&gt;&lt;/li&gt;
 &lt;/ul&gt;</v>
       </c>
-      <c r="I20" t="str">
+      <c r="I28" t="str">
         <v>/images/blogs/how-to-weld-a-broken-gate-hinge-using-a-budget-inverter-welder.jpg</v>
       </c>
     </row>
-    <row r="21" xml:space="preserve">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="str">
+    <row r="29" xml:space="preserve">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="str">
         <v>how-to-reset-a-frequently-tripping-home-mcb-circuit-breaker</v>
       </c>
-      <c r="C21" t="str">
+      <c r="C29" t="str">
         <v>How to Reset a Frequently Tripping Home MCB Circuit Breaker</v>
       </c>
-      <c r="D21" t="str">
+      <c r="D29" t="str">
         <v>How to</v>
       </c>
-      <c r="E21" t="str">
+      <c r="E29" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F21" t="str">
+      <c r="F29" t="str">
         <v>8 min read</v>
       </c>
-      <c r="G21" t="str">
+      <c r="G29" t="str">
         <v>MCB tripping repeatedly at home? Learn how to safely reset it and diagnose whether it's overload, a short circuit, or a faulty breaker.</v>
       </c>
-      <c r="H21" t="str" xml:space="preserve">
+      <c r="H29" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
   &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
   &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To reset a frequently tripping MCB, first unplug or switch off all appliances on that circuit, flip the tripped breaker fully to OFF then back to ON, then reconnect appliances one at a time to identify which one is causing an overload; if the MCB trips instantly even with everything disconnected, this points to a short circuit in the wiring itself and needs an electrician's assessment.&lt;/p&gt;
@@ -3137,33 +4727,33 @@
   &lt;li&gt;&lt;a href="/blog/how-to-replace-a-cracked-wall-socket-plate-safely"&gt;How to Replace a Cracked Wall Socket Plate Safely&lt;/a&gt;&lt;/li&gt;
 &lt;/ul&gt;</v>
       </c>
-      <c r="I21" t="str">
+      <c r="I29" t="str">
         <v>/images/blogs/how-to-reset-a-frequently-tripping-home-mcb-circuit-breaker.jpg</v>
       </c>
     </row>
-    <row r="22" xml:space="preserve">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" t="str">
+    <row r="30" xml:space="preserve">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="str">
         <v>how-to-fix-an-extension-cord-reel-that-wont-retract</v>
       </c>
-      <c r="C22" t="str">
+      <c r="C30" t="str">
         <v>How to Fix an Extension Cord Reel That Won't Retract</v>
       </c>
-      <c r="D22" t="str">
+      <c r="D30" t="str">
         <v>How to</v>
       </c>
-      <c r="E22" t="str">
+      <c r="E30" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F22" t="str">
+      <c r="F30" t="str">
         <v>8 min read</v>
       </c>
-      <c r="G22" t="str">
+      <c r="G30" t="str">
         <v>Extension cord reel jammed, won't retract, or dead at the socket? Here's how to diagnose and fix the spring mechanism or internal wiring fault.</v>
       </c>
-      <c r="H22" t="str" xml:space="preserve">
+      <c r="H30" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
   &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
   &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To fix an extension cord reel that won't retract, open the reel casing to check if the internal retraction spring has slipped off its mount or lost tension, reset or re-tension it as needed; if the reel isn't powering up at all, check the internal wiring connections and the slip-ring contact where the rotating drum meets the fixed base, since this is the most common failure point in reel-type extension cords.&lt;/p&gt;
@@ -3264,33 +4854,33 @@
   &lt;li&gt;&lt;a href="/blog/how-to-replace-a-burnt-switch-in-a-modular-switchboard"&gt;How to Replace a Burnt Switch in a Modular Switchboard&lt;/a&gt;&lt;/li&gt;
 &lt;/ul&gt;</v>
       </c>
-      <c r="I22" t="str">
+      <c r="I30" t="str">
         <v>/images/blogs/how-to-fix-an-extension-cord-reel-that-wont-retract.jpg</v>
       </c>
     </row>
-    <row r="23" xml:space="preserve">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" t="str">
+    <row r="31" xml:space="preserve">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="str">
         <v>how-to-change-a-broken-tube-light-starter-or-ballast-to-led</v>
       </c>
-      <c r="C23" t="str">
+      <c r="C31" t="str">
         <v>How to Change a Broken Tube Light Starter or Ballast to LED</v>
       </c>
-      <c r="D23" t="str">
+      <c r="D31" t="str">
         <v>How to</v>
       </c>
-      <c r="E23" t="str">
+      <c r="E31" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F23" t="str">
+      <c r="F31" t="str">
         <v>8 min read</v>
       </c>
-      <c r="G23" t="str">
+      <c r="G31" t="str">
         <v>Old tube light flickering or won't start? Here's how to convert it to LED by bypassing the starter and ballast, or replacing the fixture entirely.</v>
       </c>
-      <c r="H23" t="str" xml:space="preserve">
+      <c r="H31" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
   &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
   &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To change a broken tube light starter or convert to LED, first try replacing the starter (a cheap, cylindrical component at one end of the fixture) if the tube only flickers at startup, but for a more permanent, energy-efficient fix, remove the old starter and ballast entirely, rewire the fixture to bypass them, and install a direct-wire LED tube light in the same fixture.&lt;/p&gt;
@@ -3397,33 +4987,33 @@
   &lt;li&gt;&lt;a href="/blog/how-to-change-a-faulty-ceiling-fan-regulator-at-home"&gt;How to Change a Faulty Ceiling Fan Regulator at Home&lt;/a&gt;&lt;/li&gt;
 &lt;/ul&gt;</v>
       </c>
-      <c r="I23" t="str">
+      <c r="I31" t="str">
         <v>/images/blogs/how-to-change-a-broken-tube-light-starter-or-ballast-to-led.jpg</v>
       </c>
     </row>
-    <row r="24" xml:space="preserve">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" t="str">
+    <row r="32" xml:space="preserve">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="str">
         <v>how-to-troubleshoot-a-smart-bulb-that-keeps-flickering</v>
       </c>
-      <c r="C24" t="str">
+      <c r="C32" t="str">
         <v>How to Troubleshoot a Smart Bulb That Keeps Flickering</v>
       </c>
-      <c r="D24" t="str">
+      <c r="D32" t="str">
         <v>How to</v>
       </c>
-      <c r="E24" t="str">
+      <c r="E32" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F24" t="str">
+      <c r="F32" t="str">
         <v>8 min read</v>
       </c>
-      <c r="G24" t="str">
+      <c r="G32" t="str">
         <v>Smart bulb flickering or losing WiFi connection repeatedly? Here's how to diagnose whether it's power, network, or app-related — and fix it.</v>
       </c>
-      <c r="H24" t="str" xml:space="preserve">
+      <c r="H32" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
   &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
   &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To troubleshoot a flickering smart bulb, first check if the flickering happens on a dimmer-enabled switch (smart bulbs often conflict with old-style dimmers), then verify your WiFi signal strength at the bulb's location, restart the bulb and router, and if the issue persists, factory reset the bulb and re-pair it with your smart home app.&lt;/p&gt;
@@ -3519,33 +5109,33 @@
   &lt;li&gt;&lt;a href="/blog/how-to-change-a-faulty-ceiling-fan-regulator-at-home"&gt;How to Change a Faulty Ceiling Fan Regulator at Home&lt;/a&gt;&lt;/li&gt;
 &lt;/ul&gt;</v>
       </c>
-      <c r="I24" t="str">
+      <c r="I32" t="str">
         <v>/images/blogs/how-to-troubleshoot-a-smart-bulb-that-keeps-flickering.jpg</v>
       </c>
     </row>
-    <row r="25" xml:space="preserve">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25" t="str">
+    <row r="33" xml:space="preserve">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="str">
         <v>how-to-replace-a-cracked-wall-socket-plate-safely</v>
       </c>
-      <c r="C25" t="str">
+      <c r="C33" t="str">
         <v>How to Replace a Cracked Wall Socket Plate Safely</v>
       </c>
-      <c r="D25" t="str">
+      <c r="D33" t="str">
         <v>How to</v>
       </c>
-      <c r="E25" t="str">
+      <c r="E33" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F25" t="str">
+      <c r="F33" t="str">
         <v>8 min read</v>
       </c>
-      <c r="G25" t="str">
+      <c r="G33" t="str">
         <v>Cracked or broken socket plate exposing wiring? Here's how to safely replace it in a modular switchboard without professional help.</v>
       </c>
-      <c r="H25" t="str" xml:space="preserve">
+      <c r="H33" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
   &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
   &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To replace a cracked wall socket plate, switch off the MCB for that circuit, verify power is off with a voltage tester, remove the damaged socket from the modular plate, transfer the live, neutral, and earth wires to the corresponding terminals on a matching new socket, then snap it into the plate and restore power to test.&lt;/p&gt;
@@ -3647,33 +5237,33 @@
   &lt;li&gt;&lt;a href="/blog/how-to-change-a-faulty-ceiling-fan-regulator-at-home"&gt;How to Change a Faulty Ceiling Fan Regulator at Home&lt;/a&gt;&lt;/li&gt;
 &lt;/ul&gt;</v>
       </c>
-      <c r="I25" t="str">
+      <c r="I33" t="str">
         <v>/images/blogs/how-to-replace-a-cracked-wall-socket-plate-safely.jpg</v>
       </c>
     </row>
-    <row r="26" xml:space="preserve">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="str">
+    <row r="34" xml:space="preserve">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="str">
         <v>how-to-wire-a-new-3-pin-plug-securely-for-appliances</v>
       </c>
-      <c r="C26" t="str">
+      <c r="C34" t="str">
         <v>How to Wire a New 3-Pin Plug Securely for Appliances</v>
       </c>
-      <c r="D26" t="str">
+      <c r="D34" t="str">
         <v>How to</v>
       </c>
-      <c r="E26" t="str">
+      <c r="E34" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F26" t="str">
+      <c r="F34" t="str">
         <v>8 min read</v>
       </c>
-      <c r="G26" t="str">
+      <c r="G34" t="str">
         <v>Learn to wire a 3-pin plug the correct way — live, neutral, earth — with proper terminal grip so your appliance stays safe and shock-free.</v>
       </c>
-      <c r="H26" t="str" xml:space="preserve">
+      <c r="H34" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
   &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
   &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To wire a new 3-pin plug, strip the outer cable sheath, connect the brown (live) wire to the L terminal, the blue (neutral) wire to the N terminal, and the green/yellow (earth) wire to the E terminal, ensure each wire is securely clamped under its terminal screw with no loose strands, then secure the cable grip before closing the plug casing.&lt;/p&gt;
@@ -3774,33 +5364,33 @@
   &lt;li&gt;&lt;a href="/blog/how-to-fix-a-doorbell-switch-thats-stuck-and-buzzing"&gt;How to Fix a Doorbell Switch That's Stuck and Buzzing&lt;/a&gt;&lt;/li&gt;
 &lt;/ul&gt;</v>
       </c>
-      <c r="I26" t="str">
+      <c r="I34" t="str">
         <v>/images/blogs/how-to-wire-a-new-3-pin-plug-securely-for-appliances.jpg</v>
       </c>
     </row>
-    <row r="27" xml:space="preserve">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" t="str">
+    <row r="35" xml:space="preserve">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="str">
         <v>how-to-fix-a-doorbell-switch-thats-stuck-and-buzzing</v>
       </c>
-      <c r="C27" t="str">
+      <c r="C35" t="str">
         <v>How to Fix a Doorbell Switch That's Stuck and Buzzing</v>
       </c>
-      <c r="D27" t="str">
+      <c r="D35" t="str">
         <v>How to</v>
       </c>
-      <c r="E27" t="str">
+      <c r="E35" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F27" t="str">
+      <c r="F35" t="str">
         <v>8 min read</v>
       </c>
-      <c r="G27" t="str">
+      <c r="G35" t="str">
         <v>Doorbell buzzing non-stop or button jammed in? Here's how to safely fix or replace a stuck doorbell switch without professional help.</v>
       </c>
-      <c r="H27" t="str" xml:space="preserve">
+      <c r="H35" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
   &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
   &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To fix a stuck, buzzing doorbell switch, first switch off the low-voltage supply or the MCB feeding the doorbell circuit, remove the switch cover to check if the button mechanism is physically jammed by dust or a broken spring, clean or replace the internal contact, and if the switch is beyond repair, install a matching replacement doorbell button.&lt;/p&gt;
@@ -3894,33 +5484,33 @@
   &lt;li&gt;&lt;a href="/blog/how-to-repair-loose-modular-wardrobe-handles-safely"&gt;How to Repair Loose Modular Wardrobe Handles Safely&lt;/a&gt;&lt;/li&gt;
 &lt;/ul&gt;</v>
       </c>
-      <c r="I27" t="str">
+      <c r="I35" t="str">
         <v>/images/blogs/how-to-fix-a-doorbell-switch-thats-stuck-and-buzzing.jpg</v>
       </c>
     </row>
-    <row r="28" xml:space="preserve">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" t="str">
+    <row r="36" xml:space="preserve">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="str">
         <v>how-to-change-a-faulty-ceiling-fan-regulator-at-home</v>
       </c>
-      <c r="C28" t="str">
+      <c r="C36" t="str">
         <v>How to Change a Faulty Ceiling Fan Regulator at Home</v>
       </c>
-      <c r="D28" t="str">
+      <c r="D36" t="str">
         <v>How to</v>
       </c>
-      <c r="E28" t="str">
+      <c r="E36" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F28" t="str">
+      <c r="F36" t="str">
         <v>8 min read</v>
       </c>
-      <c r="G28" t="str">
+      <c r="G36" t="str">
         <v>Fan stuck on one speed or regulator knob not working? Here's how to safely replace a step-type or electronic fan regulator yourself.</v>
       </c>
-      <c r="H28" t="str" xml:space="preserve">
+      <c r="H36" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
   &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
   &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To change a faulty ceiling fan regulator, switch off the MCB for that circuit, verify power is off with a voltage tester, remove the old regulator from its wall mounting box, note the wiring connections, connect the same wires to a matching new regulator (step-type or electronic, matching your fan's motor type), then restore power and test all speed settings.&lt;/p&gt;
@@ -4014,33 +5604,33 @@
   &lt;li&gt;&lt;a href="/blog/how-to-fix-a-sagging-wire-basket-drawer-in-a-kitchen-larder"&gt;How to Fix a Sagging Wire Basket Drawer in a Kitchen Larder&lt;/a&gt;&lt;/li&gt;
 &lt;/ul&gt;</v>
       </c>
-      <c r="I28" t="str">
+      <c r="I36" t="str">
         <v>/images/blogs/how-to-change-a-faulty-ceiling-fan-regulator-at-home.jpg</v>
       </c>
     </row>
-    <row r="29" xml:space="preserve">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" t="str">
+    <row r="37" xml:space="preserve">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="str">
         <v>how-to-replace-a-burnt-switch-in-a-modular-switchboard</v>
       </c>
-      <c r="C29" t="str">
+      <c r="C37" t="str">
         <v>How to Replace a Burnt Switch in a Modular Switchboard</v>
       </c>
-      <c r="D29" t="str">
+      <c r="D37" t="str">
         <v>How to</v>
       </c>
-      <c r="E29" t="str">
+      <c r="E37" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F29" t="str">
+      <c r="F37" t="str">
         <v>8 min read</v>
       </c>
-      <c r="G29" t="str">
+      <c r="G37" t="str">
         <v>Switch stopped working or shows burn marks? Here's how to safely replace it in a modular switchboard after switching off the MCB first.</v>
       </c>
-      <c r="H29" t="str" xml:space="preserve">
+      <c r="H37" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
   &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
   &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To replace a burnt switch in a modular switchboard, first switch off the main MCB for that circuit, verify power is off using a voltage tester, unscrew the switch plate, disconnect the wiring from the old switch terminals, connect the same wires to the new matching switch, then screw it back into the modular plate and restore power to test.&lt;/p&gt;
@@ -4142,33 +5732,33 @@
   &lt;li&gt;&lt;a href="/blog/how-to-re-attach-peeling-pvc-edge-banding-on-furniture"&gt;How to Re-Attach Peeling PVC Edge Banding on Furniture&lt;/a&gt;&lt;/li&gt;
 &lt;/ul&gt;</v>
       </c>
-      <c r="I29" t="str">
+      <c r="I37" t="str">
         <v>/images/blogs/how-to-replace-a-burnt-switch-in-a-modular-switchboard.jpg</v>
       </c>
     </row>
-    <row r="30" xml:space="preserve">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30" t="str">
+    <row r="38" xml:space="preserve">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="str">
         <v>how-to-repair-loose-modular-wardrobe-handles-safely</v>
       </c>
-      <c r="C30" t="str">
+      <c r="C38" t="str">
         <v>How to Repair Loose Modular Wardrobe Handles Safely</v>
       </c>
-      <c r="D30" t="str">
+      <c r="D38" t="str">
         <v>How to</v>
       </c>
-      <c r="E30" t="str">
+      <c r="E38" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F30" t="str">
+      <c r="F38" t="str">
         <v>7 min read</v>
       </c>
-      <c r="G30" t="str">
+      <c r="G38" t="str">
         <v>Wardrobe handle wobbly or about to fall off? Here's how to re-secure it without cracking the veneer or laminate finish around the mounting holes.</v>
       </c>
-      <c r="H30" t="str" xml:space="preserve">
+      <c r="H38" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
   &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
   &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To repair a loose modular wardrobe handle without damaging the veneer, remove the handle carefully by unscrewing from the inside, check if the mounting holes are stripped, pack them with a glue-and-toothpick fix if needed, then reinsert the screws gradually and evenly rather than fully tightening one side first, which prevents veneer cracking around the hole.&lt;/p&gt;
@@ -4266,33 +5856,33 @@
   &lt;li&gt;&lt;a href="/blog/how-to-fix-a-kitchen-drawer-front-that-fell-off-the-runner"&gt;How to Fix a Kitchen Drawer Front That Fell Off the Runner&lt;/a&gt;&lt;/li&gt;
 &lt;/ul&gt;</v>
       </c>
-      <c r="I30" t="str">
+      <c r="I38" t="str">
         <v>/images/blogs/how-to-repair-loose-modular-wardrobe-handles-safely.jpg</v>
       </c>
     </row>
-    <row r="31" xml:space="preserve">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31" t="str">
+    <row r="39" xml:space="preserve">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="str">
         <v>how-to-fix-a-sagging-wire-basket-drawer-in-a-kitchen-larder</v>
       </c>
-      <c r="C31" t="str">
+      <c r="C39" t="str">
         <v>How to Fix a Sagging Wire Basket Drawer in a Kitchen Larder</v>
       </c>
-      <c r="D31" t="str">
+      <c r="D39" t="str">
         <v>How to</v>
       </c>
-      <c r="E31" t="str">
+      <c r="E39" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F31" t="str">
+      <c r="F39" t="str">
         <v>8 min read</v>
       </c>
-      <c r="G31" t="str">
+      <c r="G39" t="str">
         <v>Wire basket pull-out sagging or scraping the shelf below? Here's how to realign the telescopic runners and reinforce a bent basket frame.</v>
       </c>
-      <c r="H31" t="str" xml:space="preserve">
+      <c r="H39" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
   &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
   &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To fix a sagging wire basket drawer in a kitchen larder, check whether the telescopic runner brackets have loosened from the cabinet side panel and retighten them, or if the wire basket frame itself has bent under overloading, gently reshape it back to level, and redistribute weight evenly across the basket to prevent recurring sag.&lt;/p&gt;
@@ -4386,33 +5976,33 @@
   &lt;li&gt;&lt;a href="/blog/how-to-adjust-loose-modular-kitchen-cabinet-hinges"&gt;How to Adjust Loose Modular Kitchen Cabinet Hinges&lt;/a&gt;&lt;/li&gt;
 &lt;/ul&gt;</v>
       </c>
-      <c r="I31" t="str">
+      <c r="I39" t="str">
         <v>/images/blogs/how-to-fix-a-sagging-wire-basket-drawer-in-a-kitchen-larder.jpg</v>
       </c>
     </row>
-    <row r="32" xml:space="preserve">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32" t="str">
+    <row r="40" xml:space="preserve">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="str">
         <v>how-to-re-attach-peeling-pvc-edge-banding-on-furniture</v>
       </c>
-      <c r="C32" t="str">
+      <c r="C40" t="str">
         <v>How to Re-Attach Peeling PVC Edge Banding on Furniture</v>
       </c>
-      <c r="D32" t="str">
+      <c r="D40" t="str">
         <v>How to</v>
       </c>
-      <c r="E32" t="str">
+      <c r="E40" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F32" t="str">
+      <c r="F40" t="str">
         <v>7 min read</v>
       </c>
-      <c r="G32" t="str">
+      <c r="G40" t="str">
         <v>PVC edge banding peeling off your modular cabinets? Here's how to re-glue it properly using a hot iron and contact adhesive for a permanent bond.</v>
       </c>
-      <c r="H32" t="str" xml:space="preserve">
+      <c r="H40" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
   &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
   &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To re-attach peeling PVC edge banding, clean off old, failed adhesive from both the banding and the panel edge, apply fresh contact adhesive or use a hot iron to reactivate the existing hot-melt glue, press firmly while the adhesive is still tacky, then trim excess overhang with a utility knife and sand the edges smooth.&lt;/p&gt;
@@ -4506,33 +6096,33 @@
   &lt;li&gt;&lt;a href="/blog/how-to-fix-a-kitchen-drawer-front-that-fell-off-the-runner"&gt;How to Fix a Kitchen Drawer Front That Fell Off the Runner&lt;/a&gt;&lt;/li&gt;
 &lt;/ul&gt;</v>
       </c>
-      <c r="I32" t="str">
+      <c r="I40" t="str">
         <v>/images/blogs/how-to-re-attach-peeling-pvc-edge-banding-on-furniture.jpg</v>
       </c>
     </row>
-    <row r="33" xml:space="preserve">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="str">
+    <row r="41" xml:space="preserve">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="str">
         <v>how-to-repair-a-deep-scratch-in-a-laminate-countertop</v>
       </c>
-      <c r="C33" t="str">
+      <c r="C41" t="str">
         <v>How to Repair a Deep Scratch in a Laminate Countertop</v>
       </c>
-      <c r="D33" t="str">
+      <c r="D41" t="str">
         <v>How to</v>
       </c>
-      <c r="E33" t="str">
+      <c r="E41" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F33" t="str">
+      <c r="F41" t="str">
         <v>8 min read</v>
       </c>
-      <c r="G33" t="str">
+      <c r="G41" t="str">
         <v>Deep gouge or scratch in your kitchen laminate counter? Here's how to fill, blend, and seal it invisibly using color-matched repair compound.</v>
       </c>
-      <c r="H33" t="str" xml:space="preserve">
+      <c r="H41" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
   &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
   &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To repair a deep scratch in a laminate countertop, clean the scratch thoroughly, fill it with a color-matched laminate repair paste or seam filler, press it in flush using a putty knife, let it cure fully, then buff and seal the surface so the repair blends with the surrounding sheen and texture.&lt;/p&gt;
@@ -4626,33 +6216,33 @@
   &lt;li&gt;&lt;a href="/blog/how-to-replace-soft-close-drawer-slides-in-a-modular-kitchen"&gt;How to Replace Soft Close Drawer Slides in a Modular Kitchen&lt;/a&gt;&lt;/li&gt;
 &lt;/ul&gt;</v>
       </c>
-      <c r="I33" t="str">
+      <c r="I41" t="str">
         <v>/images/blogs/how-to-repair-a-deep-scratch-in-a-laminate-countertop.jpg</v>
       </c>
     </row>
-    <row r="34" xml:space="preserve">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="str">
+    <row r="42" xml:space="preserve">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="str">
         <v>how-to-replace-soft-close-drawer-slides-in-a-modular-kitchen</v>
       </c>
-      <c r="C34" t="str">
+      <c r="C42" t="str">
         <v>How to Replace Soft Close Drawer Slides in a Modular Kitchen</v>
       </c>
-      <c r="D34" t="str">
+      <c r="D42" t="str">
         <v>How to</v>
       </c>
-      <c r="E34" t="str">
+      <c r="E42" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F34" t="str">
+      <c r="F42" t="str">
         <v>8 min read</v>
       </c>
-      <c r="G34" t="str">
+      <c r="G42" t="str">
         <v>Soft-close drawer slamming or not closing smoothly? Here's how to remove and replace the runner mechanism yourself, brand-matched and aligned.</v>
       </c>
-      <c r="H34" t="str" xml:space="preserve">
+      <c r="H42" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
   &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
   &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To replace soft close drawer slides, remove the drawer box from the cabinet, unscrew the old runner rails from both the cabinet side panel and the drawer box, install matching replacement slides (same brand, length, and load rating), then screw them into the same mounting positions and test the soft-close action before loading the drawer.&lt;/p&gt;
@@ -4754,33 +6344,33 @@
   &lt;li&gt;&lt;a href="/blog/how-to-repair-water-damaged-swollen-mdf-cabinet-bases"&gt;How to Repair Water Damaged Swollen MDF Cabinet Bases&lt;/a&gt;&lt;/li&gt;
 &lt;/ul&gt;</v>
       </c>
-      <c r="I34" t="str">
+      <c r="I42" t="str">
         <v>/images/blogs/how-to-replace-soft-close-drawer-slides-in-a-modular-kitchen.jpg</v>
       </c>
     </row>
-    <row r="35" xml:space="preserve">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35" t="str">
+    <row r="43" xml:space="preserve">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="str">
         <v>how-to-fix-a-kitchen-drawer-front-that-fell-off-the-runner</v>
       </c>
-      <c r="C35" t="str">
+      <c r="C43" t="str">
         <v>How to Fix a Kitchen Drawer Front That Fell Off the Runner</v>
       </c>
-      <c r="D35" t="str">
+      <c r="D43" t="str">
         <v>How to</v>
       </c>
-      <c r="E35" t="str">
+      <c r="E43" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F35" t="str">
+      <c r="F43" t="str">
         <v>7 min read</v>
       </c>
-      <c r="G35" t="str">
+      <c r="G43" t="str">
         <v>Kitchen drawer front detached or hanging loose? Here's how to re-clip it back onto the runner mechanism the right way, step by step.</v>
       </c>
-      <c r="H35" t="str" xml:space="preserve">
+      <c r="H43" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
         &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
         &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To fix a kitchen drawer front that fell off the runner, locate the plastic connector clips on the inside back of the drawer front, align them with the runner's front bracket, press firmly until you hear or feel a click, then test by pulling the drawer open and closed to confirm it's securely locked in place.&lt;/p&gt;
@@ -4871,33 +6461,33 @@
         &lt;li&gt;&lt;a href="/blog/how-to-repair-water-damaged-swollen-mdf-cabinet-bases"&gt;How to Repair Water Damaged Swollen MDF Cabinet Bases&lt;/a&gt;&lt;/li&gt;
       &lt;/ul&gt;</v>
       </c>
-      <c r="I35" t="str">
+      <c r="I43" t="str">
         <v>https://images.unsplash.com/photo-1556911220-e15b29be8c8f?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="36" xml:space="preserve">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" t="str">
+    <row r="44" xml:space="preserve">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="str">
         <v>how-to-repair-water-damaged-swollen-mdf-cabinet-bases</v>
       </c>
-      <c r="C36" t="str">
+      <c r="C44" t="str">
         <v>How to Repair Water Damaged Swollen MDF Cabinet Bases</v>
       </c>
-      <c r="D36" t="str">
+      <c r="D44" t="str">
         <v>How to</v>
       </c>
-      <c r="E36" t="str">
+      <c r="E44" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F36" t="str">
+      <c r="F44" t="str">
         <v>9 min read</v>
       </c>
-      <c r="G36" t="str">
+      <c r="G44" t="str">
         <v>Kitchen cabinet base swollen and crumbling from water exposure? Learn how to cut out, reinforce, and seal damaged MDF before it spreads further.</v>
       </c>
-      <c r="H36" t="str" xml:space="preserve">
+      <c r="H44" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
         &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
         &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To repair a water-damaged swollen MDF cabinet base, cut away the swollen, disintegrated section completely since MDF doesn't shrink back once wet, rebuild the area with a moisture-resistant plywood insert or exterior filler compound, seal all edges with a waterproof sealant, and address the actual water source before finishing the repair.&lt;/p&gt;
@@ -5027,33 +6617,33 @@
         &lt;/ul&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I36" t="str">
+      <c r="I44" t="str">
         <v>https://images.unsplash.com/photo-1584622650111-993a426fbf0a?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="37" xml:space="preserve">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" t="str">
+    <row r="45" xml:space="preserve">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="str">
         <v>how-to-fix-a-hydraulic-bed-lift-that-wont-stay-down</v>
       </c>
-      <c r="C37" t="str">
+      <c r="C45" t="str">
         <v>How to Fix a Hydraulic Bed Lift That Won't Stay Down</v>
       </c>
-      <c r="D37" t="str">
+      <c r="D45" t="str">
         <v>How to</v>
       </c>
-      <c r="E37" t="str">
+      <c r="E45" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F37" t="str">
+      <c r="F45" t="str">
         <v>9 min read</v>
       </c>
-      <c r="G37" t="str">
+      <c r="G45" t="str">
         <v>Storage bed lifting up on its own or bouncing back? Here's how to fix a faulty hydraulic gas spring mechanism without replacing the whole bed.</v>
       </c>
-      <c r="H37" t="str" xml:space="preserve">
+      <c r="H45" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
         &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
         &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To fix a hydraulic bed lift that won't stay down, first check if the gas springs are mismatched to your mattress weight (too strong for a lighter setup), then either add counterweight to the base, adjust the spring tension bracket if your model has one, or replace worn-out gas spring cylinders that have lost their internal pressure and no longer hold the bed frame securely closed.&lt;/p&gt;
@@ -5182,33 +6772,33 @@
         &lt;/ul&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I37" t="str">
+      <c r="I45" t="str">
         <v>https://images.unsplash.com/photo-1505693416388-ac5ce068fe85?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="38" xml:space="preserve">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="str">
+    <row r="46" xml:space="preserve">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="str">
         <v>how-to-adjust-loose-modular-kitchen-cabinet-hinges</v>
       </c>
-      <c r="C38" t="str">
+      <c r="C46" t="str">
         <v>How to Adjust Loose Modular Kitchen Cabinet Hinges</v>
       </c>
-      <c r="D38" t="str">
+      <c r="D46" t="str">
         <v>How to</v>
       </c>
-      <c r="E38" t="str">
+      <c r="E46" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F38" t="str">
+      <c r="F46" t="str">
         <v>7 min read</v>
       </c>
-      <c r="G38" t="str">
+      <c r="G46" t="str">
         <v>Kitchen cabinet shutter hanging crooked or won't close flush? Learn the 3-screw adjustment trick for soft-close modular hinges — no tools upgrade needed.</v>
       </c>
-      <c r="H38" t="str" xml:space="preserve">
+      <c r="H46" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
         &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
         &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To adjust loose modular kitchen cabinet hinges, locate the three adjustment screws on the hinge arm inside the cabinet — the depth screw (front-to-back), side screw (left-right), and height screw (up-down) — and turn each in small quarter-turns, testing the shutter after every adjustment until it sits flush and level.&lt;/p&gt;
@@ -5326,33 +6916,33 @@
         &lt;/ul&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I38" t="str">
+      <c r="I46" t="str">
         <v>https://images.unsplash.com/photo-1556909212-d5b604d0c90d?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="39" xml:space="preserve">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="str">
+    <row r="47" xml:space="preserve">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="str">
         <v>how-to-square-up-a-warped-cabinet-door-that-wont-close</v>
       </c>
-      <c r="C39" t="str">
+      <c r="C47" t="str">
         <v>How to Square Up a Warped Cabinet Door That Won't Close</v>
       </c>
-      <c r="D39" t="str">
+      <c r="D47" t="str">
         <v>How to</v>
       </c>
-      <c r="E39" t="str">
+      <c r="E47" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F39" t="str">
+      <c r="F47" t="str">
         <v>9 min read</v>
       </c>
-      <c r="G39" t="str">
+      <c r="G47" t="str">
         <v>Cabinet door bowing out and won't sit flush? Learn how to straighten a warped panel using clamps, moisture correction, and hinge realignment.</v>
       </c>
-      <c r="H39" t="str" xml:space="preserve">
+      <c r="H47" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
         &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
         &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To square up a warped cabinet door, first identify whether the warp is in the panel itself or the hinge alignment, then correct genuine wood warping by applying moisture to the concave side and clamping it flat while it dries, or fix hinge-related misalignment by adjusting the mounting screws so the door sits square in its frame opening.&lt;/p&gt;
@@ -5481,33 +7071,33 @@
         &lt;/ul&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I39" t="str">
+      <c r="I47" t="str">
         <v>https://images.unsplash.com/photo-1556911220-e15b29be8c8f?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="40" xml:space="preserve">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="str">
+    <row r="48" xml:space="preserve">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="str">
         <v>how-to-fix-a-loose-wooden-railing-or-baluster-on-stairs</v>
       </c>
-      <c r="C40" t="str">
+      <c r="C48" t="str">
         <v>How to Fix a Loose Wooden Railing or Baluster on Stairs</v>
       </c>
-      <c r="D40" t="str">
+      <c r="D48" t="str">
         <v>How to</v>
       </c>
-      <c r="E40" t="str">
+      <c r="E48" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F40" t="str">
+      <c r="F48" t="str">
         <v>8 min read</v>
       </c>
-      <c r="G40" t="str">
+      <c r="G48" t="str">
         <v>Wobbly stair railing or baluster? Here's how to re-secure it permanently using wood glue, screws, and dowel reinforcement — a genuine safety fix.</v>
       </c>
-      <c r="H40" t="str" xml:space="preserve">
+      <c r="H48" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
         &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
         &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To fix a loose wooden stair railing or baluster, identify whether the wobble is at the base, the handrail connection, or a stripped screw, then remove and reset the loose joint with fresh wood glue, reinforce with longer screws or a dowel pin, and clamp firmly until the glue cures fully before allowing weight on it again.&lt;/p&gt;
@@ -5629,33 +7219,33 @@
         &lt;/ul&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I40" t="str">
+      <c r="I48" t="str">
         <v>https://images.unsplash.com/photo-1600585154340-be6161a56a0c?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="41" xml:space="preserve">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="str">
+    <row r="49" xml:space="preserve">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="str">
         <v>how-to-adjust-a-hydraulic-screen-door-closers-tension</v>
       </c>
-      <c r="C41" t="str">
+      <c r="C49" t="str">
         <v>How to Adjust a Hydraulic Screen Door Closer's Tension</v>
       </c>
-      <c r="D41" t="str">
+      <c r="D49" t="str">
         <v>How to</v>
       </c>
-      <c r="E41" t="str">
+      <c r="E49" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F41" t="str">
+      <c r="F49" t="str">
         <v>7 min read</v>
       </c>
-      <c r="G41" t="str">
+      <c r="G49" t="str">
         <v>Screen door slamming shut or closing too slowly? Learn how to adjust the hydraulic closer's speed and tension screws the right way.</v>
       </c>
-      <c r="H41" t="str" xml:space="preserve">
+      <c r="H49" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
         &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
         &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To adjust the tension on a hydraulic screen door closer, locate the small adjustment screw on the end of the cylinder body, then turn it clockwise in small increments to slow the closing speed (preventing slamming), or counterclockwise to speed it up if the door is closing too slowly or not latching at all.&lt;/p&gt;
@@ -5769,33 +7359,33 @@
         &lt;/ul&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I41" t="str">
+      <c r="I49" t="str">
         <v>https://images.unsplash.com/photo-1534349762230-e0cadf78f5da?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="42" xml:space="preserve">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="str">
+    <row r="50" xml:space="preserve">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="str">
         <v>how-to-install-weather-stripping-on-a-leaky-door-frame</v>
       </c>
-      <c r="C42" t="str">
+      <c r="C50" t="str">
         <v>How to Install Weather Stripping on a Leaky Door Frame</v>
       </c>
-      <c r="D42" t="str">
+      <c r="D50" t="str">
         <v>How to</v>
       </c>
-      <c r="E42" t="str">
+      <c r="E50" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F42" t="str">
+      <c r="F50" t="str">
         <v>8 min read</v>
       </c>
-      <c r="G42" t="str">
+      <c r="G50" t="str">
         <v>Stop rain, dust, and drafts sneaking under your exterior door. Here's how to fit door sweeps and frame weather stripping the right way.</v>
       </c>
-      <c r="H42" t="str" xml:space="preserve">
+      <c r="H50" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
         &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
         &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To install weather stripping on a leaky exterior door, clean the door frame edges thoroughly, measure and cut adhesive foam or rubber weather strip to match each side of the frame, press it firmly along the door stop so it compresses slightly when closed, and fit a separate door sweep along the bottom edge to seal the floor gap.&lt;/p&gt;
@@ -5916,33 +7506,33 @@
         &lt;/ul&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I42" t="str">
+      <c r="I50" t="str">
         <v>https://images.unsplash.com/photo-1588854337236-6889d631faa8?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="43" xml:space="preserve">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="str">
+    <row r="51" xml:space="preserve">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="str">
         <v>how-to-repair-a-cracked-wooden-chair-leg-securely</v>
       </c>
-      <c r="C43" t="str">
+      <c r="C51" t="str">
         <v>How to Repair a Cracked Wooden Chair Leg Securely</v>
       </c>
-      <c r="D43" t="str">
+      <c r="D51" t="str">
         <v>How to</v>
       </c>
-      <c r="E43" t="str">
+      <c r="E51" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F43" t="str">
+      <c r="F51" t="str">
         <v>9 min read</v>
       </c>
-      <c r="G43" t="str">
+      <c r="G51" t="str">
         <v>Wobbly or cracked chair leg? Here's how to reinforce it permanently using wood glue, clamps, and dowel pins — stronger than the original joint.</v>
       </c>
-      <c r="H43" t="str" xml:space="preserve">
+      <c r="H51" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
         &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
         &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To repair a cracked wooden chair leg, clean out the crack thoroughly, inject wood glue (Fevicol) deep into the split, clamp it tightly for at least 24 hours to cure, then reinforce the repair with a dowel pin drilled through the crack for extra strength, or a metal L-bracket for legs bearing heavy weight.&lt;/p&gt;
@@ -6072,33 +7662,33 @@
         &lt;/ul&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I43" t="str">
+      <c r="I51" t="str">
         <v>https://images.unsplash.com/photo-1503602642458-232111445657?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="44" xml:space="preserve">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="str">
+    <row r="52" xml:space="preserve">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="str">
         <v>how-to-fix-a-wooden-drawer-that-sticks-and-wont-slide</v>
       </c>
-      <c r="C44" t="str">
+      <c r="C52" t="str">
         <v>How to Fix a Wooden Drawer That Sticks and Won't Slide</v>
       </c>
-      <c r="D44" t="str">
+      <c r="D52" t="str">
         <v>How to</v>
       </c>
-      <c r="E44" t="str">
+      <c r="E52" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F44" t="str">
+      <c r="F52" t="str">
         <v>7 min read</v>
       </c>
-      <c r="G44" t="str">
+      <c r="G52" t="str">
         <v>Wooden drawer jamming halfway every time? Learn the candle wax, alignment, and sanding fixes carpenters use to make it glide smoothly again.</v>
       </c>
-      <c r="H44" t="str" xml:space="preserve">
+      <c r="H52" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
         &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
         &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To fix a wooden drawer that sticks, first check if the drawer box has swollen from humidity by inspecting for rubbing marks on the sides, sand down the rubbing points lightly if swollen, then rub candle wax along the wooden runners on both the drawer and cabinet frame for smooth, long-lasting glide without staining the wood.&lt;/p&gt;
@@ -6215,33 +7805,33 @@
         &lt;/ul&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I44" t="str">
+      <c r="I52" t="str">
         <v>https://images.unsplash.com/photo-1538688525198-9b88f6f53126?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="45" xml:space="preserve">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="str">
+    <row r="53" xml:space="preserve">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="str">
         <v>how-to-trim-a-wooden-door-bottom-without-removing-it</v>
       </c>
-      <c r="C45" t="str">
+      <c r="C53" t="str">
         <v>How to Trim a Wooden Door Bottom Without Removing It</v>
       </c>
-      <c r="D45" t="str">
+      <c r="D53" t="str">
         <v>How to</v>
       </c>
-      <c r="E45" t="str">
+      <c r="E53" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F45" t="str">
+      <c r="F53" t="str">
         <v>8 min read</v>
       </c>
-      <c r="G45" t="str">
+      <c r="G53" t="str">
         <v>Door dragging on new flooring or a rug? Here's how to shave down the bottom of a wooden door in place — no need to unhinge or remove it.</v>
       </c>
-      <c r="H45" t="str" xml:space="preserve">
+      <c r="H53" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
         &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
         &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To trim the bottom of a wooden door without removing it, mark the excess wood using a pencil and a flat spacer resting on the floor, protect the surrounding area with masking tape, then use a hand plane or power planer to shave down the marked line in thin, even passes while the door stays on its hinges, working in small increments and checking fit frequently.&lt;/p&gt;
@@ -6359,33 +7949,33 @@
         &lt;/ul&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I45" t="str">
+      <c r="I53" t="str">
         <v>https://images.unsplash.com/photo-1540555700478-4be289fbecef?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="46" xml:space="preserve">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="str">
+    <row r="54" xml:space="preserve">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="str">
         <v>how-to-replace-a-broken-window-latch-aluminum-frame</v>
       </c>
-      <c r="C46" t="str">
+      <c r="C54" t="str">
         <v>How to Replace a Broken Window Latch (Aluminum Frame)</v>
       </c>
-      <c r="D46" t="str">
+      <c r="D54" t="str">
         <v>How to</v>
       </c>
-      <c r="E46" t="str">
+      <c r="E54" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F46" t="str">
+      <c r="F54" t="str">
         <v>7 min read</v>
       </c>
-      <c r="G46" t="str">
+      <c r="G54" t="str">
         <v>Aluminum window latch snapped or won't lock? Here's the step-by-step fix for replacing it without damaging your window frame or glass.</v>
       </c>
-      <c r="H46" t="str" xml:space="preserve">
+      <c r="H54" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
         &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
         &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To replace a broken window latch on an aluminum frame, remove the old latch's mounting screws, detach it from the frame, buy a matching replacement latch (same brand/size — take the old one to the store), then screw the new latch into the same mounting holes, using fresh pilot holes with plastic wall plugs if the aluminum has stripped out.&lt;/p&gt;
@@ -6497,33 +8087,33 @@
         &lt;/ul&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I46" t="str">
+      <c r="I54" t="str">
         <v>https://images.unsplash.com/photo-1513694203232-719a280e022f?q=80&amp;w=2069&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="47" xml:space="preserve">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="str">
+    <row r="55" xml:space="preserve">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="str">
         <v>how-to-adjust-sliding-wardrobe-doors-coming-off-track</v>
       </c>
-      <c r="C47" t="str">
+      <c r="C55" t="str">
         <v>How to Adjust Sliding Wardrobe Doors Coming Off Track</v>
       </c>
-      <c r="D47" t="str">
+      <c r="D55" t="str">
         <v>How to</v>
       </c>
-      <c r="E47" t="str">
+      <c r="E55" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F47" t="str">
+      <c r="F55" t="str">
         <v>9 min read</v>
       </c>
-      <c r="G47" t="str">
+      <c r="G55" t="str">
         <v>Sliding wardrobe door keeps jumping off its track? Learn the roller adjustment and track cleaning fix that stops it derailing for good.</v>
       </c>
-      <c r="H47" t="str" xml:space="preserve">
+      <c r="H55" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
         &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
         &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To fix a sliding wardrobe door coming off track, first clean the top and bottom tracks of dust and debris, then adjust the roller height screws on the door's top bracket so the door sits centered and level in the channel, and finally check the bottom guide pin or floor guide is correctly seated to stop the door swinging outward.&lt;/p&gt;
@@ -6648,33 +8238,33 @@
         &lt;/ul&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I47" t="str">
+      <c r="I55" t="str">
         <v>https://images.unsplash.com/photo-1558997519-83ea9252def8?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="48" xml:space="preserve">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="str">
+    <row r="56" xml:space="preserve">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="str">
         <v>how-to-silence-a-squeaky-wooden-floorboard-from-above</v>
       </c>
-      <c r="C48" t="str">
+      <c r="C56" t="str">
         <v>How to Silence a Squeaky Wooden Floorboard From Above</v>
       </c>
-      <c r="D48" t="str">
+      <c r="D56" t="str">
         <v>How to</v>
       </c>
-      <c r="E48" t="str">
+      <c r="E56" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F48" t="str">
+      <c r="F56" t="str">
         <v>8 min read</v>
       </c>
-      <c r="G48" t="str">
+      <c r="G56" t="str">
         <v>Stop that creaking wooden floor without lifting a single plank. Learn the talcum powder, screw, and shim tricks that fix squeaks from the top side.</v>
       </c>
-      <c r="H48" t="str" xml:space="preserve">
+      <c r="H56" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
         &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
         &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To silence a squeaky wooden floorboard from above, first locate the exact squeaking spot by walking slowly across it, then either sprinkle talcum powder or graphite powder into the gap to reduce friction, or drive a trim-head screw through the board into the joist below at an angle, punching the screw head slightly below the surface and filling the hole to hide it.&lt;/p&gt;
@@ -6794,33 +8384,33 @@
         &lt;/ul&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I48" t="str">
+      <c r="I56" t="str">
         <v>https://images.unsplash.com/photo-1581858726788-75bc0f6a952d?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="49" xml:space="preserve">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="str">
+    <row r="57" xml:space="preserve">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="str">
         <v>how-to-fix-a-hollow-core-door-with-a-hole-in-it</v>
       </c>
-      <c r="C49" t="str">
+      <c r="C57" t="str">
         <v>How to Fix a Hollow Core Door With a Hole In It (DIY)</v>
       </c>
-      <c r="D49" t="str">
+      <c r="D57" t="str">
         <v>How to</v>
       </c>
-      <c r="E49" t="str">
+      <c r="E57" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F49" t="str">
+      <c r="F57" t="str">
         <v>9 min read</v>
       </c>
-      <c r="G49" t="str">
+      <c r="G57" t="str">
         <v>Punched or kicked a hole in your hollow core door? Here's how to patch it invisibly using expanding foam, mesh, and filler — no replacement needed.</v>
       </c>
-      <c r="H49" t="str" xml:space="preserve">
+      <c r="H57" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
         &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
         &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To fix a hole in a hollow core door, cut back the damaged area to a clean edge, fill the hollow cavity with expanding foam or crumpled newspaper backing, bridge the hole with a fiberglass mesh patch or cardboard, then cover with wood filler, sand smooth, and repaint or repolish to blend seamlessly with the surrounding door.&lt;/p&gt;
@@ -6945,33 +8535,33 @@
         &lt;/ul&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I49" t="str">
+      <c r="I57" t="str">
         <v>/images/blog/hollow-door-hero.jpg</v>
       </c>
     </row>
-    <row r="50" xml:space="preserve">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
+    <row r="58" xml:space="preserve">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="str">
         <v>how-to-repair-a-stripped-wood-screw-hole-in-a-hinge</v>
       </c>
-      <c r="C50" t="str">
+      <c r="C58" t="str">
         <v>How to Repair a Stripped Wood Screw Hole in a Hinge</v>
       </c>
-      <c r="D50" t="str">
+      <c r="D58" t="str">
         <v>How to</v>
       </c>
-      <c r="E50" t="str">
+      <c r="E58" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F50" t="str">
+      <c r="F58" t="str">
         <v>7 min read</v>
       </c>
-      <c r="G50" t="str">
+      <c r="G58" t="str">
         <v>Screw spinning loose in your door hinge hole? Here's the exact toothpick, dowel, and epoxy fix carpenters use to make it grip again — permanently.</v>
       </c>
-      <c r="H50" t="str" xml:space="preserve">
+      <c r="H58" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
         &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
         &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To repair a stripped screw hole in a door hinge, remove the loose screw, pack the enlarged hole with glue-coated wooden toothpicks or a matchstick dowel, let the Fevicol cure for 30-45 minutes, then re-drive the original screw into the now-solid wood. For badly worn holes, an Araldite-and-sawdust paste gives a permanently stronger grip.&lt;/p&gt;
@@ -7085,33 +8675,33 @@
         &lt;/ul&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I50" t="str">
+      <c r="I58" t="str">
         <v>/images/blog/stripped-screw-hero.jpg</v>
       </c>
     </row>
-    <row r="51" xml:space="preserve">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
+    <row r="59" xml:space="preserve">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="str">
         <v>how-to-fix-a-door-that-wont-latch-because-it-sags</v>
       </c>
-      <c r="C51" t="str">
+      <c r="C59" t="str">
         <v>How to Fix a Door That Won't Latch Because It Sags</v>
       </c>
-      <c r="D51" t="str">
+      <c r="D59" t="str">
         <v>How to</v>
       </c>
-      <c r="E51" t="str">
+      <c r="E59" t="str">
         <v>September 26, 2026</v>
       </c>
-      <c r="F51" t="str">
+      <c r="F59" t="str">
         <v>8 min read</v>
       </c>
-      <c r="G51" t="str">
+      <c r="G59" t="str">
         <v>A sagging door not latching? Learn the exact hinge-shim trick Indian carpenters use to realign it in under 30 minutes — no new door needed.</v>
       </c>
-      <c r="H51" t="str" xml:space="preserve">
+      <c r="H59" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;div style="background: rgba(37, 99, 235, 0.08); border-left: 4px solid var(--primary, #2563eb); padding: 1.25rem 1.5rem; border-radius: 8px; margin: 1.5rem 0 2rem 0;"&gt;
         &lt;p style="font-weight: 700; font-size: 1.05rem; margin: 0 0 0.5rem 0; color: var(--primary, #2563eb);"&gt;⚡ Quick Takeaway (Position-0 Summary)&lt;/p&gt;
         &lt;p style="margin: 0; line-height: 1.7; font-size: 1rem;"&gt;To fix a sagging door that won't latch, you need to realign the strike plate or shim the top hinge so the latch bolt meets the strike plate hole again. In most Indian homes this happens because the door has dropped slightly on its hinges over time, throwing off the alignment by just a few millimeters — a cardboard or matchbox shim behind the top hinge usually solves it without removing the door.&lt;/p&gt;
@@ -7232,33 +8822,33 @@
         &lt;/ul&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I51" t="str">
+      <c r="I59" t="str">
         <v>/images/blog/door-sag-hero.jpg</v>
       </c>
     </row>
-    <row r="52" xml:space="preserve">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
+    <row r="60" xml:space="preserve">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="str">
         <v>how-to-get-rid-of-pigeons-balcony-nets-spikes-diy-guide</v>
       </c>
-      <c r="C52" t="str">
+      <c r="C60" t="str">
         <v>How to Get Rid of Pigeons Spoiling Your House &amp; Balcony (Spikes, Nets, Invisible Grills &amp; Safe DIY Solutions)</v>
       </c>
-      <c r="D52" t="str">
+      <c r="D60" t="str">
         <v>Pest Control</v>
       </c>
-      <c r="E52" t="str">
+      <c r="E60" t="str">
         <v>July 08, 2026</v>
       </c>
-      <c r="F52" t="str">
+      <c r="F60" t="str">
         <v>16 min read</v>
       </c>
-      <c r="G52" t="str">
+      <c r="G60" t="str">
         <v>Tired of pigeons ruining your balcony, AC units, and windows with toxic droppings? Discover the most effective pigeon spikes, heavy-duty bird netting, invisible stainless steel grills, safe guano sanitization protocols, and proven humane DIY repellents.</v>
       </c>
-      <c r="H52" t="str" xml:space="preserve">
+      <c r="H60" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;If you live in a high-rise apartment or independent house in any metropolitan city like Bangalore, Mumbai, Delhi-NCR, or Hyderabad, you are almost certainly fighting an ongoing war against urban rock pigeons (&lt;em&gt;Columba livia&lt;/em&gt;). You scrub and mop your balcony on Sunday morning, only to find the floor, parapet wall, laundry drying rack, and AC outdoor condenser encrusted with fresh, foul-smelling white-and-green droppings by Tuesday afternoon.&lt;/p&gt;
       &lt;p&gt;Beyond the frustrating mess and ruined morning coffee, pigeon infestation poses severe architectural, financial, and respiratory health hazards. Pigeon droppings (scientifically termed &lt;strong&gt;guano&lt;/strong&gt;) are highly acidic, harboring pathogenic fungi and microscopic mites that trigger severe lung diseases. Moreover, once pigeons establish your balcony ledge as their nocturnal roosting or nesting habitat, subtle clapping or hanging old CDs will do nothing to stop their instinctual homing behavior.&lt;/p&gt;
       &lt;p&gt;To permanently reclaim your outdoor living space, you need an engineered, multi-layered physical exclusion strategy. In this definitive guide, our Senior Avian Control &amp;amp; Balcony Safety Specialist, &lt;strong&gt;Kamal Yadav&lt;/strong&gt;, breaks down the exact barrier systems—from heavy-duty UV-stabilized bird nets and 304-grade anti-roosting spikes to sleek invisible stainless steel safety grills and safe biological DIY repellents—to permanently keep pigeons away from your home without harming the birds.&lt;/p&gt;
@@ -7408,33 +8998,33 @@
         &lt;p&gt;Very minimal. Made from 316 marine-grade stainless steel cables coated in UV nylon, they do not rust. Wiping them down with a damp microfiber cloth once every 6 months to remove environmental pollution dust keeps them looking brand new for 15+ years.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I52" t="str">
+      <c r="I60" t="str">
         <v>https://images.unsplash.com/photo-1548767797-d8c844163c4c?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="53" xml:space="preserve">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
+    <row r="61" xml:space="preserve">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="str">
         <v>why-painted-walls-bubble-peel-root-causes-and-fix</v>
       </c>
-      <c r="C53" t="str">
+      <c r="C61" t="str">
         <v>Why Your Freshly Painted Wall is Bubbling and Peeling (5 Root Causes &amp; How to Fix It)</v>
       </c>
-      <c r="D53" t="str">
+      <c r="D61" t="str">
         <v>Painting</v>
       </c>
-      <c r="E53" t="str">
+      <c r="E61" t="str">
         <v>July 05, 2026</v>
       </c>
-      <c r="F53" t="str">
+      <c r="F61" t="str">
         <v>14 min read</v>
       </c>
-      <c r="G53" t="str">
+      <c r="G61" t="str">
         <v>Spent thousands on repainting only to see blisters, bubbles, and peeling sheets? Discover the 5 root causes of paint failure and the permanent 6-step repair protocol.</v>
       </c>
-      <c r="H53" t="str" xml:space="preserve">
+      <c r="H61" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;Few home improvement experiences are as demoralizing as spending ₹40,000 to ₹80,000 repainting your apartment with premium paints, only to notice unsightly blisters, ballooning bubbles, and large rubbery sheets of paint peeling off your living room or bedroom walls just three to six months later. When you confront the contractor, they often shrug and blame "weather humidity" or "wall quality," offering to slap another coat of paint over the damaged area—a shortcut that guarantees the exact same paint failure within 90 days.&lt;/p&gt;
       &lt;p&gt;Paint does not bubble or peel without a distinct chemical, physical, or mechanical trigger. Modern acrylic and &lt;a href="/blog/asian-paints-royale-vs-berger-silk-luxury-paint-comparison-guide"&gt;luxury emulsion paints&lt;/a&gt; form tough, flexible polymer films. When those films lift, detach, or balloon away from masonry, it indicates an &lt;strong&gt;interfacial bond failure&lt;/strong&gt; between the paint layer, the underlying wall putty, and the cement plaster substrate.&lt;/p&gt;
       &lt;p&gt;Whether you are dealing with water-filled blisters near your bathroom, flaking paint scales above your baseboards, or peeling sheets across your ceiling, this definitive guide breaks down the &lt;strong&gt;5 scientific root causes of paint bubbling and peeling&lt;/strong&gt; in Indian homes and provides a step-by-step master protocol to permanently repair the damage.&lt;/p&gt;
@@ -7615,33 +9205,33 @@
       &lt;p&gt;For more detailed technical guides, explore our manuals on &lt;a href="/blog/how-to-choose-primer-vs-putty-when-to-skip-guide"&gt;when to use primer vs putty&lt;/a&gt;, &lt;a href="/blog/how-to-calculate-paint-coverage-litres-needed-guide"&gt;the paint coverage calculator formula&lt;/a&gt;, &lt;a href="/blog/asian-paints-royale-vs-berger-silk-luxury-paint-comparison-guide"&gt;Asian Paints Royale vs Berger Silk&lt;/a&gt;, and &lt;a href="/blog/how-to-waterproof-paint-balcony-exterior-walls-monsoon-guide"&gt;monsoon exterior wall waterproofing&lt;/a&gt;.&lt;/p&gt;
       &lt;p&gt;For certified, professional damp wall repairs, laser moisture diagnostics, chemical DPC waterproofing, and seamless luxury repainting across Bangalore, book through &lt;a href="/services/painting"&gt;Carpenterwala Painting Services&lt;/a&gt; and &lt;a href="/services/carpentry"&gt;Carpenterwala Carpentry Services&lt;/a&gt; serving &lt;a href="/services/painting/koramangala"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/painting/indiranagar"&gt;Indiranagar&lt;/a&gt;, &lt;a href="/services/painting/whitefield"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/painting/hsr-layout"&gt;HSR Layout&lt;/a&gt;, and &lt;a href="/services/painting/thanisandra"&gt;Thanisandra&lt;/a&gt;.&lt;/p&gt;</v>
       </c>
-      <c r="I53" t="str">
+      <c r="I61" t="str">
         <v>https://images.unsplash.com/photo-1562259949-e8e7689d7828?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="54" xml:space="preserve">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
+    <row r="62" xml:space="preserve">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="str">
         <v>asian-paints-royale-vs-berger-silk-luxury-paint-comparison-guide</v>
       </c>
-      <c r="C54" t="str">
+      <c r="C62" t="str">
         <v>Asian Paints Royale vs. Berger Silk: Which Luxury Interior Paint Lasts Longer? (Complete Comparison Guide)</v>
       </c>
-      <c r="D54" t="str">
+      <c r="D62" t="str">
         <v>Painting</v>
       </c>
-      <c r="E54" t="str">
+      <c r="E62" t="str">
         <v>July 04, 2026</v>
       </c>
-      <c r="F54" t="str">
+      <c r="F62" t="str">
         <v>15 min read</v>
       </c>
-      <c r="G54" t="str">
+      <c r="G62" t="str">
         <v>Choosing between Asian Paints Royale and Berger Silk? Compare Teflon surface protection, scrub resistance, sheen levels, per-liter pricing, and 10-year durability.</v>
       </c>
-      <c r="H54" t="str" xml:space="preserve">
+      <c r="H62" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;When renovating or furnishing a home in India, choosing the right luxury interior paint comes down to two undisputed market giants: &lt;strong&gt;Asian Paints Royale&lt;/strong&gt; and &lt;strong&gt;Berger Silk&lt;/strong&gt;. Both flagship brands promise ultra-smooth finishes, rich color depth, superior washability against stubborn turmeric and crayon stains, and 8 to 10 years of showroom-like durability. But with Asian Paints commanding a premium price and Berger claiming superior silk sheen and anti-pollution tech, which luxury paint actually delivers better long-term performance in real Indian households?&lt;/p&gt;
       &lt;p&gt;Interior paint durability is not just about aesthetic shine on day one. It is determined by four critical chemical and physical factors: &lt;strong&gt;cross-linked polymer binder quality&lt;/strong&gt;, &lt;strong&gt;scrub cycle endurance (ASTM D2486)&lt;/strong&gt;, &lt;strong&gt;stain-repellent surface additives (Teflon vs. Micro-Silica)&lt;/strong&gt;, and &lt;strong&gt;resistance to high-humidity mold and yellowing&lt;/strong&gt;. If you choose the wrong variant for high-traffic corridors or kids' rooms, even a ₹600/liter luxury paint can lose its sheen or develop burnish marks after a few wet wipes.&lt;/p&gt;
       &lt;p&gt;In this comprehensive brand manual, we put &lt;strong&gt;Asian Paints Royale (Luxury, Matt, Glitz, Shyne)&lt;/strong&gt; head-to-head against &lt;strong&gt;Berger Silk (Glamor, Breathe Easy, Luxury Emulsion)&lt;/strong&gt; across real-world testing parameters, cost per square foot, washability, application protocols, and lifespan.&lt;/p&gt;
@@ -7841,33 +9431,33 @@
       &lt;p&gt;Explore our companion home painting guides on &lt;a href="/blog/how-to-choose-primer-vs-putty-when-to-skip-guide"&gt;when to use primer vs putty&lt;/a&gt;, the &lt;a href="/blog/how-to-calculate-paint-coverage-litres-needed-guide"&gt;paint coverage calculator (litres needed formula)&lt;/a&gt;, and &lt;a href="/blog/how-to-waterproof-paint-balcony-exterior-walls-monsoon-guide"&gt;monsoon exterior wall waterproofing&lt;/a&gt;.&lt;/p&gt;
       &lt;p&gt;For verified luxury painting crews, computerized shade sampling, automated laser square footage billing, and 100% genuine factory-sealed paint buckets across Bangalore, book through &lt;a href="/services/painting"&gt;Carpenterwala Painting Services&lt;/a&gt; and &lt;a href="/services/carpentry"&gt;Carpenterwala Carpentry Services&lt;/a&gt; serving &lt;a href="/services/painting/koramangala"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/painting/indiranagar"&gt;Indiranagar&lt;/a&gt;, &lt;a href="/services/painting/whitefield"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/painting/hsr-layout"&gt;HSR Layout&lt;/a&gt;, and &lt;a href="/services/painting/thanisandra"&gt;Thanisandra&lt;/a&gt;.&lt;/p&gt;</v>
       </c>
-      <c r="I54" t="str">
+      <c r="I62" t="str">
         <v>https://images.unsplash.com/photo-1589939705384-5185137a7f0f?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="55" xml:space="preserve">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
+    <row r="63" xml:space="preserve">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="str">
         <v>how-to-waterproof-paint-balcony-exterior-walls-monsoon-guide</v>
       </c>
-      <c r="C55" t="str">
+      <c r="C63" t="str">
         <v>Balcony &amp; Exterior Wall Protection: Heavy Monsoon Painting Guide (Elastomeric Coating)</v>
       </c>
-      <c r="D55" t="str">
+      <c r="D63" t="str">
         <v>Painting</v>
       </c>
-      <c r="E55" t="str">
+      <c r="E63" t="str">
         <v>July 03, 2026</v>
       </c>
-      <c r="F55" t="str">
+      <c r="F63" t="str">
         <v>14 min read</v>
       </c>
-      <c r="G55" t="str">
+      <c r="G63" t="str">
         <v>Chalky exterior walls and damp balcony plaster? Learn how to apply crack-bridging elastomeric waterproof coatings, seal parapets, and survive heavy Indian monsoons.</v>
       </c>
-      <c r="H55" t="str" xml:space="preserve">
+      <c r="H63" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;Your exterior building facade paint looks faded, chalky, and blotchy within just 24 months of application. Meanwhile, your balcony walls develop spiderweb cracks, peeling paint scales, and dark damp patches after every single torrential monsoon downpour. You have tried touching up the walls with standard exterior emulsion paint, but by July, water breaches the paint film once again, causing indoor ceiling seepage and bubbling plaster inside your adjacent bedrooms.&lt;/p&gt;
       &lt;p&gt;Standard interior paints—and even basic builder-grade exterior acrylic emulsions—are fundamentally incapable of surviving the extreme physical forces of the Indian monsoon. Exterior walls endure severe &lt;strong&gt;thermal shock cycles&lt;/strong&gt; (baking under 38°C summer heat followed by sudden cold torrential cloudbursts), intense &lt;strong&gt;ultraviolet (UV) resin breakdown&lt;/strong&gt;, and horizontal &lt;strong&gt;wind-driven rain pressure&lt;/strong&gt; that forces water through microscopic hairline fissures.&lt;/p&gt;
       &lt;p&gt;To truly weatherproof your balcony and exterior facades, you need a high-build &lt;strong&gt;elastomeric waterproof coating system&lt;/strong&gt;. Unlike rigid conventional paints, elastomeric coatings possess up to &lt;strong&gt;200% to 300% elongation elasticity&lt;/strong&gt;, expanding and contracting across shifting masonry cracks like a continuous rubberized shield. Here is your definitive engineering and DIY guide to prepping, repairing, priming, and applying elastomeric waterproof coatings that keep your balconies dry and vibrant for 7 to 10+ years.&lt;/p&gt;
@@ -8068,33 +9658,33 @@
       &lt;p&gt;Explore our companion exterior maintenance and painting guides on &lt;a href="/blog/how-to-paint-rusted-window-grills-iron-gates-anti-rust-guide"&gt;painting rusted window safety grills and gates&lt;/a&gt;, &lt;a href="/blog/how-to-choose-primer-vs-putty-when-to-skip-guide"&gt;when to use primer vs putty&lt;/a&gt;, the &lt;a href="/blog/how-to-calculate-paint-coverage-litres-needed-guide"&gt;paint coverage calculator formula&lt;/a&gt;, and &lt;a href="/blog/how-to-fix-ceiling-seepage-patches-stains-leak"&gt;repairing ceiling seepage stains&lt;/a&gt;.&lt;/p&gt;
       &lt;p&gt;For certified, professional exterior facade waterproofing, boom-lift high-rise painting, laser moisture diagnostics, and 10-year waterproofing warranties across Bangalore, book through &lt;a href="/services/painting"&gt;Carpenterwala Painting Services&lt;/a&gt; and &lt;a href="/services/carpentry"&gt;Carpenterwala Carpentry Services&lt;/a&gt; serving &lt;a href="/services/painting/koramangala"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/painting/indiranagar"&gt;Indiranagar&lt;/a&gt;, &lt;a href="/services/painting/whitefield"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/painting/hsr-layout"&gt;HSR Layout&lt;/a&gt;, and &lt;a href="/services/painting/thanisandra"&gt;Thanisandra&lt;/a&gt;.&lt;/p&gt;</v>
       </c>
-      <c r="I55" t="str">
+      <c r="I63" t="str">
         <v>https://images.unsplash.com/photo-1590381105924-c72589b9ef3f?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="56" xml:space="preserve">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
+    <row r="64" xml:space="preserve">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="str">
         <v>how-to-paint-rusted-window-grills-iron-gates-anti-rust-guide</v>
       </c>
-      <c r="C56" t="str">
+      <c r="C64" t="str">
         <v>Painting Rusted Window Grills &amp; Iron Gates: Anti-Rust Guide (Red Oxide &amp; Enamel)</v>
       </c>
-      <c r="D56" t="str">
+      <c r="D64" t="str">
         <v>Painting</v>
       </c>
-      <c r="E56" t="str">
+      <c r="E64" t="str">
         <v>July 02, 2026</v>
       </c>
-      <c r="F56" t="str">
+      <c r="F64" t="str">
         <v>14 min read</v>
       </c>
-      <c r="G56" t="str">
+      <c r="G64" t="str">
         <v>Flaking paint and orange rust bleeding through window grills or main gates? Learn how to wire-brush, apply red oxide zinc chromate primer, and spray high-gloss enamel.</v>
       </c>
-      <c r="H56" t="str" xml:space="preserve">
+      <c r="H64" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;That unsightly reddish-orange rust bleeding through the black enamel on your bedroom window safety grills. The heavy wrought-iron main entrance gate whose bottom frame is flaking off in brittle paint scales, revealing deeply pitted, crumbling steel underneath. In Indian homes, rusted metalwork is often treated as a minor aesthetic nuisance and addressed with a hasty "touch-up coat" of black paint directly over the corroded bars.&lt;/p&gt;
       &lt;p&gt;Painting directly over active iron oxide (rust) is completely futile. Rust is an electrochemical cancer: iron reacting with atmospheric oxygen and moisture to form hydrated iron(III) oxide. Trapped beneath a fresh film of paint, rust continues to spread aggressively, hollowing out mild steel (MS) square tubes, weakening welded joints, and causing security bars to shear off under hand pressure within 2 to 3 monsoon cycles.&lt;/p&gt;
       &lt;p&gt;Proper metal restoration demands an uncompromising, systematic approach: &lt;strong&gt;100% mechanical de-scaling&lt;/strong&gt; down to bare white metal, &lt;strong&gt;chemical rust conversion of microscopic pits&lt;/strong&gt;, &lt;strong&gt;sacrificial zinc-chromate / red oxide barrier priming&lt;/strong&gt;, and &lt;strong&gt;UV-resistant high-gloss synthetic enamel topcoats&lt;/strong&gt;. Here is the complete DIY and professional guide to saving your window grills, balcony railings, and main gates from corrosion.&lt;/p&gt;
@@ -8289,33 +9879,33 @@
       &lt;p&gt;Explore our companion surface preparation and painting guides on &lt;a href="/blog/how-to-choose-primer-vs-putty-when-to-skip-guide"&gt;when to use primer vs putty&lt;/a&gt;, the &lt;a href="/blog/how-to-calculate-paint-coverage-litres-needed-guide"&gt;paint coverage calculator formula&lt;/a&gt;, &lt;a href="/blog/how-to-estimate-interior-painting-cost-distemper-emulsion-royale"&gt;interior painting cost breakdowns&lt;/a&gt;, and &lt;a href="/blog/how-to-repaint-wooden-furniture-deco-pu-paint"&gt;repainting wooden furniture with PU Deco paint&lt;/a&gt;.&lt;/p&gt;
       &lt;p&gt;For certified, professional metal fabrication repairs, high-pressure sandblasting, airless spray painting, and anti-corrosion treatments across Bangalore, connect with verified experts on &lt;a href="/services/painting"&gt;Carpenterwala Painting Services&lt;/a&gt; and &lt;a href="/services/carpentry"&gt;Carpenterwala Carpentry Services&lt;/a&gt; serving &lt;a href="/services/painting/koramangala"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/painting/indiranagar"&gt;Indiranagar&lt;/a&gt;, &lt;a href="/services/painting/whitefield"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/painting/hsr-layout"&gt;HSR Layout&lt;/a&gt;, and &lt;a href="/services/painting/thanisandra"&gt;Thanisandra&lt;/a&gt;.&lt;/p&gt;</v>
       </c>
-      <c r="I56" t="str">
+      <c r="I64" t="str">
         <v>https://images.unsplash.com/photo-1513694203232-719a280e022f?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="57" xml:space="preserve">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
+    <row r="65" xml:space="preserve">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="str">
         <v>how-to-choose-primer-vs-putty-when-to-skip-guide</v>
       </c>
-      <c r="C57" t="str">
+      <c r="C65" t="str">
         <v>Primer vs. Putty: When Can You Skip Them (And When You Absolutely Can’t)? (Complete Guide)</v>
       </c>
-      <c r="D57" t="str">
+      <c r="D65" t="str">
         <v>Painting</v>
       </c>
-      <c r="E57" t="str">
+      <c r="E65" t="str">
         <v>July 01, 2026</v>
       </c>
-      <c r="F57" t="str">
+      <c r="F65" t="str">
         <v>14 min read</v>
       </c>
-      <c r="G57" t="str">
+      <c r="G65" t="str">
         <v>Contractor pushing expensive putty and specialized primer? Learn what putty and primer actually do, when you can safely skip them, and when skipping ruins your paint.</v>
       </c>
-      <c r="H57" t="str" xml:space="preserve">
+      <c r="H65" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;Your local painting contractor insists that your 5-year-old flat requires two full coats of wall putty and two coats of premium primer before applying paint. Meanwhile, your neighbor mentions they skipped putty entirely during their Diwali repainting and their walls look perfectly smooth. To add to the confusion, another painter quotes an expensive "alkali-resistant primer" that costs double standard primer, leaving you wondering if it is a genuine technical requirement or just an aggressive contractor upsell.&lt;/p&gt;
       &lt;p&gt;&lt;strong&gt;Wall putty&lt;/strong&gt; and &lt;strong&gt;primer&lt;/strong&gt; are the two most frequently misunderstood—and most frequently skipped—surface preparation steps in Indian home painting. Skipping or misapplying them is the number one reason why expensive ₹600/liter topcoat paints fail within 12 months (bubbling, flaking, chalking, and patchy discoloration) instead of lasting their intended 7 to 10-year lifespan.&lt;/p&gt;
       &lt;p&gt;Putty and primer serve completely different chemical and physical functions: &lt;strong&gt;putty is a physical filler&lt;/strong&gt; designed for structural flatness and smoothness, while &lt;strong&gt;primer is a chemical bonding sealer&lt;/strong&gt; designed for paint adhesion, porosity control, and barrier protection against plaster alkalinity and moisture. Here is your definitive, no-nonsense homeowner guide to determining exactly when you can safely skip putty or primer to save money, and when skipping them is a guaranteed recipe for paint failure.&lt;/p&gt;
@@ -8530,33 +10120,33 @@
       &lt;p&gt;To accurately plan your painting budget and material requirements, check our companion guides on &lt;a href="/blog/how-to-estimate-interior-painting-cost-distemper-emulsion-royale"&gt;interior painting cost per sq. ft. breakdowns&lt;/a&gt; and the &lt;a href="/blog/how-to-calculate-paint-coverage-litres-needed-guide"&gt;paint coverage calculator (litres needed formula)&lt;/a&gt;. If your walls have underlying water damage, read our guides on &lt;a href="/blog/how-to-fix-ground-dampness-capillary-action-walls"&gt;ground dampness capillary action&lt;/a&gt;, &lt;a href="/blog/how-to-fix-bathroom-wall-efflorescence-salt-formation"&gt;bathroom wall efflorescence&lt;/a&gt;, and &lt;a href="/blog/how-to-fix-ceiling-seepage-patches-stains-leak"&gt;ceiling seepage stain repairs&lt;/a&gt;.&lt;/p&gt;
       &lt;p&gt;For guaranteed showroom finishes, laser-level surface preparation, certified alkali-resistant primers, and verified master painters across Bangalore, book through &lt;a href="/services/painting"&gt;Carpenterwala Painting Services&lt;/a&gt; and &lt;a href="/services/carpentry"&gt;Carpenterwala Carpentry Services&lt;/a&gt; serving &lt;a href="/services/painting/koramangala"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/painting/indiranagar"&gt;Indiranagar&lt;/a&gt;, &lt;a href="/services/painting/whitefield"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/painting/hsr-layout"&gt;HSR Layout&lt;/a&gt;, and &lt;a href="/services/painting/thanisandra"&gt;Thanisandra&lt;/a&gt;.&lt;/p&gt;</v>
       </c>
-      <c r="I57" t="str">
+      <c r="I65" t="str">
         <v>https://images.unsplash.com/photo-1595428774223-ef52624120d2?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="58" xml:space="preserve">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
+    <row r="66" xml:space="preserve">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="str">
         <v>how-to-calculate-paint-coverage-litres-needed-guide</v>
       </c>
-      <c r="C58" t="str">
+      <c r="C66" t="str">
         <v>Paint Coverage Calculator: How Many Litres of Paint Do You Actually Need? (Formula &amp; Guide)</v>
       </c>
-      <c r="D58" t="str">
+      <c r="D66" t="str">
         <v>Painting</v>
       </c>
-      <c r="E58" t="str">
+      <c r="E66" t="str">
         <v>June 30, 2026</v>
       </c>
-      <c r="F58" t="str">
+      <c r="F66" t="str">
         <v>14 min read</v>
       </c>
-      <c r="G58" t="str">
+      <c r="G66" t="str">
         <v>Standing in the paint shop wondering "kitne litre chahiye"? Learn the exact formula to calculate paint litres for walls and ceilings with zero wastage or shortages.</v>
       </c>
-      <c r="H58" t="str" xml:space="preserve">
+      <c r="H66" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;You are standing at the counter of your neighborhood paint shop in Bangalore, looking at walls of colorful shade cards, and the dealer asks the standard question: &lt;em&gt;"Sir, kitne litre chahiye?"&lt;/em&gt; (How many litres do you need?). You hesitate. Buy too little, and you are forced to make an emergency second trip mid-project—only to discover that the newly mixed paint from a different manufacturing batch has a subtle shade variation that leaves an obvious patch on your living room wall. Buy too much, and you have expensive ₹3,500 10-litre plastic buckets sitting half-used in your balcony storeroom for the next five years until the paint dries into solid rubber.&lt;/p&gt;
       &lt;p&gt;Calculating the exact quantity of paint you need for any room or entire apartment is not guesswork—it is a straightforward mathematical formula based on &lt;strong&gt;net paintable surface area&lt;/strong&gt;, &lt;strong&gt;paint chemical tier coverage rates&lt;/strong&gt;, and &lt;strong&gt;application coat multipliers&lt;/strong&gt;. Once you understand how to subtract door/window openings and factor in wall porosity, you can walk into any paint store with total confidence, buy the exact tin sizes you need, and verify your contractor's material requisition down to the last liter.&lt;/p&gt;
       &lt;p&gt;Whether you are calculating paint for a single bedroom accent wall or estimating the full material requirement for a 2BHK or 3BHK flat, this practical guide walks you through the step-by-step mathematical formulas, brand-wise coverage benchmarks, and real-world calculation examples.&lt;/p&gt;
@@ -8810,33 +10400,33 @@
       &lt;p&gt;Pair this coverage guide with our comprehensive &lt;a href="/blog/how-to-estimate-interior-painting-cost-distemper-emulsion-royale"&gt;interior painting cost guide (Distemper vs. Emulsion vs. Royale per sq. ft. breakdown)&lt;/a&gt;. If your walls have underlying moisture or surface defects before you start painting, consult our guides on &lt;a href="/blog/how-to-fix-ground-dampness-capillary-action-walls"&gt;treating ground dampness&lt;/a&gt;, &lt;a href="/blog/how-to-fix-bathroom-wall-efflorescence-salt-formation"&gt;fixing wall efflorescence&lt;/a&gt;, &lt;a href="/blog/how-to-repaint-wooden-furniture-deco-pu-paint"&gt;repainting wooden furniture with PU Deco paint&lt;/a&gt;, and &lt;a href="/blog/how-to-chalk-paint-old-furniture-vintage-distressed-look"&gt;upcycling vintage furniture with chalk paint&lt;/a&gt;.&lt;/p&gt;
       &lt;p&gt;For certified, professional home painting with digital laser measurements, transparent material billing, automated site masking, and verified post-job cleanup across Bangalore, connect with trusted pros on &lt;a href="/services/painting"&gt;Carpenterwala Painting Services&lt;/a&gt; and &lt;a href="/services/carpentry"&gt;Carpenterwala Carpentry Services&lt;/a&gt; serving &lt;a href="/services/painting/koramangala"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/painting/indiranagar"&gt;Indiranagar&lt;/a&gt;, &lt;a href="/services/painting/whitefield"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/painting/hsr-layout"&gt;HSR Layout&lt;/a&gt;, and &lt;a href="/services/painting/thanisandra"&gt;Thanisandra&lt;/a&gt;.&lt;/p&gt;</v>
       </c>
-      <c r="I58" t="str">
+      <c r="I66" t="str">
         <v>https://images.unsplash.com/photo-1562259949-e8e7689d7828?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="59" xml:space="preserve">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="str">
+    <row r="67" xml:space="preserve">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="str">
         <v>how-to-estimate-interior-painting-cost-distemper-emulsion-royale</v>
       </c>
-      <c r="C59" t="str">
+      <c r="C67" t="str">
         <v>Interior Painting Cost Guide: Distemper vs. Plastic Emulsion vs. Royale (Per Sq. Ft. Breakdown)</v>
       </c>
-      <c r="D59" t="str">
+      <c r="D67" t="str">
         <v>Painting</v>
       </c>
-      <c r="E59" t="str">
+      <c r="E67" t="str">
         <v>June 29, 2026</v>
       </c>
-      <c r="F59" t="str">
+      <c r="F67" t="str">
         <v>14 min read</v>
       </c>
-      <c r="G59" t="str">
+      <c r="G67" t="str">
         <v>Confused by wildly varying painter quotes? Learn how to calculate accurate interior painting costs per sq. ft. across Distemper, Plastic Emulsion, and Luxury Royale finishes.</v>
       </c>
-      <c r="H59" t="str" xml:space="preserve">
+      <c r="H67" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;You have collected quotes from three different local painting contractors to repaint your 2BHK or 3BHK flat in Bangalore, and the numbers are completely baffling: Contractor A quotes &lt;strong&gt;₹14 per sq. ft.&lt;/strong&gt;, Contractor B demands &lt;strong&gt;₹32 per sq. ft.&lt;/strong&gt;, and Contractor C submits an estimate of &lt;strong&gt;₹58 per sq. ft.&lt;/strong&gt; for what ostensibly sounds like the exact same four-room apartment. How can two painters looking at the same living room differ by over 300% on price?&lt;/p&gt;
       &lt;p&gt;Interior painting pricing in India is notoriously opaque. Estimates depend heavily on four moving targets: &lt;strong&gt;paint chemical tier&lt;/strong&gt; (chalky distemper vs. washable plastic emulsion vs. luxury Teflon-coated Royale), &lt;strong&gt;number of applied coats&lt;/strong&gt;, &lt;strong&gt;wall condition &amp;amp; base preparation&lt;/strong&gt; (putty leveling vs. patch priming), and &lt;strong&gt;labor billing models&lt;/strong&gt; (turnkey material+labor vs. daily wages). When contractors fail to itemize these variables, homeowners often end up comparing apples to oranges—or worse, signing an alluringly cheap quote only to face massive surprise bills for "extra coats" and "essential putty work" halfway through the job.&lt;/p&gt;
       &lt;p&gt;Whether you are repainting a rental flat, refreshing your family home before Diwali, or moving into a newly handed-over builder apartment, this definitive guide breaks down the real mathematics of interior painting in India so you can estimate your budget with pinpoint accuracy, verify contractor quotes, and protect yourself against contractor shortcuts.&lt;/p&gt;
@@ -9073,33 +10663,33 @@
       &lt;p&gt;Explore our companion home renovation guides on &lt;a href="/blog/how-to-fix-ground-dampness-capillary-action-walls"&gt;fixing ground dampness and capillary seepage&lt;/a&gt;, &lt;a href="/blog/how-to-fix-bathroom-wall-efflorescence-salt-formation"&gt;treating wall salt efflorescence&lt;/a&gt;, &lt;a href="/blog/how-to-repaint-wooden-furniture-deco-pu-paint"&gt;repainting wooden furniture with PU Deco paint&lt;/a&gt;, and &lt;a href="/blog/how-to-chalk-paint-old-furniture-vintage-distressed-look"&gt;chalk painting old vintage furniture&lt;/a&gt;.&lt;/p&gt;
       &lt;p&gt;For verified, background-checked painters, transparent laser-measured square footage billing, automated material tracking, and dedicated site supervision across Bangalore, book through &lt;a href="/services/painting"&gt;Carpenterwala Painting Services&lt;/a&gt; and &lt;a href="/services/carpentry"&gt;Carpenterwala Carpentry Services&lt;/a&gt; serving &lt;a href="/services/painting/koramangala"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/painting/indiranagar"&gt;Indiranagar&lt;/a&gt;, &lt;a href="/services/painting/whitefield"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/painting/hsr-layout"&gt;HSR Layout&lt;/a&gt;, and &lt;a href="/services/painting/thanisandra"&gt;Thanisandra&lt;/a&gt;.&lt;/p&gt;</v>
       </c>
-      <c r="I59" t="str">
+      <c r="I67" t="str">
         <v>https://images.unsplash.com/photo-1589939705384-5185137a7f0f?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="60" xml:space="preserve">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="str">
+    <row r="68" xml:space="preserve">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="str">
         <v>how-to-chalk-paint-old-furniture-vintage-distressed-look</v>
       </c>
-      <c r="C60" t="str">
+      <c r="C68" t="str">
         <v>Chalk Painting Old Furniture: How to Upcycle Vintage Tables &amp; Chairs (Matte &amp; Distressed Guide)</v>
       </c>
-      <c r="D60" t="str">
+      <c r="D68" t="str">
         <v>Painting</v>
       </c>
-      <c r="E60" t="str">
+      <c r="E68" t="str">
         <v>June 28, 2026</v>
       </c>
-      <c r="F60" t="str">
+      <c r="F68" t="str">
         <v>13 min read</v>
       </c>
-      <c r="G60" t="str">
+      <c r="G68" t="str">
         <v>Tired old wooden chair or study table? Learn how to chalk paint, create authentic distressed vintage edges, and seal with clear furniture wax with zero heavy sanding.</v>
       </c>
-      <c r="H60" t="str" xml:space="preserve">
+      <c r="H68" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;That heavy, wobbly Sheesham wood chair from your grandparents' ancestral home, the solid study desk that survived three siblings' board exams, or the dark-polished bedside table sitting neglected in your storeroom. Structurally, the wood is sound and heavy—crafted decades ago from solid timber that puts modern flimsy flatpack furniture to shame. But cosmetically, the dated orange-brown spirit polish and surface scratches make it clash with your contemporary home aesthetic.&lt;/p&gt;
       &lt;p&gt;Enter &lt;strong&gt;chalk paint upcycling&lt;/strong&gt;—the DIY furniture revolution that has taken Indian home decor enthusiasts by storm. Unlike traditional enamel or &lt;a href="/blog/how-to-repaint-wooden-furniture-deco-pu-paint"&gt;PU Deco paint&lt;/a&gt;, which demands days of grueling orbital sanding down to raw timber and toxic chemical solvent primers, chalk paint is specifically formulated to adhere stubbornly to almost any surface—varnished, lacquered, polished, or laminated—with virtually &lt;strong&gt;zero heavy sanding or chemical priming&lt;/strong&gt;.&lt;/p&gt;
       &lt;p&gt;With its ultra-matte, velvety texture, forgiving brushability, and natural aptitude for vintage French-country or rustic farmhouse distressing, chalk painting lets you transform a dated ₹500 thrift-store find into an Instagram-worthy ₹15,000 designer accent piece in a single afternoon. Here is the complete step-by-step master guide to prepping, painting, distressing, and sealing your furniture with protective wax.&lt;/p&gt;
@@ -9283,33 +10873,33 @@
       &lt;p&gt;Explore our companion home upcycling and woodworking guides on &lt;a href="/blog/how-to-repaint-wooden-furniture-deco-pu-paint"&gt;repainting wooden furniture with PU Deco paint&lt;/a&gt;, &lt;a href="/blog/how-to-refurbish-teak-wood-sanding-repolishing-doors-tables"&gt;refurbishing and repolishing solid teak wood&lt;/a&gt;, &lt;a href="/blog/how-to-fix-ceiling-seepage-patches-stains-leak"&gt;repairing ceiling seepage stains&lt;/a&gt;, and &lt;a href="/blog/how-to-fix-bathroom-wall-efflorescence-salt-formation"&gt;treating wall efflorescence&lt;/a&gt;.&lt;/p&gt;
       &lt;p&gt;For custom handcrafted cabinetry, wooden furniture structural repairs, antique chair joinery restoration, or professional spray painting across Bangalore, connect with verified experts on &lt;a href="/services/painting"&gt;Carpenterwala Painting Services&lt;/a&gt; and &lt;a href="/services/carpentry"&gt;Carpenterwala Carpentry Services&lt;/a&gt; serving &lt;a href="/services/painting/koramangala"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/painting/indiranagar"&gt;Indiranagar&lt;/a&gt;, &lt;a href="/services/painting/whitefield"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/painting/hsr-layout"&gt;HSR Layout&lt;/a&gt;, and &lt;a href="/services/painting/thanisandra"&gt;Thanisandra&lt;/a&gt;.&lt;/p&gt;</v>
       </c>
-      <c r="I60" t="str">
+      <c r="I68" t="str">
         <v>https://images.unsplash.com/photo-1586023492125-27b2c045efd7?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="61" xml:space="preserve">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="str">
+    <row r="69" xml:space="preserve">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="str">
         <v>how-to-repaint-wooden-furniture-deco-pu-paint</v>
       </c>
-      <c r="C61" t="str">
+      <c r="C69" t="str">
         <v>Repainting Wooden Furniture with Deco Paint: How to Transform Old Tables &amp; Cupboards (PU Finish Guide)</v>
       </c>
-      <c r="D61" t="str">
+      <c r="D69" t="str">
         <v>Painting</v>
       </c>
-      <c r="E61" t="str">
+      <c r="E69" t="str">
         <v>June 27, 2026</v>
       </c>
-      <c r="F61" t="str">
+      <c r="F69" t="str">
         <v>13 min read</v>
       </c>
-      <c r="G61" t="str">
+      <c r="G69" t="str">
         <v>Dated wood-tone furniture? Learn how to sand, prime, and spray-paint old wooden cupboards and tables with boutique-grade solid color Deco and PU finishes.</v>
       </c>
-      <c r="H61" t="str" xml:space="preserve">
+      <c r="H69" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;That heavy solid-wood wardrobe, vintage side-table, or 6-seater dining set sitting in the corner of your home. It was built with sturdy seasoned timber, but its dark, dated reddish-brown varnish clashes with your modern Scandinavian, minimalist, or contemporary pastel interiors. Instead of discarding high-grade, heirloom-quality solid wood in favor of flimsy particleboard furniture, a solid-color &lt;strong&gt;Deco or Polyurethane (PU) paint makeover&lt;/strong&gt; can completely transform it into a luxury boutique statement piece for a fraction of the cost of new furniture.&lt;/p&gt;
       &lt;p&gt;In India, "Deco paint" (traditionally &lt;em&gt;Duco&lt;/em&gt; nitrocellulose automotive lacquer or modern two-pack PU enamel) creates a smooth, glass-like opaque shell that hides mismatched timber grains while providing rock-hard resistance against daily scratches, spills, and moisture. The difference between a cheap, streaky DIY paint job and a factory-smooth, showroom finish comes down to two non-negotiable fundamentals: &lt;strong&gt;proper surface de-glazing with progressive sanding&lt;/strong&gt; and &lt;strong&gt;high-adhesion stain-blocking wood primer&lt;/strong&gt;.&lt;/p&gt;
       &lt;p&gt;Whether you're transforming an inherited teak wardrobe, updating rental flat furniture, or flipping a secondhand study desk, this step-by-step master guide walks you through prepping, priming, spray-painting, and hardware upgrades for lasting beauty.&lt;/p&gt;
@@ -9495,33 +11085,33 @@
       &lt;p&gt;Explore our companion home restoration and woodworking guides on &lt;a href="/blog/how-to-refurbish-teak-wood-sanding-repolishing-doors-tables"&gt;refurbishing and repolishing teak wood furniture&lt;/a&gt;, &lt;a href="/blog/how-to-fix-ceiling-seepage-patches-stains-leak"&gt;fixing ceiling water seepage patches&lt;/a&gt;, &lt;a href="/blog/how-to-fix-bathroom-wall-efflorescence-salt-formation"&gt;treating bathroom wall efflorescence&lt;/a&gt;, and &lt;a href="/blog/how-to-fix-ground-dampness-capillary-action-walls"&gt;repairing rising ground dampness&lt;/a&gt;.&lt;/p&gt;
       &lt;p&gt;For large-scale modular furniture painting, PU spray booth finishing, antique wood restoration, or custom carpentry across Bangalore, connect with verified professionals on &lt;a href="/services/painting"&gt;Carpenterwala Painting Services&lt;/a&gt; and &lt;a href="/services/carpentry"&gt;Carpenterwala Carpentry Services&lt;/a&gt; serving &lt;a href="/services/painting/koramangala"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/painting/indiranagar"&gt;Indiranagar&lt;/a&gt;, &lt;a href="/services/painting/whitefield"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/painting/hsr-layout"&gt;HSR Layout&lt;/a&gt;, and &lt;a href="/services/painting/thanisandra"&gt;Thanisandra&lt;/a&gt;.&lt;/p&gt;</v>
       </c>
-      <c r="I61" t="str">
+      <c r="I69" t="str">
         <v>https://images.unsplash.com/photo-1555041469-a586c61ea9bc?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="62" xml:space="preserve">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" t="str">
+    <row r="70" xml:space="preserve">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="str">
         <v>how-to-refurbish-teak-wood-sanding-repolishing-doors-tables</v>
       </c>
-      <c r="C62" t="str">
+      <c r="C70" t="str">
         <v>Teak Wood Refurbishing: How to Sand, Stain &amp; Repolish Old Doors &amp; Tables (Melamine &amp; PU Guide)</v>
       </c>
-      <c r="D62" t="str">
+      <c r="D70" t="str">
         <v>Carpentry</v>
       </c>
-      <c r="E62" t="str">
+      <c r="E70" t="str">
         <v>June 26, 2026</v>
       </c>
-      <c r="F62" t="str">
+      <c r="F70" t="str">
         <v>13 min read</v>
       </c>
-      <c r="G62" t="str">
+      <c r="G70" t="str">
         <v>Old teak door or dining table looking faded and scratched? Learn how to strip old varnish, sand wood grain, apply stain, and finish with durable Melamine or PU polish.</v>
       </c>
-      <c r="H62" t="str" xml:space="preserve">
+      <c r="H70" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;That solid teak wood main door or heirloom 6-seater dining table that has graced your family home for the past 15 to 25 years. Once radiating a golden-honey luster with deep, undulating natural grain patterns, it now looks dull, faded, scratched, and discolored with white water rings and dark monsoon humidity patches. The magnificent timber underneath is still 100% rock-solid—genuine Indian teak (&lt;em&gt;Sagwan / CP Teak / Nilambur Teak&lt;/em&gt;) is practically indestructible, packed with natural silica and preservative oils that resist termites and rot for generations.&lt;/p&gt;
       &lt;p&gt;The problem is not the wood; it is simply that the sacrificial surface finish (the old varnish, wax, or traditional &lt;em&gt;chapra&lt;/em&gt; French polish) has reached the end of its lifespan. Many homeowners mistakenly pay ₹15,000 to ₹30,000 to carpenters or consider replacing genuine solid wood with hollow engineered veneer doors. In reality, with a random orbital sander, quality sandpaper grits, and modern two-component &lt;strong&gt;Melamine or Polyurethane (PU) wood finishes&lt;/strong&gt;, you can completely strip, stain, and repolish your teak door or table to a showroom-grade gloss in a single weekend.&lt;/p&gt;
       &lt;p&gt;This comprehensive woodworking guide walks you through the exact professional sanding progressions, grain filling methods, color staining techniques, and topcoat spray/brush applications needed for a flawless finish.&lt;/p&gt;
@@ -9665,33 +11255,33 @@
       &lt;p&gt;If you're upgrading other home woodwork or fixing common fixture issues, explore our practical DIY guides on &lt;a href="/blog/how-to-fix-ceiling-seepage-patches-stains-leak"&gt;fixing ceiling water seepage patches&lt;/a&gt;, &lt;a href="/blog/how-to-fix-bathroom-wall-efflorescence-salt-formation"&gt;treating bathroom wall efflorescence&lt;/a&gt;, &lt;a href="/blog/how-to-fix-ground-dampness-capillary-action-walls"&gt;repairing rising ground dampness&lt;/a&gt;, and &lt;a href="/blog/how-to-clear-drainage-p-trap-clogs-sewer-smell"&gt;clearing drainage and floor trap clogs&lt;/a&gt;.&lt;/p&gt;
       &lt;p&gt;For custom handcrafted furniture, antique teak door restoration, PU spray polishing, or structural door repairs across Bangalore, connect with verified master carpenters on &lt;a href="/services/carpentry"&gt;Carpenterwala Carpentry Services&lt;/a&gt; serving &lt;a href="/services/carpentry/koramangala"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/carpentry/indiranagar"&gt;Indiranagar&lt;/a&gt;, &lt;a href="/services/carpentry/whitefield"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/carpentry/hsr-layout"&gt;HSR Layout&lt;/a&gt;, and &lt;a href="/services/carpentry/thanisandra"&gt;Thanisandra&lt;/a&gt;.&lt;/p&gt;</v>
       </c>
-      <c r="I62" t="str">
+      <c r="I70" t="str">
         <v>https://images.unsplash.com/photo-1538688525198-9b88f6f53126?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="63" xml:space="preserve">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63" t="str">
+    <row r="71" xml:space="preserve">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="str">
         <v>how-to-fix-ceiling-seepage-patches-stains-leak</v>
       </c>
-      <c r="C63" t="str">
+      <c r="C71" t="str">
         <v>Ceiling Seepage Patches: How to Fix Yellow Water Stains, Slab Moisture &amp; Peeling Paint (DIY Guide)</v>
       </c>
-      <c r="D63" t="str">
+      <c r="D71" t="str">
         <v>Painting</v>
       </c>
-      <c r="E63" t="str">
+      <c r="E71" t="str">
         <v>June 25, 2026</v>
       </c>
-      <c r="F63" t="str">
+      <c r="F71" t="str">
         <v>13 min read</v>
       </c>
-      <c r="G63" t="str">
+      <c r="G71" t="str">
         <v>Dark yellow water stains and peeling paint on your ceiling? Learn how to verify upstream leak fixes, apply stain-blocking primers, and replaster ceiling patches.</v>
       </c>
-      <c r="H63" t="str" xml:space="preserve">
+      <c r="H71" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;That unsightly, brownish-yellow ring spreading across your living room or bedroom ceiling. The paint around the edges blisters, curls into dry flakes, and periodically drops dusty debris onto your furniture below. If you live in an apartment on any floor below the penthouse terrace, this moisture is almost always coming from your upstairs neighbor's bathroom, kitchen, utility balcony, or sunken slab drainage lines.&lt;/p&gt;
       &lt;p&gt;Many homeowners make the frustrating mistake of immediately painting over the yellow ring with standard ceiling white paint. Within two to three weeks, the dark tannin-and-mineral watermark bleeds right through the new paint film like a ghost. Worse, if the slab hasn't dried from the inside or if the upstairs leak is still active, the fresh paint bubbles up and falls off within a month.&lt;/p&gt;
       &lt;p&gt;Ceiling seepage repairs require a disciplined, two-part strategy: &lt;strong&gt;coordinating with your upstairs neighbor to completely eliminate the moisture source&lt;/strong&gt;, and &lt;strong&gt;treating the damaged reinforced cement concrete (RCC) slab with specialized stain-blocking and waterproofing chemistry&lt;/strong&gt;. Here is the definitive, step-by-step restoration guide.&lt;/p&gt;
@@ -9829,33 +11419,33 @@
       &lt;p&gt;Explore our companion home waterproofing and plumbing guides on &lt;a href="/blog/how-to-fix-bathroom-wall-efflorescence-salt-formation"&gt;treating bathroom wall efflorescence &amp;amp; tile seepage&lt;/a&gt;, &lt;a href="/blog/how-to-fix-ground-dampness-capillary-action-walls"&gt;fixing rising ground dampness on lower walls&lt;/a&gt;, &lt;a href="/blog/how-to-clear-drainage-p-trap-clogs-sewer-smell"&gt;clearing drainage &amp;amp; floor trap clogs&lt;/a&gt;, and &lt;a href="/blog/how-to-fix-leaking-angle-valves-connector-hoses"&gt;repairing leaking angle stop valves and connector hoses&lt;/a&gt;.&lt;/p&gt;
       &lt;p&gt;For complex sunken slab leakage investigations, professional PU pressure injection grouting, or full-apartment painting across Bangalore, connect with verified master painters and plumbers on &lt;a href="/services/painting"&gt;Carpenterwala Painting Services&lt;/a&gt; and &lt;a href="/services/plumbing"&gt;Carpenterwala Plumbing Services&lt;/a&gt; serving &lt;a href="/services/painting/koramangala"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/painting/indiranagar"&gt;Indiranagar&lt;/a&gt;, &lt;a href="/services/painting/whitefield"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/painting/hsr-layout"&gt;HSR Layout&lt;/a&gt;, and &lt;a href="/services/painting/thanisandra"&gt;Thanisandra&lt;/a&gt;.&lt;/p&gt;</v>
       </c>
-      <c r="I63" t="str">
+      <c r="I71" t="str">
         <v>https://images.unsplash.com/photo-1595428774223-ef52624120d2?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="64" xml:space="preserve">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" t="str">
+    <row r="72" xml:space="preserve">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="str">
         <v>how-to-fix-bathroom-wall-efflorescence-salt-formation</v>
       </c>
-      <c r="C64" t="str">
+      <c r="C72" t="str">
         <v>Bathroom Wall Efflorescence: How to Treat White Salt Crust, Tile Seepage &amp; Stop Paint Blistering (DIY Guide)</v>
       </c>
-      <c r="D64" t="str">
+      <c r="D72" t="str">
         <v>Maintenance</v>
       </c>
-      <c r="E64" t="str">
+      <c r="E72" t="str">
         <v>June 24, 2026</v>
       </c>
-      <c r="F64" t="str">
+      <c r="F72" t="str">
         <v>13 min read</v>
       </c>
-      <c r="G64" t="str">
+      <c r="G72" t="str">
         <v>Chalky white salt powder on walls next to your bathroom? Learn how to diagnose tile seepage vs hidden pipe leaks, neutralize efflorescence, regrout, and waterproof.</v>
       </c>
-      <c r="H64" t="str" xml:space="preserve">
+      <c r="H72" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;That powdery, chalky white patch that keeps blooming across the bedroom or hallway wall right on the other side of your bathroom. You wipe it down with a damp cloth or scrape and repaint it before guests arrive, but within three to four weeks, the paint bubbles up, flakes off into crisp flakes, and that white, salty crust returns with a vengeance. It looks like dried salt because that is &lt;em&gt;precisely&lt;/em&gt; what it is—&lt;strong&gt;efflorescence (commonly known in India as &lt;em&gt;shora&lt;/em&gt; or &lt;em&gt;khar&lt;/em&gt;)&lt;/strong&gt;.&lt;/p&gt;
       &lt;p&gt;Efflorescence is not a cosmetic paint defect; it is a direct visible symptom of active water seepage traveling through the brickwork from the wet bathroom side. As shower water, floor washings, or pipe leakage soak through microscopic voids behind bathroom tiles, the water dissolves soluble calcium, sodium, and magnesium salts present within the cement plaster, bricks, and mineral-heavy tap water. When this moisture migrates to the dry bedroom wall and evaporates, it leaves behind crystallized salt deposits that expand with immense force, destroying wall putty and paint adhesion.&lt;/p&gt;
       &lt;p&gt;Simply repainting over salt-damaged plaster is guaranteed to fail every time. A permanent repair requires a two-pronged approach: &lt;strong&gt;stopping the water intrusion at the bathroom source&lt;/strong&gt; and &lt;strong&gt;chemically neutralizing and waterproofing the salt-damaged wall&lt;/strong&gt; before applying fresh paint.&lt;/p&gt;
@@ -9995,33 +11585,33 @@
       &lt;p&gt;For more home waterproofing and plumbing solutions, check out our practical guides on &lt;a href="/blog/how-to-fix-ground-dampness-capillary-action-walls"&gt;treating rising ground dampness and capillary action&lt;/a&gt;, &lt;a href="/blog/how-to-clear-drainage-p-trap-clogs-sewer-smell"&gt;clearing drainage &amp;amp; P-trap clogs&lt;/a&gt;, &lt;a href="/blog/how-to-fix-bathroom-flush-tank-cistern-repairs"&gt;fixing running toilet flush tanks&lt;/a&gt;, and &lt;a href="/blog/how-to-fix-leaking-angle-valves-connector-hoses"&gt;repairing leaking angle stop valves and connector hoses&lt;/a&gt;.&lt;/p&gt;
       &lt;p&gt;If you have widespread tile hollows, concealed pipe leaks, or need complete bathroom regrouting and interior painting across Bangalore, connect with verified professionals on &lt;a href="/services/painting"&gt;Carpenterwala Painting Services&lt;/a&gt; and &lt;a href="/services/plumbing"&gt;Carpenterwala Plumbing Services&lt;/a&gt; serving &lt;a href="/services/painting/koramangala"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/painting/indiranagar"&gt;Indiranagar&lt;/a&gt;, &lt;a href="/services/painting/whitefield"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/painting/hsr-layout"&gt;HSR Layout&lt;/a&gt;, and &lt;a href="/services/painting/thanisandra"&gt;Thanisandra&lt;/a&gt;.&lt;/p&gt;</v>
       </c>
-      <c r="I64" t="str">
+      <c r="I72" t="str">
         <v>https://images.unsplash.com/photo-1584622650111-993a426fbf0a?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="65" xml:space="preserve">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65" t="str">
+    <row r="73" xml:space="preserve">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="str">
         <v>how-to-fix-ground-dampness-capillary-action-walls</v>
       </c>
-      <c r="C65" t="str">
+      <c r="C73" t="str">
         <v>Dealing with Ground Dampness: How to Treat Rising Moisture, Efflorescence &amp; Peeling Paint (Capillary Action Guide)</v>
       </c>
-      <c r="D65" t="str">
+      <c r="D73" t="str">
         <v>Painting</v>
       </c>
-      <c r="E65" t="str">
+      <c r="E73" t="str">
         <v>June 23, 2026</v>
       </c>
-      <c r="F65" t="str">
+      <c r="F73" t="str">
         <v>13 min read</v>
       </c>
-      <c r="G65" t="str">
+      <c r="G73" t="str">
         <v>Peeling, bubbling paint and white salty crust on lower walls? Learn how to treat rising ground dampness, remove efflorescence, and apply waterproof base coats properly.</v>
       </c>
-      <c r="H65" t="str" xml:space="preserve">
+      <c r="H73" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;That persistent, ugly horizontal band of bubbling, blistering, and flaking paint that hugs the bottom one to three feet of your living room or bedroom wall. Every festive season before Diwali or Pongal, you spend thousands of rupees scraping and repainting it, only for the chalky white crust (&lt;em&gt;efflorescence&lt;/em&gt;) to reappear and push the brand-new paint off the wall within four months. This is not a paint quality defect, nor is it a painter's application flaw. It is &lt;strong&gt;rising ground dampness caused by capillary action&lt;/strong&gt;.&lt;/p&gt;
       &lt;p&gt;In Indian ground-floor apartments, independent villas, and row houses, walls act like giant brick-and-mortar sponges. Subsoil moisture is drawn upward through microscopic capillary pores in the brickwork, dragging dissolved mineral salts with it. When the water evaporates into the room's warm air, it leaves behind rock-hard salt crystals that expand with immense crystalline pressure, blowing the plaster and paint right off the brick substrate. Painting over active rising dampness without a specialized crystallization chemical barrier is simply throwing good money after bad.&lt;/p&gt;
       &lt;p&gt;In this comprehensive, step-by-step waterproofing guide, you will learn how to diagnose rising dampness, completely eradicate salt efflorescence, apply professional-grade waterproof base coat barriers, and protect your foundation from ground saturation for good.&lt;/p&gt;
@@ -10164,33 +11754,33 @@
       &lt;p&gt;If you're tackling other home maintenance and moisture issues, explore our comprehensive DIY guides on &lt;a href="/blog/how-to-clear-drainage-p-trap-clogs-sewer-smell"&gt;clearing drainage and P-trap clogs&lt;/a&gt;, &lt;a href="/blog/how-to-fix-bathroom-flush-tank-cistern-repairs"&gt;fixing running toilet flush tanks&lt;/a&gt;, &lt;a href="/blog/how-to-fix-leaking-angle-valves-connector-hoses"&gt;repairing leaking angle stop valves and braided hoses&lt;/a&gt;, and &lt;a href="/blog/how-to-fix-dripping-sink-basin-faucet"&gt;fixing dripping sink and basin faucets&lt;/a&gt;.&lt;/p&gt;
       &lt;p&gt;For extensive multi-room wall seepage, building-wide exterior waterproofing, or flawless interior and exterior painting across Bangalore, connect with verified, background-checked master painters on &lt;a href="/services/painting"&gt;Carpenterwala Painting Services&lt;/a&gt; serving &lt;a href="/services/painting/koramangala"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/painting/indiranagar"&gt;Indiranagar&lt;/a&gt;, &lt;a href="/services/painting/whitefield"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/painting/hsr-layout"&gt;HSR Layout&lt;/a&gt;, and &lt;a href="/services/painting/thanisandra"&gt;Thanisandra&lt;/a&gt;.&lt;/p&gt;</v>
       </c>
-      <c r="I65" t="str">
+      <c r="I73" t="str">
         <v>https://images.unsplash.com/photo-1589939705384-5185137a7f0f?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="66" xml:space="preserve">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" t="str">
+    <row r="74" xml:space="preserve">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="str">
         <v>how-to-clear-drainage-p-trap-clogs-sewer-smell</v>
       </c>
-      <c r="C66" t="str">
+      <c r="C74" t="str">
         <v>Drainage &amp; P-Trap Clogs: How to Clear Bottle-Traps, Kitchen Grease &amp; Stop Sewer Odors (No Harsh Acids)</v>
       </c>
-      <c r="D66" t="str">
+      <c r="D74" t="str">
         <v>Plumbing</v>
       </c>
-      <c r="E66" t="str">
+      <c r="E74" t="str">
         <v>June 22, 2026</v>
       </c>
-      <c r="F66" t="str">
+      <c r="F74" t="str">
         <v>12 min read</v>
       </c>
-      <c r="G66" t="str">
+      <c r="G74" t="str">
         <v>Foul drain smell or slow-draining sink? Learn how to clean bathroom bottle-traps, clear hardened kitchen grease, and stop dry trap sewer odors without damaging pipes.</v>
       </c>
-      <c r="H66" t="str" xml:space="preserve">
+      <c r="H74" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;That rancid, nauseating sewage smell that hits you the moment you walk into the kitchen in the morning. The bathroom washbasin that takes three minutes just to drain a handful of water. The floor drain (&lt;em&gt;nahani trap&lt;/em&gt;) that gurgles ominously and releases foul odors whenever the shower runs. Drainage clogs and foul pipe odors are among the most frustrating plumbing issues in Indian apartments and independent houses.&lt;/p&gt;
       &lt;p&gt;Most people's immediate reaction is to run to the neighborhood &lt;em&gt;kirana&lt;/em&gt; store, buy a cheap ₹40 bottle of concentrated commercial acid or caustic soda, and dump it straight down the drain. While caustic acid creates a violent, sizzling reaction that might burn a pinhole through hair clogs, it wreaks havoc on your home's plumbing. Harsh acids dissolve delicate rubber O-rings, warp thin-walled PVC pipes, melt silicone seals, and emit toxic, corrosive fumes that tarnish expensive chrome taps. Crucially, acid does absolutely nothing to fix the actual root cause sitting inside your &lt;strong&gt;P-trap or bottle-trap&lt;/strong&gt;.&lt;/p&gt;
       &lt;p&gt;In this comprehensive guide, you will learn how household drain traps actually work, how to disassemble and descale bathroom bottle-traps, how to melt kitchen grease blockages safely using household non-acid solutions, and how to permanently eliminate stubborn sewer gas odors.&lt;/p&gt;
@@ -10318,33 +11908,33 @@
       &lt;p&gt;If you're upgrading other bathroom fittings or dealing with persistent moisture, explore our step-by-step guides on &lt;a href="/blog/how-to-fix-bathroom-flush-tank-cistern-repairs"&gt;fixing running flush tanks and faulty float valves&lt;/a&gt;, &lt;a href="/blog/how-to-fix-leaking-angle-valves-connector-hoses"&gt;repairing leaking angle stop cocks &amp;amp; braided hoses&lt;/a&gt;, &lt;a href="/blog/how-to-clean-replace-blocked-tap-aerator-water-pressure"&gt;cleaning blocked tap aerators for better water pressure&lt;/a&gt;, and &lt;a href="/blog/how-to-fix-dripping-sink-basin-faucet"&gt;fixing dripping sink and basin mixer faucets&lt;/a&gt;.&lt;/p&gt;
       &lt;p&gt;For complex building stack blockages, cracked concealed PVC drain lines, or whole-house plumbing overhauls across Bangalore, connect with verified, background-checked master plumbers on &lt;a href="/services/plumbing"&gt;Carpenterwala Plumbing Services&lt;/a&gt; serving &lt;a href="/services/plumbing/hsr-layout"&gt;HSR Layout&lt;/a&gt;, &lt;a href="/services/plumbing/koramangala"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/plumbing/indiranagar"&gt;Indiranagar&lt;/a&gt;, &lt;a href="/services/plumbing/whitefield"&gt;Whitefield&lt;/a&gt;, and &lt;a href="/services/plumbing/thanisandra"&gt;Thanisandra&lt;/a&gt;.&lt;/p&gt;</v>
       </c>
-      <c r="I66" t="str">
+      <c r="I74" t="str">
         <v>https://images.unsplash.com/photo-1585704032915-c3400ca199e7?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="67" xml:space="preserve">
-      <c r="A67">
-        <v>66</v>
-      </c>
-      <c r="B67" t="str">
+    <row r="75" xml:space="preserve">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="str">
         <v>how-to-fix-bathroom-flush-tank-cistern-repairs</v>
       </c>
-      <c r="C67" t="str">
+      <c r="C75" t="str">
         <v>Bathroom Flush Tank &amp; Cistern Repairs: Fixing Running Water, Syphons &amp; Float Valves</v>
       </c>
-      <c r="D67" t="str">
+      <c r="D75" t="str">
         <v>Plumbing</v>
       </c>
-      <c r="E67" t="str">
+      <c r="E75" t="str">
         <v>June 21, 2026</v>
       </c>
-      <c r="F67" t="str">
+      <c r="F75" t="str">
         <v>11 min read</v>
       </c>
-      <c r="G67" t="str">
+      <c r="G75" t="str">
         <v>Toilet tank running continuously or hissing loudly? Learn how to replace syphon flush valves, adjust float ball cocks, descale hard water crust, and fix cistern leaks in 20 mins.</v>
       </c>
-      <c r="H67" t="str" xml:space="preserve">
+      <c r="H75" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;That constant, ghostly hissing sound coming from your bathroom toilet tank, even hours after the last flush. A flush button that feels loose and requires three vigorous presses to actually release water. A thin, continuous trickle weeping silently down the ceramic toilet bowl, wasting hundreds of liters of water and silently driving up your monthly water bill. A running or malfunctioning toilet cistern is one of the most common and water-wasteful plumbing problems in an Indian household.&lt;/p&gt;
       &lt;p&gt;In most Indian flats, a running flush tank wastes between &lt;strong&gt;200 to 500 liters of treated water every single day&lt;/strong&gt;. Homeowners often put off fixing it because they assume it requires an expensive new commode or a plumber's visit costing ₹500–₹800. In reality, modern toilet cisterns operate on simple mechanical principles: a fill valve that brings water in, and a flush valve/syphon that releases it. 95% of cistern issues are caused by a single worn-out ₹50 rubber flapper, an uncalibrated float valve, or mineral scale buildup.&lt;/p&gt;
       &lt;p&gt;With basic household hand tools, a replacement seal or fill valve from your local hardware store, and a little white vinegar, you can diagnose and repair your flush tank completely in under 20 minutes.&lt;/p&gt;
@@ -10502,33 +12092,33 @@
         &lt;p&gt;If your bathroom has concealed cisterns requiring brand-certified Geberit/Grohe service, close-coupled tank bolt replacements, or whole-bathroom plumbing overhauls, Carpenterwala connects you with background-checked master plumbers across Bangalore in &lt;a href="/services/plumbing/whitefield" style="color: var(--primary); font-weight: bold;"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/plumbing/koramangala" style="color: var(--primary); font-weight: bold;"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/plumbing/indiranagar" style="color: var(--primary); font-weight: bold;"&gt;Indiranagar&lt;/a&gt;, &lt;a href="/services/plumbing/hsr-layout" style="color: var(--primary); font-weight: bold;"&gt;HSR Layout&lt;/a&gt;, and &lt;a href="/services/plumbing/thanisandra" style="color: var(--primary); font-weight: bold;"&gt;Thanisandra&lt;/a&gt;.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I67" t="str">
+      <c r="I75" t="str">
         <v>https://images.unsplash.com/photo-1584622650111-993a426fbf0a?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="68" xml:space="preserve">
-      <c r="A68">
-        <v>67</v>
-      </c>
-      <c r="B68" t="str">
+    <row r="76" xml:space="preserve">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="str">
         <v>how-to-fix-leaking-angle-valves-connector-hoses</v>
       </c>
-      <c r="C68" t="str">
+      <c r="C76" t="str">
         <v>How to Fix Leaking Angle Valves &amp; Braided Connector Hoses: Under-Sink &amp; Geyser Guide</v>
       </c>
-      <c r="D68" t="str">
+      <c r="D76" t="str">
         <v>Plumbing</v>
       </c>
-      <c r="E68" t="str">
+      <c r="E76" t="str">
         <v>June 20, 2026</v>
       </c>
-      <c r="F68" t="str">
+      <c r="F76" t="str">
         <v>11 min read</v>
       </c>
-      <c r="G68" t="str">
+      <c r="G76" t="str">
         <v>Water pooling under your washbasin or behind your geyser? Learn how to replace rusted angle stop cocks, re-thread braided connector hoses, and seal wall leaks in 25 mins.</v>
       </c>
-      <c r="H68" t="str" xml:space="preserve">
+      <c r="H76" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;That slow puddle forming silently inside your washbasin modular vanity cabinet. The rusty orange streak running down the wall tiles behind your bathroom geyser. A dripping angle valve (stop cock) or a weeping braided connector hose is one of those plumbing leaks Indian homeowners ignore for months because it is "just a tiny drop." But left unaddressed, that slow drip swells expensive plywood cabinetry, breeds toxic black mold inside wall plaster, or suddenly rusts through and blows out at 11 PM on a Sunday night.&lt;/p&gt;
       &lt;p&gt;Angle valves and flexible connector hoses are the vital isolation bridges connecting your home's concealed wall piping to your basin mixers, geysers, and toilet cisterns. Because they endure continuous municipal pressure (2 to 4 bar), thermal cycling from water heaters, and heavy mineral exposure from hard groundwater, their seals and threads eventually degrade.&lt;/p&gt;
       &lt;p&gt;The good news: &lt;strong&gt;replacing a faulty angle stop cock or a weeping braided hose is a straightforward 25-minute DIY task.&lt;/strong&gt; Once you understand how to isolate the water line, wrap Teflon tape properly, and seat internal rubber washers, you can complete a permanent, leak-proof repair and save both the cost and delay of an emergency plumber's visit.&lt;/p&gt;
@@ -10680,33 +12270,33 @@
         &lt;p&gt;If your angle valves are seized inside wall masonry, your geyser inlet lines need complete re-piping, or you want warranty-backed plumbing overhauls, Carpenterwala connects you with verified master plumbers across Bangalore in &lt;a href="/services/plumbing/whitefield" style="color: var(--primary); font-weight: bold;"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/plumbing/koramangala" style="color: var(--primary); font-weight: bold;"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/plumbing/indiranagar" style="color: var(--primary); font-weight: bold;"&gt;Indiranagar&lt;/a&gt;, &lt;a href="/services/plumbing/hsr-layout" style="color: var(--primary); font-weight: bold;"&gt;HSR Layout&lt;/a&gt;, and &lt;a href="/services/plumbing/thanisandra" style="color: var(--primary); font-weight: bold;"&gt;Thanisandra&lt;/a&gt;.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I68" t="str">
+      <c r="I76" t="str">
         <v>https://images.unsplash.com/photo-1585704032915-c3400ca199e7?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="69" xml:space="preserve">
-      <c r="A69">
-        <v>68</v>
-      </c>
-      <c r="B69" t="str">
+    <row r="77" xml:space="preserve">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="str">
         <v>how-to-fix-kitchen-bathroom-mixer-taps-leaks-diverter</v>
       </c>
-      <c r="C69" t="str">
+      <c r="C77" t="str">
         <v>Fixing Kitchen &amp; Bathroom Mixer Taps: Leaking Swivel Spouts, Diverters &amp; Temperature Imbalance</v>
       </c>
-      <c r="D69" t="str">
+      <c r="D77" t="str">
         <v>Plumbing</v>
       </c>
-      <c r="E69" t="str">
+      <c r="E77" t="str">
         <v>June 19, 2026</v>
       </c>
-      <c r="F69" t="str">
+      <c r="F77" t="str">
         <v>12 min read</v>
       </c>
-      <c r="G69" t="str">
+      <c r="G77" t="str">
         <v>Water pooling around your kitchen sink swivel neck or bathroom wall-mixer diverter leaking into the shower? Learn how to replace O-rings, descale diverters, and balance dual hot-cold lines in 30 mins.</v>
       </c>
-      <c r="H69" t="str" xml:space="preserve">
+      <c r="H77" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;Your kitchen sink mixer tap is pooling water around its rotating swivel collar every time you wash dishes, slowly seeping into and swelling your expensive modular under-counter plywood carcase. Or in your bathroom, your 2-in-1 or 3-in-1 wall mixer's central diverter knob won't hold pressure — leaking water simultaneously from both the lower bucket spout and the overhead shower rose. Or worse, turning on the single-lever basin mixer scalds your hands with steaming geyser water because the hot and cold water pressures are wildly out of balance.&lt;/p&gt;
       &lt;p&gt;Dual hot-and-cold mixer faucets are among the most hard-working mechanical fixtures in modern Indian homes. Unlike basic single-line taps, mixer taps house dynamic rotating spigots, spring-loaded diverter pistons, and dual ceramic flow chambers. In Indian metro cities, high-TDS hard water (600–1,200+ ppm) calcifies moving parts, while constant 180-degree rotational friction grinds rubber O-rings flat within 1 to 2 years.&lt;/p&gt;
       &lt;p&gt;The good news: &lt;strong&gt;you don't need to replace an expensive ₹3,000–₹8,000 mixer unit.&lt;/strong&gt; Armed with a ₹30 O-ring replacement kit, a tube of plumber's silicone grease, and basic hand tools, you can repair leaking swivel necks, descale stuck diverter valves, and balance water temperatures in under 30 minutes.&lt;/p&gt;
@@ -10840,33 +12430,33 @@
         &lt;p&gt;If your bathroom wall mixers need brand-certified diverter replacements, concealed valve overhauls, or kitchen sink mixer replacements with warranty protection, Carpenterwala connects you with vetted master plumbers across Bangalore in &lt;a href="/services/plumbing/whitefield" style="color: var(--primary); font-weight: bold;"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/plumbing/koramangala" style="color: var(--primary); font-weight: bold;"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/plumbing/indiranagar" style="color: var(--primary); font-weight: bold;"&gt;Indiranagar&lt;/a&gt;, &lt;a href="/services/plumbing/hsr-layout" style="color: var(--primary); font-weight: bold;"&gt;HSR Layout&lt;/a&gt;, and &lt;a href="/services/plumbing/thanisandra" style="color: var(--primary); font-weight: bold;"&gt;Thanisandra&lt;/a&gt;.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I69" t="str">
+      <c r="I77" t="str">
         <v>https://images.unsplash.com/photo-1584622650111-993a426fbf0a?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="70" xml:space="preserve">
-      <c r="A70">
-        <v>69</v>
-      </c>
-      <c r="B70" t="str">
+    <row r="78" xml:space="preserve">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="str">
         <v>how-to-clean-replace-blocked-tap-aerator-water-pressure</v>
       </c>
-      <c r="C70" t="str">
+      <c r="C78" t="str">
         <v>Low Water Pressure in Taps? How to Clean or Replace Blocked Tap Aerators (*Jali*)</v>
       </c>
-      <c r="D70" t="str">
+      <c r="D78" t="str">
         <v>Plumbing</v>
       </c>
-      <c r="E70" t="str">
+      <c r="E78" t="str">
         <v>June 18, 2026</v>
       </c>
-      <c r="F70" t="str">
+      <c r="F78" t="str">
         <v>10 min read</v>
       </c>
-      <c r="G70" t="str">
+      <c r="G78" t="str">
         <v>Tap water reduced to a sputtering trickle? Learn how to unscrew, descale, clean, or replace blocked faucet aerators (*jali*) choked by borewell silt and hard water in 15 mins.</v>
       </c>
-      <c r="H70" t="str" xml:space="preserve">
+      <c r="H78" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;You open your bathroom washbasin or kitchen sink tap expecting a brisk, foaming stream of water, but all you get is a pathetic trickle or an annoying sideways spray that splatters all over your clothes and countertop. You check the health faucet next to the commode or the overhead shower, and both have roaring high pressure. That means your apartment building's rooftop Sintex tank is full and the pressure pump is working perfectly — the problem is isolated strictly to that single tap.&lt;/p&gt;
       &lt;p&gt;In 95% of Indian homes, the culprit is not a broken pipeline or a faulty wall mixer. It is a choked &lt;strong&gt;tap aerator (commonly called the tap *jali* or nozzle mesh)&lt;/strong&gt; screwed into the very tip of your faucet spout. In Indian metro cities, municipal water mixed with deep borewell and tanker supply carries fine silt, sand grains, overhead tank rust, and heavy dissolved calcium-magnesium minerals (TDS often exceeding 800–1,200 ppm). The multi-layered micro-mesh inside your faucet aerator traps all this debris to soften the stream, but within 4 to 6 months, it becomes completely suffocated.&lt;/p&gt;
       &lt;p&gt;The good news: &lt;strong&gt;you don't need a plumber's visit or a new faucet.&lt;/strong&gt; With an old toothbrush, a ₹20 bottle of white vinegar or citric acid (*nimbu ka phool*), and a simple wrench, you can unscrew, dissolve the rock-hard limescale crust, flush out trapped borewell sand, and restore full, champagne-smooth water pressure in under 15 minutes.&lt;/p&gt;
@@ -10998,33 +12588,33 @@
         &lt;p&gt;If low water pressure persists across your home, or you want whole-house scale inhibitors, pressure pumps, and brand-certified tap cartridge replacements installed with warranty coverage, Carpenterwala connects you with vetted, background-checked master plumbers across Bangalore in &lt;a href="/services/plumbing/whitefield" style="color: var(--primary); font-weight: bold;"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/plumbing/koramangala" style="color: var(--primary); font-weight: bold;"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/plumbing/indiranagar" style="color: var(--primary); font-weight: bold;"&gt;Indiranagar&lt;/a&gt;, &lt;a href="/services/plumbing/hsr-layout" style="color: var(--primary); font-weight: bold;"&gt;HSR Layout&lt;/a&gt;, and &lt;a href="/services/plumbing/thanisandra" style="color: var(--primary); font-weight: bold;"&gt;Thanisandra&lt;/a&gt;.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I70" t="str">
+      <c r="I78" t="str">
         <v>https://images.unsplash.com/photo-1585704032915-c3400ca199e7?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="71" xml:space="preserve">
-      <c r="A71">
-        <v>70</v>
-      </c>
-      <c r="B71" t="str">
+    <row r="79" xml:space="preserve">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="str">
         <v>how-to-fix-dripping-sink-basin-faucet</v>
       </c>
-      <c r="C71" t="str">
+      <c r="C79" t="str">
         <v>Fixing a Dripping Sink/Basin Faucet: How to Diagnose &amp; Fix Washer and Cartridge Leaks</v>
       </c>
-      <c r="D71" t="str">
+      <c r="D79" t="str">
         <v>Plumbing</v>
       </c>
-      <c r="E71" t="str">
+      <c r="E79" t="str">
         <v>June 17, 2026</v>
       </c>
-      <c r="F71" t="str">
+      <c r="F79" t="str">
         <v>12 min read</v>
       </c>
-      <c r="G71" t="str">
+      <c r="G79" t="str">
         <v>You've tightened the tap as far as it'll go and it's still dripping? Learn how to diagnose washer vs ceramic disc cartridge faucets, replace worn seals, descale parts, and fix leaks yourself in 25 mins.</v>
       </c>
-      <c r="H71" t="str" xml:space="preserve">
+      <c r="H79" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;You've tightened the tap as far as it'll go, and it's still dripping into the basin. Or worse — it's a modern single-lever basin mixer that just won't stop weeping from the spout no matter what position you set it to. Basin and sink faucets today aren't all the same simple washer-and-spindle design your grandfather's plumber dealt with — many modern fixtures have ceramic disc cartridges inside. Diagnosing the actual internal cause before you start disassembling anything is the key to a fast, permanent fix. Here is how to figure out what is broken and fix it yourself in under 30 minutes.&lt;/p&gt;
       &lt;h2&gt;Why Basin Faucets Keep Dripping in Indian Homes&lt;/h2&gt;
       &lt;p&gt;Plumbing fixtures in Indian metro apartments operate under challenging local water and usage conditions:&lt;/p&gt;
@@ -11179,33 +12769,33 @@
         &lt;p&gt;If your bathroom fixtures need brand-specific cartridge replacements, under-counter angle valve overhauls, or full basin tap installations, Carpenterwala connects you with verified master plumbers across Bangalore in &lt;a href="/services/plumbing/whitefield" style="color: var(--primary); font-weight: bold;"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/plumbing/koramangala" style="color: var(--primary); font-weight: bold;"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/plumbing/indiranagar" style="color: var(--primary); font-weight: bold;"&gt;Indiranagar&lt;/a&gt;, &lt;a href="/services/plumbing/hsr-layout" style="color: var(--primary); font-weight: bold;"&gt;HSR Layout&lt;/a&gt;, and &lt;a href="/services/plumbing/thanisandra" style="color: var(--primary); font-weight: bold;"&gt;Thanisandra&lt;/a&gt;.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I71" t="str">
+      <c r="I79" t="str">
         <v>https://images.unsplash.com/photo-1584622650111-993a426fbf0a?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="72" xml:space="preserve">
-      <c r="A72">
-        <v>71</v>
-      </c>
-      <c r="B72" t="str">
+    <row r="80" xml:space="preserve">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="str">
         <v>fix-overhead-cabinet-hydraulic-struts-crooked-drawers</v>
       </c>
-      <c r="C72" t="str">
+      <c r="C80" t="str">
         <v>Overhead Cabinet Won't Stay Up, or Drawer Sliding Crooked? Here's the Fix</v>
       </c>
-      <c r="D72" t="str">
+      <c r="D80" t="str">
         <v>Carpentry</v>
       </c>
-      <c r="E72" t="str">
+      <c r="E80" t="str">
         <v>June 16, 2026</v>
       </c>
-      <c r="F72" t="str">
+      <c r="F80" t="str">
         <v>11 min read</v>
       </c>
-      <c r="G72" t="str">
+      <c r="G80" t="str">
         <v>Overhead kitchen cabinet slamming down or drawer scraping sideways? Learn how to replace gas-lift hydraulic struts and realign modular drawer channels in 20 minutes.</v>
       </c>
-      <c r="H72" t="str" xml:space="preserve">
+      <c r="H80" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;Your overhead modular kitchen cabinet door used to glide open smoothly and hover effortlessly in the air. Now, the moment you let go, it violently slams shut on your fingers or slowly droops down, forcing you to hold it open with one elbow while rummaging for spice jars. Or downstairs, your heavy cutlery and utensil drawer is sliding out crooked, scraping against the laminate cabinet frame, or jamming stubbornly halfway through its track.&lt;/p&gt;
       &lt;p&gt;Both issues are among the most common hardware failures in Indian modular kitchens. The good news: &lt;strong&gt;you don't need an expensive carpenter's visit to fix them.&lt;/strong&gt; Kitchen lift-up flap doors use standardized gas-charged hydraulic struts, and drawers use telescopic ball-bearing channels. With a simple screwdriver, a ₹150 replacement strut, and 20 minutes of DIY adjustment, you can restore butter-smooth, silent operation to your kitchen cabinetry.&lt;/p&gt;
       &lt;h2&gt;Why Kitchen Cabinet Hardware Fails in Indian Homes&lt;/h2&gt;
@@ -11293,33 +12883,33 @@
         &lt;p&gt;If your modular kitchen needs complete hardware overhauls, custom carcass repairs, or soft-close hinge upgrades, Carpenterwala connects you with verified master carpenters across Bangalore in &lt;a href="/services/carpentry/whitefield" style="color: var(--primary); font-weight: bold;"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/carpentry/koramangala" style="color: var(--primary); font-weight: bold;"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/carpentry/indiranagar" style="color: var(--primary); font-weight: bold;"&gt;Indiranagar&lt;/a&gt;, and &lt;a href="/services/carpentry/hsr-layout" style="color: var(--primary); font-weight: bold;"&gt;HSR Layout&lt;/a&gt;.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I72" t="str">
+      <c r="I80" t="str">
         <v>https://images.unsplash.com/photo-1556911220-e15b29be8c8f?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="73" xml:space="preserve">
-      <c r="A73">
-        <v>72</v>
-      </c>
-      <c r="B73" t="str">
+    <row r="81" xml:space="preserve">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="str">
         <v>wd-40-vs-m-seal-vs-araldite-diy-guide-uses</v>
       </c>
-      <c r="C73" t="str">
+      <c r="C81" t="str">
         <v>WD-40, M-Seal, or Araldite? Here's Exactly When to Use Which (And How)</v>
       </c>
-      <c r="D73" t="str">
+      <c r="D81" t="str">
         <v>Maintenance</v>
       </c>
-      <c r="E73" t="str">
+      <c r="E81" t="str">
         <v>June 15, 2026</v>
       </c>
-      <c r="F73" t="str">
+      <c r="F81" t="str">
         <v>11 min read</v>
       </c>
-      <c r="G73" t="str">
+      <c r="G81" t="str">
         <v>Confused between WD-40, M-Seal, and Araldite? Master the ultimate Indian home repair decision guide: when to lubricate, when to seal water leaks, and when to bond.</v>
       </c>
-      <c r="H73" t="str" xml:space="preserve">
+      <c r="H81" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;A bathroom drain pipe joint is weeping water at 10 PM. Your bedroom door hinge is screeching loudly every time the fan blows it shut. And a plastic bucket handle or decorative ceramic bowl has snapped in half. You open your utility cupboard and find a yellow can of WD-40, a pack of M-Seal epoxy putty, and two red-and-white tubes of Araldite adhesive.&lt;/p&gt;
       &lt;p&gt;Which one do you reach for? Most Indian homeowners treat these three legendary products as interchangeable "magic fixes" — spraying WD-40 onto leaking pipes, molding M-Seal onto broken ceramic handles, or expecting Araldite to seal active water leaks. Using the wrong product guarantees a messy failure. Once you master the fundamental distinction — &lt;strong&gt;WD-40 lubricates and frees stuck metal, M-Seal molds and seals damp water leaks, and Araldite structurally bonds solid materials under heavy load&lt;/strong&gt; — you can repair 90% of household breakdowns in minutes.&lt;/p&gt;
       &lt;h2&gt;Why Household Confusion Happens Around These Three Classics&lt;/h2&gt;
@@ -11442,33 +13032,33 @@
         &lt;p&gt;When a home repair needs specialized tools, pipe cutting, hinge realignment, or modular kitchen adjustments, Carpenterwala provides background-checked, trusted trade experts across Bangalore in &lt;a href="/services/carpentry/whitefield" style="color: var(--primary); font-weight: bold;"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/carpentry/koramangala" style="color: var(--primary); font-weight: bold;"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/carpentry/indiranagar" style="color: var(--primary); font-weight: bold;"&gt;Indiranagar&lt;/a&gt;, and &lt;a href="/services/carpentry/hsr-layout" style="color: var(--primary); font-weight: bold;"&gt;HSR Layout&lt;/a&gt;.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I73" t="str">
+      <c r="I81" t="str">
         <v>https://images.unsplash.com/photo-1581783898377-1c85bf937427?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="74" xml:space="preserve">
-      <c r="A74">
-        <v>73</v>
-      </c>
-      <c r="B74" t="str">
+    <row r="82" xml:space="preserve">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="str">
         <v>remove-hard-water-scaling-taps-tiles-vinegar-guide</v>
       </c>
-      <c r="C74" t="str">
+      <c r="C82" t="str">
         <v>That Crusty White Buildup on Your Taps and Tiles? Here's How to Clear It Properly</v>
       </c>
-      <c r="D74" t="str">
+      <c r="D82" t="str">
         <v>Plumbing</v>
       </c>
-      <c r="E74" t="str">
+      <c r="E82" t="str">
         <v>June 14, 2026</v>
       </c>
-      <c r="F74" t="str">
+      <c r="F82" t="str">
         <v>10 min read</v>
       </c>
-      <c r="G74" t="str">
+      <c r="G82" t="str">
         <v>Chalky white mineral crust on chrome taps and foggy shower glass? Learn the vinegar-wrap method and citric acid formulas to dissolve hard water scale safely.</v>
       </c>
-      <c r="H74" t="str" xml:space="preserve">
+      <c r="H82" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;Your chrome bathroom faucet has developed an ugly, stone-hard crust of white and greenish-yellow buildup around the spout. Your transparent shower glass partition looks permanently foggy and frosted with water drip streaks no matter how many times you wipe it down with glass cleaner. Your glazed bathroom tiles and grout lines around the shower area feel rough and chalky.&lt;/p&gt;
       &lt;p&gt;This chalky buildup is &lt;strong&gt;hard water mineral scaling (limescale)&lt;/strong&gt;, and it is a universal frustration across Indian metro apartments. The biggest mistake homeowners make is aggressively scrubbing with harsh caustic detergents or wire wool — which scratches expensive chrome plating without dissolving the mineral deposit. Because limescale is alkaline calcium carbonate, you need a mild, controlled acid like &lt;strong&gt;white vinegar or citric acid (*nimbu ka phool*)&lt;/strong&gt; to break down the chemical bond safely in under 30 minutes.&lt;/p&gt;
       &lt;h2&gt;Why Hard Water Scaling Is So Persistent in Indian Homes&lt;/h2&gt;
@@ -11558,33 +13148,33 @@
         &lt;p&gt;If your bathroom fittings have severe internal calcification, leaky wall diverters, or you want whole-home water softening systems installed with warranty protection, Carpenterwala connects you with certified plumbing professionals across Bangalore in &lt;a href="/services/plumbing/whitefield" style="color: var(--primary); font-weight: bold;"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/plumbing/koramangala" style="color: var(--primary); font-weight: bold;"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/plumbing/indiranagar" style="color: var(--primary); font-weight: bold;"&gt;Indiranagar&lt;/a&gt;, and &lt;a href="/services/plumbing/hsr-layout" style="color: var(--primary); font-weight: bold;"&gt;HSR Layout&lt;/a&gt;.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I74" t="str">
+      <c r="I82" t="str">
         <v>https://images.unsplash.com/photo-1584622650111-993a426fbf0a?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="75" xml:space="preserve">
-      <c r="A75">
-        <v>74</v>
-      </c>
-      <c r="B75" t="str">
+    <row r="83" xml:space="preserve">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="str">
         <v>ultimate-home-tool-kit-checklist-indian-household-guide</v>
       </c>
-      <c r="C75" t="str">
+      <c r="C83" t="str">
         <v>The Ultimate Home Tool Kit Checklist: What Every Indian Household Actually Needs</v>
       </c>
-      <c r="D75" t="str">
+      <c r="D83" t="str">
         <v>Maintenance</v>
       </c>
-      <c r="E75" t="str">
+      <c r="E83" t="str">
         <v>June 13, 2026</v>
       </c>
-      <c r="F75" t="str">
+      <c r="F83" t="str">
         <v>11 min read</v>
       </c>
-      <c r="G75" t="str">
+      <c r="G83" t="str">
         <v>Stop hunting through junk drawers for rusted tools. Build a compact, practical Indian home tool kit with the exact 15 essentials for 90% of plumbing, electrical, and carpentry fixes.</v>
       </c>
-      <c r="H75" t="str" xml:space="preserve">
+      <c r="H83" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;A kitchen cabinet hinge is loose and scraping the laminate. A bathroom tap connection is weeping water at 10 PM. You want to hang a family photo frame or tighten a wobbly dining chair leg. You spend twenty minutes rummaging through random junk drawers, old biscuit tins, and shoe boxes, only to unearth a rusty screwdriver with a stripped head, a bent butter knife, and no pliers in sight.&lt;/p&gt;
       &lt;p&gt;In most Indian households, tools are either completely missing or exist as an unorganized heap accumulated over decades — a free Allen key from IKEA, an old rusted spanner borrowed from a relative, and electrical tape with dried-out adhesive. Neither helps during an emergency. Building a &lt;strong&gt;focused, organized, 15-piece home tool kit&lt;/strong&gt; costs less than ₹2,000, fits into a compact box, and handles 90% of day-to-day plumbing, electrical, and carpentry repairs without waiting days for a technician.&lt;/p&gt;
       &lt;h2&gt;Why Every Indian Home Needs a Dedicated Toolkit&lt;/h2&gt;
@@ -11702,33 +13292,33 @@
         &lt;p&gt;When a repair exceeds DIY scope — from modular kitchen installations and electrical rewiring to bathroom plumbing overhauls — Carpenterwala connects you with verified, background-checked trade experts across Bangalore in &lt;a href="/services/carpentry/whitefield" style="color: var(--primary); font-weight: bold;"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/carpentry/koramangala" style="color: var(--primary); font-weight: bold;"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/carpentry/indiranagar" style="color: var(--primary); font-weight: bold;"&gt;Indiranagar&lt;/a&gt;, and &lt;a href="/services/carpentry/hsr-layout" style="color: var(--primary); font-weight: bold;"&gt;HSR Layout&lt;/a&gt;.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I75" t="str">
+      <c r="I83" t="str">
         <v>https://images.unsplash.com/photo-1581783898377-1c85bf937427?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="76" xml:space="preserve">
-      <c r="A76">
-        <v>75</v>
-      </c>
-      <c r="B76" t="str">
+    <row r="84" xml:space="preserve">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="str">
         <v>diy-balcony-automatic-drip-irrigation-setup-guide</v>
       </c>
-      <c r="C76" t="str">
+      <c r="C84" t="str">
         <v>Coming Back From a Trip to Dead Plants? Here's How to Set Up Automatic Drip Irrigation</v>
       </c>
-      <c r="D76" t="str">
+      <c r="D84" t="str">
         <v>Maintenance</v>
       </c>
-      <c r="E76" t="str">
+      <c r="E84" t="str">
         <v>June 12, 2026</v>
       </c>
-      <c r="F76" t="str">
+      <c r="F84" t="str">
         <v>10 min read</v>
       </c>
-      <c r="G76" t="str">
+      <c r="G84" t="str">
         <v>Wilted leaves after a holiday? Set up an automatic battery-operated drip irrigation kit with 16mm main line, 4mm micro-tubing, and adjustable emitters in under an hour.</v>
       </c>
-      <c r="H76" t="str" xml:space="preserve">
+      <c r="H84" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;You care for your potted balcony garden every single day, keeping your hibiscus, money plants, areca palms, and basil blooming. But the moment you leave town for a five-day family vacation or a busy work trip during hot weather, you return home to brittle yellow foliage, shriveled buds, and dried-out pots that cannot be salvaged. Or you're simply tired of carrying heavy watering cans across your living room twice a day during peak 40°C Indian summers.&lt;/p&gt;
       &lt;p&gt;An automated balcony drip irrigation system eliminates both headaches permanently. The best part: &lt;strong&gt;setting up a complete automated drip network requires zero electrical wiring and zero plumbing alterations.&lt;/strong&gt; With a simple battery-powered digital tap timer, push-fit poly-tubing, and adjustable micro-emitters, you can build a customized precision watering grid in under 60 minutes for less than ₹1,500.&lt;/p&gt;
       &lt;h2&gt;Why Automatic Drip Irrigation Is Essential for Indian Balconies&lt;/h2&gt;
@@ -11841,33 +13431,33 @@
         &lt;p&gt;If you need new outdoor water bib taps installed, pressure booster pumps connected, or complete terrace garden irrigation designed, our verified professionals provide trusted service across Bangalore in &lt;a href="/services/plumbing/whitefield" style="color: var(--primary); font-weight: bold;"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/plumbing/koramangala" style="color: var(--primary); font-weight: bold;"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/plumbing/indiranagar" style="color: var(--primary); font-weight: bold;"&gt;Indiranagar&lt;/a&gt;, and &lt;a href="/services/plumbing/hsr-layout" style="color: var(--primary); font-weight: bold;"&gt;HSR Layout&lt;/a&gt;.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I76" t="str">
+      <c r="I84" t="str">
         <v>https://images.unsplash.com/photo-1585320806297-9794b3e4eeae?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="77" xml:space="preserve">
-      <c r="A77">
-        <v>76</v>
-      </c>
-      <c r="B77" t="str">
+    <row r="85" xml:space="preserve">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="str">
         <v>diy-balcony-privacy-pigeon-nets-bamboo-mats-artificial-grass</v>
       </c>
-      <c r="C77" t="str">
+      <c r="C85" t="str">
         <v>DIY Balcony Privacy: How to Install Pigeon Nets, Bamboo Mats, and Artificial Grass Yourself</v>
       </c>
-      <c r="D77" t="str">
+      <c r="D85" t="str">
         <v>Maintenance</v>
       </c>
-      <c r="E77" t="str">
+      <c r="E85" t="str">
         <v>June 11, 2026</v>
       </c>
-      <c r="F77" t="str">
+      <c r="F85" t="str">
         <v>11 min read</v>
       </c>
-      <c r="G77" t="str">
+      <c r="G85" t="str">
         <v>Stop pigeon mess, block nosy neighbours, and transform cold concrete floors. A complete DIY guide to installing UV bird nets, bamboo chiks, and artificial grass.</v>
       </c>
-      <c r="H77" t="str" xml:space="preserve">
+      <c r="H85" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;Pigeons have turned your apartment balcony into their personal roosting ground, leaving toxic acidic droppings that ruin your floor tiles. Or your balcony directly faces the neighbouring residential tower, leaving you zero privacy to sip morning chai or dry clothes in peace. Or the cold, stained concrete flooring makes your outdoor space feel dreary and uninviting.&lt;/p&gt;
       &lt;p&gt;These are three of the most universal complaints among Indian apartment dwellers. While private installation agencies frequently quote ₹3,000 to ₹8,000 for these simple upgrades, &lt;strong&gt;installing bird protection nets, rolled bamboo privacy mats (*chik blinds*), and lush artificial grass is 100% doable as an afternoon DIY project.&lt;/strong&gt; In this complete master guide, we break down each makeover step with safety protocols, fastening techniques, and drainage safeguards.&lt;/p&gt;
       &lt;h2&gt;Why Balcony Makeovers Go Wrong in Indian Apartments&lt;/h2&gt;
@@ -11974,33 +13564,33 @@
         &lt;p&gt;If you're looking for professional high-rise pigeon net installation, customized wooden balcony panelling, or terrace waterproofing, our verified experts deliver reliable, warranty-backed solutions across Bangalore in &lt;a href="/services/carpentry/whitefield" style="color: var(--primary); font-weight: bold;"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/carpentry/koramangala" style="color: var(--primary); font-weight: bold;"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/carpentry/indiranagar" style="color: var(--primary); font-weight: bold;"&gt;Indiranagar&lt;/a&gt;, and &lt;a href="/services/carpentry/hsr-layout" style="color: var(--primary); font-weight: bold;"&gt;HSR Layout&lt;/a&gt;.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I77" t="str">
+      <c r="I85" t="str">
         <v>https://images.unsplash.com/photo-1512917774080-9991f1c4c750?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="78" xml:space="preserve">
-      <c r="A78">
-        <v>77</v>
-      </c>
-      <c r="B78" t="str">
+    <row r="86" xml:space="preserve">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="str">
         <v>tighten-sagging-clothesline-taut-line-hitch-turnbuckle-guide</v>
       </c>
-      <c r="C78" t="str">
+      <c r="C86" t="str">
         <v>Clothesline Sagging Under Wet Clothes? Here's How to Tie It Tight and Keep It That Way</v>
       </c>
-      <c r="D78" t="str">
+      <c r="D86" t="str">
         <v>Maintenance</v>
       </c>
-      <c r="E78" t="str">
+      <c r="E86" t="str">
         <v>June 10, 2026</v>
       </c>
-      <c r="F78" t="str">
+      <c r="F86" t="str">
         <v>10 min read</v>
       </c>
-      <c r="G78" t="str">
+      <c r="G86" t="str">
         <v>Wet clothes brushing dusty balcony railings? Learn how to tie the self-locking Taut-Line Hitch knot or install an M6 steel turnbuckle for a rock-solid, sag-free clothesline.</v>
       </c>
-      <c r="H78" t="str" xml:space="preserve">
+      <c r="H86" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;You hang a heavy load of freshly washed cotton bedsheets, thick bath towels, and denim jeans across your balcony clothesline. Within twenty minutes, the rope stretches under the weight, sagging down so severely that your clean laundry is brushing against the dusty balcony floor tiles or pigeon-soiled railing. You try pulling the knot tighter with brute force, only for the nylon to slip back to its sagging state two days later.&lt;/p&gt;
       &lt;p&gt;A sagging clothesline is a constant household annoyance that forces you to re-wash clean garments and risks snapping under monsoon wind gusts. The solution isn't tying ten random double-knots — it comes down to &lt;strong&gt;selecting weather-resistant line materials and mastering the friction-based Taut-Line Hitch knot (or installing a threaded steel turnbuckle).&lt;/strong&gt; With this simple 15-minute DIY technique, you can keep your drying line guitar-string taut year-round.&lt;/p&gt;
       &lt;h2&gt;Why Balcony Clotheslines Sag So Badly in Indian Homes&lt;/h2&gt;
@@ -12086,33 +13676,33 @@
         &lt;p&gt;If you're upgrading to individual pulley-operated ceiling cloth drying racks, wall-mounted collapsible drying wings, or heavy hardware installations, our verified technicians provide fast, mess-free service across Bangalore in &lt;a href="/services/carpentry/whitefield" style="color: var(--primary); font-weight: bold;"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/carpentry/koramangala" style="color: var(--primary); font-weight: bold;"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/carpentry/indiranagar" style="color: var(--primary); font-weight: bold;"&gt;Indiranagar&lt;/a&gt;, and &lt;a href="/services/carpentry/hsr-layout" style="color: var(--primary); font-weight: bold;"&gt;HSR Layout&lt;/a&gt;.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I78" t="str">
+      <c r="I86" t="str">
         <v>https://images.unsplash.com/photo-1582735689369-4fe89db7114c?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="79" xml:space="preserve">
-      <c r="A79">
-        <v>78</v>
-      </c>
-      <c r="B79" t="str">
+    <row r="87" xml:space="preserve">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="str">
         <v>regenerate-hard-potting-soil-repot-balcony-plants-guide</v>
       </c>
-      <c r="C79" t="str">
+      <c r="C87" t="str">
         <v>Soil Gone Hard as Concrete? Here's How to Regenerate It and Repot Your Balcony Plants</v>
       </c>
-      <c r="D79" t="str">
+      <c r="D87" t="str">
         <v>Maintenance</v>
       </c>
-      <c r="E79" t="str">
+      <c r="E87" t="str">
         <v>June 09, 2026</v>
       </c>
-      <c r="F79" t="str">
+      <c r="F87" t="str">
         <v>10 min read</v>
       </c>
-      <c r="G79" t="str">
+      <c r="G87" t="str">
         <v>Water pooling on cement-like pot soil? Discover the 50:30:20 coco-peat, vermicompost, and aeration mix to revive compacted balcony pots and repot root-bound plants.</v>
       </c>
-      <c r="H79" t="str" xml:space="preserve">
+      <c r="H87" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;You step out onto your balcony with a watering can, pour water into your potted money plant, snake plant, or hibiscus, and watch the water pool on the surface like it's sitting on a cement driveway — refusing to soak down. When you poke the surface with a stick, the dirt feels rock-hard, cracked, and completely lifeless. Despite regular watering and plant food, leaves are turning yellow, growth has stalled, and the plant looks permanently parched.&lt;/p&gt;
       &lt;p&gt;This is one of the most common frustrations among Indian apartment gardeners. The good news: &lt;strong&gt;your plant isn't dead, and you don't need to throw away your expensive planters.&lt;/strong&gt; Compacted balcony soil is 100% reversible through organic soil regeneration and methodical root-ball repotting. In under 45 minutes, you can restore rich microbial structure, fluffy aeration, and rapid drainage to your balcony garden.&lt;/p&gt;
       &lt;h2&gt;Why Potting Soil Turns Hard as Rock in Indian Apartments&lt;/h2&gt;
@@ -12225,33 +13815,33 @@
         &lt;p&gt;From repairing balcony seepage and installing wooden planter ledges to complete home repairs, our verified service professionals deliver trusted solutions across Bangalore in &lt;a href="/services/carpentry/whitefield" style="color: var(--primary); font-weight: bold;"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/carpentry/koramangala" style="color: var(--primary); font-weight: bold;"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/carpentry/indiranagar" style="color: var(--primary); font-weight: bold;"&gt;Indiranagar&lt;/a&gt;, and &lt;a href="/services/carpentry/hsr-layout" style="color: var(--primary); font-weight: bold;"&gt;HSR Layout&lt;/a&gt;.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I79" t="str">
+      <c r="I87" t="str">
         <v>https://images.unsplash.com/photo-1416879595882-3373a0480b5b?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="80" xml:space="preserve">
-      <c r="A80">
-        <v>79</v>
-      </c>
-      <c r="B80" t="str">
+    <row r="88" xml:space="preserve">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="str">
         <v>how-to-wall-mount-tv-safely-step-by-step-guide</v>
       </c>
-      <c r="C80" t="str">
+      <c r="C88" t="str">
         <v>How to Wall-Mount Your TV Safely (Without It Ending Up Crooked or Falling Off)</v>
       </c>
-      <c r="D80" t="str">
+      <c r="D88" t="str">
         <v>Carpentry</v>
       </c>
-      <c r="E80" t="str">
+      <c r="E88" t="str">
         <v>June 08, 2026</v>
       </c>
-      <c r="F80" t="str">
+      <c r="F88" t="str">
         <v>10 min read</v>
       </c>
-      <c r="G80" t="str">
+      <c r="G88" t="str">
         <v>Mounting a 43 to 65-inch LED TV? Learn how to calculate seated eye-level height, drill solid 10mm masonry anchor bolts, align bracket levels, and conceal HDMI cables cleanly.</v>
       </c>
-      <c r="H80" t="str" xml:space="preserve">
+      <c r="H88" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;You've treated yourself to a sleek 43-inch, 55-inch, or 65-inch 4K Smart TV and a heavy-duty wall bracket, ready to eliminate bulky entertainment units and free up floor space. But wall-mounting a television is in a completely different engineering category than hanging a framed picture — you are suspending a costly 10–20 kg electronic appliance where poor anchor selection or inaccurate leveling can lead to catastrophic wall failures.&lt;/p&gt;
       &lt;p&gt;While hiring a store installation technician often means waiting days and paying ₹600–1,200 in extra visit charges, &lt;strong&gt;mounting your own TV is a completely manageable 45-minute DIY task.&lt;/strong&gt; The secret lies in respecting two golden rules: anchoring deep into structural masonry using heavy-gauge sleeve bolts, and performing precise digital spirit level calibration before drilling a single hole.&lt;/p&gt;
       &lt;h2&gt;Why TV Wall Mounting Goes Wrong in Indian Homes&lt;/h2&gt;
@@ -12374,33 +13964,33 @@
         &lt;p&gt;If you're designing a customized floating TV media console, fluted wooden backdrops with LED cove lighting, or mounting heavy large-screen displays with concealed in-wall cabling, our expert carpenters deliver precision craftsmanship with complete peace of mind. Book verified carpentry specialists across Bangalore in &lt;a href="/services/carpentry/whitefield" style="color: var(--primary); font-weight: bold;"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/carpentry/koramangala" style="color: var(--primary); font-weight: bold;"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/carpentry/indiranagar" style="color: var(--primary); font-weight: bold;"&gt;Indiranagar&lt;/a&gt;, and &lt;a href="/services/carpentry/hsr-layout" style="color: var(--primary); font-weight: bold;"&gt;HSR Layout&lt;/a&gt;.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I80" t="str">
+      <c r="I88" t="str">
         <v>https://images.unsplash.com/photo-1593784991095-a205069470b6?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="81" xml:space="preserve">
-      <c r="A81">
-        <v>80</v>
-      </c>
-      <c r="B81" t="str">
+    <row r="89" xml:space="preserve">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="str">
         <v>fix-wall-cracks-flaking-paint-nail-holes-putty-guide</v>
       </c>
-      <c r="C81" t="str">
+      <c r="C89" t="str">
         <v>Wall Cracks, Flaking Paint, or Old Nail Holes? Here's How to Fix Them Properly with Putty</v>
       </c>
-      <c r="D81" t="str">
+      <c r="D89" t="str">
         <v>Painting</v>
       </c>
-      <c r="E81" t="str">
+      <c r="E89" t="str">
         <v>June 07, 2026</v>
       </c>
-      <c r="F81" t="str">
+      <c r="F89" t="str">
         <v>10 min read</v>
       </c>
-      <c r="G81" t="str">
+      <c r="G89" t="str">
         <v>Peeling wall paint or unsightly nail holes? Learn how to V-groove hairline cracks, apply Birla White putty in thin feathered coats, sand smooth, and prime for a seamless paint finish.</v>
       </c>
-      <c r="H81" t="str" xml:space="preserve">
+      <c r="H89" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;That spiderweb hairline crack creeping across your living room wall. The chalky paint peeling and flaking in the bedroom corner no matter how many times you sweep it away. The cluster of old rusty nail holes left behind by past tenants or relocated art frames. These small blemishes make even the cleanest homes look tired and neglected.&lt;/p&gt;
       &lt;p&gt;The good news: &lt;strong&gt;repairing minor wall cracks, peeling paint patches, and anchor holes with wall putty is one of the most forgiving and satisfying DIY home improvement skills.&lt;/strong&gt; Unlike precision electrical work or plumbing, wall patching does not require expensive power tools — just a flexible putty knife, the right grade of sandpaper, a methodical 2-coat application technique, and a little patience between drying cycles.&lt;/p&gt;
       &lt;h2&gt;Why Wall Cracks and Flaking Happen So Often in Indian Homes&lt;/h2&gt;
@@ -12517,33 +14107,33 @@
         &lt;p&gt;If your home suffers from recurring monsoon wall seepage, ceiling dampness, or requires high-speed dustless machine sanding and premium Royale emulsion painting, our verified painters deliver flawless results with warranty protection. Book certified painting specialists across Bangalore in &lt;a href="/services/painting/whitefield" style="color: var(--primary); font-weight: bold;"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/painting/koramangala" style="color: var(--primary); font-weight: bold;"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/painting/indiranagar" style="color: var(--primary); font-weight: bold;"&gt;Indiranagar&lt;/a&gt;, and &lt;a href="/services/painting/hsr-layout" style="color: var(--primary); font-weight: bold;"&gt;HSR Layout&lt;/a&gt;.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I81" t="str">
+      <c r="I89" t="str">
         <v>https://images.unsplash.com/photo-1589939705384-5185137a7f0f?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="82" xml:space="preserve">
-      <c r="A82">
-        <v>81</v>
-      </c>
-      <c r="B82" t="str">
+    <row r="90" xml:space="preserve">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="str">
         <v>how-to-hang-photo-frames-clocks-mirrors-straight</v>
       </c>
-      <c r="C82" t="str">
+      <c r="C90" t="str">
         <v>How to Hang Photo Frames, Clocks, and Mirrors Straight (Without Them Falling Off Later)</v>
       </c>
-      <c r="D82" t="str">
+      <c r="D90" t="str">
         <v>Carpentry</v>
       </c>
-      <c r="E82" t="str">
+      <c r="E90" t="str">
         <v>June 06, 2026</v>
       </c>
-      <c r="F82" t="str">
+      <c r="F90" t="str">
         <v>10 min read</v>
       </c>
-      <c r="G82" t="str">
+      <c r="G90" t="str">
         <v>Crooked frames or falling mirrors? Master eye-level gallery alignment using phone level apps, dual D-ring measurements, and heavy-duty masonry anchors for up to 15 kg.</v>
       </c>
-      <c r="H82" t="str" xml:space="preserve">
+      <c r="H90" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;You've finally picked out that beautiful framed family portrait, an ornate wall clock, or a full-width decorative foyer mirror. You measure hastily, drive in a nail or screw, hang it up — and five minutes later, you notice it's visibly tilted. Worse, a few weeks later, the anchor pulls out of soft plaster and the mirror comes crashing down onto the floor.&lt;/p&gt;
       &lt;p&gt;Hanging wall decor seems like a trivial weekend chore, but Indian homeowners frequently run into two major stumbling blocks: &lt;strong&gt;visual alignment errors&lt;/strong&gt; (eyeballing "straight" against uneven ceiling cornices or baseboards) and &lt;strong&gt;dangerous anchor mismatches&lt;/strong&gt; (using a flimsy 6mm plastic plug to hold a 12 kg bevelled mirror). Both are completely preventable when you combine a digital level app with proper masonry wall anchor engineering.&lt;/p&gt;
       &lt;h2&gt;Why Wall Hanging Goes Wrong in Indian Homes&lt;/h2&gt;
@@ -12659,33 +14249,33 @@
         &lt;p&gt;If you're installing full-length dressing mirrors, heavy backlit LED bathroom vanities, or complex wall panelling displays, our expert carpenters ensure rock-solid structural anchoring and flawless alignment. Book verified carpentry specialists across Bangalore in &lt;a href="/services/carpentry/whitefield" style="color: var(--primary); font-weight: bold;"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/carpentry/koramangala" style="color: var(--primary); font-weight: bold;"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/carpentry/indiranagar" style="color: var(--primary); font-weight: bold;"&gt;Indiranagar&lt;/a&gt;, and &lt;a href="/services/carpentry/hsr-layout" style="color: var(--primary); font-weight: bold;"&gt;HSR Layout&lt;/a&gt;.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I82" t="str">
+      <c r="I90" t="str">
         <v>https://images.unsplash.com/photo-1513519245088-0e12902e5a38?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="83" xml:space="preserve">
-      <c r="A83">
-        <v>82</v>
-      </c>
-      <c r="B83" t="str">
+    <row r="91" xml:space="preserve">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="str">
         <v>how-to-drill-wall-without-cracking-tiles-hitting-wires</v>
       </c>
-      <c r="C83" t="str">
+      <c r="C91" t="str">
         <v>How to Drill a Wall Perfectly Without Cracking Tiles, Hitting Wires, or Wasting Screws</v>
       </c>
-      <c r="D83" t="str">
+      <c r="D91" t="str">
         <v>Carpentry</v>
       </c>
-      <c r="E83" t="str">
+      <c r="E91" t="str">
         <v>June 05, 2026</v>
       </c>
-      <c r="F83" t="str">
+      <c r="F91" t="str">
         <v>10 min read</v>
       </c>
-      <c r="G83" t="str">
+      <c r="G91" t="str">
         <v>Cracked bathroom tiles or spinning wall plugs? Master clean drilling across RCC concrete, brick masonry, and glazed tiles without hitting concealed electrical wires or plumbing.</v>
       </c>
-      <c r="H83" t="str" xml:space="preserve">
+      <c r="H91" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;You want to hang a family photo frame, mount a heavy curtain rod, fix floating bookshelf brackets, or install a 55-inch TV wall mount. Sounds like a simple 10-minute job — until you actually switch on the drill machine in an Indian apartment. Either the bathroom tile shatters with an ugly diagonal crack, you hit an embedded metal rebar with alarming sparks, or the drilled hole turns out so powdery and loose that your plastic wall plug (*gitti*) spins in circles without holding any weight.&lt;/p&gt;
       &lt;p&gt;Drilling into a wall seems like the most basic DIY task, but in Indian construction (where homes feature a mix of dense RCC columns, red clay brick, porous AAC blocks, and vitrified tiles), one wrong move can damage concealed conduit pipes or ruin expensive wall finishes. The good news: &lt;strong&gt;with the right drill bit, proper rotary vs hammer speed control, and a systematic 10-step sequence, anyone can drill neat, rock-solid anchor holes cleanly.&lt;/strong&gt;&lt;/p&gt;
       &lt;h2&gt;Why Drilling Goes Wrong So Often in Indian Homes&lt;/h2&gt;
@@ -12805,33 +14395,33 @@
         &lt;p&gt;If you're installing customized floating TV media units, large crockery lofts, or heavy wall-hung vanities, our expert carpenters are equipped with high-torque rotary tools and structural fasteners for a pristine finish. Book verified carpentry specialists across Bangalore in &lt;a href="/services/carpentry/whitefield" style="color: var(--primary); font-weight: bold;"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/carpentry/koramangala" style="color: var(--primary); font-weight: bold;"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/carpentry/indiranagar" style="color: var(--primary); font-weight: bold;"&gt;Indiranagar&lt;/a&gt;, and &lt;a href="/services/carpentry/hsr-layout" style="color: var(--primary); font-weight: bold;"&gt;HSR Layout&lt;/a&gt;.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I83" t="str">
+      <c r="I91" t="str">
         <v>https://images.unsplash.com/photo-1504148455328-c376907d081c?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="84" xml:space="preserve">
-      <c r="A84">
-        <v>83</v>
-      </c>
-      <c r="B84" t="str">
+    <row r="92" xml:space="preserve">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="str">
         <v>electrical-safety-basics-testers-tape-mcbs-guide</v>
       </c>
-      <c r="C84" t="str">
+      <c r="C92" t="str">
         <v>Electrical Safety Basics Every Indian Homeowner Should Know: Testers, Tape, and MCBs</v>
       </c>
-      <c r="D84" t="str">
+      <c r="D92" t="str">
         <v>Electrical</v>
       </c>
-      <c r="E84" t="str">
+      <c r="E92" t="str">
         <v>June 04, 2026</v>
       </c>
-      <c r="F84" t="str">
+      <c r="F92" t="str">
         <v>10 min read</v>
       </c>
-      <c r="G84" t="str">
+      <c r="G92" t="str">
         <v>Master fundamental home electrical safety: how to test live phase wires with a neon tester, wrap 50% overlapping flame-retardant PVC tape, and safely reset and map tripped DB box MCBs.</v>
       </c>
-      <c r="H84" t="str" xml:space="preserve">
+      <c r="H92" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;Your lights suddenly go off in one part of the house while the rest works fine. Or you're about to touch a wire and have that split-second "wait, is this actually off?" moment. Or you've opened your DB box (distribution board) and you're staring at a row of switches, completely unsure which one to flip back on.&lt;/p&gt;
       &lt;p&gt;This article is different from our other electrical guides — instead of walking you through one specific repair, this is the &lt;strong&gt;foundation skill set&lt;/strong&gt; you need before doing any electrical DIY safely: using a neon line tester correctly, applying electrical insulation tape properly, and understanding your MCB box well enough to reset a tripped breaker with confidence instead of guesswork.&lt;/p&gt;
       &lt;h2&gt;Why Every Indian Homeowner Needs This Skill Set&lt;/h2&gt;
@@ -12941,33 +14531,33 @@
         &lt;p&gt;If your distribution panel needs clean rewiring, fresh RCCB installation, or dedicated AC/geyser line additions, our licensed electricians are ready with transparent pricing and verified expertise. Book doorstep electrical specialists across Bangalore in &lt;a href="/services/electrical/whitefield" style="color: var(--primary); font-weight: bold;"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/electrical/koramangala" style="color: var(--primary); font-weight: bold;"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/electrical/indiranagar" style="color: var(--primary); font-weight: bold;"&gt;Indiranagar&lt;/a&gt;, and &lt;a href="/services/electrical/hsr-layout" style="color: var(--primary); font-weight: bold;"&gt;HSR Layout&lt;/a&gt;.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I84" t="str">
+      <c r="I92" t="str">
         <v>https://images.unsplash.com/photo-1621905251189-08b45d6a269e?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="85" xml:space="preserve">
-      <c r="A85">
-        <v>84</v>
-      </c>
-      <c r="B85" t="str">
+    <row r="93" xml:space="preserve">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="str">
         <v>doorbell-not-working-fix-replace-wireless-guide</v>
       </c>
-      <c r="C85" t="str">
+      <c r="C93" t="str">
         <v>Doorbell Not Working? Here's How to Fix, Replace, or Upgrade It to Wireless</v>
       </c>
-      <c r="D85" t="str">
+      <c r="D93" t="str">
         <v>Electrical</v>
       </c>
-      <c r="E85" t="str">
+      <c r="E93" t="str">
         <v>June 03, 2026</v>
       </c>
-      <c r="F85" t="str">
+      <c r="F93" t="str">
         <v>10 min read</v>
       </c>
-      <c r="G85" t="str">
+      <c r="G93" t="str">
         <v>Silent chime or sticky outdoor bell switch? Learn how to diagnose button continuity, replace 240V buzzers, weatherproof with M-Seal, or upgrade to a wireless doorbell in 20 minutes.</v>
       </c>
-      <c r="H85" t="str" xml:space="preserve">
+      <c r="H93" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;You press the doorbell button outside your front door, and... nothing. Or it rings faintly, buzzes intermittently, or only works if visitors press the switch at a strange 45-degree angle. Or your indoor chime unit has just gone completely silent.&lt;/p&gt;
       &lt;p&gt;Doorbell issues are one of those small annoyances that Indian homeowners and tenants tend to live with for months — partly because it feels like a minor issue, and partly because most people assume it requires an electrician's visit costing ₹300–500. It usually doesn't. In most cases, this is a &lt;strong&gt;straightforward 20–30 minute DIY fix&lt;/strong&gt; involving either the outdoor push button, the wiring, or the buzzer unit itself — and upgrading to a modern wireless doorbell sidesteps in-wall wiring issues entirely.&lt;/p&gt;
       &lt;h2&gt;Why Doorbells Fail So Often in Indian Homes&lt;/h2&gt;
@@ -13090,33 +14680,33 @@
         &lt;p&gt;If you're installing a smart video doorbell system, upgrading your distribution board, or rewiring damaged conduit lines, our licensed electricians provide prompt, transparent doorstep service. Book verified electrical specialists across Bangalore in &lt;a href="/services/electrical/whitefield" style="color: var(--primary); font-weight: bold;"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/electrical/koramangala" style="color: var(--primary); font-weight: bold;"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/electrical/indiranagar" style="color: var(--primary); font-weight: bold;"&gt;Indiranagar&lt;/a&gt;, and &lt;a href="/services/electrical/hsr-layout" style="color: var(--primary); font-weight: bold;"&gt;HSR Layout&lt;/a&gt;.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I85" t="str">
+      <c r="I93" t="str">
         <v>https://images.unsplash.com/photo-1558002038-1055907df827?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="86" xml:space="preserve">
-      <c r="A86">
-        <v>85</v>
-      </c>
-      <c r="B86" t="str">
+    <row r="94" xml:space="preserve">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="str">
         <v>how-to-fix-noisy-wobbling-slow-ceiling-fan</v>
       </c>
-      <c r="C86" t="str">
+      <c r="C94" t="str">
         <v>How to Fix a Noisy, Wobbling, or Slow Ceiling Fan? Here's the Complete Fix</v>
       </c>
-      <c r="D86" t="str">
+      <c r="D94" t="str">
         <v>Electrical</v>
       </c>
-      <c r="E86" t="str">
+      <c r="E94" t="str">
         <v>June 02, 2026</v>
       </c>
-      <c r="F86" t="str">
+      <c r="F94" t="str">
         <v>10 min read</v>
       </c>
-      <c r="G86" t="str">
+      <c r="G94" t="str">
         <v>Wobbly ceiling fan or slow blade speed? Learn how to tighten down-rod shackle bolts, balance blades using the coin test, and replace 2.25 µF motor capacitors in 30 minutes.</v>
       </c>
-      <c r="H86" t="str" xml:space="preserve">
+      <c r="H94" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;That ticking or grinding sound from your ceiling fan every night. The visible wobble that makes you nervously glance up every time you walk under it. Or the blades barely turning even at full speed, while the room stays hot and humid.&lt;/p&gt;
       &lt;p&gt;These are three of the most common ceiling fan complaints in Indian homes, and here's the good news: &lt;strong&gt;all three usually come down to one of three fixable causes&lt;/strong&gt; — a loose down-rod shackle, unbalanced dusty blades, or a degraded motor capacitor. None of these need an electrician's visit costing ₹300–500. With basic tools and 30–45 minutes, you can fix this yourself.&lt;/p&gt;
       &lt;h2&gt;Why Ceiling Fans Act Up So Often in Indian Homes&lt;/h2&gt;
@@ -13223,33 +14813,33 @@
         &lt;p&gt;If your ceiling fan requires new heavy-duty anchor fasteners, bearing replacements, or complete decorative fan installations in high ceilings, our licensed electricians are ready to help. Book verified doorstep electrical specialists across Bangalore in &lt;a href="/services/electrical/whitefield" style="color: var(--primary); font-weight: bold;"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/electrical/koramangala" style="color: var(--primary); font-weight: bold;"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/electrical/indiranagar" style="color: var(--primary); font-weight: bold;"&gt;Indiranagar&lt;/a&gt;, and &lt;a href="/services/electrical/hsr-layout" style="color: var(--primary); font-weight: bold;"&gt;HSR Layout&lt;/a&gt;.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I86" t="str">
+      <c r="I94" t="str">
         <v>https://images.unsplash.com/photo-1595846519845-68e298c2edd8?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="87" xml:space="preserve">
-      <c r="A87">
-        <v>86</v>
-      </c>
-      <c r="B87" t="str">
+    <row r="95" xml:space="preserve">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="str">
         <v>step-by-step-guide-changing-damaged-wall-switch-socket</v>
       </c>
-      <c r="C87" t="str">
+      <c r="C95" t="str">
         <v>Step-by-Step Guide to Changing a Damaged Wall Switch or Socket</v>
       </c>
-      <c r="D87" t="str">
+      <c r="D95" t="str">
         <v>Electrical</v>
       </c>
-      <c r="E87" t="str">
+      <c r="E95" t="str">
         <v>June 01, 2026</v>
       </c>
-      <c r="F87" t="str">
+      <c r="F95" t="str">
         <v>10 min read</v>
       </c>
-      <c r="G87" t="str">
+      <c r="G95" t="str">
         <v>Sparking switch or loose plug socket? Learn how to safely isolate DB box MCBs, test phase lines with a neon tester, and replace modular switches and 16A power sockets in 20 minutes.</v>
       </c>
-      <c r="H87" t="str" xml:space="preserve">
+      <c r="H95" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;That little snap-crackle spark when you plug in your phone charger. The water geyser switch that feels loose, spongy, or warm to the touch. The laptop plug that keeps falling out of the 3-pin socket because the internal brass grip has lost its tension. A damaged wall switch or socket isn't just an everyday irritation — in Indian homes with high load demands, a loose or burned switch is a real short-circuit and electrical fire hazard.&lt;/p&gt;
       &lt;p&gt;Calling an electrician for a single ₹30 switch replacement usually means waiting days and paying a ₹300–500 service visit fee. The truth is: &lt;strong&gt;replacing a modern modular switch or 6A/16A socket is a straightforward 20-minute DIY task&lt;/strong&gt; that any homeowner or tenant can safely perform, provided you respect electrical safety protocols and know how to verify Phase, Neutral, and Earth lines with a neon tester.&lt;/p&gt;
       &lt;h2&gt;Why Switches and Sockets Fail So Often in Indian Homes&lt;/h2&gt;
@@ -13381,33 +14971,33 @@
         &lt;p&gt;If your switchboard needs new 16A power lines, ELCB earthing diagnostics, or complete modular plate upgrades across your home, our licensed electricians are available with same-day doorstep service. Book verified electrical specialists across Bangalore in &lt;a href="/services/electrical/whitefield" style="color: var(--primary); font-weight: bold;"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/electrical/koramangala" style="color: var(--primary); font-weight: bold;"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/electrical/indiranagar" style="color: var(--primary); font-weight: bold;"&gt;Indiranagar&lt;/a&gt;, and &lt;a href="/services/electrical/hsr-layout" style="color: var(--primary); font-weight: bold;"&gt;HSR Layout&lt;/a&gt;.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I87" t="str">
+      <c r="I95" t="str">
         <v>https://images.unsplash.com/photo-1558494949-ef010cbdcc31?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="88" xml:space="preserve">
-      <c r="A88">
-        <v>87</v>
-      </c>
-      <c r="B88" t="str">
+    <row r="96" xml:space="preserve">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="str">
         <v>tubelight-flickering-replacement-led-batten-upgrade</v>
       </c>
-      <c r="C88" t="str">
+      <c r="C96" t="str">
         <v>Tubelight Flickering or Dead? Here's How to Replace It (or Upgrade to LED Batten) Safely</v>
       </c>
-      <c r="D88" t="str">
+      <c r="D96" t="str">
         <v>Electrical</v>
       </c>
-      <c r="E88" t="str">
+      <c r="E96" t="str">
         <v>May 31, 2026</v>
       </c>
-      <c r="F88" t="str">
+      <c r="F96" t="str">
         <v>9 min read</v>
       </c>
-      <c r="G88" t="str">
+      <c r="G96" t="str">
         <v>Annoying tubelight flicker or choke buzzing? Learn how to safely replace fluorescent tubes, troubleshoot starters, and upgrade to energy-saving LED battens in 20 minutes.</v>
       </c>
-      <c r="H88" t="str" xml:space="preserve">
+      <c r="H96" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;That old tubelight in your hall or kitchen has been flickering for weeks. Or it's making that annoying buzzing sound before switching on. Or it's just gone completely dead, and you're standing on a stool staring at it, wondering if this is a "call an electrician" job or something you can handle yourself.&lt;/p&gt;
       &lt;p&gt;Here's the honest answer: &lt;strong&gt;replacing a tubelight, or upgrading the entire fitting to a modern LED batten, is one of the most beginner-friendly electrical jobs in the house&lt;/strong&gt; — as long as you respect the mains switch and follow the steps in order. No rewiring is needed for a straight swap, and even the LED batten upgrade is mostly straightforward mechanical mounting.&lt;/p&gt;
       &lt;h2&gt;Why This Keeps Happening in Indian Homes&lt;/h2&gt;
@@ -13515,33 +15105,33 @@
         &lt;p&gt;If your DB box needs an ELCB upgrade, your switchboard is sparking, or you require heavy appliance load wiring for geysers and ACs, our licensed electricians are ready to help. Book verified doorstep electrical specialists across Bangalore in &lt;a href="/services/electrical/whitefield" style="color: var(--primary); font-weight: bold;"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/electrical/koramangala" style="color: var(--primary); font-weight: bold;"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/electrical/indiranagar" style="color: var(--primary); font-weight: bold;"&gt;Indiranagar&lt;/a&gt;, and &lt;a href="/services/electrical/hsr-layout" style="color: var(--primary); font-weight: bold;"&gt;HSR Layout&lt;/a&gt;.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I88" t="str">
+      <c r="I96" t="str">
         <v>https://images.unsplash.com/photo-1513506003901-1e6a229e2d15?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="89" xml:space="preserve">
-      <c r="A89">
-        <v>88</v>
-      </c>
-      <c r="B89" t="str">
+    <row r="97" xml:space="preserve">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="str">
         <v>ro-water-filter-cleaning-replacement-guide</v>
       </c>
-      <c r="C89" t="str">
+      <c r="C97" t="str">
         <v>RO Water Not Tasting Right? Here's How to Clean Your Filters at Home</v>
       </c>
-      <c r="D89" t="str">
+      <c r="D97" t="str">
         <v>Plumbing</v>
       </c>
-      <c r="E89" t="str">
+      <c r="E97" t="str">
         <v>May 30, 2026</v>
       </c>
-      <c r="F89" t="str">
+      <c r="F97" t="str">
         <v>9 min read</v>
       </c>
-      <c r="G89" t="str">
+      <c r="G97" t="str">
         <v>Tired of foul-tasting water or weak purifier flow? Learn how to safely replace sediment pre-filter sponges, descale housing bowls, and inspect push-fit RO pipes in 15 minutes.</v>
       </c>
-      <c r="H89" t="str" xml:space="preserve">
+      <c r="H97" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;Your RO water suddenly tastes off. Or the flow has slowed to a trickle. Or that "Filter Change" light on your Kent, Aquaguard, Pureit, or Livpure unit has been blinking for weeks and you've been ignoring it. Sound familiar?&lt;/p&gt;
       &lt;p&gt;Most Indian households now run an RO purifier full-time, and most of us call the service technician for even the smallest filter change — paying ₹300–600 as a "visit charge" plus inflated filter costs, for a job that genuinely takes 15 minutes once you know what you're doing.&lt;/p&gt;
       &lt;h2&gt;Why RO Filters Clog Up Fast in Indian Homes&lt;/h2&gt;
@@ -13666,33 +15256,33 @@
         &lt;p&gt;If your water purifier requires complete 4-stage filter overhauls, TDS recalibration, booster pump rewinding, or kitchen under-sink plumbing diverters, our verified technicians are ready to help. Book verified doorstep specialists in &lt;a href="/services/plumbing/whitefield" style="color: var(--primary); font-weight: bold;"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/plumbing/koramangala" style="color: var(--primary); font-weight: bold;"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/plumbing/indiranagar" style="color: var(--primary); font-weight: bold;"&gt;Indiranagar&lt;/a&gt;, and &lt;a href="/services/plumbing/hsr-layout" style="color: var(--primary); font-weight: bold;"&gt;HSR Layout&lt;/a&gt;.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I89" t="str">
+      <c r="I97" t="str">
         <v>https://images.unsplash.com/photo-1548839140-29a749e1bc4e?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="90" xml:space="preserve">
-      <c r="A90">
-        <v>89</v>
-      </c>
-      <c r="B90" t="str">
+    <row r="98" xml:space="preserve">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="str">
         <v>flush-tank-running-continuously-diy-fix</v>
       </c>
-      <c r="C90" t="str">
+      <c r="C98" t="str">
         <v>Flush Tank Running Continuously? Here's How to Fix It Yourself</v>
       </c>
-      <c r="D90" t="str">
+      <c r="D98" t="str">
         <v>Plumbing</v>
       </c>
-      <c r="E90" t="str">
+      <c r="E98" t="str">
         <v>May 29, 2026</v>
       </c>
-      <c r="F90" t="str">
+      <c r="F98" t="str">
         <v>9 min read</v>
       </c>
-      <c r="G90" t="str">
+      <c r="G98" t="str">
         <v>Stop the constant hissing sound and high water bills. Learn how to diagnose, descale, and repair a running flush tank, float ball-valve, and siphon flapper in under an hour.</v>
       </c>
-      <c r="H90" t="str" xml:space="preserve">
+      <c r="H98" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;That hissing sound from your bathroom at 2 AM. The water bill that's mysteriously gone up by 30%. The flush tank that just won't stop filling. If you're dealing with a &lt;strong&gt;continuously running flush tank&lt;/strong&gt;, you're not alone — it's one of the most common plumbing complaints in Indian homes, whether you're in a Mumbai high-rise, a Bangalore independent house, or a Delhi builder-floor.&lt;/p&gt;
       &lt;h2&gt;Why This Happens So Often in Indian Homes&lt;/h2&gt;
       &lt;p&gt;Before you call a plumber and pay ₹300–500 for a 10-minute job, understand the root causes — because 90% of the time, this is a job you can do yourself in under an hour with inexpensive spare parts:&lt;/p&gt;
@@ -13806,33 +15396,33 @@
         &lt;p&gt;If your concealed wall-hung flush tank is leaking, your commode needs reseating, or you are renovating your bathroom with wall-mounted sanitaryware, our verified plumbing engineers are available across Bangalore. Book verified specialists in &lt;a href="/services/plumbing/whitefield" style="color: var(--primary); font-weight: bold;"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/plumbing/koramangala" style="color: var(--primary); font-weight: bold;"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/plumbing/indiranagar" style="color: var(--primary); font-weight: bold;"&gt;Indiranagar&lt;/a&gt;, and &lt;a href="/services/plumbing/hsr-layout" style="color: var(--primary); font-weight: bold;"&gt;HSR Layout&lt;/a&gt;.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I90" t="str">
+      <c r="I98" t="str">
         <v>https://images.unsplash.com/photo-1584622650111-993a426fbf0a?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="91" xml:space="preserve">
-      <c r="A91">
-        <v>90</v>
-      </c>
-      <c r="B91" t="str">
+    <row r="99" xml:space="preserve">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="str">
         <v>how-to-change-damaged-health-faucet-jet-spray</v>
       </c>
-      <c r="C91" t="str">
+      <c r="C99" t="str">
         <v>How to Change a Damaged Health Faucet or Jet Spray Yourself</v>
       </c>
-      <c r="D91" t="str">
+      <c r="D99" t="str">
         <v>Plumbing</v>
       </c>
-      <c r="E91" t="str">
+      <c r="E99" t="str">
         <v>May 28, 2026</v>
       </c>
-      <c r="F91" t="str">
+      <c r="F99" t="str">
         <v>8 min read</v>
       </c>
-      <c r="G91" t="str">
+      <c r="G99" t="str">
         <v>Leaking or stuck jet spray? Learn how to replace a damaged health faucet, verify thread compatibility, seal angle valves with Teflon tape, and clear hard water nozzle clogs in 20 minutes.</v>
       </c>
-      <c r="H91" t="str" xml:space="preserve">
+      <c r="H99" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;That constant hiss from your health faucet even when it's not in use. The trigger that stays stuck halfway. Water leaking from the connection point every time someone uses it. A broken health faucet (jet spray) is one of the most common bathroom complaints in Indian homes — and thankfully, one of the easiest plumbing fixes to DIY, usually done in under 20 minutes.&lt;/p&gt;
       &lt;h2&gt;Why Health Faucets Fail So Often in Indian Homes&lt;/h2&gt;
       &lt;p&gt;Health faucets in Indian households endure continuous physical and chemical stress compared to standard bathroom fittings:&lt;/p&gt;
@@ -13923,33 +15513,33 @@
         &lt;p&gt;If your angle stop-cock is jammed inside the wall, your concealed flush tank is leaking, or you are upgrading your bathroom with luxury wall-hung commodes, our certified plumbers are ready to help. Book verified doorstep specialists across Bangalore in &lt;a href="/services/plumbing/whitefield" style="color: var(--primary); font-weight: bold;"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/plumbing/koramangala" style="color: var(--primary); font-weight: bold;"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/plumbing/indiranagar" style="color: var(--primary); font-weight: bold;"&gt;Indiranagar&lt;/a&gt;, and &lt;a href="/services/plumbing/hsr-layout" style="color: var(--primary); font-weight: bold;"&gt;HSR Layout&lt;/a&gt;.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I91" t="str">
+      <c r="I99" t="str">
         <v>https://images.unsplash.com/photo-1584622650111-993a426fbf0a?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="92" xml:space="preserve">
-      <c r="A92">
-        <v>91</v>
-      </c>
-      <c r="B92" t="str">
+    <row r="100" xml:space="preserve">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="str">
         <v>unclogging-bathroom-kitchen-drains-household-items</v>
       </c>
-      <c r="C92" t="str">
+      <c r="C100" t="str">
         <v>Unclogging Bathroom and Kitchen Drains Using Household Items</v>
       </c>
-      <c r="D92" t="str">
+      <c r="D100" t="str">
         <v>Plumbing</v>
       </c>
-      <c r="E92" t="str">
+      <c r="E100" t="str">
         <v>May 27, 2026</v>
       </c>
-      <c r="F92" t="str">
+      <c r="F100" t="str">
         <v>9 min read</v>
       </c>
-      <c r="G92" t="str">
+      <c r="G100" t="str">
         <v>Water pooling in your shower or kitchen sink? Learn safe, chemical-free methods to clear choked drains using baking soda, vinegar, plungers, and bottle-trap cleanouts.</v>
       </c>
-      <c r="H92" t="str" xml:space="preserve">
+      <c r="H100" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;Water pooling around your feet in the shower. The kitchen sink draining slower every day until it just... stops. A choked drain is one of the most common household headaches in India, and most people either panic-call a plumber for something they could fix in 15 minutes, or dump a bottle of harsh chemical drain cleaner down the pipe and hope for the best. There's a better way — and it's sitting in your kitchen right now.&lt;/p&gt;
       &lt;h2&gt;Why Drains Clog So Often in Indian Homes&lt;/h2&gt;
       &lt;p&gt;Drainage systems in Indian apartments and houses face distinct buildup factors that gradually restrict waste water flow:&lt;/p&gt;
@@ -14057,33 +15647,33 @@
         &lt;p&gt;If your bathroom gully traps, kitchen main waste lines, or terrace stormwater downpipes are completely choked, our verified plumbing specialists carry commercial motorized drain snakes and pressure jetters. Explore our &lt;a href="/services/plumbing" style="color: var(--primary); font-weight: bold;"&gt;Drain Cleaning &amp;amp; Plumbing Services&lt;/a&gt; or book local plumbers in &lt;a href="/services/plumbing/whitefield" style="color: var(--primary); font-weight: bold;"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/plumbing/koramangala" style="color: var(--primary); font-weight: bold;"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/plumbing/indiranagar" style="color: var(--primary); font-weight: bold;"&gt;Indiranagar&lt;/a&gt;, and &lt;a href="/services/plumbing/hsr-layout" style="color: var(--primary); font-weight: bold;"&gt;HSR Layout&lt;/a&gt;.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I92" t="str">
+      <c r="I100" t="str">
         <v>https://images.unsplash.com/photo-1504148455328-497c5efdf13d?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="93" xml:space="preserve">
-      <c r="A93">
-        <v>92</v>
-      </c>
-      <c r="B93" t="str">
+    <row r="101" xml:space="preserve">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="str">
         <v>how-to-fix-leaking-pipe-dripping-tap</v>
       </c>
-      <c r="C93" t="str">
+      <c r="C101" t="str">
         <v>How to Fix a Leaking Pipe &amp; Dripping Tap: A Step-by-Step Guide</v>
       </c>
-      <c r="D93" t="str">
+      <c r="D101" t="str">
         <v>Plumbing</v>
       </c>
-      <c r="E93" t="str">
+      <c r="E101" t="str">
         <v>May 26, 2026</v>
       </c>
-      <c r="F93" t="str">
+      <c r="F101" t="str">
         <v>9 min read</v>
       </c>
-      <c r="G93" t="str">
+      <c r="G101" t="str">
         <v>Wasting water and losing sleep over a dripping tap? Learn how to replace worn-out washers, reseal threaded pipe joints with Teflon tape, and apply emergency M-Seal patches.</v>
       </c>
-      <c r="H93" t="str" xml:space="preserve">
+      <c r="H101" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;That "tip... tip... tip..." sound at 2 AM. The water bill that's mysteriously higher this month. The damp patch spreading under the kitchen sink. A dripping tap or leaking pipe joint isn't just annoying — left alone, it wastes thousands of litres a year and can quietly cause seepage damage to your walls and cabinets. Most of these fixes cost under ₹150 and take 20–30 minutes once you know the process.&lt;/p&gt;
       &lt;h2&gt;Why Taps and Pipes Leak So Often in Indian Homes&lt;/h2&gt;
       &lt;p&gt;Plumbing systems in Indian flats and houses undergo continuous wear from local water conditions and pressure variations:&lt;/p&gt;
@@ -14189,33 +15779,33 @@
         &lt;p&gt;If you have hidden in-wall pipe bursts, corroded GI line replacement needs, or want to upgrade to premium CPVC pipelines, our certified plumbers are ready to assist. Calculate your leakage loss with the &lt;a href="/services/plumbing#calculator" style="color: var(--primary); font-weight: bold;"&gt;Water Wastage Calculator&lt;/a&gt; or book verified local plumbers across Bangalore in &lt;a href="/services/plumbing/whitefield" style="color: var(--primary); font-weight: bold;"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/plumbing/koramangala" style="color: var(--primary); font-weight: bold;"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/plumbing/indiranagar" style="color: var(--primary); font-weight: bold;"&gt;Indiranagar&lt;/a&gt;, and &lt;a href="/services/plumbing/hsr-layout" style="color: var(--primary); font-weight: bold;"&gt;HSR Layout&lt;/a&gt;.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I93" t="str">
+      <c r="I101" t="str">
         <v>https://images.unsplash.com/photo-1584622650111-993a426fbf0a?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="94" xml:space="preserve">
-      <c r="A94">
-        <v>93</v>
-      </c>
-      <c r="B94" t="str">
+    <row r="102" xml:space="preserve">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="str">
         <v>how-to-install-magnetic-door-catchers-tower-bolts</v>
       </c>
-      <c r="C94" t="str">
+      <c r="C102" t="str">
         <v>How to Install Magnetic Door Catchers and Tower Bolts at Home</v>
       </c>
-      <c r="D94" t="str">
+      <c r="D102" t="str">
         <v>Carpentry</v>
       </c>
-      <c r="E94" t="str">
+      <c r="E102" t="str">
         <v>May 25, 2026</v>
       </c>
-      <c r="F94" t="str">
+      <c r="F102" t="str">
         <v>9 min read</v>
       </c>
-      <c r="G94" t="str">
+      <c r="G102" t="str">
         <v>Tired of balcony doors slamming during monsoon winds? Learn how to install heavy-duty magnetic door catchers and align tower bolts (kundis) without cracking floor tiles.</v>
       </c>
-      <c r="H94" t="str" xml:space="preserve">
+      <c r="H102" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;That bang your balcony door makes every time the wind picks up before monsoon rains hit? It's not just annoying — it's slowly cracking your glass panes, loosening your hinges, and rattling everyone's nerves. The fix is a ₹100–200 hardware job: a magnetic door catcher or a properly aligned tower bolt (aka the classic &lt;em&gt;saakal/kundi&lt;/em&gt;). Here's how to install both correctly.&lt;/p&gt;
       &lt;h2&gt;Why This Is Such a Common Problem in Indian Homes&lt;/h2&gt;
       &lt;p&gt;Doors in Indian apartments and independent houses are exposed to severe atmospheric forces and everyday hardware oversights:&lt;/p&gt;
@@ -14305,33 +15895,33 @@
         &lt;p&gt;If you prefer an expert to drill safely into designer vitrified tiles, install multi-point balcony locks, or realign heavy solid teak doors, our verified carpenters are ready to assist across Bangalore. Explore our &lt;a href="/services/carpentry" style="color: var(--primary); font-weight: bold;"&gt;Door &amp;amp; Hardware Carpentry Services&lt;/a&gt; or book verified specialists in &lt;a href="/services/carpentry/indiranagar" style="color: var(--primary); font-weight: bold;"&gt;Indiranagar&lt;/a&gt;, &lt;a href="/services/carpentry/koramangala" style="color: var(--primary); font-weight: bold;"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/carpentry/whitefield" style="color: var(--primary); font-weight: bold;"&gt;Whitefield&lt;/a&gt;, and &lt;a href="/services/carpentry/hsr-layout" style="color: var(--primary); font-weight: bold;"&gt;HSR Layout&lt;/a&gt;.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I94" t="str">
+      <c r="I102" t="str">
         <v>https://images.unsplash.com/photo-1513694203232-719a280e022f?q=80&amp;w=2069&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="95" xml:space="preserve">
-      <c r="A95">
-        <v>94</v>
-      </c>
-      <c r="B95" t="str">
+    <row r="103" xml:space="preserve">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="str">
         <v>fixing-stuck-drawers-jammed-sliding-wardrobe-tracks</v>
       </c>
-      <c r="C95" t="str">
+      <c r="C103" t="str">
         <v>Fixing Stuck Drawers and Jammed Sliding Wardrobe Tracks</v>
       </c>
-      <c r="D95" t="str">
+      <c r="D103" t="str">
         <v>Carpentry</v>
       </c>
-      <c r="E95" t="str">
+      <c r="E103" t="str">
         <v>May 24, 2026</v>
       </c>
-      <c r="F95" t="str">
+      <c r="F103" t="str">
         <v>9 min read</v>
       </c>
-      <c r="G95" t="str">
+      <c r="G103" t="str">
         <v>Stiff drawers or sticking sliding wardrobe doors? Discover simple DIY techniques for Indian homes—from vacuuming debris and applying candle wax to replacing worn-out roller wheels.</v>
       </c>
-      <c r="H95" t="str" xml:space="preserve">
+      <c r="H103" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;You yank the drawer, it moves an inch, then stops dead. Or your sliding wardrobe door needs a running start and a prayer to open smoothly. This is one of the most common complaints in Indian homes with modular furniture — and almost always, it's not the furniture that's broken. It's just dirty, dry, or has one small worn-out part.&lt;/p&gt;
       &lt;h2&gt;Why Drawers and Sliding Tracks Jam So Often in Indian Homes&lt;/h2&gt;
       &lt;p&gt;Modular drawers and sliding wardrobes in India operate in environments with unique environmental factors:&lt;/p&gt;
@@ -14437,33 +16027,33 @@
         &lt;p&gt;If your sliding wardrobe doors need heavy-duty top track replacements, soft-close channel retrofits, or custom drawer box carpentry, our verified local carpenters are ready to help. Explore our &lt;a href="/services/carpentry" style="color: var(--primary); font-weight: bold;"&gt;Wardrobe &amp;amp; Furniture Carpentry Services&lt;/a&gt; or book verified specialists in &lt;a href="/services/carpentry/whitefield" style="color: var(--primary); font-weight: bold;"&gt;Whitefield&lt;/a&gt;, &lt;a href="/services/carpentry/indiranagar" style="color: var(--primary); font-weight: bold;"&gt;Indiranagar&lt;/a&gt;, &lt;a href="/services/carpentry/koramangala" style="color: var(--primary); font-weight: bold;"&gt;Koramangala&lt;/a&gt;, and &lt;a href="/services/carpentry/hsr-layout" style="color: var(--primary); font-weight: bold;"&gt;HSR Layout&lt;/a&gt;.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I95" t="str">
+      <c r="I103" t="str">
         <v>https://images.unsplash.com/photo-1595428774223-ef52624120d2?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="96" xml:space="preserve">
-      <c r="A96">
-        <v>95</v>
-      </c>
-      <c r="B96" t="str">
+    <row r="104" xml:space="preserve">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="str">
         <v>diy-guide-replacing-broken-door-lock</v>
       </c>
-      <c r="C96" t="str">
+      <c r="C104" t="str">
         <v>DIY Guide to Replacing a Broken Door Lock (Mortise Locks &amp; Cylindrical Handles)</v>
       </c>
-      <c r="D96" t="str">
+      <c r="D104" t="str">
         <v>Carpentry</v>
       </c>
-      <c r="E96" t="str">
+      <c r="E104" t="str">
         <v>May 23, 2026</v>
       </c>
-      <c r="F96" t="str">
+      <c r="F104" t="str">
         <v>10 min read</v>
       </c>
-      <c r="G96" t="str">
+      <c r="G104" t="str">
         <v>A jammed key, stuck latch, or loose handle doesn’t always need a carpenter. Follow this step-by-step DIY guide to replace mortise locks and cylindrical knobs in Indian homes—from cavity chiseling to strike plate alignment.</v>
       </c>
-      <c r="H96" t="str" xml:space="preserve">
+      <c r="H104" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;A handle that comes off in your hand. A key that turns but the latch doesn't budge. A lock that's jammed shut with you standing on the wrong side of the door. Broken door locks are one of those problems that feel like they need a professional — but replacing a mortise lock body or swapping out a bedroom cylindrical knob is genuinely a beginner-friendly job once you understand how the parts fit together.&lt;/p&gt;
       &lt;h2&gt;Why Locks Fail So Often in Indian Homes&lt;/h2&gt;
       &lt;p&gt;Door locks in Indian apartments and houses face unique stresses that wear down internal components faster:&lt;/p&gt;
@@ -14554,33 +16144,33 @@
         &lt;p&gt;If you need high-security mortise lock installation, deadbolt fitting, or wooden chaukhat repairs, our certified carpenters are available across Bangalore. Explore our &lt;a href="/services/carpentry" style="color: var(--primary); font-weight: bold;"&gt;Door Repair &amp;amp; Lock Fitting Services&lt;/a&gt; or book verified local experts in &lt;a href="/services/carpentry/indiranagar" style="color: var(--primary); font-weight: bold;"&gt;Indiranagar&lt;/a&gt;, &lt;a href="/services/carpentry/koramangala" style="color: var(--primary); font-weight: bold;"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/carpentry/whitefield" style="color: var(--primary); font-weight: bold;"&gt;Whitefield&lt;/a&gt;, and &lt;a href="/services/carpentry/hsr-layout" style="color: var(--primary); font-weight: bold;"&gt;HSR Layout&lt;/a&gt;.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I96" t="str">
+      <c r="I104" t="str">
         <v>https://images.unsplash.com/photo-1558036117-15d82a90b9b1?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="97" xml:space="preserve">
-      <c r="A97">
-        <v>96</v>
-      </c>
-      <c r="B97" t="str">
+    <row r="105" xml:space="preserve">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="str">
         <v>how-to-fix-squeaky-misaligned-loose-door-hinges</v>
       </c>
-      <c r="C97" t="str">
+      <c r="C105" t="str">
         <v>How to Fix Squeaky, Misaligned, or Loose Door Hinges</v>
       </c>
-      <c r="D97" t="str">
+      <c r="D105" t="str">
         <v>Carpentry</v>
       </c>
-      <c r="E97" t="str">
+      <c r="E105" t="str">
         <v>May 22, 2026</v>
       </c>
-      <c r="F97" t="str">
+      <c r="F105" t="str">
         <v>9 min read</v>
       </c>
-      <c r="G97" t="str">
+      <c r="G105" t="str">
         <v>Got a squeaky, sagging, or misaligned door? Learn simple 15-minute DIY fixes for Indian homes—from silencing noisy hinges to repairing stripped screw holes with toothpicks and adjusting modular cabinet shutters.</v>
       </c>
-      <c r="H97" t="str" xml:space="preserve">
+      <c r="H105" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;Every Indian home eventually develops that one door that announces your midnight fridge run to the entire house. Or the bedroom door that's started scraping the floor tiles. Or the kitchen cabinet shutter hanging at a drunken angle. These aren't signs you need a carpenter — 90% of the time, they're 15-minute fixes you can do yourself with stuff already in your house.&lt;/p&gt;
       &lt;h2&gt;Why This Happens So Often in Indian Homes&lt;/h2&gt;
       &lt;p&gt;Door hinges in India take a beating that hinges in drier climates simply don't face.&lt;/p&gt;
@@ -14689,33 +16279,33 @@
         &lt;p&gt;If your door frame has severe structural sag, termite damage, or your modular kitchen shutters need complete channel replacements, our verified local carpenters are ready to help. Explore our &lt;a href="/services/carpentry" style="color: var(--primary); font-weight: bold;"&gt;Door &amp;amp; Furniture Carpentry Services&lt;/a&gt; or book verified doorstep specialists across Bangalore in &lt;a href="/services/carpentry/koramangala" style="color: var(--primary); font-weight: bold;"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/carpentry/indiranagar" style="color: var(--primary); font-weight: bold;"&gt;Indiranagar&lt;/a&gt;, &lt;a href="/services/carpentry/whitefield" style="color: var(--primary); font-weight: bold;"&gt;Whitefield&lt;/a&gt;, and &lt;a href="/services/carpentry/hsr-layout" style="color: var(--primary); font-weight: bold;"&gt;HSR Layout&lt;/a&gt;.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I97" t="str">
+      <c r="I105" t="str">
         <v>https://images.unsplash.com/photo-1581141849291-1125c7b692b5?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="98" xml:space="preserve">
-      <c r="A98">
-        <v>97</v>
-      </c>
-      <c r="B98" t="str">
+    <row r="106" xml:space="preserve">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="str">
         <v>5-essential-carpentry-tips</v>
       </c>
-      <c r="C98" t="str">
+      <c r="C106" t="str">
         <v>5 Essential Carpentry Tips for Every Homeowner</v>
       </c>
-      <c r="D98" t="str">
+      <c r="D106" t="str">
         <v>Carpentry</v>
       </c>
-      <c r="E98" t="str">
+      <c r="E106" t="str">
         <v>May 10, 2026</v>
       </c>
-      <c r="F98" t="str">
+      <c r="F106" t="str">
         <v>8 min read</v>
       </c>
-      <c r="G98" t="str">
+      <c r="G106" t="str">
         <v>Maintenance is key to making your furniture last. Learn these simple yet effective carpentry tips to keep your home in top shape.</v>
       </c>
-      <c r="H98" t="str" xml:space="preserve">
+      <c r="H106" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;Wood is a living material. Even after it's been harvested, treated, and turned into a beautiful piece of furniture or a structural beam, it continues to react to its environment. For homeowners, understanding how to care for the wood in their homes is essential for preserving both aesthetics and structural integrity.&lt;/p&gt;
       &lt;p&gt;Whether you're dealing with a squeaky cabinet door, a scratched dining table, or a loose floorboard, these five essential carpentry tips will help you maintain your home like a professional.&lt;/p&gt;
       &lt;div style="margin: 3rem 0; border-radius: 12px; overflow: hidden;"&gt;
@@ -14745,33 +16335,33 @@
         &lt;p&gt;Carpentry maintenance is an ongoing process. While minor fixes can be handled DIY, structural modifications and custom kitchen fittings require experienced craftsmen. Browse our verified &lt;a href="/services/carpentry" style="color: var(--primary); font-weight: bold;"&gt;Bangalore Carpenters&lt;/a&gt; or check doorstep service availability in &lt;a href="/services/carpentry/koramangala" style="color: var(--primary); font-weight: bold;"&gt;Koramangala&lt;/a&gt;, &lt;a href="/services/carpentry/indiranagar" style="color: var(--primary); font-weight: bold;"&gt;Indiranagar&lt;/a&gt;, and &lt;a href="/services/carpentry/whitefield" style="color: var(--primary); font-weight: bold;"&gt;Whitefield&lt;/a&gt;.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I98" t="str">
+      <c r="I106" t="str">
         <v>https://images.unsplash.com/photo-1533090161767-e6ffed986c88?q=80&amp;w=2069&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="99" xml:space="preserve">
-      <c r="A99">
-        <v>98</v>
-      </c>
-      <c r="B99" t="str">
+    <row r="107" xml:space="preserve">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="str">
         <v>choosing-the-right-paint</v>
       </c>
-      <c r="C99" t="str">
+      <c r="C107" t="str">
         <v>How to Choose the Perfect Paint for Your Living Room</v>
       </c>
-      <c r="D99" t="str">
+      <c r="D107" t="str">
         <v>Painting</v>
       </c>
-      <c r="E99" t="str">
+      <c r="E107" t="str">
         <v>May 8, 2026</v>
       </c>
-      <c r="F99" t="str">
+      <c r="F107" t="str">
         <v>7 min read</v>
       </c>
-      <c r="G99" t="str">
+      <c r="G107" t="str">
         <v>Colors can change the mood of your home. Discover how to pick the right finish and shade for your space with our expert guide.</v>
       </c>
-      <c r="H99" t="str" xml:space="preserve">
+      <c r="H107" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;Your living room is the heart of your home—it's where you entertain guests, relax after a long day, and spend quality time with family. Choosing the right paint color is one of the most impactful ways to define the atmosphere of this space. However, with thousands of shades available, the process can be overwhelming.&lt;/p&gt;
       &lt;p&gt;Here is our expert guide to choosing the perfect paint for your living room, focusing on lighting, finishes, and the importance of testing.&lt;/p&gt;
       &lt;div style="margin: 3rem 0; border-radius: 12px; overflow: hidden;"&gt;
@@ -14807,33 +16397,33 @@
         &lt;p&gt;While DIY painting can be fun, achieving a flawless, professional finish takes time and skill. If you want a perfect transformation without the mess, browse our verified &lt;a href="/services/painting" style="color: var(--primary); font-weight: bold;"&gt;Bangalore House Painters&lt;/a&gt; today.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I99" t="str">
+      <c r="I107" t="str">
         <v>https://images.unsplash.com/photo-1562259949-e8e7689d7828?q=80&amp;w=2031&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="100" xml:space="preserve">
-      <c r="A100">
-        <v>99</v>
-      </c>
-      <c r="B100" t="str">
+    <row r="108" xml:space="preserve">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="str">
         <v>preventing-common-plumbing-issues</v>
       </c>
-      <c r="C100" t="str">
+      <c r="C108" t="str">
         <v>Preventing Common Plumbing Issues: A Homeowner’s Guide</v>
       </c>
-      <c r="D100" t="str">
+      <c r="D108" t="str">
         <v>Plumbing</v>
       </c>
-      <c r="E100" t="str">
+      <c r="E108" t="str">
         <v>May 5, 2026</v>
       </c>
-      <c r="F100" t="str">
+      <c r="F108" t="str">
         <v>6 min read</v>
       </c>
-      <c r="G100" t="str">
+      <c r="G108" t="str">
         <v>Leaks and clogs can be a nightmare. Learn how to identify early signs of plumbing problems and how to prevent them.</v>
       </c>
-      <c r="H100" t="str" xml:space="preserve">
+      <c r="H108" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;Plumbing issues are often the "silent killers" of a home's infrastructure. A small drip or a slow drain might seem like a minor annoyance, but left unaddressed, they can lead to massive water bills, mold growth, and even structural damage.&lt;/p&gt;
       &lt;p&gt;Prevention is always cheaper than repair. Here's how you can keep your home's plumbing system flowing smoothly.&lt;/p&gt;
       &lt;div style="margin: 3rem 0; border-radius: 12px; overflow: hidden;"&gt;
@@ -14860,33 +16450,33 @@
         &lt;p&gt;If you're dealing with a major leak or a stubborn clog that a plunger can't fix, don't wait. Contact our verified &lt;a href="/services/plumbing" style="color: var(--primary); font-weight: bold;"&gt;Bangalore Plumbers&lt;/a&gt; for immediate assistance.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I100" t="str">
+      <c r="I108" t="str">
         <v>https://images.unsplash.com/photo-1504148455328-497c5efdf13d?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="101" xml:space="preserve">
-      <c r="A101">
-        <v>100</v>
-      </c>
-      <c r="B101" t="str">
+    <row r="109" xml:space="preserve">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="str">
         <v>smart-home-electrical-upgrades</v>
       </c>
-      <c r="C101" t="str">
+      <c r="C109" t="str">
         <v>Top 5 Smart Home Electrical Upgrades for Modern Homes</v>
       </c>
-      <c r="D101" t="str">
+      <c r="D109" t="str">
         <v>Electrical</v>
       </c>
-      <c r="E101" t="str">
+      <c r="E109" t="str">
         <v>May 2, 2026</v>
       </c>
-      <c r="F101" t="str">
+      <c r="F109" t="str">
         <v>8 min read</v>
       </c>
-      <c r="G101" t="str">
+      <c r="G109" t="str">
         <v>Make your home more efficient and secure with these must-have electrical upgrades, from smart switches to video doorbells.</v>
       </c>
-      <c r="H101" t="str" xml:space="preserve">
+      <c r="H109" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;The concept of a "smart home" has moved beyond science fiction. In 2026, smart electrical upgrades are about more than just convenience—they are about safety, energy efficiency, and reducing your carbon footprint.&lt;/p&gt;
       &lt;p&gt;If you're looking to modernize your home, these five electrical upgrades offer the best return on investment.&lt;/p&gt;
       &lt;div style="margin: 3rem 0; border-radius: 12px; overflow: hidden;"&gt;
@@ -14905,33 +16495,33 @@
         &lt;p&gt;Electrical work can be dangerous. Always ensure your smart home upgrades are installed by a certified electrician to prevent fire hazards and ensure everything is up to code.&lt;/p&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I101" t="str">
+      <c r="I109" t="str">
         <v>https://images.unsplash.com/photo-1558403194-611308249627?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="102" xml:space="preserve">
-      <c r="A102">
-        <v>101</v>
-      </c>
-      <c r="B102" t="str">
+    <row r="110" xml:space="preserve">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="str">
         <v>termite-prevention-guide</v>
       </c>
-      <c r="C102" t="str">
+      <c r="C110" t="str">
         <v>The Ultimate Guide to Termite Prevention in Bangalore Homes</v>
       </c>
-      <c r="D102" t="str">
+      <c r="D110" t="str">
         <v>Carpentry</v>
       </c>
-      <c r="E102" t="str">
+      <c r="E110" t="str">
         <v>May 12, 2026</v>
       </c>
-      <c r="F102" t="str">
+      <c r="F110" t="str">
         <v>12 min read</v>
       </c>
-      <c r="G102" t="str">
+      <c r="G110" t="str">
         <v>Termites are a silent threat to your wooden furniture. Learn the professional techniques to identify, prevent, and treat infestations.</v>
       </c>
-      <c r="H102" t="str" xml:space="preserve">
+      <c r="H110" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;In Bangalore's humid climate, termites are a constant threat to structural woodwork and valuable furniture. These wood-boring pests can quietly hollow out door frames, custom cabinets, and wardrobes long before any visual signs appear. Implementing an effective strategy for &lt;strong&gt;termite prevention Bangalore&lt;/strong&gt; is vital to safeguarding your home’s assets.&lt;/p&gt;
       &lt;h2&gt;Understanding the Threat&lt;/h2&gt;
       &lt;p&gt;The most destructive wood pests in India are subterranean termites. They live in underground colonies and construct mud tunnels to reach wood surfaces inside your home. Because they feed on cellulose from the inside out, infested wood often looks perfectly fine on the surface until it collapses.&lt;/p&gt;
@@ -14946,33 +16536,33 @@
       &lt;/ul&gt;
       &lt;p&gt;Regular maintenance and hiring verified carpentry specialists will ensure your custom furniture remains secure and free from destructive infestations.&lt;/p&gt;</v>
       </c>
-      <c r="I102" t="str">
+      <c r="I110" t="str">
         <v>https://images.unsplash.com/photo-1589939705384-5185137a7f0f?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="103" xml:space="preserve">
-      <c r="A103">
-        <v>102</v>
-      </c>
-      <c r="B103" t="str">
+    <row r="111" xml:space="preserve">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="str">
         <v>monsoon-proofing-external-walls</v>
       </c>
-      <c r="C103" t="str">
+      <c r="C111" t="str">
         <v>Monsoon-Proofing Your External Walls: A Guide for Bangalore Homes</v>
       </c>
-      <c r="D103" t="str">
+      <c r="D111" t="str">
         <v>Painting</v>
       </c>
-      <c r="E103" t="str">
+      <c r="E111" t="str">
         <v>May 11, 2026</v>
       </c>
-      <c r="F103" t="str">
+      <c r="F111" t="str">
         <v>10 min read</v>
       </c>
-      <c r="G103" t="str">
+      <c r="G111" t="str">
         <v>Bangalore rains can be beautiful but brutal on your exterior paint. Learn how to protect your home from dampness and algae.</v>
       </c>
-      <c r="H103" t="str" xml:space="preserve">
+      <c r="H111" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;The heavy monsoon rains in Bangalore demand more than just aesthetic painting. Without adequate protection, continuous water exposure leads to severe moisture absorption in brickwork, causing damp patches, peeling plaster, and black mold inside your rooms. Planning ahead for &lt;strong&gt;monsoon proofing external walls&lt;/strong&gt; is the only way to avoid structural degradation.&lt;/p&gt;
       &lt;h2&gt;The Causes of Exterior Dampness&lt;/h2&gt;
       &lt;p&gt;During the rainy season, concrete and brick walls act like sponges. If there are hairline cracks in the exterior plaster, rainwater penetrates deep. Combined with Bangalore’s cool winds, this trapped moisture leads to rapid growth of algae, moss, and fungal spores on your exterior wall surfaces, ruining the paint finish.&lt;/p&gt;
@@ -14985,33 +16575,33 @@
       &lt;/ul&gt;
       &lt;p&gt;Proactive waterproofing not only preserves your home’s visual appeal but also maintains a healthy indoor climate free from allergens. For high-rise walls or detailed exterior waterproofing, always hire a verified painting service to ensure a durable shield.&lt;/p&gt;</v>
       </c>
-      <c r="I103" t="str">
+      <c r="I111" t="str">
         <v>https://images.unsplash.com/photo-1541888941259-7b3b95d7c32b?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="104" xml:space="preserve">
-      <c r="A104">
-        <v>103</v>
-      </c>
-      <c r="B104" t="str">
+    <row r="112" xml:space="preserve">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" t="str">
         <v>solving-hard-water-issues-bangalore</v>
       </c>
-      <c r="C104" t="str">
+      <c r="C112" t="str">
         <v>Hard Water Problems in Bangalore: Choosing the Right Water Softener</v>
       </c>
-      <c r="D104" t="str">
+      <c r="D112" t="str">
         <v>Plumbing</v>
       </c>
-      <c r="E104" t="str">
+      <c r="E112" t="str">
         <v>May 9, 2026</v>
       </c>
-      <c r="F104" t="str">
+      <c r="F112" t="str">
         <v>11 min read</v>
       </c>
-      <c r="G104" t="str">
+      <c r="G112" t="str">
         <v>High TDS levels in Bangalore water can damage your plumbing and skin. Discover the best water softening solutions.</v>
       </c>
-      <c r="H104" t="str" xml:space="preserve">
+      <c r="H112" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;Most of Bangalore relies on groundwater sourced from deep borewells, which is notoriously hard due to high mineral concentrations. Calcium and magnesium carbonates dissolve in the subterranean aquifers and create severe &lt;strong&gt;hard water problems in Bangalore&lt;/strong&gt;. This results in scale buildup inside internal plumbing pipes, failing bathroom fittings, calcified water heaters, ruined laundry, and persistent skin and hair issues. Selecting the right water softener is critical to preserving your plumbing health and home comfort.&lt;/p&gt;
       &lt;h2&gt;What is Water Hardness &amp; TDS?&lt;/h2&gt;
       &lt;p&gt;Total Dissolved Solids (TDS) measures the concentration of inorganic salts and organic matter dissolved in water. Borewell water in Bangalore regularly registers TDS levels exceeding 1000 parts per million (ppm). Hardness refers specifically to the concentration of multivalent calcium and magnesium cations. High TDS hard water ruins internal heating elements in geysers, leading to a 30% increase in power bills, and reduces washing machine efficiency by preventing soap lather.&lt;/p&gt;
@@ -15063,33 +16653,33 @@
       &lt;h2&gt;Signs Your Home Needs Plumbing Relief&lt;/h2&gt;
       &lt;p&gt;Look out for these indicators that calcium scales are damaging your plumbing system: white crusty deposits around faucet nozzles, reduced water pressure from showers, white spots on glassware after washing, and scratchy clothes. If you are experiencing any of these symptoms or have low flow rates, contact our verified plumbers to run a hardness test, clean calcified aerators, and install a suitable filter system today.&lt;/p&gt;</v>
       </c>
-      <c r="I104" t="str">
+      <c r="I112" t="str">
         <v>https://images.unsplash.com/photo-1584622650111-993a426fbf0a?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="105" xml:space="preserve">
-      <c r="A105">
-        <v>104</v>
-      </c>
-      <c r="B105" t="str">
+    <row r="113" xml:space="preserve">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" t="str">
         <v>mcb-vs-elcb-understanding-safety</v>
       </c>
-      <c r="C105" t="str">
+      <c r="C113" t="str">
         <v>MCB vs. ELCB: The Silent Guardians of Your Home</v>
       </c>
-      <c r="D105" t="str">
+      <c r="D113" t="str">
         <v>Electrical</v>
       </c>
-      <c r="E105" t="str">
+      <c r="E113" t="str">
         <v>May 7, 2026</v>
       </c>
-      <c r="F105" t="str">
+      <c r="F113" t="str">
         <v>9 min read</v>
       </c>
-      <c r="G105" t="str">
+      <c r="G113" t="str">
         <v>Understand the difference between MCBs and ELCBs and why your home needs both for complete electrical safety.</v>
       </c>
-      <c r="H105" t="str" xml:space="preserve">
+      <c r="H113" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;Do you know what actually trips your power during an electrical fault? Modern residential switchboards rely on specialized safety switches to prevent fires and protect residents from accidental electrocution. Understanding the structural differences and functions of an &lt;strong&gt;MCB vs ELCB&lt;/strong&gt; is essential for ensuring robust &lt;strong&gt;electrical safety home&lt;/strong&gt; conditions.&lt;/p&gt;
       &lt;h2&gt;MCB: Miniature Circuit Breaker&lt;/h2&gt;
       &lt;p&gt;An MCB is designed to protect your home's wiring and connected appliances from overcurrent and short circuits. If you connect too many heavy loads (like running an AC, geyser, and microwave simultaneously on a single circuit) or if a live wire directly contacts a neutral wire, the MCB detects the massive magnetic/thermal surge and trips instantly, cutting off power. This prevents the copper wires inside your walls from melting and starting a fire.&lt;/p&gt;
@@ -15136,33 +16726,33 @@
       &lt;h2&gt;Why Your Switchboard Needs Both&lt;/h2&gt;
       &lt;p&gt;An MCB will not trip if you get a minor shock, and an ELCB will not protect your geyser or AC compressor from drawing high currents and frying. Complete residential security requires installing a master RCCB/ELCB as the entry-level guardian, followed by individual MCBs for each sub-circuit group (lighting, sockets, geysers). If your switchboard is older or is missing an ELCB, hire a verified local electrician to perform an electrical panel audit and replace old fuses with modern circuit breakers.&lt;/p&gt;</v>
       </c>
-      <c r="I105" t="str">
+      <c r="I113" t="str">
         <v>https://images.unsplash.com/photo-1558002038-1055907df827?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="106" xml:space="preserve">
-      <c r="A106">
-        <v>105</v>
-      </c>
-      <c r="B106" t="str">
+    <row r="114" xml:space="preserve">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" t="str">
         <v>bangalore-home-maintenance-checklist</v>
       </c>
-      <c r="C106" t="str">
+      <c r="C114" t="str">
         <v>The Annual Bangalore Home Maintenance Checklist</v>
       </c>
-      <c r="D106" t="str">
+      <c r="D114" t="str">
         <v>Maintenance</v>
       </c>
-      <c r="E106" t="str">
+      <c r="E114" t="str">
         <v>May 4, 2026</v>
       </c>
-      <c r="F106" t="str">
+      <c r="F114" t="str">
         <v>15 min read</v>
       </c>
-      <c r="G106" t="str">
+      <c r="G114" t="str">
         <v>From pre-monsoon waterproofing to festive season cleaning, stay ahead of home repairs with our month-by-month guide.</v>
       </c>
-      <c r="H106" t="str" xml:space="preserve">
+      <c r="H114" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;Home maintenance in a growing city like Bangalore is a year-round task. With shifting monsoons, dry summers, and dust levels from ongoing urban development, keeping your property in top shape requires regular checkups. Following a structured &lt;strong&gt;Bangalore home maintenance checklist&lt;/strong&gt; helps prevent minor wears from turning into costly emergency repairs.&lt;/p&gt;
       &lt;h2&gt;Month-by-Month Preventive Tasks&lt;/h2&gt;
       &lt;p&gt;Here is a professional guide to help you schedule your home maintenance throughout the year:&lt;/p&gt;
@@ -15174,33 +16764,33 @@
       &lt;/ul&gt;
       &lt;p&gt;Setting aside a few hours every quarter for these checks keeps your home safe, hygienic, and highly valued. If you need support with waterproofing or structural carpentry fixes, connect with our verified local handymen.&lt;/p&gt;</v>
       </c>
-      <c r="I106" t="str">
+      <c r="I114" t="str">
         <v>https://images.unsplash.com/photo-1581578731548-c64695cc6954?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="107" xml:space="preserve">
-      <c r="A107">
-        <v>106</v>
-      </c>
-      <c r="B107" t="str">
+    <row r="115" xml:space="preserve">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" t="str">
         <v>bedroom-color-psychology</v>
       </c>
-      <c r="C107" t="str">
+      <c r="C115" t="str">
         <v>The Psychology of Bedroom Colors: Choosing Hues for Better Sleep</v>
       </c>
-      <c r="D107" t="str">
+      <c r="D115" t="str">
         <v>Painting</v>
       </c>
-      <c r="E107" t="str">
+      <c r="E115" t="str">
         <v>May 1, 2026</v>
       </c>
-      <c r="F107" t="str">
+      <c r="F115" t="str">
         <v>8 min read</v>
       </c>
-      <c r="G107" t="str">
+      <c r="G115" t="str">
         <v>How the color of your bedroom walls affects your sleep quality and mood. Discover the science behind peaceful interiors.</v>
       </c>
-      <c r="H107" t="str" xml:space="preserve">
+      <c r="H115" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;Colors have a profound impact on our psychological state and physiological responses. Since we spend a third of our lives sleeping, selecting the correct wall colors is critical to creating a restful environment. Understanding &lt;strong&gt;bedroom color psychology&lt;/strong&gt; can help you choose the &lt;strong&gt;best colors for bedroom sleep&lt;/strong&gt; quality and overall peace.&lt;/p&gt;
       &lt;h2&gt;The Science of Color and Sleep&lt;/h2&gt;
       &lt;p&gt;Our eyes contain specialized receptors that detect light and communicate directly with the brain area responsible for our circadian rhythm. High-energy colors stimulate brain activity, while calm, low-frequency colors send signals that invite relaxation and melatonin production.&lt;/p&gt;
@@ -15213,33 +16803,33 @@
       &lt;/ul&gt;
       &lt;p&gt;Avoid high-intensity colors like bright red, orange, or neon yellow on primary bedroom walls. These shades trigger alertness and raise blood pressure, which can lead to sleep disruptions. For professional advice on shade palettes and eco-friendly coatings, get in touch with our verified painters.&lt;/p&gt;</v>
       </c>
-      <c r="I107" t="str">
+      <c r="I115" t="str">
         <v>https://images.unsplash.com/photo-1595526114035-0d45ed16cfbf?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="108" xml:space="preserve">
-      <c r="A108">
-        <v>107</v>
-      </c>
-      <c r="B108" t="str">
+    <row r="116" xml:space="preserve">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" t="str">
         <v>modern-wardrobe-ergonomics</v>
       </c>
-      <c r="C108" t="str">
+      <c r="C116" t="str">
         <v>Modern Wardrobe Ergonomics: Planning Your Perfect Closet</v>
       </c>
-      <c r="D108" t="str">
+      <c r="D116" t="str">
         <v>Carpentry</v>
       </c>
-      <c r="E108" t="str">
+      <c r="E116" t="str">
         <v>April 28, 2026</v>
       </c>
-      <c r="F108" t="str">
+      <c r="F116" t="str">
         <v>10 min read</v>
       </c>
-      <c r="G108" t="str">
+      <c r="G116" t="str">
         <v>Maximize every inch of your wardrobe. Learn the professional standards for hanging space, shelving, and accessory drawers.</v>
       </c>
-      <c r="H108" t="str" xml:space="preserve">
+      <c r="H116" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;Planning a new bedroom wardrobe involves much more than selecting modular shutters or laminate patterns. To build a highly functional closet, you must focus on the layout's structural dimensions. Implementing correct &lt;strong&gt;modern wardrobe ergonomics&lt;/strong&gt; and standard measurements prevents awkward reaching and maximizes storage space.&lt;/p&gt;
       &lt;h2&gt;Standard Dimensions for Indian Closets&lt;/h2&gt;
       &lt;p&gt;Professional interior carpenters utilize specific &lt;strong&gt;wardrobe closet design standards&lt;/strong&gt; to customize storage compartments:&lt;/p&gt;
@@ -15251,33 +16841,33 @@
       &lt;/ul&gt;
       &lt;p&gt;Custom wardrobes built by skilled handymen allow you to adjust shelves to fit your unique heights. For custom carpentry layouts that match your space perfectly, browse our directory of verified carpenters.&lt;/p&gt;</v>
       </c>
-      <c r="I108" t="str">
+      <c r="I116" t="str">
         <v>https://images.unsplash.com/photo-1595428774223-ef52624120d2?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="109" xml:space="preserve">
-      <c r="A109">
-        <v>108</v>
-      </c>
-      <c r="B109" t="str">
+    <row r="117" xml:space="preserve">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" t="str">
         <v>kitchen-cabinet-materials-guide</v>
       </c>
-      <c r="C109" t="str">
+      <c r="C117" t="str">
         <v>Kitchen Cabinet Materials: Plywood vs. MDF vs. HDF</v>
       </c>
-      <c r="D109" t="str">
+      <c r="D117" t="str">
         <v>Carpentry</v>
       </c>
-      <c r="E109" t="str">
+      <c r="E117" t="str">
         <v>April 25, 2026</v>
       </c>
-      <c r="F109" t="str">
+      <c r="F117" t="str">
         <v>12 min read</v>
       </c>
-      <c r="G109" t="str">
+      <c r="G117" t="str">
         <v>Choosing the right base material for your Indian kitchen. A comparison of durability, moisture resistance, and cost.</v>
       </c>
-      <c r="H109" t="str" xml:space="preserve">
+      <c r="H117" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;Indian kitchens are uniquely demanding environments due to heavy cooking steam, spice stains, water splashes, and tropical humidity. Choosing the right base material for your custom carpentry is critical. We break down the differences between &lt;strong&gt;plywood vs MDF vs HDF&lt;/strong&gt; to help you choose the best &lt;strong&gt;kitchen cabinet materials&lt;/strong&gt;.&lt;/p&gt;
       &lt;h2&gt;1. BWR Plywood: Boiling Water Resistant&lt;/h2&gt;
       &lt;p&gt;For Indian homes, BWR (Boiling Water Resistant) plywood is the gold standard for kitchen cabinets. Unlike standard board, BWR ply is cross-laminated with phenolic resins, making it highly resistant to moisture, humidity, and termite attacks. It possesses excellent screw-holding capacity and durability.&lt;/p&gt;
@@ -15286,33 +16876,33 @@
       &lt;h2&gt;3. Laminate vs Acrylic Finish&lt;/h2&gt;
       &lt;p&gt;For high-wear cabinets, laminates are the most cost-effective and scratch-resistant choice. Acrylic sheets, while more expensive, offer a premium, mirror-like high-gloss finish that makes small kitchens appear brighter. Make sure to consult a verified professional carpenter before finalizing your material specifications.&lt;/p&gt;</v>
       </c>
-      <c r="I109" t="str">
+      <c r="I117" t="str">
         <v>https://images.unsplash.com/photo-1556911220-e15021349196?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="110" xml:space="preserve">
-      <c r="A110">
-        <v>109</v>
-      </c>
-      <c r="B110" t="str">
+    <row r="118" xml:space="preserve">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" t="str">
         <v>emergency-pipe-repair-guide</v>
       </c>
-      <c r="C110" t="str">
+      <c r="C118" t="str">
         <v>Emergency Pipe Repair: A Homeowner’s Survival Guide</v>
       </c>
-      <c r="D110" t="str">
+      <c r="D118" t="str">
         <v>Plumbing</v>
       </c>
-      <c r="E110" t="str">
+      <c r="E118" t="str">
         <v>April 22, 2026</v>
       </c>
-      <c r="F110" t="str">
+      <c r="F118" t="str">
         <v>7 min read</v>
       </c>
-      <c r="G110" t="str">
+      <c r="G118" t="str">
         <v>What to do when a pipe bursts in the middle of the night. Temporary fixes to stop flooding before a professional arrives.</v>
       </c>
-      <c r="H110" t="str" xml:space="preserve">
+      <c r="H118" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;A plumbing emergency can strike at any hour, turning a peaceful home into a stressful flood zone. If a pipe leaks or bursts, waiting for a plumber can result in extensive damage to your floors and walls. Knowing how to execute an &lt;strong&gt;emergency pipe repair&lt;/strong&gt; can save you thousands in restoration costs.&lt;/p&gt;
       &lt;h2&gt;Step 1: Shut Off the Main Valve&lt;/h2&gt;
       &lt;p&gt;Every second counts during a leak. Go immediately to your main water shut-off valve and turn it off clockwise to stop the water flow. Ensure everyone in your household knows where this valve is located.&lt;/p&gt;
@@ -15321,33 +16911,33 @@
       &lt;h2&gt;Step 3: Apply Temporary Sealants&lt;/h2&gt;
       &lt;p&gt;For a quick, temporary &lt;strong&gt;burst pipe repair&lt;/strong&gt;, apply silicone self-fusing tape tightly around the leaking joint. You can also use a pipe clamp with a rubber gasket over the leak area to secure the pipe. Remember, these patches are only temporary fixes to stop flooding before a certified plumber arrives. Contact our verified plumbers for a permanent, high-quality replacement.&lt;/p&gt;</v>
       </c>
-      <c r="I110" t="str">
+      <c r="I118" t="str">
         <v>https://images.unsplash.com/photo-1542013936693-884638332954?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="111" xml:space="preserve">
-      <c r="A111">
-        <v>110</v>
-      </c>
-      <c r="B111" t="str">
+    <row r="119" xml:space="preserve">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" t="str">
         <v>solar-energy-home-integration</v>
       </c>
-      <c r="C111" t="str">
+      <c r="C119" t="str">
         <v>Solar Energy Integration: Preparing Your Home’s Electrical Grid</v>
       </c>
-      <c r="D111" t="str">
+      <c r="D119" t="str">
         <v>Electrical</v>
       </c>
-      <c r="E111" t="str">
+      <c r="E119" t="str">
         <v>April 20, 2026</v>
       </c>
-      <c r="F111" t="str">
+      <c r="F119" t="str">
         <v>14 min read</v>
       </c>
-      <c r="G111" t="str">
+      <c r="G119" t="str">
         <v>Considering solar panels? Learn how to prepare your home’s wiring and meter for a solar power transition in Bangalore.</v>
       </c>
-      <c r="H111" t="str" xml:space="preserve">
+      <c r="H119" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;Transitioning to clean energy is a smart investment, but installing solar panels on your roof is only half the battle. To ensure a successful &lt;strong&gt;solar energy home integration&lt;/strong&gt;, you must prepare your home's internal wiring, electrical panel, and metering infrastructure. A proper upgrade ensures compatibility with the local grid and optimal power generation.&lt;/p&gt;
       &lt;h2&gt;1. The Electrical Load Audit&lt;/h2&gt;
       &lt;p&gt;Before buying panels, have a certified professional audit your monthly power usage. This audit helps size your solar array correctly and determines if your current wiring needs a reinforcement to handle solar generation current.&lt;/p&gt;
@@ -15357,33 +16947,33 @@
       &lt;p&gt;Bangalore's local electricity board requires a bidirectional net-meter. This meter records both the energy you consume from the grid and the excess solar power you feed back into it. Your electrical panel must be configured to accommodate this bidirectional metering safely.&lt;/p&gt;
       &lt;p&gt;Proper grid integration prevents damage to your appliances and ensures compliance with local safety regulations. Contact our verified electricians to audit your panel before starting your solar installation.&lt;/p&gt;</v>
       </c>
-      <c r="I111" t="str">
+      <c r="I119" t="str">
         <v>https://images.unsplash.com/photo-1508514177221-188b1cf16e9d?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="112" xml:space="preserve">
-      <c r="A112">
-        <v>111</v>
-      </c>
-      <c r="B112" t="str">
+    <row r="120" xml:space="preserve">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" t="str">
         <v>dangers-of-old-wiring</v>
       </c>
-      <c r="C112" t="str">
+      <c r="C120" t="str">
         <v>The Dangers of Old Wiring: When to Rewire Your Bangalore Home</v>
       </c>
-      <c r="D112" t="str">
+      <c r="D120" t="str">
         <v>Electrical</v>
       </c>
-      <c r="E112" t="str">
+      <c r="E120" t="str">
         <v>April 15, 2026</v>
       </c>
-      <c r="F112" t="str">
+      <c r="F120" t="str">
         <v>11 min read</v>
       </c>
-      <c r="G112" t="str">
+      <c r="G120" t="str">
         <v>Is your 20-year-old home a fire hazard? Learn the warning signs of deteriorating electrical systems and when it’s time for a full rewiring.</v>
       </c>
-      <c r="H112" t="str" xml:space="preserve">
+      <c r="H120" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;Many older apartments and independent houses in Bangalore still rely on their original electrical systems from the 1990s or early 2000s. These outdated grids were not designed to support modern high-draw appliances like microwave ovens, ACs, and geysers. Understanding the &lt;strong&gt;dangers of old wiring&lt;/strong&gt; is vital to protecting your family from electrical fires.&lt;/p&gt;
       &lt;h2&gt;The Risks of Outdated Infrastructure&lt;/h2&gt;
       &lt;p&gt;Aged wiring insulation degrades over time, becoming brittle and cracking. This exposes live copper or aluminum wires, leading to short circuits and dangerous sparks behind walls. Outdated aluminum electrical wiring is particularly hazardous, as aluminum joints expand and loosen over time, creating high-resistance points that heat up rapidly.&lt;/p&gt;
@@ -15397,33 +16987,33 @@
       &lt;/ul&gt;
       &lt;p&gt;If your home is over 20 years old and has never been audited, planning a complete &lt;strong&gt;rewiring home Bangalore&lt;/strong&gt; project is recommended. Get in touch with our certified electrical professionals to inspect your home wiring today.&lt;/p&gt;</v>
       </c>
-      <c r="I112" t="str">
+      <c r="I120" t="str">
         <v>https://images.unsplash.com/photo-1558403194-611308249627?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="113" xml:space="preserve">
-      <c r="A113">
-        <v>112</v>
-      </c>
-      <c r="B113" t="str">
+    <row r="121" xml:space="preserve">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" t="str">
         <v>outdoor-lighting-design</v>
       </c>
-      <c r="C113" t="str">
+      <c r="C121" t="str">
         <v>Outdoor Lighting Design: Enhancing Security and Aesthetics</v>
       </c>
-      <c r="D113" t="str">
+      <c r="D121" t="str">
         <v>Electrical</v>
       </c>
-      <c r="E113" t="str">
+      <c r="E121" t="str">
         <v>April 12, 2026</v>
       </c>
-      <c r="F113" t="str">
+      <c r="F121" t="str">
         <v>9 min read</v>
       </c>
-      <c r="G113" t="str">
+      <c r="G121" t="str">
         <v>Protect your home and increase its curb appeal with strategic outdoor lighting. Tips for gardens, pathways, and entrance gates.</v>
       </c>
-      <c r="H113" t="str" xml:space="preserve">
+      <c r="H121" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;A well-planned exterior layout can completely transform the look of your home while protecting it from unwanted intrusions. When designing your garden or entrance, incorporating a smart &lt;strong&gt;outdoor lighting design&lt;/strong&gt; creates a warm, premium environment and acts as a robust &lt;strong&gt;home security lighting&lt;/strong&gt; system. Balancing aesthetic appeal with physical safety is the secret to a great layout.&lt;/p&gt;
       &lt;h2&gt;Three Pillars of Outdoor Illumination&lt;/h2&gt;
       &lt;p&gt;A balanced plan uses different layers of light to achieve beauty and function:&lt;/p&gt;
@@ -15435,33 +17025,33 @@
       &lt;h2&gt;Weatherproofing and Safety Standards&lt;/h2&gt;
       &lt;p&gt;Outdoor electrical elements face high humidity and monsoon rains. Always verify that all exterior light fixtures have an IP65 or higher weather-proofing score to prevent water short circuits. Ensure all cables are run through heavy conduit pipes buried underground. Contact our verified electricians to plan and install a safe outdoor wiring system.&lt;/p&gt;</v>
       </c>
-      <c r="I113" t="str">
+      <c r="I121" t="str">
         <v>https://images.unsplash.com/photo-1563298723-dcfebaa392e3?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="114" xml:space="preserve">
-      <c r="A114">
-        <v>113</v>
-      </c>
-      <c r="B114" t="str">
+    <row r="122" xml:space="preserve">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122" t="str">
         <v>vastu-for-home-carpentry</v>
       </c>
-      <c r="C114" t="str">
+      <c r="C122" t="str">
         <v>Vastu for Home: Carpentry and Layout Tips for Positive Energy</v>
       </c>
-      <c r="D114" t="str">
+      <c r="D122" t="str">
         <v>Maintenance</v>
       </c>
-      <c r="E114" t="str">
+      <c r="E122" t="str">
         <v>April 8, 2026</v>
       </c>
-      <c r="F114" t="str">
+      <c r="F122" t="str">
         <v>10 min read</v>
       </c>
-      <c r="G114" t="str">
+      <c r="G122" t="str">
         <v>Align your furniture and wooden fixtures with traditional Vastu principles to enhance the harmony and prosperity of your living space.</v>
       </c>
-      <c r="H114" t="str" xml:space="preserve">
+      <c r="H122" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;For many Indian homeowners, aligning a property with the traditional principles of Vastu Shastra is essential for welcoming harmony, health, and prosperity. During an interior renovation, incorporating practical &lt;strong&gt;Vastu for home carpentry&lt;/strong&gt; and smart furniture placement can make a massive difference in the room's energy flow.&lt;/p&gt;
       &lt;h2&gt;Key Guidelines for Furniture and Layout&lt;/h2&gt;
       &lt;p&gt;Traditional Vastu principles dictate the weight, shape, and placement directions for standard household items:&lt;/p&gt;
@@ -15472,33 +17062,33 @@
       &lt;/ul&gt;
       &lt;p&gt;Using natural wood like teak or mahogany for primary doors and bedroom furniture is highly recommended. For custom Vastu furniture layouts built to fit your home's exact dimensions, browse our directory of verified carpenters.&lt;/p&gt;</v>
       </c>
-      <c r="I114" t="str">
+      <c r="I122" t="str">
         <v>https://images.unsplash.com/photo-1513519245088-0e12902e5a38?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="115" xml:space="preserve">
-      <c r="A115">
-        <v>114</v>
-      </c>
-      <c r="B115" t="str">
+    <row r="123" xml:space="preserve">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123" t="str">
         <v>hiring-a-professional-checklist</v>
       </c>
-      <c r="C115" t="str">
+      <c r="C123" t="str">
         <v>Hiring a Professional: 10 Questions to Ask Before You Book</v>
       </c>
-      <c r="D115" t="str">
+      <c r="D123" t="str">
         <v>Maintenance</v>
       </c>
-      <c r="E115" t="str">
+      <c r="E123" t="str">
         <v>April 5, 2026</v>
       </c>
-      <c r="F115" t="str">
+      <c r="F123" t="str">
         <v>8 min read</v>
       </c>
-      <c r="G115" t="str">
+      <c r="G123" t="str">
         <v>Don’t hire the wrong person for your home renovation. Use this checklist to vet contractors and independent handymen effectively.</v>
       </c>
-      <c r="H115" t="str" xml:space="preserve">
+      <c r="H123" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;Hiring the wrong contractor for a home renovation can turn your dream project into an expensive nightmare of delays and poor finishes. Vetting tradesmen effectively is the most critical step before any work begins. Having a clear &lt;strong&gt;hiring a professional checklist&lt;/strong&gt; helps you select a reliable partner with confidence.&lt;/p&gt;
       &lt;h2&gt;Critical Questions to Ask Candidates&lt;/h2&gt;
       &lt;p&gt;Before signing a contract or handing over an advance payment, make sure to ask these essential &lt;strong&gt;questions to ask contractor&lt;/strong&gt; candidates:&lt;/p&gt;
@@ -15510,33 +17100,33 @@
       &lt;/ul&gt;
       &lt;p&gt;Ensuring your tradesperson is fully insured and background-verified gives you peace of mind. For a transparent booking experience, consider selecting verified handymen from Carpenterwala, where we physically screen all professionals beforehand.&lt;/p&gt;</v>
       </c>
-      <c r="I115" t="str">
+      <c r="I123" t="str">
         <v>https://images.unsplash.com/photo-1521791136064-7986c2959d99?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="116" xml:space="preserve">
-      <c r="A116">
-        <v>115</v>
-      </c>
-      <c r="B116" t="str">
+    <row r="124" xml:space="preserve">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124" t="str">
         <v>rust-proofing-metal-grills</v>
       </c>
-      <c r="C116" t="str">
+      <c r="C124" t="str">
         <v>Rust-Proofing Metal Grills: A Step-by-Step Painting Tutorial</v>
       </c>
-      <c r="D116" t="str">
+      <c r="D124" t="str">
         <v>Painting</v>
       </c>
-      <c r="E116" t="str">
+      <c r="E124" t="str">
         <v>April 2, 2026</v>
       </c>
-      <c r="F116" t="str">
+      <c r="F124" t="str">
         <v>12 min read</v>
       </c>
-      <c r="G116" t="str">
+      <c r="G124" t="str">
         <v>Protect your balcony and window grills from corrosion. A detailed guide on cleaning, priming, and painting metal surfaces.</v>
       </c>
-      <c r="H116" t="str" xml:space="preserve">
+      <c r="H124" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;Balcony and window grills in Bangalore are constantly exposed to fluctuating humidity, causing them to corrode and rust quickly. If left untreated, rust weakens the metal structure, creating safety issues. Following a structured guide for &lt;strong&gt;rust-proofing metal grills&lt;/strong&gt; not only enhances security but also gives your home a fresh look with professional &lt;strong&gt;balcony grill painting&lt;/strong&gt;.&lt;/p&gt;
       &lt;h2&gt;Step 1: Thorough Surface Preparation&lt;/h2&gt;
       &lt;p&gt;You cannot paint over active rust. Use a wire brush or medium-grit emery paper to sand down the entire surface, removing loose rust flakes, peeling paint, and dirt until the bare metal is exposed. Wipe the grill clean with mineral spirits to remove remaining dust.&lt;/p&gt;
@@ -15545,33 +17135,33 @@
       &lt;h2&gt;Step 3: Finishing Paint&lt;/h2&gt;
       &lt;p&gt;Apply two coats of weather-resistant exterior enamel paint in your chosen shade. Gloss finishes are highly recommended because they shed rainwater easily. For high-rise windows or complex grill designs, hire a verified painting professional to ensure complete, even coverage.&lt;/p&gt;</v>
       </c>
-      <c r="I116" t="str">
+      <c r="I124" t="str">
         <v>https://images.unsplash.com/photo-1589939705384-5185137a7f0f?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="117" xml:space="preserve">
-      <c r="A117">
-        <v>116</v>
-      </c>
-      <c r="B117" t="str">
+    <row r="125" xml:space="preserve">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125" t="str">
         <v>eco-friendly-paints-guide</v>
       </c>
-      <c r="C117" t="str">
+      <c r="C125" t="str">
         <v>Eco-Friendly Paints: Why You Should Switch to Low-VOC Options</v>
       </c>
-      <c r="D117" t="str">
+      <c r="D125" t="str">
         <v>Painting</v>
       </c>
-      <c r="E117" t="str">
+      <c r="E125" t="str">
         <v>March 28, 2026</v>
       </c>
-      <c r="F117" t="str">
+      <c r="F125" t="str">
         <v>11 min read</v>
       </c>
-      <c r="G117" t="str">
+      <c r="G125" t="str">
         <v>Protect your health and the environment. Discover the benefits of low-VOC and zero-VOC paints for your home’s interiors.</v>
       </c>
-      <c r="H117" t="str" xml:space="preserve">
+      <c r="H125" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;Traditional wall paints release Volatile Organic Compounds (VOCs) into the air for years after application, contributing to indoor air pollution. These chemicals are responsible for that sharp, chemical smell of fresh paint and can trigger headaches, dizziness, and respiratory issues. Switching to &lt;strong&gt;eco-friendly paints India&lt;/strong&gt; options is better for both your health and the environment.&lt;/p&gt;
       &lt;h2&gt;The Benefits of Low-VOC and Zero-VOC Options&lt;/h2&gt;
       &lt;p&gt;Choosing green paint solutions offers several important advantages for your family:&lt;/p&gt;
@@ -15582,33 +17172,33 @@
       &lt;/ul&gt;
       &lt;p&gt;Modern low-VOC emulsions offer the same durability, coverage, and rich color options as traditional paints. When planning your next painting project, check the product label for green certifications or consult our verified painters to select the best eco-friendly paints for your walls.&lt;/p&gt;</v>
       </c>
-      <c r="I117" t="str">
+      <c r="I125" t="str">
         <v>https://images.unsplash.com/photo-1562259949-e8e7689d7828?q=80&amp;w=2031&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="118" xml:space="preserve">
-      <c r="A118">
-        <v>117</v>
-      </c>
-      <c r="B118" t="str">
+    <row r="126" xml:space="preserve">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126" t="str">
         <v>carpenter-vs-modular-furniture</v>
       </c>
-      <c r="C118" t="str">
+      <c r="C126" t="str">
         <v>Custom Carpenter vs. Modular Furniture: Which is Better for Indian Homes?</v>
       </c>
-      <c r="D118" t="str">
+      <c r="D126" t="str">
         <v>Carpentry</v>
       </c>
-      <c r="E118" t="str">
+      <c r="E126" t="str">
         <v>May 15, 2026</v>
       </c>
-      <c r="F118" t="str">
+      <c r="F126" t="str">
         <v>6 min read</v>
       </c>
-      <c r="G118" t="str">
+      <c r="G126" t="str">
         <v>Planning home interiors? Learn the key differences between custom on-site carpentry work and factory-made modular fittings for Indian homes.</v>
       </c>
-      <c r="H118" t="str" xml:space="preserve">
+      <c r="H126" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;When you are setting up or renovating a home in India, you have a big choice to make: &lt;strong&gt;carpenter vs modular furniture&lt;/strong&gt;. Should you hire a local carpenter to build custom pieces right inside your home? Or is it better to buy factory-made modular units?&lt;/p&gt;
       &lt;p&gt;Both choices have clear pros and cons. Let us compare the cost, strength, customization options, and setup times. This will help you pick between a custom carpenter and a modular kitchen or wardrobe.&lt;/p&gt;
       &lt;h2&gt;1. Customization and Fitting&lt;/h2&gt;
@@ -15621,33 +17211,33 @@
       &lt;h2&gt;Conclusion&lt;/h2&gt;
       &lt;p&gt;If you want a standard kitchen or wardrobe layout, modular furniture is quick and easy. But if you need custom TV units, corner wardrobes, or heavy teak wood furniture, hiring a local carpenter is still the best choice.&lt;/p&gt;</v>
       </c>
-      <c r="I118" t="str">
+      <c r="I126" t="str">
         <v>https://images.unsplash.com/photo-1540555700478-4be289fbecef?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="119" xml:space="preserve">
-      <c r="A119">
-        <v>118</v>
-      </c>
-      <c r="B119" t="str">
+    <row r="127" xml:space="preserve">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127" t="str">
         <v>diwali-home-renovation-checklist</v>
       </c>
-      <c r="C119" t="str">
+      <c r="C127" t="str">
         <v>The Ultimate Diwali Home Renovation Checklist for a Festive Makeover</v>
       </c>
-      <c r="D119" t="str">
+      <c r="D127" t="str">
         <v>Maintenance</v>
       </c>
-      <c r="E119" t="str">
+      <c r="E127" t="str">
         <v>May 14, 2026</v>
       </c>
-      <c r="F119" t="str">
+      <c r="F127" t="str">
         <v>5 min read</v>
       </c>
-      <c r="G119" t="str">
+      <c r="G127" t="str">
         <v>Get your home festive-ready. Here is the ultimate Diwali home renovation and makeover checklist to upgrade your space before the festival.</v>
       </c>
-      <c r="H119" t="str" xml:space="preserve">
+      <c r="H127" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;Diwali is the festival of lights, prosperity, and fresh starts. In India, it is a long-standing tradition to clean, repair, and decorate homes before welcoming Goddess Lakshmi. If you are planning a &lt;strong&gt;diwali home renovation&lt;/strong&gt; or a quick home makeover before diwali, starting early is key.&lt;/p&gt;
       &lt;p&gt;Use our step-by-step checklist to ensure your home looks stunning and stays welcoming for guests during the festive season.&lt;/p&gt;
       &lt;h2&gt;1. Deep Cleaning and Decluttering&lt;/h2&gt;
@@ -15659,33 +17249,33 @@
       &lt;h2&gt;4. Checking Electrical and Lighting&lt;/h2&gt;
       &lt;p&gt;Verify that your main switchboards, geysers, and decorative lighting sockets are in perfect working order. Install warm ambient LED strip lights behind TV units or false ceilings to create a cozy, premium environment.&lt;/p&gt;</v>
       </c>
-      <c r="I119" t="str">
+      <c r="I127" t="str">
         <v>https://images.unsplash.com/photo-1608933221976-577884877bb8?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="120" xml:space="preserve">
-      <c r="A120">
-        <v>119</v>
-      </c>
-      <c r="B120" t="str">
+    <row r="128" xml:space="preserve">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128" t="str">
         <v>wood-polish-vs-laminate-finish</v>
       </c>
-      <c r="C120" t="str">
+      <c r="C128" t="str">
         <v>Wood Polish vs. Laminate Finish: Choosing the Best Furniture Finish</v>
       </c>
-      <c r="D120" t="str">
+      <c r="D128" t="str">
         <v>Carpentry</v>
       </c>
-      <c r="E120" t="str">
+      <c r="E128" t="str">
         <v>May 13, 2026</v>
       </c>
-      <c r="F120" t="str">
+      <c r="F128" t="str">
         <v>6 min read</v>
       </c>
-      <c r="G120" t="str">
+      <c r="G128" t="str">
         <v>Confused between wood polish vs laminate finish? Learn about durability, costs, and aesthetics to make the right choice for your Indian home.</v>
       </c>
-      <c r="H120" t="str" xml:space="preserve">
+      <c r="H128" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;When designing wooden furniture, the finish determines not just how the piece looks, but also how long it lasts. Two of the most popular furniture finishing options in India are &lt;strong&gt;wood polish vs laminate&lt;/strong&gt; finishes.&lt;/p&gt;
       &lt;p&gt;Let's compare these finishes to see which option is best for your custom home projects.&lt;/p&gt;
       &lt;h2&gt;1. Aesthetic Appearance&lt;/h2&gt;
@@ -15697,33 +17287,33 @@
       &lt;h2&gt;Verdict&lt;/h2&gt;
       &lt;p&gt;For high-wear areas like kitchen cabinets, kids' study desks, and internal shelves, laminates are the best choice. For formal dining tables, primary entrance doors, and focal living room showpieces, wood polish offers unmatched aesthetic luxury.&lt;/p&gt;</v>
       </c>
-      <c r="I120" t="str">
+      <c r="I128" t="str">
         <v>https://images.unsplash.com/photo-1533090161767-e6ffed986c88?q=80&amp;w=2069&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="121" xml:space="preserve">
-      <c r="A121">
-        <v>120</v>
-      </c>
-      <c r="B121" t="str">
+    <row r="129" xml:space="preserve">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129" t="str">
         <v>fall-ceiling-repair-cost-india</v>
       </c>
-      <c r="C121" t="str">
+      <c r="C129" t="str">
         <v>Fall Ceiling Repair Cost: A Homeowner's Pricing Guide for India</v>
       </c>
-      <c r="D121" t="str">
+      <c r="D129" t="str">
         <v>Maintenance</v>
       </c>
-      <c r="E121" t="str">
+      <c r="E129" t="str">
         <v>May 16, 2026</v>
       </c>
-      <c r="F121" t="str">
+      <c r="F129" t="str">
         <v>6 min read</v>
       </c>
-      <c r="G121" t="str">
+      <c r="G129" t="str">
         <v>Need a plaster board or POP repair? Learn about typical fall ceiling repair cost in India per sq ft, gypsum sheet rates, sagging fixes, and contractor labour charges.</v>
       </c>
-      <c r="H121" t="str" xml:space="preserve">
+      <c r="H129" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;False ceilings (often searched as "fall ceilings" in India) add a touch of luxury and improve lighting across modern Indian apartments. However, water leakage, structural sagging, or general aging can quickly result in damage. If you are experiencing cracks or water patches, knowing the typical &lt;strong&gt;fall ceiling repair cost&lt;/strong&gt; is essential before hiring a contractor.&lt;/p&gt;
       &lt;p&gt;Here is an itemized breakdown of repair prices, POP board costs, and painter/carpentry labour rates in major Indian cities.&lt;/p&gt;
       &lt;h2&gt;1. Types of Damage and Repair Costs&lt;/h2&gt;
@@ -15745,33 +17335,33 @@
       &lt;h2&gt;Summary&lt;/h2&gt;
       &lt;p&gt;For small repairs, hiring an independent professional is usually more cost-effective. Ensure the root cause—such as bathroom piping leaks from the floor above—is resolved first, or your new ceiling repairs will warp again within one monsoon season.&lt;/p&gt;</v>
       </c>
-      <c r="I121" t="str">
+      <c r="I129" t="str">
         <v>https://images.unsplash.com/photo-1513694203232-719a280e022f?q=80&amp;w=2069&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="122" xml:space="preserve">
-      <c r="A122">
-        <v>121</v>
-      </c>
-      <c r="B122" t="str">
+    <row r="130" xml:space="preserve">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130" t="str">
         <v>modern-wall-panel-designs</v>
       </c>
-      <c r="C122" t="str">
+      <c r="C130" t="str">
         <v>Modern Wall Panel Designs: Material Options and Ideas for Your Home</v>
       </c>
-      <c r="D122" t="str">
+      <c r="D130" t="str">
         <v>Carpentry</v>
       </c>
-      <c r="E122" t="str">
+      <c r="E130" t="str">
         <v>May 17, 2026</v>
       </c>
-      <c r="F122" t="str">
+      <c r="F130" t="str">
         <v>7 min read</v>
       </c>
-      <c r="G122" t="str">
+      <c r="G130" t="str">
         <v>Explore trending wall panel designs, popular wall panel material options, and tips for installing acoustic wall panels for your home.</v>
       </c>
-      <c r="H122" t="str" xml:space="preserve">
+      <c r="H130" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;Wall paneling has become one of the most popular interior design trends in India. It is a quick and elegant way to cover damp walls, conceal messy wiring, and give a premium feel to bedrooms and living spaces. If you are searching for the perfect interior backdrop, understanding modern &lt;strong&gt;wall panel designs&lt;/strong&gt; and materials is key.&lt;/p&gt;
       &lt;p&gt;Here is our comprehensive guide to modern wall paneling, mapping wall panel design ideas, material options, and acoustic upgrades.&lt;/p&gt;
       &lt;h2&gt;1. Trending Wall Panel Design Ideas&lt;/h2&gt;
@@ -15794,33 +17384,33 @@
       &lt;h2&gt;Summary&lt;/h2&gt;
       &lt;p&gt;Choosing the right wall panel designs depends on your budget, style, and dampness levels. For standard PVC fittings, ready-made panels are quick. However, for high-end custom veneer work, detailed moldings, or installing acoustic grids, hiring a verified carpenter is recommended to ensure seamless joint alignments.&lt;/p&gt;</v>
       </c>
-      <c r="I122" t="str">
+      <c r="I130" t="str">
         <v>https://images.unsplash.com/photo-1618219908412-a29a1bb7b86e?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="123" xml:space="preserve">
-      <c r="A123">
-        <v>122</v>
-      </c>
-      <c r="B123" t="str">
+    <row r="131" xml:space="preserve">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131" t="str">
         <v>service-pro-free-registration-guide</v>
       </c>
-      <c r="C123" t="str">
+      <c r="C131" t="str">
         <v>How Skilled Service Pros Can Register Free on Carpenterwala &amp; Get Direct Customer Leads</v>
       </c>
-      <c r="D123" t="str">
+      <c r="D131" t="str">
         <v>Carpentry</v>
       </c>
-      <c r="E123" t="str">
+      <c r="E131" t="str">
         <v>May 20, 2026</v>
       </c>
-      <c r="F123" t="str">
+      <c r="F131" t="str">
         <v>9 min read</v>
       </c>
-      <c r="G123" t="str">
+      <c r="G131" t="str">
         <v>A complete step-by-step guide for skilled carpenters, painters, electricians, plumbers, and handymen across India to register for free on Carpenterwala, complete online police verification, and get direct customer leads with 0% commission.</v>
       </c>
-      <c r="H123" t="str" xml:space="preserve">
+      <c r="H131" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;Whether you are a skilled &lt;strong&gt;carpenter, wall painter, certified electrician, plumber, or general handyman technician&lt;/strong&gt; operating in &lt;strong&gt;Bangalore, Delhi NCR, Mumbai, Pune, Chennai, or Hyderabad&lt;/strong&gt;, getting consistent customer job orders without paying heavy contractor commissions is essential for your business growth.&lt;/p&gt;
       &lt;p&gt;With Carpenterwala, any skilled service professional can register for free, upload their identity and skill details, and start receiving direct phone calls and booking requests from local homeowners—keeping 100% of their hard-earned daily income!&lt;/p&gt;
       &lt;!-- PRO_ONBOARDING_TOUR_WIDGET --&gt;
@@ -15855,33 +17445,33 @@
         &lt;a href="/pro/login" style="display: inline-block; background: #10b981; color: #fff; padding: 12px 24px; border-radius: 8px; font-weight: bold; text-decoration: none;"&gt;Register Free on Carpenterwala Pro ➔&lt;/a&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I123" t="str">
+      <c r="I131" t="str">
         <v>https://images.unsplash.com/photo-1581141849291-1125c7b692b5?q=80&amp;w=2070&amp;auto=format&amp;fit=crop</v>
       </c>
     </row>
-    <row r="124" xml:space="preserve">
-      <c r="A124">
-        <v>123</v>
-      </c>
-      <c r="B124" t="str">
+    <row r="132" xml:space="preserve">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132" t="str">
         <v>bangalore-mein-carpenter-painter-plumber-direct-kaam-zero-commission</v>
       </c>
-      <c r="C124" t="str">
+      <c r="C132" t="str">
         <v>बैंगलोर में कारपेंटर, पेंटर, प्लंबर और इलेक्ट्रीशियन: 0% कमीशन पर सीधे काम कैसे पाएं? (Pro Guide)</v>
       </c>
-      <c r="D124" t="str">
+      <c r="D132" t="str">
         <v>Pro Guide</v>
       </c>
-      <c r="E124" t="str">
+      <c r="E132" t="str">
         <v>June 20, 2026</v>
       </c>
-      <c r="F124" t="str">
+      <c r="F132" t="str">
         <v>8 min read</v>
       </c>
-      <c r="G124" t="str">
+      <c r="G132" t="str">
         <v>बैंगलोर में बिना किसी ऐप कमीशन के सीधे होमओनर से काम पाने और हर महीने ₹15,000 से ₹25,000 ज्यादा कमाने की पूरी गाइड।</v>
       </c>
-      <c r="H124" t="str" xml:space="preserve">
+      <c r="H132" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;p&gt;अगर आप बैंगलोर में कारपेंटरी (बढ़ई का काम), पेंटिंग (पुट्टी व रंगाई), प्लंबिंग (नल व पाइप फिटिंग), या इलेक्ट्रिकल (बिजली का काम) करते हैं, तो आपने एक बात जरूर महसूस की होगी: &lt;strong&gt;पारंपरिक एग्रीगेटर ऐप्स आपकी मेहनत की कमाई का 20% से 30% हिस्सा कमीशन में काट लेते हैं।&lt;/strong&gt;&lt;/p&gt;
       &lt;p&gt;यानी अगर आपने पूरे दिन पसीना बहाकर ₹4,000 का काम किया, तो ₹1,000 से ज्यादा कंपनी अपनी जेब में रख लेती है। इसके अलावा देरी से पेमेंट, मनमाने जुर्माने और आईडी ब्लॉक होने का डर अलग रहता है।&lt;/p&gt;
       &lt;p&gt;लेकिन अब आपके पास एक बेहतर और सम्मानजनक विकल्प है — &lt;strong&gt;Carpenterwala&lt;/strong&gt;, जो भारत का पहला &lt;strong&gt;0% कमीशन डायरेक्ट मार्केटप्लेस&lt;/strong&gt; है। यहाँ ग्राहक सीधे आपको फोन करता है और काम खत्म होने पर पूरा 100% पैसा सीधे आपके हाथ या व्यक्तिगत UPI पर मिलता है।&lt;/p&gt;
@@ -15943,13 +17533,13 @@
         &lt;/div&gt;
       &lt;/div&gt;</v>
       </c>
-      <c r="I124" t="str">
+      <c r="I132" t="str">
         <v>https://carpenterwala.com/images/pro-campaign-hi.jpg</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I124"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I132"/>
   </ignoredErrors>
 </worksheet>
 </file>